--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="18" activeTab="24"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2159" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2287" uniqueCount="653">
   <si>
     <t>ID</t>
   </si>
@@ -533,6 +533,9 @@
     <t>[0,0,0,0,0,90,0]</t>
   </si>
   <si>
+    <t>angles</t>
+  </si>
+  <si>
     <t>speed</t>
   </si>
   <si>
@@ -542,30 +545,207 @@
     <t>send_angles</t>
   </si>
   <si>
+    <t>[10,10,10,5,10,90,10]</t>
+  </si>
+  <si>
+    <t>正确设置多关节角度，速度50</t>
+  </si>
+  <si>
+    <t>[-10,-10,-10,-10,-10,90,-10]</t>
+  </si>
+  <si>
+    <t>正确设置多关节角度，速度90</t>
+  </si>
+  <si>
+    <t>[20,20,20,0,20,90,-20]</t>
+  </si>
+  <si>
+    <t>左臂一关节运动到正限位</t>
+  </si>
+  <si>
+    <t>[165,0,0,0,0,90,0]</t>
+  </si>
+  <si>
+    <t>left</t>
+  </si>
+  <si>
+    <t>左臂一关节运动到负限位</t>
+  </si>
+  <si>
+    <t>[-165,0,0,0,0,90,0]</t>
+  </si>
+  <si>
+    <t>左臂二关节运动到正限位</t>
+  </si>
+  <si>
+    <t>[0,120,0,0,0,90,0]</t>
+  </si>
+  <si>
+    <t>左臂二关节运动到负限位</t>
+  </si>
+  <si>
+    <t>[0,-50,0,0,0,90,0]</t>
+  </si>
+  <si>
+    <t>左臂三关节运动到正限位</t>
+  </si>
+  <si>
+    <t>[0,0,165,0,0,90,0]</t>
+  </si>
+  <si>
+    <t>左臂三关节运动到负限位</t>
+  </si>
+  <si>
+    <t>[0,0,-165,0,0,90,0]</t>
+  </si>
+  <si>
+    <t>左臂四关节运动到正限位</t>
+  </si>
+  <si>
+    <t>[0,0,0,1,0,90,0]</t>
+  </si>
+  <si>
+    <t>左臂四关节运动到负限位</t>
+  </si>
+  <si>
+    <t>[0,0,0,-165,0,90,0]</t>
+  </si>
+  <si>
+    <t>左臂五关节运动到正限位</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,165,90,0]</t>
+  </si>
+  <si>
+    <t>左臂五关节运动到负限位</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,-165,90,0]</t>
+  </si>
+  <si>
+    <t>左臂六关节运动到正限位</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,0,255,0]</t>
+  </si>
+  <si>
+    <t>左臂六关节运动到负限位</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,0,-75,0]</t>
+  </si>
+  <si>
+    <t>左臂七关节运动到正限位</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,0,90,165]</t>
+  </si>
+  <si>
+    <t>左臂七关节运动到负限位</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,0,90,-165]</t>
+  </si>
+  <si>
+    <t>右臂一关节运动到正限位</t>
+  </si>
+  <si>
+    <t>right</t>
+  </si>
+  <si>
+    <t>右臂一关节运动到负限位</t>
+  </si>
+  <si>
+    <t>右臂二关节运动到正限位</t>
+  </si>
+  <si>
+    <t>右臂二关节运动到负限位</t>
+  </si>
+  <si>
+    <t>右臂三关节运动到正限位</t>
+  </si>
+  <si>
+    <t>右臂三关节运动到负限位</t>
+  </si>
+  <si>
+    <t>右臂四关节运动到正限位</t>
+  </si>
+  <si>
+    <t>右臂四关节运动到负限位</t>
+  </si>
+  <si>
+    <t>右臂五关节运动到正限位</t>
+  </si>
+  <si>
+    <t>右臂五关节运动到负限位</t>
+  </si>
+  <si>
+    <t>右臂六关节运动到正限位</t>
+  </si>
+  <si>
+    <t>右臂六关节运动到负限位</t>
+  </si>
+  <si>
+    <t>右臂七关节运动到正限位</t>
+  </si>
+  <si>
+    <t>右臂七关节运动到负限位</t>
+  </si>
+  <si>
+    <t>右臂十一关节运动到正限位</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,0,90,0,0,0,0]</t>
+  </si>
+  <si>
+    <t>右臂十一关节运动到负限位</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,0,90,0,-55,0,0]</t>
+  </si>
+  <si>
+    <t>右臂十二关节运动到正限位</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,0,90,0,0,245,0]</t>
+  </si>
+  <si>
+    <t>右臂十二关节运动到负限位</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,0,90,0,0,-70,0]</t>
+  </si>
+  <si>
+    <t>右臂十三关节运动到正限位</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,0,90,0,0,0,160]</t>
+  </si>
+  <si>
+    <t>右臂十三关节运动到负限位</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,0,90,0,0,0,-160]</t>
+  </si>
+  <si>
+    <t>设置多关节角度，速度超限（-1）</t>
+  </si>
+  <si>
+    <t>[0,0,0,-10,0,90,-20]</t>
+  </si>
+  <si>
+    <t>设置多关节角度，速度超限（0）</t>
+  </si>
+  <si>
     <t>[10,0,0,-30,0,90,0]</t>
   </si>
   <si>
-    <t>正确设置多关节角度，速度50</t>
+    <t>设置多关节角度，速度超限（101）</t>
   </si>
   <si>
     <t>[0,10,0,0,0,90,60]</t>
   </si>
   <si>
-    <t>正确设置多关节角度，速度90</t>
-  </si>
-  <si>
-    <t>[0,0,0,-10,0,90,-20]</t>
-  </si>
-  <si>
-    <t>设置多关节角度，速度超限（-1）</t>
-  </si>
-  <si>
-    <t>设置多关节角度，速度超限（0）</t>
-  </si>
-  <si>
-    <t>设置多关节角度，速度超限（101）</t>
-  </si>
-  <si>
     <t>设置多关节角度，1关节超限（-170）</t>
   </si>
   <si>
@@ -728,9 +908,6 @@
     <t>正确设置11关节角度，正限位</t>
   </si>
   <si>
-    <t>right</t>
-  </si>
-  <si>
     <t>正确设置11关节角度，负限位</t>
   </si>
   <si>
@@ -864,9 +1041,6 @@
   </si>
   <si>
     <t>[322.5, 0.0, 630, 179.99, 19.99, 0.0]</t>
-  </si>
-  <si>
-    <t>left</t>
   </si>
   <si>
     <t>设置全坐标z轴超限（min）左臂</t>
@@ -5295,17 +5469,16 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="26.6666666666667" style="1" customWidth="1"/>
-    <col min="5" max="6" width="17.2222222222222" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="13.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="32.7777777777778" customWidth="1"/>
+    <col min="5" max="6" width="17.2222222222222" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:8">
@@ -5319,10 +5492,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -5339,456 +5512,1096 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E2" s="1">
         <v>10</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" ht="51" customHeight="1" spans="1:8">
+    <row r="3" customFormat="1" ht="51" customHeight="1" spans="1:8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E3" s="1">
         <v>50</v>
       </c>
       <c r="F3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" ht="51" customHeight="1" spans="1:8">
+    <row r="4" customFormat="1" ht="51" customHeight="1" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E4" s="1">
         <v>90</v>
       </c>
       <c r="F4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" ht="43.2" spans="1:8">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
+    <row r="5" customFormat="1" ht="28.8" spans="1:8">
       <c r="B5" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E5" s="1">
-        <v>-1</v>
+        <v>50</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" ht="43.2" spans="1:8">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="28.8" spans="1:8">
       <c r="B6" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E6" s="1">
+        <v>30</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" ht="28.8" spans="1:8">
+      <c r="B7" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" ht="43.2" spans="1:8">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E7" s="1">
-        <v>101</v>
+        <v>10</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" ht="43.2" spans="1:8">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" ht="28.8" spans="1:8">
       <c r="B8" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E8" s="1">
+        <v>70</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E8" s="1">
-        <v>50</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" ht="43.2" spans="1:8">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
+    </row>
+    <row r="9" customFormat="1" ht="28.8" spans="1:8">
       <c r="B9" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E9" s="1">
-        <v>50</v>
+        <v>60</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" ht="43.2" spans="1:8">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" ht="28.8" spans="1:8">
       <c r="B10" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E10" s="1">
-        <v>50</v>
+        <v>90</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" ht="43.2" spans="1:8">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" ht="28.8" spans="1:8">
       <c r="B11" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
       <c r="H11" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" ht="43.2" spans="1:8">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" ht="28.8" spans="1:8">
       <c r="B12" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E12" s="1">
-        <v>50</v>
+        <v>30</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" ht="43.2" spans="1:8">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" ht="28.8" spans="1:8">
       <c r="B13" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E13" s="1">
-        <v>50</v>
+        <v>10</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" ht="43.2" spans="1:8">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" ht="28.8" spans="1:8">
       <c r="B14" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E14" s="1">
-        <v>50</v>
+        <v>70</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" ht="43.2" spans="1:8">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" ht="28.8" spans="1:8">
       <c r="B15" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E15" s="1">
-        <v>50</v>
+        <v>60</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" ht="43.2" spans="1:8">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" ht="28.8" spans="1:8">
       <c r="B16" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E16" s="1">
-        <v>50</v>
+        <v>90</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" ht="43.2" spans="1:8">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" ht="28.8" spans="2:8">
       <c r="B17" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E17" s="1">
-        <v>50</v>
+        <v>70</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" ht="43.2" spans="1:8">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" ht="28.8" spans="2:8">
       <c r="B18" s="1" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="E18" s="1">
-        <v>50</v>
+        <v>60</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" ht="43.2" spans="1:8">
-      <c r="A19" s="2">
-        <v>18</v>
-      </c>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" ht="28.8" spans="2:8">
       <c r="B19" s="1" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
       </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
       <c r="H19" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" ht="28.8" spans="2:8">
+      <c r="B20" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E20" s="1">
+        <v>30</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" ht="28.8" spans="2:8">
+      <c r="B21" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E21" s="1">
+        <v>10</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" ht="28.8" spans="2:8">
+      <c r="B22" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E22" s="1">
+        <v>70</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" ht="28.8" spans="2:8">
+      <c r="B23" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E23" s="1">
+        <v>60</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" ht="28.8" spans="2:8">
+      <c r="B24" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E24" s="1">
+        <v>90</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" ht="28.8" spans="2:8">
+      <c r="B25" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E25" s="1">
+        <v>50</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" ht="28.8" spans="2:8">
+      <c r="B26" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E26" s="1">
+        <v>30</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" ht="28.8" spans="2:8">
+      <c r="B27" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E27" s="1">
+        <v>10</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" ht="28.8" spans="2:8">
+      <c r="B28" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E28" s="1">
+        <v>70</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" ht="28.8" spans="2:8">
+      <c r="B29" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E29" s="1">
+        <v>60</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" ht="28.8" spans="2:8">
+      <c r="B30" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E30" s="1">
+        <v>90</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" ht="28.8" spans="2:8">
+      <c r="B31" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E31" s="1">
+        <v>70</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" ht="28.8" spans="2:8">
+      <c r="B32" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E32" s="1">
+        <v>60</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" ht="28.8" spans="1:8">
+      <c r="B33" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E33" s="1">
+        <v>70</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" ht="28.8" spans="1:8">
+      <c r="B34" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E34" s="1">
+        <v>60</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" ht="28.8" spans="1:8">
+      <c r="B35" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E35" s="1">
+        <v>90</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" ht="28.8" spans="1:8">
+      <c r="B36" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E36" s="1">
+        <v>70</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" ht="28.8" spans="1:8">
+      <c r="B37" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E37" s="1">
+        <v>60</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" ht="28.8" spans="1:8">
+      <c r="B38" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E38" s="1">
+        <v>60</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A39" s="2">
+        <v>4</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E39" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" ht="43.2" spans="1:8">
-      <c r="A20" s="2">
+    <row r="40" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A40" s="2">
+        <v>5</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A41" s="2">
+        <v>6</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E41" s="1">
+        <v>101</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A42" s="2">
+        <v>7</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E42" s="1">
+        <v>50</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A43" s="2">
+        <v>8</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E43" s="1">
+        <v>50</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A44" s="2">
+        <v>9</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E44" s="1">
+        <v>50</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A45" s="2">
+        <v>10</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E45" s="1">
+        <v>50</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A46" s="2">
+        <v>11</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E46" s="1">
+        <v>50</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A47" s="2">
+        <v>12</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E47" s="1">
+        <v>50</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A48" s="2">
+        <v>13</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E48" s="1">
+        <v>50</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A49" s="2">
+        <v>14</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E49" s="1">
+        <v>50</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A50" s="2">
+        <v>15</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E50" s="1">
+        <v>50</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A51" s="2">
+        <v>16</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E51" s="1">
+        <v>50</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A52" s="2">
+        <v>17</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E52" s="1">
+        <v>50</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A53" s="2">
+        <v>18</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E53" s="1">
+        <v>50</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A54" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E20" s="1">
+      <c r="B54" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E54" s="1">
         <v>50</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H54" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="21" ht="43.2" spans="1:8">
-      <c r="A21" s="2">
+    <row r="55" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A55" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E21" s="1">
+      <c r="B55" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E55" s="1">
         <v>50</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" ht="43.2" spans="1:8">
-      <c r="A22" s="2">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E22" s="1">
-        <v>50</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" ht="43.2" spans="1:8">
-      <c r="A23" s="2">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="E23" s="1">
-        <v>50</v>
-      </c>
-      <c r="H23" s="1" t="s">
+      <c r="H55" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -5821,7 +6634,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>183</v>
+        <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -5838,10 +6651,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>184</v>
+        <v>244</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -5861,10 +6674,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>186</v>
+        <v>246</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -5884,10 +6697,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>187</v>
+        <v>247</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -5907,10 +6720,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>188</v>
+        <v>248</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -5930,10 +6743,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -5953,10 +6766,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -5976,10 +6789,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>191</v>
+        <v>251</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -5999,10 +6812,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>192</v>
+        <v>252</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="D9" s="1">
         <v>8</v>
@@ -6016,10 +6829,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>192</v>
+        <v>252</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -6061,13 +6874,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>183</v>
+        <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -6084,10 +6897,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -6113,10 +6926,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -6142,10 +6955,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>196</v>
+        <v>256</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -6171,10 +6984,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>197</v>
+        <v>257</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -6200,10 +7013,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>198</v>
+        <v>258</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -6229,10 +7042,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>199</v>
+        <v>259</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -6258,10 +7071,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -6287,10 +7100,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>201</v>
+        <v>261</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -6316,10 +7129,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>202</v>
+        <v>262</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -6345,10 +7158,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>203</v>
+        <v>263</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -6374,10 +7187,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>204</v>
+        <v>264</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -6403,10 +7216,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>205</v>
+        <v>265</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -6432,10 +7245,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>206</v>
+        <v>266</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -6461,10 +7274,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>207</v>
+        <v>267</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -6490,10 +7303,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>208</v>
+        <v>268</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D16" s="1">
         <v>11</v>
@@ -6511,7 +7324,7 @@
         <v>-2</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -6519,10 +7332,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>210</v>
+        <v>269</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D17" s="1">
         <v>11</v>
@@ -6540,7 +7353,7 @@
         <v>-2</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -6548,10 +7361,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>211</v>
+        <v>270</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D18" s="1">
         <v>12</v>
@@ -6569,7 +7382,7 @@
         <v>-2</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -6577,10 +7390,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>212</v>
+        <v>271</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D19" s="1">
         <v>12</v>
@@ -6598,7 +7411,7 @@
         <v>-2</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -6606,10 +7419,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>213</v>
+        <v>272</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D20" s="1">
         <v>13</v>
@@ -6627,7 +7440,7 @@
         <v>-2</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -6635,10 +7448,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>214</v>
+        <v>273</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D21" s="1">
         <v>13</v>
@@ -6656,7 +7469,7 @@
         <v>-2</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -6664,10 +7477,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>215</v>
+        <v>274</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -6687,10 +7500,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>216</v>
+        <v>275</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D23" s="1">
         <v>3</v>
@@ -6710,10 +7523,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>217</v>
+        <v>276</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D24" s="1">
         <v>5</v>
@@ -6733,10 +7546,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>218</v>
+        <v>277</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D25" s="1">
         <v>1</v>
@@ -6756,10 +7569,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>219</v>
+        <v>278</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
@@ -6779,10 +7592,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>220</v>
+        <v>279</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
@@ -6802,10 +7615,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>221</v>
+        <v>280</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
@@ -6825,10 +7638,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>222</v>
+        <v>281</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D29" s="1">
         <v>3</v>
@@ -6848,10 +7661,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>223</v>
+        <v>282</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
@@ -6871,10 +7684,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D31" s="1">
         <v>4</v>
@@ -6894,10 +7707,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>225</v>
+        <v>284</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D32" s="1">
         <v>4</v>
@@ -6917,10 +7730,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>226</v>
+        <v>285</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D33" s="1">
         <v>5</v>
@@ -6940,10 +7753,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>227</v>
+        <v>286</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D34" s="1">
         <v>5</v>
@@ -6963,10 +7776,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>228</v>
+        <v>287</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D35" s="1">
         <v>6</v>
@@ -6986,10 +7799,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>229</v>
+        <v>288</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D36" s="1">
         <v>6</v>
@@ -7009,10 +7822,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>230</v>
+        <v>289</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D37" s="1">
         <v>7</v>
@@ -7032,10 +7845,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>231</v>
+        <v>290</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="D38" s="1">
         <v>7</v>
@@ -7099,19 +7912,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>232</v>
+        <v>291</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>233</v>
+        <v>292</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>234</v>
+        <v>293</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>235</v>
+        <v>294</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>235</v>
+        <v>294</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -7122,19 +7935,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>236</v>
+        <v>295</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>233</v>
+        <v>292</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>143</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>237</v>
+        <v>296</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>237</v>
+        <v>296</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>34</v>
@@ -7175,7 +7988,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -7192,13 +8005,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>238</v>
+        <v>297</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>240</v>
+        <v>299</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -7218,13 +8031,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>238</v>
+        <v>297</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>241</v>
+        <v>300</v>
       </c>
       <c r="E3" s="1">
         <v>50</v>
@@ -7244,13 +8057,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>242</v>
+        <v>301</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>243</v>
+        <v>302</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -7270,13 +8083,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>242</v>
+        <v>301</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -7296,13 +8109,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>246</v>
+        <v>305</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
@@ -7316,13 +8129,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>247</v>
+        <v>306</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
@@ -7336,13 +8149,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>249</v>
+        <v>308</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>250</v>
+        <v>309</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
@@ -7356,13 +8169,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>252</v>
+        <v>311</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
@@ -7376,19 +8189,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>253</v>
+        <v>312</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>255</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="1:8">
@@ -7396,19 +8209,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>256</v>
+        <v>314</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>257</v>
+        <v>315</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>255</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" ht="28.8" spans="1:8">
@@ -7416,19 +8229,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>258</v>
+        <v>316</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>259</v>
+        <v>317</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="1:8">
@@ -7436,19 +8249,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>260</v>
+        <v>318</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>261</v>
+        <v>319</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14" ht="28.8" spans="1:8">
@@ -7456,13 +8269,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>262</v>
+        <v>320</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>263</v>
+        <v>321</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
@@ -7476,13 +8289,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>265</v>
+        <v>323</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
@@ -7496,13 +8309,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>266</v>
+        <v>324</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
@@ -7516,13 +8329,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>268</v>
+        <v>326</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>269</v>
+        <v>327</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
@@ -7536,13 +8349,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>266</v>
+        <v>324</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>270</v>
+        <v>328</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
@@ -7556,13 +8369,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>268</v>
+        <v>326</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>271</v>
+        <v>329</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
@@ -7576,13 +8389,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>272</v>
+        <v>330</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>241</v>
+        <v>300</v>
       </c>
       <c r="E20" s="1">
         <v>101</v>
@@ -7596,13 +8409,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>272</v>
+        <v>330</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>241</v>
+        <v>300</v>
       </c>
       <c r="E21" s="1">
         <v>-1</v>
@@ -7736,13 +8549,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>273</v>
+        <v>331</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -7759,10 +8572,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>274</v>
+        <v>332</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -7788,10 +8601,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>276</v>
+        <v>334</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -7809,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -7817,10 +8630,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>278</v>
+        <v>336</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -7838,7 +8651,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -7846,10 +8659,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>279</v>
+        <v>337</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -7867,7 +8680,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -7875,10 +8688,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>280</v>
+        <v>338</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -7896,7 +8709,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -7904,10 +8717,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>281</v>
+        <v>339</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -7925,7 +8738,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" ht="28.8" spans="1:9">
@@ -7933,10 +8746,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>282</v>
+        <v>340</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -7956,10 +8769,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>283</v>
+        <v>341</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -7979,10 +8792,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>284</v>
+        <v>342</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
@@ -8002,10 +8815,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>285</v>
+        <v>343</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
@@ -8025,10 +8838,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>286</v>
+        <v>344</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D12" s="1">
         <v>3</v>
@@ -8040,7 +8853,7 @@
         <v>70</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>255</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="1:9">
@@ -8048,10 +8861,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>287</v>
+        <v>345</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D13" s="1">
         <v>3</v>
@@ -8063,7 +8876,7 @@
         <v>70</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>255</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" ht="28.8" spans="1:9">
@@ -8071,10 +8884,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>288</v>
+        <v>346</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
@@ -8086,7 +8899,7 @@
         <v>70</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" ht="28.8" spans="1:9">
@@ -8094,10 +8907,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>289</v>
+        <v>347</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D15" s="1">
         <v>3</v>
@@ -8109,7 +8922,7 @@
         <v>70</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" ht="28.8" spans="1:9">
@@ -8117,10 +8930,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>290</v>
+        <v>348</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D16" s="1">
         <v>4</v>
@@ -8140,10 +8953,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D17" s="1">
         <v>4</v>
@@ -8163,10 +8976,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>292</v>
+        <v>350</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -8186,10 +8999,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>293</v>
+        <v>351</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D19" s="1">
         <v>5</v>
@@ -8209,10 +9022,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>294</v>
+        <v>352</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D20" s="1">
         <v>6</v>
@@ -8232,10 +9045,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>295</v>
+        <v>353</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D21" s="1">
         <v>6</v>
@@ -8255,10 +9068,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>296</v>
+        <v>354</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -8278,10 +9091,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>296</v>
+        <v>354</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -8301,10 +9114,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>297</v>
+        <v>355</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D24" s="1">
         <v>7</v>
@@ -8324,10 +9137,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>297</v>
+        <v>355</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -8392,10 +9205,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>298</v>
+        <v>356</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>299</v>
+        <v>357</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -8415,10 +9228,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>298</v>
+        <v>356</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>299</v>
+        <v>357</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -8438,10 +9251,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>300</v>
+        <v>358</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>299</v>
+        <v>357</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -8455,10 +9268,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>300</v>
+        <v>358</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>299</v>
+        <v>357</v>
       </c>
       <c r="D5" s="1">
         <v>-3</v>
@@ -8517,10 +9330,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>301</v>
+        <v>359</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>299</v>
+        <v>357</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -8538,10 +9351,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>302</v>
+        <v>360</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>299</v>
+        <v>357</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -8604,10 +9417,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>303</v>
+        <v>361</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>304</v>
+        <v>362</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -8627,10 +9440,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>305</v>
+        <v>363</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>304</v>
+        <v>362</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -8650,10 +9463,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>364</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>304</v>
+        <v>362</v>
       </c>
       <c r="D4" s="1">
         <v>-3</v>
@@ -8667,10 +9480,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>306</v>
+        <v>364</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>304</v>
+        <v>362</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -8729,10 +9542,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>307</v>
+        <v>365</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>308</v>
+        <v>366</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -8752,10 +9565,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>309</v>
+        <v>367</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>308</v>
+        <v>366</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -8775,10 +9588,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>310</v>
+        <v>368</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>308</v>
+        <v>366</v>
       </c>
       <c r="D4" s="1">
         <v>-3</v>
@@ -8792,10 +9605,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>310</v>
+        <v>368</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>308</v>
+        <v>366</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -8840,7 +9653,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>311</v>
+        <v>369</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -8857,13 +9670,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>312</v>
+        <v>370</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>313</v>
+        <v>371</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>314</v>
+        <v>372</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -8875,7 +9688,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>315</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="57.6" spans="1:8">
@@ -8883,13 +9696,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>316</v>
+        <v>374</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>313</v>
+        <v>371</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>314</v>
+        <v>372</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -8901,7 +9714,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>315</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="57.6" spans="1:8">
@@ -8909,13 +9722,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>317</v>
+        <v>375</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>313</v>
+        <v>371</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>318</v>
+        <v>376</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -8927,7 +9740,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>319</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="57.6" spans="1:8">
@@ -8935,13 +9748,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>320</v>
+        <v>378</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>313</v>
+        <v>371</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>318</v>
+        <v>376</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -8953,7 +9766,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>319</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" ht="57.6" spans="1:8">
@@ -8961,13 +9774,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>321</v>
+        <v>379</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>313</v>
+        <v>371</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>318</v>
+        <v>376</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -8979,7 +9792,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>319</v>
+        <v>377</v>
       </c>
     </row>
     <row r="7" ht="57" customHeight="1" spans="1:8">
@@ -8987,10 +9800,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>322</v>
+        <v>380</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>313</v>
+        <v>371</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -9002,7 +9815,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>323</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8" ht="57.6" spans="1:8">
@@ -9010,10 +9823,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>324</v>
+        <v>382</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>313</v>
+        <v>371</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -9025,7 +9838,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>323</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9" ht="57.6" spans="1:8">
@@ -9033,10 +9846,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>325</v>
+        <v>383</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>313</v>
+        <v>371</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -9048,7 +9861,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>323</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -9056,10 +9869,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>326</v>
+        <v>384</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>313</v>
+        <v>371</v>
       </c>
       <c r="E10" s="1">
         <v>-1</v>
@@ -9073,10 +9886,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>326</v>
+        <v>384</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>313</v>
+        <v>371</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -9135,10 +9948,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>327</v>
+        <v>385</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>328</v>
+        <v>386</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -9155,10 +9968,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>329</v>
+        <v>387</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>328</v>
+        <v>386</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -9221,10 +10034,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>330</v>
+        <v>388</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>331</v>
+        <v>389</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -9244,10 +10057,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>332</v>
+        <v>390</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>331</v>
+        <v>389</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -9267,10 +10080,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>326</v>
+        <v>384</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>331</v>
+        <v>389</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -9284,10 +10097,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>326</v>
+        <v>384</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>331</v>
+        <v>389</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -9332,7 +10145,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>311</v>
+        <v>369</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -9349,10 +10162,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>333</v>
+        <v>391</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>334</v>
+        <v>392</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -9375,10 +10188,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>335</v>
+        <v>393</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>334</v>
+        <v>392</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -9401,10 +10214,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>336</v>
+        <v>394</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>334</v>
+        <v>392</v>
       </c>
       <c r="D4" s="1">
         <v>151</v>
@@ -9421,10 +10234,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>336</v>
+        <v>394</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>334</v>
+        <v>392</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -9441,10 +10254,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>337</v>
+        <v>395</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>334</v>
+        <v>392</v>
       </c>
       <c r="D6" s="1">
         <v>201</v>
@@ -9461,10 +10274,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>337</v>
+        <v>395</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>334</v>
+        <v>392</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -9481,10 +10294,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>326</v>
+        <v>384</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>334</v>
+        <v>392</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -9501,10 +10314,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>326</v>
+        <v>384</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>334</v>
+        <v>392</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -9524,7 +10337,7 @@
         <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>334</v>
+        <v>392</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -9550,7 +10363,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>334</v>
+        <v>392</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -9601,7 +10414,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>311</v>
+        <v>369</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -9618,10 +10431,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>338</v>
+        <v>396</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>339</v>
+        <v>397</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -9641,10 +10454,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>340</v>
+        <v>398</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>339</v>
+        <v>397</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -9664,10 +10477,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>326</v>
+        <v>384</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>339</v>
+        <v>397</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -9681,10 +10494,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>326</v>
+        <v>384</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>339</v>
+        <v>397</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -9825,7 +10638,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>311</v>
+        <v>369</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -9842,10 +10655,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>341</v>
+        <v>399</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>342</v>
+        <v>400</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -9868,10 +10681,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>343</v>
+        <v>401</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>342</v>
+        <v>400</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -9894,10 +10707,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>344</v>
+        <v>402</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>342</v>
+        <v>400</v>
       </c>
       <c r="D4" s="1">
         <v>201</v>
@@ -9914,10 +10727,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>344</v>
+        <v>402</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>342</v>
+        <v>400</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -9934,10 +10747,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>345</v>
+        <v>403</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>342</v>
+        <v>400</v>
       </c>
       <c r="D6" s="1">
         <v>401</v>
@@ -9954,10 +10767,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>345</v>
+        <v>403</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>342</v>
+        <v>400</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -9974,10 +10787,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>326</v>
+        <v>384</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>342</v>
+        <v>400</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -9994,10 +10807,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>326</v>
+        <v>384</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>342</v>
+        <v>400</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -10014,10 +10827,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>346</v>
+        <v>404</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>342</v>
+        <v>400</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -10040,10 +10853,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>347</v>
+        <v>405</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>342</v>
+        <v>400</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -10105,16 +10918,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>348</v>
+        <v>406</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>349</v>
+        <v>407</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>350</v>
+        <v>408</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>351</v>
+        <v>409</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>34</v>
@@ -10164,10 +10977,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>352</v>
+        <v>410</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>353</v>
+        <v>411</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -10228,16 +11041,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>354</v>
+        <v>412</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>355</v>
+        <v>413</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>356</v>
+        <v>414</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>357</v>
+        <v>415</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -10292,16 +11105,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>358</v>
+        <v>416</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>359</v>
+        <v>417</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>360</v>
+        <v>418</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>360</v>
+        <v>418</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -10356,16 +11169,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>361</v>
+        <v>419</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>362</v>
+        <v>420</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>360</v>
+        <v>418</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>360</v>
+        <v>418</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -10420,16 +11233,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>363</v>
+        <v>421</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>364</v>
+        <v>422</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>360</v>
+        <v>418</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>365</v>
+        <v>423</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -10467,13 +11280,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>366</v>
+        <v>424</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>367</v>
+        <v>425</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>368</v>
+        <v>426</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -10490,10 +11303,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>369</v>
+        <v>427</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>370</v>
+        <v>428</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10519,10 +11332,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>369</v>
+        <v>427</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>370</v>
+        <v>428</v>
       </c>
       <c r="D3" s="1">
         <v>255</v>
@@ -10548,10 +11361,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>369</v>
+        <v>427</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>370</v>
+        <v>428</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -10577,10 +11390,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>371</v>
+        <v>429</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>370</v>
+        <v>428</v>
       </c>
       <c r="D5" s="1">
         <v>256</v>
@@ -10644,10 +11457,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>372</v>
+        <v>430</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>373</v>
+        <v>431</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -10708,10 +11521,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>374</v>
+        <v>432</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>375</v>
+        <v>433</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -10731,10 +11544,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>374</v>
+        <v>432</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>375</v>
+        <v>433</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -10754,10 +11567,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>376</v>
+        <v>434</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>375</v>
+        <v>433</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -10771,10 +11584,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>376</v>
+        <v>434</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>375</v>
+        <v>433</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -10919,7 +11732,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>183</v>
+        <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -10939,10 +11752,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>377</v>
+        <v>435</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>378</v>
+        <v>436</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -10965,10 +11778,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>379</v>
+        <v>437</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>378</v>
+        <v>436</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -10991,10 +11804,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>380</v>
+        <v>438</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>378</v>
+        <v>436</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -11017,10 +11830,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>381</v>
+        <v>439</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>378</v>
+        <v>436</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -11043,10 +11856,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>382</v>
+        <v>440</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>378</v>
+        <v>436</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -11069,10 +11882,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>383</v>
+        <v>441</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>378</v>
+        <v>436</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -11095,10 +11908,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>384</v>
+        <v>442</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>378</v>
+        <v>436</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -11121,10 +11934,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>385</v>
+        <v>443</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>378</v>
+        <v>436</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -11141,10 +11954,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>385</v>
+        <v>443</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>378</v>
+        <v>436</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -11161,10 +11974,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>386</v>
+        <v>444</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>378</v>
+        <v>436</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -11181,10 +11994,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>386</v>
+        <v>444</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>378</v>
+        <v>436</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -11201,10 +12014,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>387</v>
+        <v>445</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>378</v>
+        <v>436</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -11213,10 +12026,10 @@
         <v>120</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>388</v>
+        <v>446</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>388</v>
+        <v>446</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -11271,17 +12084,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>389</v>
+        <v>447</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>390</v>
+        <v>448</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>391</v>
+        <v>449</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>391</v>
+        <v>449</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11319,7 +12132,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>183</v>
+        <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -11339,10 +12152,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>392</v>
+        <v>450</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>393</v>
+        <v>451</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -11365,10 +12178,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>394</v>
+        <v>452</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>393</v>
+        <v>451</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -11391,10 +12204,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>395</v>
+        <v>453</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>393</v>
+        <v>451</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -11417,10 +12230,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>396</v>
+        <v>454</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>393</v>
+        <v>451</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -11443,10 +12256,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>397</v>
+        <v>455</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>393</v>
+        <v>451</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -11469,10 +12282,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>398</v>
+        <v>456</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>393</v>
+        <v>451</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -11495,10 +12308,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>399</v>
+        <v>457</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>393</v>
+        <v>451</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -11521,10 +12334,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>400</v>
+        <v>458</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>393</v>
+        <v>451</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -11541,10 +12354,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>400</v>
+        <v>458</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>393</v>
+        <v>451</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -11561,10 +12374,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>401</v>
+        <v>459</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>393</v>
+        <v>451</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -11581,10 +12394,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>401</v>
+        <v>459</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>393</v>
+        <v>451</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -11601,10 +12414,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>387</v>
+        <v>445</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>393</v>
+        <v>451</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -11613,10 +12426,10 @@
         <v>100</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>402</v>
+        <v>460</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>402</v>
+        <v>460</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -11671,19 +12484,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>403</v>
+        <v>461</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>404</v>
+        <v>462</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>405</v>
+        <v>463</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>405</v>
+        <v>463</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11738,10 +12551,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>406</v>
+        <v>464</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>407</v>
+        <v>465</v>
       </c>
       <c r="E2" s="1">
         <v>50</v>
@@ -11802,10 +12615,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>408</v>
+        <v>466</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>409</v>
+        <v>467</v>
       </c>
       <c r="D2" s="1">
         <v>30</v>
@@ -11825,10 +12638,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>410</v>
+        <v>468</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>409</v>
+        <v>467</v>
       </c>
       <c r="D3" s="1">
         <v>301</v>
@@ -11842,10 +12655,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>410</v>
+        <v>468</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>409</v>
+        <v>467</v>
       </c>
       <c r="D4" s="1">
         <v>-301</v>
@@ -11859,10 +12672,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>387</v>
+        <v>445</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>409</v>
+        <v>467</v>
       </c>
       <c r="D5" s="1">
         <v>21</v>
@@ -11910,13 +12723,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>183</v>
+        <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -11933,10 +12746,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>411</v>
+        <v>469</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -11962,10 +12775,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>413</v>
+        <v>471</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -11991,10 +12804,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>414</v>
+        <v>472</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -12020,10 +12833,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>415</v>
+        <v>473</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -12049,10 +12862,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>416</v>
+        <v>474</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -12078,10 +12891,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>417</v>
+        <v>475</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -12107,10 +12920,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>418</v>
+        <v>476</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -12136,10 +12949,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>419</v>
+        <v>477</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -12165,10 +12978,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>420</v>
+        <v>478</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -12194,10 +13007,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>421</v>
+        <v>479</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -12223,10 +13036,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>422</v>
+        <v>480</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -12252,10 +13065,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>423</v>
+        <v>481</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -12281,10 +13094,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>424</v>
+        <v>482</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -12310,10 +13123,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>425</v>
+        <v>483</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -12339,10 +13152,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>426</v>
+        <v>484</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -12362,10 +13175,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>427</v>
+        <v>485</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -12385,10 +13198,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>428</v>
+        <v>486</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -12408,7 +13221,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>429</v>
+        <v>487</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -12428,7 +13241,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>429</v>
+        <v>487</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -12475,13 +13288,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>273</v>
+        <v>331</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -12498,10 +13311,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>430</v>
+        <v>488</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>431</v>
+        <v>489</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12527,10 +13340,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>432</v>
+        <v>490</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>431</v>
+        <v>489</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -12556,10 +13369,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>433</v>
+        <v>491</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>431</v>
+        <v>489</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -12585,10 +13398,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>434</v>
+        <v>492</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>431</v>
+        <v>489</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -12614,10 +13427,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>435</v>
+        <v>493</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>431</v>
+        <v>489</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -12643,10 +13456,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>436</v>
+        <v>494</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>431</v>
+        <v>489</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -12672,10 +13485,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>437</v>
+        <v>495</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>431</v>
+        <v>489</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -12695,10 +13508,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>437</v>
+        <v>495</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>431</v>
+        <v>489</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -12718,10 +13531,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>438</v>
+        <v>496</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>431</v>
+        <v>489</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -12741,10 +13554,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>438</v>
+        <v>496</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>431</v>
+        <v>489</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -12791,13 +13604,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>273</v>
+        <v>331</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -12814,10 +13627,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>439</v>
+        <v>497</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12843,10 +13656,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>441</v>
+        <v>499</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -12872,10 +13685,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>442</v>
+        <v>500</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -12893,7 +13706,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -12901,10 +13714,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>443</v>
+        <v>501</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -12922,7 +13735,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -12930,10 +13743,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>444</v>
+        <v>502</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -12951,7 +13764,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -12959,10 +13772,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>445</v>
+        <v>503</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -12980,7 +13793,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -12988,10 +13801,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>446</v>
+        <v>504</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -13017,10 +13830,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>447</v>
+        <v>505</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -13046,10 +13859,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>448</v>
+        <v>506</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -13067,7 +13880,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13075,10 +13888,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>449</v>
+        <v>507</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -13096,7 +13909,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13104,10 +13917,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>450</v>
+        <v>508</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -13125,7 +13938,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13133,10 +13946,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>451</v>
+        <v>509</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -13154,7 +13967,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13162,10 +13975,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>452</v>
+        <v>510</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -13185,10 +13998,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>452</v>
+        <v>510</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -13208,10 +14021,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>453</v>
+        <v>511</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -13231,10 +14044,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>453</v>
+        <v>511</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -13282,13 +14095,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>183</v>
+        <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -13305,10 +14118,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>454</v>
+        <v>512</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13334,10 +14147,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>456</v>
+        <v>514</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13363,10 +14176,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>457</v>
+        <v>515</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13392,10 +14205,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>458</v>
+        <v>516</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13421,10 +14234,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>459</v>
+        <v>517</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -13450,10 +14263,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>460</v>
+        <v>518</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -13479,10 +14292,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>461</v>
+        <v>519</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -13508,10 +14321,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>462</v>
+        <v>520</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -13537,10 +14350,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>463</v>
+        <v>521</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -13566,10 +14379,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>464</v>
+        <v>522</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -13595,10 +14408,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>465</v>
+        <v>523</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -13624,10 +14437,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>466</v>
+        <v>524</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -13653,10 +14466,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>467</v>
+        <v>525</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -13682,10 +14495,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>468</v>
+        <v>526</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -13711,10 +14524,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>469</v>
+        <v>527</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -13734,10 +14547,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>470</v>
+        <v>528</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -13757,10 +14570,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>471</v>
+        <v>529</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -13780,7 +14593,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>472</v>
+        <v>530</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -13800,7 +14613,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>472</v>
+        <v>530</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -14158,13 +14971,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>273</v>
+        <v>331</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -14181,10 +14994,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>473</v>
+        <v>531</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>474</v>
+        <v>532</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14210,10 +15023,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>475</v>
+        <v>533</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>474</v>
+        <v>532</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14239,10 +15052,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>476</v>
+        <v>534</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>474</v>
+        <v>532</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14260,7 +15073,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -14268,10 +15081,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>477</v>
+        <v>535</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>474</v>
+        <v>532</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14289,7 +15102,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -14297,10 +15110,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>478</v>
+        <v>536</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>474</v>
+        <v>532</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14318,7 +15131,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -14326,10 +15139,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>479</v>
+        <v>537</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>474</v>
+        <v>532</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14347,7 +15160,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -14355,10 +15168,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>480</v>
+        <v>538</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>474</v>
+        <v>532</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14384,10 +15197,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>481</v>
+        <v>539</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>474</v>
+        <v>532</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14413,10 +15226,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>482</v>
+        <v>540</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>474</v>
+        <v>532</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14434,7 +15247,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -14442,10 +15255,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>483</v>
+        <v>541</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>474</v>
+        <v>532</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14463,7 +15276,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -14471,10 +15284,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>484</v>
+        <v>542</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>474</v>
+        <v>532</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14492,7 +15305,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -14500,10 +15313,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>485</v>
+        <v>543</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>474</v>
+        <v>532</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14521,7 +15334,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -14529,10 +15342,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>486</v>
+        <v>544</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>474</v>
+        <v>532</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -14552,10 +15365,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>486</v>
+        <v>544</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>474</v>
+        <v>532</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -14575,10 +15388,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>487</v>
+        <v>545</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>474</v>
+        <v>532</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -14598,10 +15411,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>487</v>
+        <v>545</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>474</v>
+        <v>532</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -14665,10 +15478,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>488</v>
+        <v>546</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>489</v>
+        <v>547</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -14717,7 +15530,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -14734,10 +15547,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>490</v>
+        <v>548</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>491</v>
+        <v>549</v>
       </c>
       <c r="D2" s="1">
         <v>45</v>
@@ -14760,10 +15573,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>490</v>
+        <v>548</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>491</v>
+        <v>549</v>
       </c>
       <c r="D3" s="1">
         <v>-45</v>
@@ -14786,10 +15599,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>492</v>
+        <v>550</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>491</v>
+        <v>549</v>
       </c>
       <c r="D4" s="1">
         <v>91</v>
@@ -14806,10 +15619,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>492</v>
+        <v>550</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>491</v>
+        <v>549</v>
       </c>
       <c r="D5" s="1">
         <v>-91</v>
@@ -14826,10 +15639,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>493</v>
+        <v>551</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>491</v>
+        <v>549</v>
       </c>
       <c r="D6" s="1">
         <v>45</v>
@@ -14846,10 +15659,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>493</v>
+        <v>551</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>491</v>
+        <v>549</v>
       </c>
       <c r="D7" s="1">
         <v>45</v>
@@ -14894,13 +15707,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>494</v>
+        <v>552</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>495</v>
+        <v>553</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -14917,16 +15730,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>496</v>
+        <v>554</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>497</v>
+        <v>555</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>498</v>
+        <v>556</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>499</v>
+        <v>557</v>
       </c>
       <c r="F2" s="1">
         <v>50</v>
@@ -14946,16 +15759,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>493</v>
+        <v>551</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>497</v>
+        <v>555</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>498</v>
+        <v>556</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>499</v>
+        <v>557</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -14969,16 +15782,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>493</v>
+        <v>551</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>497</v>
+        <v>555</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>498</v>
+        <v>556</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>499</v>
+        <v>557</v>
       </c>
       <c r="F4" s="1">
         <v>101</v>
@@ -15036,10 +15849,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>500</v>
+        <v>558</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>501</v>
+        <v>559</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -15059,10 +15872,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>500</v>
+        <v>558</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>501</v>
+        <v>559</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -15082,10 +15895,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>500</v>
+        <v>558</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>501</v>
+        <v>559</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -15105,10 +15918,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>500</v>
+        <v>558</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>501</v>
+        <v>559</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -15128,10 +15941,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>500</v>
+        <v>558</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>501</v>
+        <v>559</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
@@ -15151,10 +15964,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>502</v>
+        <v>560</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>501</v>
+        <v>559</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -15168,10 +15981,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>387</v>
+        <v>445</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>501</v>
+        <v>559</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
@@ -15235,10 +16048,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>503</v>
+        <v>561</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>501</v>
+        <v>559</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -15258,10 +16071,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>503</v>
+        <v>561</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>501</v>
+        <v>559</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -15281,10 +16094,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>504</v>
+        <v>562</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>501</v>
+        <v>559</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -15298,10 +16111,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>387</v>
+        <v>445</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>501</v>
+        <v>559</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -15365,10 +16178,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>505</v>
+        <v>563</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>501</v>
+        <v>559</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -15416,7 +16229,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -15433,13 +16246,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>506</v>
+        <v>564</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>508</v>
+        <v>566</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -15451,7 +16264,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>255</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15459,13 +16272,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>509</v>
+        <v>567</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>510</v>
+        <v>568</v>
       </c>
       <c r="E3" s="1">
         <v>30</v>
@@ -15477,7 +16290,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15485,13 +16298,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>511</v>
+        <v>569</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>512</v>
+        <v>570</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -15503,7 +16316,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>255</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15511,13 +16324,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>513</v>
+        <v>571</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>514</v>
+        <v>572</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -15529,7 +16342,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15537,19 +16350,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>515</v>
+        <v>573</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>516</v>
+        <v>574</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>517</v>
+        <v>575</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15557,19 +16370,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>518</v>
+        <v>576</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>519</v>
+        <v>577</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>517</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15577,19 +16390,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>520</v>
+        <v>578</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>521</v>
+        <v>579</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>522</v>
+        <v>580</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15597,19 +16410,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>520</v>
+        <v>578</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>523</v>
+        <v>581</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>522</v>
+        <v>580</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15617,19 +16430,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>524</v>
+        <v>582</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>525</v>
+        <v>583</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>517</v>
+        <v>575</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15637,19 +16450,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>526</v>
+        <v>584</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>527</v>
+        <v>585</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>517</v>
+        <v>575</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15657,19 +16470,19 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>528</v>
+        <v>586</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>529</v>
+        <v>587</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>522</v>
+        <v>580</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15677,19 +16490,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>528</v>
+        <v>586</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>530</v>
+        <v>588</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>522</v>
+        <v>580</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15697,19 +16510,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>531</v>
+        <v>589</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>532</v>
+        <v>590</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>517</v>
+        <v>575</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15717,19 +16530,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>533</v>
+        <v>591</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>534</v>
+        <v>592</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>517</v>
+        <v>575</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15737,19 +16550,19 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>535</v>
+        <v>593</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>536</v>
+        <v>594</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>522</v>
+        <v>580</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15757,19 +16570,19 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>537</v>
+        <v>595</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>538</v>
+        <v>596</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>522</v>
+        <v>580</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15777,19 +16590,19 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>539</v>
+        <v>597</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>540</v>
+        <v>598</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>517</v>
+        <v>575</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15797,19 +16610,19 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>541</v>
+        <v>599</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>542</v>
+        <v>600</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>517</v>
+        <v>575</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15817,19 +16630,19 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>543</v>
+        <v>601</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>544</v>
+        <v>602</v>
       </c>
       <c r="E20" s="1">
         <v>50</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>517</v>
+        <v>575</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15837,19 +16650,19 @@
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>545</v>
+        <v>603</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>546</v>
+        <v>604</v>
       </c>
       <c r="E21" s="1">
         <v>50</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>517</v>
+        <v>575</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15857,19 +16670,19 @@
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>547</v>
+        <v>605</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>548</v>
+        <v>606</v>
       </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>517</v>
+        <v>575</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15877,19 +16690,19 @@
         <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>549</v>
+        <v>607</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>550</v>
+        <v>608</v>
       </c>
       <c r="E23" s="1">
         <v>50</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>517</v>
+        <v>575</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15897,19 +16710,19 @@
         <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>539</v>
+        <v>597</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>551</v>
+        <v>609</v>
       </c>
       <c r="E24" s="1">
         <v>50</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>522</v>
+        <v>580</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15917,19 +16730,19 @@
         <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>541</v>
+        <v>599</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>552</v>
+        <v>610</v>
       </c>
       <c r="E25" s="1">
         <v>50</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>522</v>
+        <v>580</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15937,19 +16750,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>543</v>
+        <v>601</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>553</v>
+        <v>611</v>
       </c>
       <c r="E26" s="1">
         <v>50</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>522</v>
+        <v>580</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15957,19 +16770,19 @@
         <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>545</v>
+        <v>603</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>554</v>
+        <v>612</v>
       </c>
       <c r="E27" s="1">
         <v>50</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>522</v>
+        <v>580</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15977,19 +16790,19 @@
         <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>543</v>
+        <v>601</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>555</v>
+        <v>613</v>
       </c>
       <c r="E28" s="1">
         <v>50</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>522</v>
+        <v>580</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -15997,19 +16810,19 @@
         <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>545</v>
+        <v>603</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>556</v>
+        <v>614</v>
       </c>
       <c r="E29" s="1">
         <v>50</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>522</v>
+        <v>580</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -16017,19 +16830,19 @@
         <v>19</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>557</v>
+        <v>615</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>508</v>
+        <v>566</v>
       </c>
       <c r="E30" s="1">
         <v>101</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>517</v>
+        <v>575</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -16037,19 +16850,19 @@
         <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>557</v>
+        <v>615</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>510</v>
+        <v>568</v>
       </c>
       <c r="E31" s="1">
         <v>-1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>522</v>
+        <v>580</v>
       </c>
     </row>
   </sheetData>
@@ -16086,13 +16899,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>273</v>
+        <v>331</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -16109,10 +16922,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>558</v>
+        <v>616</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -16130,7 +16943,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>255</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16138,10 +16951,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>560</v>
+        <v>618</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -16159,7 +16972,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>255</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16167,10 +16980,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>561</v>
+        <v>619</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -16188,7 +17001,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>255</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16196,10 +17009,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>562</v>
+        <v>620</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -16217,7 +17030,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>255</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16225,10 +17038,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>563</v>
+        <v>621</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -16246,7 +17059,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>255</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16254,10 +17067,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>564</v>
+        <v>622</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -16275,7 +17088,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>255</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16283,10 +17096,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>565</v>
+        <v>623</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -16304,7 +17117,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16312,10 +17125,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>566</v>
+        <v>624</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -16333,7 +17146,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16341,10 +17154,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>567</v>
+        <v>625</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -16362,7 +17175,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16370,10 +17183,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>568</v>
+        <v>626</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -16391,7 +17204,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16399,10 +17212,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>569</v>
+        <v>627</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -16420,7 +17233,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16428,10 +17241,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>570</v>
+        <v>628</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -16449,7 +17262,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14" ht="28.8" spans="1:9">
@@ -16457,10 +17270,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>571</v>
+        <v>629</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -16480,10 +17293,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>571</v>
+        <v>629</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -16503,10 +17316,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>572</v>
+        <v>630</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -16526,10 +17339,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>572</v>
+        <v>630</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -16576,13 +17389,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>273</v>
+        <v>331</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -16599,10 +17412,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>573</v>
+        <v>631</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>574</v>
+        <v>632</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -16628,10 +17441,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>575</v>
+        <v>633</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>574</v>
+        <v>632</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16657,10 +17470,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>576</v>
+        <v>634</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>574</v>
+        <v>632</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16678,7 +17491,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16686,10 +17499,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>577</v>
+        <v>635</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>574</v>
+        <v>632</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -16707,7 +17520,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16715,10 +17528,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>578</v>
+        <v>636</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>574</v>
+        <v>632</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -16736,7 +17549,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16744,10 +17557,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>579</v>
+        <v>637</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>574</v>
+        <v>632</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -16765,7 +17578,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16773,10 +17586,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>580</v>
+        <v>638</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>574</v>
+        <v>632</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -16802,10 +17615,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>581</v>
+        <v>639</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>574</v>
+        <v>632</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -16831,10 +17644,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>582</v>
+        <v>640</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>574</v>
+        <v>632</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -16852,7 +17665,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16860,10 +17673,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>583</v>
+        <v>641</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>574</v>
+        <v>632</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -16881,7 +17694,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16889,10 +17702,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>584</v>
+        <v>642</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>574</v>
+        <v>632</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -16910,7 +17723,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16918,10 +17731,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>585</v>
+        <v>643</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>574</v>
+        <v>632</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -16939,7 +17752,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -16947,10 +17760,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>586</v>
+        <v>644</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>574</v>
+        <v>632</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -16970,10 +17783,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>586</v>
+        <v>644</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>574</v>
+        <v>632</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -16993,10 +17806,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>587</v>
+        <v>645</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>574</v>
+        <v>632</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -17016,10 +17829,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>587</v>
+        <v>645</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>574</v>
+        <v>632</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -17162,13 +17975,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>273</v>
+        <v>331</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -17185,10 +17998,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>430</v>
+        <v>488</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>588</v>
+        <v>646</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17214,10 +18027,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>432</v>
+        <v>490</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>588</v>
+        <v>646</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -17243,10 +18056,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>433</v>
+        <v>491</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>588</v>
+        <v>646</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -17272,10 +18085,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>434</v>
+        <v>492</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>588</v>
+        <v>646</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -17301,10 +18114,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>435</v>
+        <v>493</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>588</v>
+        <v>646</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -17330,10 +18143,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>436</v>
+        <v>494</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>588</v>
+        <v>646</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -17359,10 +18172,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>437</v>
+        <v>495</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>588</v>
+        <v>646</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -17382,10 +18195,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>437</v>
+        <v>495</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>588</v>
+        <v>646</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -17405,10 +18218,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>438</v>
+        <v>496</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>588</v>
+        <v>646</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -17428,10 +18241,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>438</v>
+        <v>496</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>588</v>
+        <v>646</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -17478,7 +18291,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>183</v>
+        <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -17498,10 +18311,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>589</v>
+        <v>647</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>590</v>
+        <v>648</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17515,10 +18328,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>589</v>
+        <v>647</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>590</v>
+        <v>648</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -17532,10 +18345,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>589</v>
+        <v>647</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>590</v>
+        <v>648</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -17549,10 +18362,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>589</v>
+        <v>647</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>590</v>
+        <v>648</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -17566,10 +18379,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>589</v>
+        <v>647</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>590</v>
+        <v>648</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -17583,10 +18396,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>589</v>
+        <v>647</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>590</v>
+        <v>648</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -17600,10 +18413,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>589</v>
+        <v>647</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>590</v>
+        <v>648</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -17661,10 +18474,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>589</v>
+        <v>647</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>590</v>
+        <v>648</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -17723,16 +18536,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>591</v>
+        <v>649</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>592</v>
+        <v>650</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>593</v>
+        <v>651</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>594</v>
+        <v>652</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>34</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="18" activeTab="24"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="18" activeTab="24"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2287" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2263" uniqueCount="641">
   <si>
     <t>ID</t>
   </si>
@@ -545,7 +545,7 @@
     <t>send_angles</t>
   </si>
   <si>
-    <t>[10,10,10,5,10,90,10]</t>
+    <t>[10,10,10,1,10,90,10]</t>
   </si>
   <si>
     <t>正确设置多关节角度，速度50</t>
@@ -692,42 +692,6 @@
     <t>右臂七关节运动到负限位</t>
   </si>
   <si>
-    <t>右臂十一关节运动到正限位</t>
-  </si>
-  <si>
-    <t>[0,0,0,0,0,90,0,0,0,0]</t>
-  </si>
-  <si>
-    <t>右臂十一关节运动到负限位</t>
-  </si>
-  <si>
-    <t>[0,0,0,0,0,90,0,-55,0,0]</t>
-  </si>
-  <si>
-    <t>右臂十二关节运动到正限位</t>
-  </si>
-  <si>
-    <t>[0,0,0,0,0,90,0,0,245,0]</t>
-  </si>
-  <si>
-    <t>右臂十二关节运动到负限位</t>
-  </si>
-  <si>
-    <t>[0,0,0,0,0,90,0,0,-70,0]</t>
-  </si>
-  <si>
-    <t>右臂十三关节运动到正限位</t>
-  </si>
-  <si>
-    <t>[0,0,0,0,0,90,0,0,0,160]</t>
-  </si>
-  <si>
-    <t>右臂十三关节运动到负限位</t>
-  </si>
-  <si>
-    <t>[0,0,0,0,0,90,0,0,0,-160]</t>
-  </si>
-  <si>
     <t>设置多关节角度，速度超限（-1）</t>
   </si>
   <si>
@@ -746,46 +710,46 @@
     <t>[0,10,0,0,0,90,60]</t>
   </si>
   <si>
-    <t>设置多关节角度，1关节超限（-170）</t>
-  </si>
-  <si>
-    <t>[-170,10,0,0,0,90,60]</t>
-  </si>
-  <si>
-    <t>设置多关节角度，1关节超限（170）</t>
-  </si>
-  <si>
-    <t>[170,10,0,0,0,90,60]</t>
-  </si>
-  <si>
-    <t>设置多关节角度，2关节超限（-60）</t>
-  </si>
-  <si>
-    <t>[0,-60,0,0,0,90,60]</t>
-  </si>
-  <si>
-    <t>设置多关节角度，2关节超限（130）</t>
-  </si>
-  <si>
-    <t>[0,130,0,0,0,90,60]</t>
-  </si>
-  <si>
-    <t>设置多关节角度，3关节超限（-170）</t>
-  </si>
-  <si>
-    <t>[0,10,-170,0,0,90,60]</t>
-  </si>
-  <si>
-    <t>设置多关节角度，3关节超限（170）</t>
-  </si>
-  <si>
-    <t>[0,10,170,0,0,90,60]</t>
-  </si>
-  <si>
-    <t>设置多关节角度，4关节超限（-170）</t>
-  </si>
-  <si>
-    <t>[0,10,0,-170,0,90,60]</t>
+    <t>设置多关节角度，1关节超限（-166）</t>
+  </si>
+  <si>
+    <t>[-166,10,0,0,0,90,60]</t>
+  </si>
+  <si>
+    <t>设置多关节角度，1关节超限（166）</t>
+  </si>
+  <si>
+    <t>[166,10,0,0,0,90,60]</t>
+  </si>
+  <si>
+    <t>设置多关节角度，2关节超限（-51）</t>
+  </si>
+  <si>
+    <t>[0,-51,0,0,0,90,60]</t>
+  </si>
+  <si>
+    <t>设置多关节角度，2关节超限（121）</t>
+  </si>
+  <si>
+    <t>[0,121,0,0,0,90,60]</t>
+  </si>
+  <si>
+    <t>设置多关节角度，3关节超限（-166）</t>
+  </si>
+  <si>
+    <t>[0,10,-166,0,0,90,60]</t>
+  </si>
+  <si>
+    <t>设置多关节角度，3关节超限（166）</t>
+  </si>
+  <si>
+    <t>[0,10,166,0,0,90,60]</t>
+  </si>
+  <si>
+    <t>设置多关节角度，4关节超限（-166）</t>
+  </si>
+  <si>
+    <t>[0,10,0,-166,0,90,60]</t>
   </si>
   <si>
     <t>设置多关节角度，4关节超限（2）</t>
@@ -794,40 +758,40 @@
     <t>[0,10,0,2,0,90,60]</t>
   </si>
   <si>
-    <t>设置多关节角度，5关节超限（-170）</t>
-  </si>
-  <si>
-    <t>[0,10,0,0,-170,90,60]</t>
-  </si>
-  <si>
-    <t>设置多关节角度，5关节超限（170）</t>
-  </si>
-  <si>
-    <t>[0,10,0,0,170,90,60]</t>
-  </si>
-  <si>
-    <t>设置多关节角度，6关节超限（-80）</t>
-  </si>
-  <si>
-    <t>[0,10,0,0,0,-80,60]</t>
-  </si>
-  <si>
-    <t>设置多关节角度，6关节超限（260）</t>
-  </si>
-  <si>
-    <t>[0,10,0,0,0,260,60]</t>
-  </si>
-  <si>
-    <t>设置多关节角度，7关节超限（-170）</t>
-  </si>
-  <si>
-    <t>[0,10,0,0,0,90,-170]</t>
-  </si>
-  <si>
-    <t>设置多关节角度，7关节超限（170）</t>
-  </si>
-  <si>
-    <t>[0,10,0,0,0,90,170]</t>
+    <t>设置多关节角度，5关节超限（-166）</t>
+  </si>
+  <si>
+    <t>[0,10,0,0,-166,90,60]</t>
+  </si>
+  <si>
+    <t>设置多关节角度，5关节超限（166）</t>
+  </si>
+  <si>
+    <t>[0,10,0,0,166,90,60]</t>
+  </si>
+  <si>
+    <t>设置多关节角度，6关节超限（-76）</t>
+  </si>
+  <si>
+    <t>[0,10,0,0,0,-76,60]</t>
+  </si>
+  <si>
+    <t>设置多关节角度，6关节超限（256）</t>
+  </si>
+  <si>
+    <t>[0,10,0,0,0,256,60]</t>
+  </si>
+  <si>
+    <t>设置多关节角度，7关节超限（-161）</t>
+  </si>
+  <si>
+    <t>[0,10,0,0,0,90,-161]</t>
+  </si>
+  <si>
+    <t>设置多关节角度，7关节超限（161）</t>
+  </si>
+  <si>
+    <t>[0,10,0,0,0,90,161]</t>
   </si>
   <si>
     <t>joint</t>
@@ -5469,7 +5433,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.2222222222222" customWidth="1"/>
@@ -5586,6 +5550,9 @@
       </c>
     </row>
     <row r="5" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
       <c r="B5" s="1" t="s">
         <v>153</v>
       </c>
@@ -5606,6 +5573,9 @@
       </c>
     </row>
     <row r="6" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
       <c r="B6" s="1" t="s">
         <v>156</v>
       </c>
@@ -5626,6 +5596,9 @@
       </c>
     </row>
     <row r="7" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
       <c r="B7" s="1" t="s">
         <v>158</v>
       </c>
@@ -5646,6 +5619,9 @@
       </c>
     </row>
     <row r="8" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
       <c r="B8" s="1" t="s">
         <v>160</v>
       </c>
@@ -5666,6 +5642,9 @@
       </c>
     </row>
     <row r="9" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
       <c r="B9" s="1" t="s">
         <v>162</v>
       </c>
@@ -5686,6 +5665,9 @@
       </c>
     </row>
     <row r="10" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
       <c r="B10" s="1" t="s">
         <v>164</v>
       </c>
@@ -5706,6 +5688,9 @@
       </c>
     </row>
     <row r="11" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
       <c r="B11" s="1" t="s">
         <v>166</v>
       </c>
@@ -5726,6 +5711,9 @@
       </c>
     </row>
     <row r="12" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
       <c r="B12" s="1" t="s">
         <v>168</v>
       </c>
@@ -5746,6 +5734,9 @@
       </c>
     </row>
     <row r="13" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
       <c r="B13" s="1" t="s">
         <v>170</v>
       </c>
@@ -5766,6 +5757,9 @@
       </c>
     </row>
     <row r="14" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
       <c r="B14" s="1" t="s">
         <v>172</v>
       </c>
@@ -5786,6 +5780,9 @@
       </c>
     </row>
     <row r="15" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
       <c r="B15" s="1" t="s">
         <v>174</v>
       </c>
@@ -5806,6 +5803,9 @@
       </c>
     </row>
     <row r="16" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
       <c r="B16" s="1" t="s">
         <v>176</v>
       </c>
@@ -5825,7 +5825,10 @@
         <v>155</v>
       </c>
     </row>
-    <row r="17" customFormat="1" ht="28.8" spans="2:8">
+    <row r="17" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
       <c r="B17" s="1" t="s">
         <v>178</v>
       </c>
@@ -5845,7 +5848,10 @@
         <v>155</v>
       </c>
     </row>
-    <row r="18" customFormat="1" ht="28.8" spans="2:8">
+    <row r="18" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
       <c r="B18" s="1" t="s">
         <v>180</v>
       </c>
@@ -5865,7 +5871,10 @@
         <v>155</v>
       </c>
     </row>
-    <row r="19" customFormat="1" ht="28.8" spans="2:8">
+    <row r="19" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
       <c r="B19" s="1" t="s">
         <v>182</v>
       </c>
@@ -5885,7 +5894,10 @@
         <v>183</v>
       </c>
     </row>
-    <row r="20" customFormat="1" ht="28.8" spans="2:8">
+    <row r="20" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
       <c r="B20" s="1" t="s">
         <v>184</v>
       </c>
@@ -5905,7 +5917,10 @@
         <v>183</v>
       </c>
     </row>
-    <row r="21" customFormat="1" ht="28.8" spans="2:8">
+    <row r="21" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
       <c r="B21" s="1" t="s">
         <v>185</v>
       </c>
@@ -5925,7 +5940,10 @@
         <v>183</v>
       </c>
     </row>
-    <row r="22" customFormat="1" ht="28.8" spans="2:8">
+    <row r="22" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
       <c r="B22" s="1" t="s">
         <v>186</v>
       </c>
@@ -5945,7 +5963,10 @@
         <v>183</v>
       </c>
     </row>
-    <row r="23" customFormat="1" ht="28.8" spans="2:8">
+    <row r="23" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
       <c r="B23" s="1" t="s">
         <v>187</v>
       </c>
@@ -5965,7 +5986,10 @@
         <v>183</v>
       </c>
     </row>
-    <row r="24" customFormat="1" ht="28.8" spans="2:8">
+    <row r="24" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
       <c r="B24" s="1" t="s">
         <v>188</v>
       </c>
@@ -5985,7 +6009,10 @@
         <v>183</v>
       </c>
     </row>
-    <row r="25" customFormat="1" ht="28.8" spans="2:8">
+    <row r="25" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
       <c r="B25" s="1" t="s">
         <v>189</v>
       </c>
@@ -6005,7 +6032,10 @@
         <v>183</v>
       </c>
     </row>
-    <row r="26" customFormat="1" ht="28.8" spans="2:8">
+    <row r="26" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
       <c r="B26" s="1" t="s">
         <v>190</v>
       </c>
@@ -6025,7 +6055,10 @@
         <v>183</v>
       </c>
     </row>
-    <row r="27" customFormat="1" ht="28.8" spans="2:8">
+    <row r="27" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
       <c r="B27" s="1" t="s">
         <v>191</v>
       </c>
@@ -6045,7 +6078,10 @@
         <v>183</v>
       </c>
     </row>
-    <row r="28" customFormat="1" ht="28.8" spans="2:8">
+    <row r="28" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
       <c r="B28" s="1" t="s">
         <v>192</v>
       </c>
@@ -6065,7 +6101,10 @@
         <v>183</v>
       </c>
     </row>
-    <row r="29" customFormat="1" ht="28.8" spans="2:8">
+    <row r="29" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
       <c r="B29" s="1" t="s">
         <v>193</v>
       </c>
@@ -6085,7 +6124,10 @@
         <v>183</v>
       </c>
     </row>
-    <row r="30" customFormat="1" ht="28.8" spans="2:8">
+    <row r="30" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
       <c r="B30" s="1" t="s">
         <v>194</v>
       </c>
@@ -6105,7 +6147,10 @@
         <v>183</v>
       </c>
     </row>
-    <row r="31" customFormat="1" ht="28.8" spans="2:8">
+    <row r="31" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
       <c r="B31" s="1" t="s">
         <v>195</v>
       </c>
@@ -6125,7 +6170,10 @@
         <v>183</v>
       </c>
     </row>
-    <row r="32" customFormat="1" ht="28.8" spans="2:8">
+    <row r="32" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
       <c r="B32" s="1" t="s">
         <v>196</v>
       </c>
@@ -6145,7 +6193,10 @@
         <v>183</v>
       </c>
     </row>
-    <row r="33" customFormat="1" ht="28.8" spans="1:8">
+    <row r="33" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
       <c r="B33" s="1" t="s">
         <v>197</v>
       </c>
@@ -6156,16 +6207,16 @@
         <v>198</v>
       </c>
       <c r="E33" s="1">
-        <v>70</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="34" customFormat="1" ht="28.8" spans="1:8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
       <c r="B34" s="1" t="s">
         <v>199</v>
       </c>
@@ -6176,16 +6227,16 @@
         <v>200</v>
       </c>
       <c r="E34" s="1">
-        <v>60</v>
-      </c>
-      <c r="G34" s="1">
         <v>0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="35" customFormat="1" ht="28.8" spans="1:8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
       <c r="B35" s="1" t="s">
         <v>201</v>
       </c>
@@ -6196,16 +6247,16 @@
         <v>202</v>
       </c>
       <c r="E35" s="1">
-        <v>90</v>
-      </c>
-      <c r="G35" s="1">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="36" customFormat="1" ht="28.8" spans="1:8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
       <c r="B36" s="1" t="s">
         <v>203</v>
       </c>
@@ -6216,16 +6267,16 @@
         <v>204</v>
       </c>
       <c r="E36" s="1">
-        <v>70</v>
-      </c>
-      <c r="G36" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="37" customFormat="1" ht="28.8" spans="1:8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
       <c r="B37" s="1" t="s">
         <v>205</v>
       </c>
@@ -6236,16 +6287,16 @@
         <v>206</v>
       </c>
       <c r="E37" s="1">
-        <v>60</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="38" customFormat="1" ht="28.8" spans="1:8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
       <c r="B38" s="1" t="s">
         <v>207</v>
       </c>
@@ -6256,18 +6307,15 @@
         <v>208</v>
       </c>
       <c r="E38" s="1">
-        <v>60</v>
-      </c>
-      <c r="G38" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>183</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" customFormat="1" ht="43.2" spans="1:8">
       <c r="A39" s="2">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>209</v>
@@ -6279,7 +6327,7 @@
         <v>210</v>
       </c>
       <c r="E39" s="1">
-        <v>-1</v>
+        <v>50</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>42</v>
@@ -6287,7 +6335,7 @@
     </row>
     <row r="40" customFormat="1" ht="43.2" spans="1:8">
       <c r="A40" s="2">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>211</v>
@@ -6299,7 +6347,7 @@
         <v>212</v>
       </c>
       <c r="E40" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>42</v>
@@ -6307,7 +6355,7 @@
     </row>
     <row r="41" customFormat="1" ht="43.2" spans="1:8">
       <c r="A41" s="2">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>213</v>
@@ -6319,7 +6367,7 @@
         <v>214</v>
       </c>
       <c r="E41" s="1">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>42</v>
@@ -6327,7 +6375,7 @@
     </row>
     <row r="42" customFormat="1" ht="43.2" spans="1:8">
       <c r="A42" s="2">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>215</v>
@@ -6347,7 +6395,7 @@
     </row>
     <row r="43" customFormat="1" ht="43.2" spans="1:8">
       <c r="A43" s="2">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>217</v>
@@ -6367,7 +6415,7 @@
     </row>
     <row r="44" customFormat="1" ht="43.2" spans="1:8">
       <c r="A44" s="2">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>219</v>
@@ -6387,7 +6435,7 @@
     </row>
     <row r="45" customFormat="1" ht="43.2" spans="1:8">
       <c r="A45" s="2">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>221</v>
@@ -6407,7 +6455,7 @@
     </row>
     <row r="46" customFormat="1" ht="43.2" spans="1:8">
       <c r="A46" s="2">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>223</v>
@@ -6427,7 +6475,7 @@
     </row>
     <row r="47" customFormat="1" ht="43.2" spans="1:8">
       <c r="A47" s="2">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>225</v>
@@ -6447,7 +6495,7 @@
     </row>
     <row r="48" customFormat="1" ht="43.2" spans="1:8">
       <c r="A48" s="2">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>227</v>
@@ -6467,7 +6515,7 @@
     </row>
     <row r="49" customFormat="1" ht="43.2" spans="1:8">
       <c r="A49" s="2">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>229</v>
@@ -6482,126 +6530,6 @@
         <v>50</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="50" customFormat="1" ht="43.2" spans="1:8">
-      <c r="A50" s="2">
-        <v>15</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="E50" s="1">
-        <v>50</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="51" customFormat="1" ht="43.2" spans="1:8">
-      <c r="A51" s="2">
-        <v>16</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E51" s="1">
-        <v>50</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="52" customFormat="1" ht="43.2" spans="1:8">
-      <c r="A52" s="2">
-        <v>17</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E52" s="1">
-        <v>50</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" ht="43.2" spans="1:8">
-      <c r="A53" s="2">
-        <v>18</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E53" s="1">
-        <v>50</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="54" customFormat="1" ht="43.2" spans="1:8">
-      <c r="A54" s="2">
-        <v>19</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="E54" s="1">
-        <v>50</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="55" customFormat="1" ht="43.2" spans="1:8">
-      <c r="A55" s="2">
-        <v>20</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="E55" s="1">
-        <v>50</v>
-      </c>
-      <c r="H55" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -6634,7 +6562,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -6651,10 +6579,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -6674,10 +6602,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -6697,10 +6625,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -6720,10 +6648,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -6743,10 +6671,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -6766,10 +6694,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -6789,10 +6717,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -6812,10 +6740,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D9" s="1">
         <v>8</v>
@@ -6829,10 +6757,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -6874,7 +6802,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -6897,10 +6825,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -6926,10 +6854,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -6955,10 +6883,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -6984,10 +6912,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -7013,10 +6941,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -7042,10 +6970,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -7071,10 +6999,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -7100,10 +7028,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -7129,10 +7057,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -7158,10 +7086,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -7187,10 +7115,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -7216,10 +7144,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -7245,10 +7173,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -7274,10 +7202,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -7303,10 +7231,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D16" s="1">
         <v>11</v>
@@ -7332,10 +7260,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D17" s="1">
         <v>11</v>
@@ -7361,10 +7289,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D18" s="1">
         <v>12</v>
@@ -7390,10 +7318,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D19" s="1">
         <v>12</v>
@@ -7419,10 +7347,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D20" s="1">
         <v>13</v>
@@ -7448,10 +7376,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D21" s="1">
         <v>13</v>
@@ -7477,10 +7405,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -7500,10 +7428,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D23" s="1">
         <v>3</v>
@@ -7523,10 +7451,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D24" s="1">
         <v>5</v>
@@ -7546,10 +7474,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D25" s="1">
         <v>1</v>
@@ -7569,10 +7497,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
@@ -7592,10 +7520,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
@@ -7615,10 +7543,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
@@ -7638,10 +7566,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D29" s="1">
         <v>3</v>
@@ -7661,10 +7589,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
@@ -7684,10 +7612,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D31" s="1">
         <v>4</v>
@@ -7707,10 +7635,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D32" s="1">
         <v>4</v>
@@ -7730,10 +7658,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D33" s="1">
         <v>5</v>
@@ -7753,10 +7681,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D34" s="1">
         <v>5</v>
@@ -7776,10 +7704,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D35" s="1">
         <v>6</v>
@@ -7799,10 +7727,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D36" s="1">
         <v>6</v>
@@ -7822,10 +7750,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D37" s="1">
         <v>7</v>
@@ -7845,10 +7773,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D38" s="1">
         <v>7</v>
@@ -7912,19 +7840,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -7935,19 +7863,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>143</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>34</v>
@@ -8005,13 +7933,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -8031,13 +7959,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="E3" s="1">
         <v>50</v>
@@ -8057,13 +7985,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -8083,13 +8011,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -8109,13 +8037,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
@@ -8129,13 +8057,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
@@ -8149,13 +8077,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
@@ -8169,13 +8097,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
@@ -8189,13 +8117,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
@@ -8209,13 +8137,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
@@ -8229,13 +8157,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
@@ -8249,13 +8177,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
@@ -8269,13 +8197,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
@@ -8289,13 +8217,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
@@ -8309,13 +8237,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
@@ -8329,13 +8257,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
@@ -8349,13 +8277,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
@@ -8369,13 +8297,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
@@ -8389,13 +8317,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="E20" s="1">
         <v>101</v>
@@ -8409,13 +8337,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="E21" s="1">
         <v>-1</v>
@@ -8549,7 +8477,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -8572,10 +8500,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -8601,10 +8529,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -8622,7 +8550,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -8630,10 +8558,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -8651,7 +8579,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -8659,10 +8587,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -8680,7 +8608,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -8688,10 +8616,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -8709,7 +8637,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -8717,10 +8645,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -8738,7 +8666,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" ht="28.8" spans="1:9">
@@ -8746,10 +8674,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -8769,10 +8697,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -8792,10 +8720,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
@@ -8815,10 +8743,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
@@ -8838,10 +8766,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D12" s="1">
         <v>3</v>
@@ -8861,10 +8789,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D13" s="1">
         <v>3</v>
@@ -8884,10 +8812,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
@@ -8907,10 +8835,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D15" s="1">
         <v>3</v>
@@ -8930,10 +8858,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D16" s="1">
         <v>4</v>
@@ -8953,10 +8881,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D17" s="1">
         <v>4</v>
@@ -8976,10 +8904,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -8999,10 +8927,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D19" s="1">
         <v>5</v>
@@ -9022,10 +8950,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D20" s="1">
         <v>6</v>
@@ -9045,10 +8973,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D21" s="1">
         <v>6</v>
@@ -9068,10 +8996,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -9091,10 +9019,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -9114,10 +9042,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D24" s="1">
         <v>7</v>
@@ -9137,10 +9065,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -9205,10 +9133,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -9228,10 +9156,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -9251,10 +9179,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -9268,10 +9196,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="D5" s="1">
         <v>-3</v>
@@ -9330,10 +9258,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -9351,10 +9279,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -9417,10 +9345,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -9440,10 +9368,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -9463,10 +9391,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="D4" s="1">
         <v>-3</v>
@@ -9480,10 +9408,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -9542,10 +9470,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -9565,10 +9493,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -9588,10 +9516,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="D4" s="1">
         <v>-3</v>
@@ -9605,10 +9533,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -9653,7 +9581,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -9670,13 +9598,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -9688,7 +9616,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="57.6" spans="1:8">
@@ -9696,13 +9624,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -9714,7 +9642,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="57.6" spans="1:8">
@@ -9722,13 +9650,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -9740,7 +9668,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="57.6" spans="1:8">
@@ -9748,13 +9676,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -9766,7 +9694,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" ht="57.6" spans="1:8">
@@ -9774,13 +9702,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -9792,7 +9720,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" ht="57" customHeight="1" spans="1:8">
@@ -9800,10 +9728,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -9815,7 +9743,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="8" ht="57.6" spans="1:8">
@@ -9823,10 +9751,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -9838,7 +9766,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" ht="57.6" spans="1:8">
@@ -9846,10 +9774,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -9861,7 +9789,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -9869,10 +9797,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="E10" s="1">
         <v>-1</v>
@@ -9886,10 +9814,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -9948,10 +9876,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -9968,10 +9896,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -10034,10 +9962,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10057,10 +9985,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10080,10 +10008,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -10097,10 +10025,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -10145,7 +10073,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -10162,10 +10090,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -10188,10 +10116,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -10214,10 +10142,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="D4" s="1">
         <v>151</v>
@@ -10234,10 +10162,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -10254,10 +10182,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="D6" s="1">
         <v>201</v>
@@ -10274,10 +10202,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -10294,10 +10222,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -10314,10 +10242,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -10337,7 +10265,7 @@
         <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -10363,7 +10291,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -10414,7 +10342,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -10431,10 +10359,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10454,10 +10382,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10477,10 +10405,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -10494,10 +10422,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -10638,7 +10566,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -10655,10 +10583,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -10681,10 +10609,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -10707,10 +10635,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="D4" s="1">
         <v>201</v>
@@ -10727,10 +10655,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -10747,10 +10675,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="D6" s="1">
         <v>401</v>
@@ -10767,10 +10695,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -10787,10 +10715,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -10807,10 +10735,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -10827,10 +10755,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -10853,10 +10781,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -10918,16 +10846,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>34</v>
@@ -10977,10 +10905,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -11041,16 +10969,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11105,16 +11033,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11169,16 +11097,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11233,16 +11161,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11280,13 +11208,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -11303,10 +11231,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -11332,10 +11260,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="D3" s="1">
         <v>255</v>
@@ -11361,10 +11289,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -11390,10 +11318,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="D5" s="1">
         <v>256</v>
@@ -11457,10 +11385,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -11521,10 +11449,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -11544,10 +11472,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -11567,10 +11495,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -11584,10 +11512,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -11732,7 +11660,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -11752,10 +11680,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -11778,10 +11706,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -11804,10 +11732,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -11830,10 +11758,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -11856,10 +11784,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -11882,10 +11810,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -11908,10 +11836,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -11934,10 +11862,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -11954,10 +11882,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -11974,10 +11902,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -11994,10 +11922,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -12014,10 +11942,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -12026,10 +11954,10 @@
         <v>120</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -12084,17 +12012,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -12132,7 +12060,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -12152,10 +12080,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12178,10 +12106,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12204,10 +12132,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12230,10 +12158,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12256,10 +12184,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12282,10 +12210,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12308,10 +12236,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12334,10 +12262,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -12354,10 +12282,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -12374,10 +12302,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -12394,10 +12322,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -12414,10 +12342,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -12426,10 +12354,10 @@
         <v>100</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -12484,19 +12412,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -12551,10 +12479,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="E2" s="1">
         <v>50</v>
@@ -12615,10 +12543,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="D2" s="1">
         <v>30</v>
@@ -12638,10 +12566,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="D3" s="1">
         <v>301</v>
@@ -12655,10 +12583,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="D4" s="1">
         <v>-301</v>
@@ -12672,10 +12600,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="D5" s="1">
         <v>21</v>
@@ -12723,7 +12651,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -12746,10 +12674,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12775,10 +12703,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -12804,10 +12732,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -12833,10 +12761,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -12862,10 +12790,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -12891,10 +12819,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -12920,10 +12848,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -12949,10 +12877,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -12978,10 +12906,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -13007,10 +12935,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -13036,10 +12964,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -13065,10 +12993,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -13094,10 +13022,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -13123,10 +13051,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -13152,10 +13080,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -13175,10 +13103,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -13198,10 +13126,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -13221,7 +13149,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -13241,7 +13169,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -13288,7 +13216,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -13311,10 +13239,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13340,10 +13268,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13369,10 +13297,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13398,10 +13326,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13427,10 +13355,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -13456,10 +13384,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -13485,10 +13413,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -13508,10 +13436,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -13531,10 +13459,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -13554,10 +13482,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -13604,7 +13532,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -13627,10 +13555,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13656,10 +13584,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13685,10 +13613,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13706,7 +13634,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13714,10 +13642,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13735,7 +13663,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13743,10 +13671,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -13764,7 +13692,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13772,10 +13700,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -13793,7 +13721,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13801,10 +13729,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -13830,10 +13758,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -13859,10 +13787,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -13880,7 +13808,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13888,10 +13816,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -13909,7 +13837,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13917,10 +13845,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -13938,7 +13866,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13946,10 +13874,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -13967,7 +13895,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13975,10 +13903,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -13998,10 +13926,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -14021,10 +13949,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -14044,10 +13972,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -14095,7 +14023,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -14118,10 +14046,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14147,10 +14075,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14176,10 +14104,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14205,10 +14133,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14234,10 +14162,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14263,10 +14191,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14292,10 +14220,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14321,10 +14249,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14350,10 +14278,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14379,10 +14307,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14408,10 +14336,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14437,10 +14365,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14466,10 +14394,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -14495,10 +14423,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -14524,10 +14452,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -14547,10 +14475,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -14570,10 +14498,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -14593,7 +14521,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -14613,7 +14541,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -14971,7 +14899,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -14994,10 +14922,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -15023,10 +14951,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -15052,10 +14980,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -15073,7 +15001,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15081,10 +15009,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -15102,7 +15030,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15110,10 +15038,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -15131,7 +15059,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15139,10 +15067,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -15160,7 +15088,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15168,10 +15096,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -15197,10 +15125,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -15226,10 +15154,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -15247,7 +15175,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15255,10 +15183,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -15276,7 +15204,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15284,10 +15212,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -15305,7 +15233,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15313,10 +15241,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -15334,7 +15262,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15342,10 +15270,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -15365,10 +15293,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -15388,10 +15316,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -15411,10 +15339,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -15478,10 +15406,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -15547,10 +15475,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="D2" s="1">
         <v>45</v>
@@ -15573,10 +15501,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="D3" s="1">
         <v>-45</v>
@@ -15599,10 +15527,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="D4" s="1">
         <v>91</v>
@@ -15619,10 +15547,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="D5" s="1">
         <v>-91</v>
@@ -15639,10 +15567,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="D6" s="1">
         <v>45</v>
@@ -15659,10 +15587,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="D7" s="1">
         <v>45</v>
@@ -15707,10 +15635,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>145</v>
@@ -15730,16 +15658,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="F2" s="1">
         <v>50</v>
@@ -15759,16 +15687,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -15782,16 +15710,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="F4" s="1">
         <v>101</v>
@@ -15849,10 +15777,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -15872,10 +15800,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -15895,10 +15823,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -15918,10 +15846,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -15941,10 +15869,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
@@ -15964,10 +15892,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -15981,10 +15909,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
@@ -16048,10 +15976,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16071,10 +15999,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16094,10 +16022,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16111,10 +16039,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -16178,10 +16106,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16246,13 +16174,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -16272,13 +16200,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="E3" s="1">
         <v>30</v>
@@ -16298,13 +16226,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -16324,13 +16252,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -16350,19 +16278,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16370,19 +16298,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>577</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16390,19 +16318,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16410,19 +16338,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16430,19 +16358,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16450,19 +16378,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16470,19 +16398,19 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16490,19 +16418,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16510,19 +16438,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16530,19 +16458,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16550,19 +16478,19 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16570,19 +16498,19 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16590,19 +16518,19 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16610,19 +16538,19 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16630,19 +16558,19 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="E20" s="1">
         <v>50</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16650,19 +16578,19 @@
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="E21" s="1">
         <v>50</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16670,19 +16598,19 @@
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16690,19 +16618,19 @@
         <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="E23" s="1">
         <v>50</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16710,19 +16638,19 @@
         <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>597</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>609</v>
       </c>
       <c r="E24" s="1">
         <v>50</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16730,19 +16658,19 @@
         <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="E25" s="1">
         <v>50</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16750,19 +16678,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="E26" s="1">
         <v>50</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16770,19 +16698,19 @@
         <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="E27" s="1">
         <v>50</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16790,19 +16718,19 @@
         <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>613</v>
       </c>
       <c r="E28" s="1">
         <v>50</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16810,19 +16738,19 @@
         <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="E29" s="1">
         <v>50</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -16830,19 +16758,19 @@
         <v>19</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="E30" s="1">
         <v>101</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -16850,19 +16778,19 @@
         <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="E31" s="1">
         <v>-1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
     </row>
   </sheetData>
@@ -16899,7 +16827,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -16922,10 +16850,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -16951,10 +16879,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -16980,10 +16908,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -17009,10 +16937,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -17038,10 +16966,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -17067,10 +16995,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -17096,10 +17024,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -17125,10 +17053,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -17154,10 +17082,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -17183,10 +17111,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -17212,10 +17140,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -17241,10 +17169,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -17270,10 +17198,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -17293,10 +17221,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -17316,10 +17244,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -17339,10 +17267,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -17389,7 +17317,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -17412,10 +17340,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17441,10 +17369,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -17470,10 +17398,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -17491,7 +17419,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17499,10 +17427,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -17520,7 +17448,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17528,10 +17456,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -17549,7 +17477,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17557,10 +17485,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -17578,7 +17506,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17586,10 +17514,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -17615,10 +17543,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -17644,10 +17572,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -17665,7 +17593,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17673,10 +17601,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -17694,7 +17622,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17702,10 +17630,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -17723,7 +17651,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17731,10 +17659,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -17752,7 +17680,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -17760,10 +17688,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -17783,10 +17711,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -17806,10 +17734,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -17829,10 +17757,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -17975,7 +17903,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -17998,10 +17926,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18027,10 +17955,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -18056,10 +17984,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -18085,10 +18013,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18114,10 +18042,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18143,10 +18071,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18172,10 +18100,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18195,10 +18123,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -18218,10 +18146,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -18241,10 +18169,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -18291,7 +18219,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -18311,10 +18239,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18328,10 +18256,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -18345,10 +18273,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -18362,10 +18290,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -18379,10 +18307,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -18396,10 +18324,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -18413,10 +18341,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -18474,10 +18402,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -18536,16 +18464,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>34</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -782,16 +782,16 @@
     <t>[0,10,0,0,0,256,60]</t>
   </si>
   <si>
-    <t>设置多关节角度，7关节超限（-161）</t>
-  </si>
-  <si>
-    <t>[0,10,0,0,0,90,-161]</t>
-  </si>
-  <si>
-    <t>设置多关节角度，7关节超限（161）</t>
-  </si>
-  <si>
-    <t>[0,10,0,0,0,90,161]</t>
+    <t>设置多关节角度，7关节超限（-166）</t>
+  </si>
+  <si>
+    <t>[0,10,0,0,0,90,-166]</t>
+  </si>
+  <si>
+    <t>设置多关节角度，7关节超限（166）</t>
+  </si>
+  <si>
+    <t>[0,10,0,0,0,90,166]</t>
   </si>
   <si>
     <t>joint</t>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="18" activeTab="24"/>
+    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="21" activeTab="26"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2263" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="623">
   <si>
     <t>ID</t>
   </si>
@@ -824,118 +824,64 @@
     <t>获取关节角度，关节（超限）</t>
   </si>
   <si>
-    <t>正确设置1关节角度，正限位</t>
+    <t>正确设置单关节角度，速度10</t>
   </si>
   <si>
     <t>send_angle</t>
   </si>
   <si>
-    <t>正确设置1关节角度，负限位</t>
-  </si>
-  <si>
-    <t>正确设置2关节角度，正限位</t>
-  </si>
-  <si>
-    <t>正确设置2关节角度，负限位</t>
-  </si>
-  <si>
-    <t>正确设置3关节角度，正限位</t>
-  </si>
-  <si>
-    <t>正确设置3关节角度，负限位</t>
-  </si>
-  <si>
-    <t>正确设置4关节角度，正限位</t>
-  </si>
-  <si>
-    <t>正确设置4关节角度，负限位</t>
-  </si>
-  <si>
-    <t>正确设置5关节角度，正限位</t>
-  </si>
-  <si>
-    <t>正确设置5关节角度，负限位</t>
-  </si>
-  <si>
-    <t>正确设置6关节角度，正限位</t>
-  </si>
-  <si>
-    <t>正确设置6关节角度，负限位</t>
-  </si>
-  <si>
-    <t>正确设置7关节角度，正限位</t>
-  </si>
-  <si>
-    <t>正确设置7关节角度，负限位</t>
-  </si>
-  <si>
-    <t>正确设置11关节角度，正限位</t>
-  </si>
-  <si>
-    <t>正确设置11关节角度，负限位</t>
-  </si>
-  <si>
-    <t>正确设置12关节角度，正限位</t>
-  </si>
-  <si>
-    <t>正确设置12关节角度，负限位</t>
-  </si>
-  <si>
-    <t>正确设置13关节角度，正限位</t>
-  </si>
-  <si>
-    <t>正确设置13关节角度，负限位</t>
-  </si>
-  <si>
-    <t>设置关节角度，速度超限（-1）</t>
-  </si>
-  <si>
-    <t>设置关节角度，速度超限（0）</t>
-  </si>
-  <si>
-    <t>设置关节角度，速度超限（101）</t>
-  </si>
-  <si>
-    <t>设置1关节角度超限（-170）</t>
-  </si>
-  <si>
-    <t>设置1关节角度超限（170）</t>
-  </si>
-  <si>
-    <t>设置2关节角度超限（-60）</t>
-  </si>
-  <si>
-    <t>设置2关节角度超限（130）</t>
-  </si>
-  <si>
-    <t>设置3关节角度超限（-170）</t>
-  </si>
-  <si>
-    <t>设置3关节超限（170）</t>
-  </si>
-  <si>
-    <t>设置4关节超限（-170）</t>
-  </si>
-  <si>
-    <t>设置4关节超限（2）</t>
-  </si>
-  <si>
-    <t>设置5关节超限（-170）</t>
-  </si>
-  <si>
-    <t>设置5关节超限（170）</t>
-  </si>
-  <si>
-    <t>设置6关节超限（-80）</t>
-  </si>
-  <si>
-    <t>设置6关节超限（260）</t>
-  </si>
-  <si>
-    <t>设置7关节超限（-170）</t>
-  </si>
-  <si>
-    <t>设置7关节超限（170）</t>
+    <t>正确设置单关节角度，速度50</t>
+  </si>
+  <si>
+    <t>正确设置单关节角度，速度90</t>
+  </si>
+  <si>
+    <t>右臂十一关节运动到负限位</t>
+  </si>
+  <si>
+    <t>右臂十一关节运动到正限位</t>
+  </si>
+  <si>
+    <t>右臂十二关节运动到负限位</t>
+  </si>
+  <si>
+    <t>右臂十二关节运动到正限位</t>
+  </si>
+  <si>
+    <t>右臂十三关节运动到负限位</t>
+  </si>
+  <si>
+    <t>右臂十三关节运动到正限位</t>
+  </si>
+  <si>
+    <t>设置单关节角度，速度超限（-1）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，速度超限（0）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，速度超限（101）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，1关节超限（-166）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，1关节超限（166）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，11关节超限（1）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，11关节超限（-56）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，12关节超限（246）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，12关节超限（-71）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，13关节超限（-161）</t>
   </si>
   <si>
     <t>正确获取机械臂全坐标</t>
@@ -2638,7 +2584,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2650,6 +2596,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3014,11 +2963,11 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="5" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="6" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="6" width="14.7777777777778" style="5" customWidth="1"/>
+    <col min="5" max="6" width="14.7777777777778" style="6" customWidth="1"/>
     <col min="7" max="7" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3056,10 +3005,10 @@
         <v>8</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="6">
-        <v>2</v>
-      </c>
-      <c r="F2" s="6">
+      <c r="E2" s="7">
+        <v>2</v>
+      </c>
+      <c r="F2" s="7">
         <v>2</v>
       </c>
       <c r="G2" t="s">
@@ -3076,10 +3025,10 @@
       <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="7">
-        <v>2</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="E3" s="8">
+        <v>2</v>
+      </c>
+      <c r="F3" s="8">
         <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -3096,10 +3045,10 @@
       <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="7">
-        <v>2</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="E4" s="8">
+        <v>2</v>
+      </c>
+      <c r="F4" s="8">
         <v>2</v>
       </c>
       <c r="G4" t="s">
@@ -3401,7 +3350,7 @@
       <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="4"/>
+      <c r="E3" s="5"/>
       <c r="G3" s="1" t="s">
         <v>60</v>
       </c>
@@ -6778,17 +6727,17 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
-    <col min="3" max="4" width="18" style="1" customWidth="1"/>
-    <col min="5" max="5" width="26.6666666666667" style="1" customWidth="1"/>
-    <col min="6" max="7" width="17.2222222222222" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="13.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="5" width="32.7777777777778" style="4" customWidth="1"/>
+    <col min="6" max="7" width="17.2222222222222" style="4" customWidth="1"/>
+    <col min="8" max="8" width="18" style="4" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="16384" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:9">
@@ -6801,19 +6750,19 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -6830,26 +6779,26 @@
       <c r="C2" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D2" s="1">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1">
-        <v>165</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
         <v>10</v>
       </c>
-      <c r="G2" s="1">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1">
-        <v>0</v>
+      <c r="F2" s="2">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="51" customHeight="1" spans="1:9">
+    <row r="3" customFormat="1" ht="51" customHeight="1" spans="1:9">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -6859,26 +6808,26 @@
       <c r="C3" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D3" s="1">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1">
-        <v>-165</v>
-      </c>
-      <c r="F3" s="1">
-        <v>10</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0</v>
+      <c r="D3" s="2">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2">
+        <v>20</v>
+      </c>
+      <c r="F3" s="2">
+        <v>50</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="51" customHeight="1" spans="1:9">
+    <row r="4" customFormat="1" ht="51" customHeight="1" spans="1:9">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -6888,906 +6837,1491 @@
       <c r="C4" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D4" s="1">
-        <v>2</v>
-      </c>
-      <c r="E4" s="1">
-        <v>120</v>
-      </c>
-      <c r="F4" s="1">
-        <v>50</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0</v>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2">
+        <v>90</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="51" customHeight="1" spans="1:9">
+    <row r="5" customFormat="1" ht="28.8" spans="1:9">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D5" s="1">
-        <v>2</v>
-      </c>
-      <c r="E5" s="1">
-        <v>-50</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>165</v>
+      </c>
+      <c r="F5" s="2">
         <v>50</v>
       </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4"/>
       <c r="I5" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="51" customHeight="1" spans="1:9">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="28.8" spans="1:9">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>246</v>
+        <v>156</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D6" s="1">
-        <v>3</v>
-      </c>
-      <c r="E6" s="1">
-        <v>165</v>
-      </c>
-      <c r="F6" s="1">
-        <v>90</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>-165</v>
+      </c>
+      <c r="F6" s="2">
+        <v>30</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4"/>
       <c r="I6" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="51" customHeight="1" spans="1:9">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" ht="28.8" spans="1:9">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>247</v>
+        <v>158</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D7" s="1">
-        <v>3</v>
-      </c>
-      <c r="E7" s="1">
-        <v>-165</v>
-      </c>
-      <c r="F7" s="1">
-        <v>50</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
+      <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2">
+        <v>120</v>
+      </c>
+      <c r="F7" s="2">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4"/>
       <c r="I7" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="51" customHeight="1" spans="1:9">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" ht="28.8" spans="1:9">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>248</v>
+        <v>160</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D8" s="1">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1">
-        <v>50</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
+      <c r="D8" s="2">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>-50</v>
+      </c>
+      <c r="F8" s="2">
+        <v>70</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4"/>
       <c r="I8" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="51" customHeight="1" spans="1:9">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" ht="28.8" spans="1:9">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>249</v>
+        <v>162</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D9" s="1">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1">
-        <v>-165</v>
-      </c>
-      <c r="F9" s="1">
-        <v>50</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
+      <c r="D9" s="2">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>165</v>
+      </c>
+      <c r="F9" s="2">
+        <v>60</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4"/>
       <c r="I9" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="51" customHeight="1" spans="1:9">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" ht="28.8" spans="1:9">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>250</v>
+        <v>164</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D10" s="1">
-        <v>5</v>
-      </c>
-      <c r="E10" s="1">
-        <v>165</v>
-      </c>
-      <c r="F10" s="1">
-        <v>50</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
+      <c r="D10" s="2">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2">
+        <v>-165</v>
+      </c>
+      <c r="F10" s="2">
+        <v>90</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4"/>
       <c r="I10" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="51" customHeight="1" spans="1:9">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" ht="28.8" spans="1:9">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>251</v>
+        <v>166</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D11" s="1">
-        <v>5</v>
-      </c>
-      <c r="E11" s="1">
-        <v>-165</v>
-      </c>
-      <c r="F11" s="1">
+      <c r="D11" s="2">
+        <v>4</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
         <v>50</v>
       </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4"/>
       <c r="I11" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="51" customHeight="1" spans="1:9">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" ht="28.8" spans="1:9">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>252</v>
+        <v>168</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D12" s="1">
-        <v>6</v>
-      </c>
-      <c r="E12" s="1">
-        <v>255</v>
-      </c>
-      <c r="F12" s="1">
-        <v>50</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
+      <c r="D12" s="2">
+        <v>4</v>
+      </c>
+      <c r="E12" s="2">
+        <v>-165</v>
+      </c>
+      <c r="F12" s="2">
+        <v>30</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4"/>
       <c r="I12" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="51" customHeight="1" spans="1:9">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" ht="28.8" spans="1:9">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>253</v>
+        <v>170</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D13" s="1">
-        <v>6</v>
-      </c>
-      <c r="E13" s="1">
-        <v>-75</v>
-      </c>
-      <c r="F13" s="1">
-        <v>50</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
+      <c r="D13" s="2">
+        <v>5</v>
+      </c>
+      <c r="E13" s="2">
+        <v>165</v>
+      </c>
+      <c r="F13" s="2">
+        <v>10</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4"/>
       <c r="I13" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="51" customHeight="1" spans="1:9">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" ht="28.8" spans="1:9">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>254</v>
+        <v>172</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D14" s="1">
-        <v>7</v>
-      </c>
-      <c r="E14" s="1">
-        <v>165</v>
-      </c>
-      <c r="F14" s="1">
-        <v>50</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
+      <c r="D14" s="2">
+        <v>5</v>
+      </c>
+      <c r="E14" s="2">
+        <v>-165</v>
+      </c>
+      <c r="F14" s="2">
+        <v>70</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4"/>
       <c r="I14" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:9">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" ht="28.8" spans="1:9">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>255</v>
+        <v>174</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D15" s="1">
-        <v>7</v>
-      </c>
-      <c r="E15" s="1">
-        <v>-165</v>
-      </c>
-      <c r="F15" s="1">
-        <v>50</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
+      <c r="D15" s="2">
+        <v>6</v>
+      </c>
+      <c r="E15" s="2">
+        <v>255</v>
+      </c>
+      <c r="F15" s="2">
+        <v>60</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4"/>
       <c r="I15" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:9">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" ht="28.8" spans="1:9">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>256</v>
+        <v>176</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D16" s="1">
-        <v>11</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0</v>
-      </c>
-      <c r="F16" s="1">
-        <v>51</v>
-      </c>
-      <c r="G16" s="1">
-        <v>-2</v>
-      </c>
-      <c r="H16" s="1">
-        <v>-2</v>
-      </c>
+      <c r="D16" s="2">
+        <v>6</v>
+      </c>
+      <c r="E16" s="2">
+        <v>-75</v>
+      </c>
+      <c r="F16" s="2">
+        <v>90</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4"/>
       <c r="I16" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:9">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" ht="28.8" spans="1:9">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>257</v>
+        <v>178</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D17" s="1">
-        <v>11</v>
-      </c>
-      <c r="E17" s="1">
-        <v>-55</v>
-      </c>
-      <c r="F17" s="1">
-        <v>52</v>
-      </c>
-      <c r="G17" s="1">
-        <v>-2</v>
-      </c>
-      <c r="H17" s="1">
-        <v>-2</v>
-      </c>
+      <c r="D17" s="2">
+        <v>7</v>
+      </c>
+      <c r="E17" s="2">
+        <v>165</v>
+      </c>
+      <c r="F17" s="2">
+        <v>70</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4"/>
       <c r="I17" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:9">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" ht="28.8" spans="1:9">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>258</v>
+        <v>180</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D18" s="1">
-        <v>12</v>
-      </c>
-      <c r="E18" s="1">
-        <v>245</v>
-      </c>
-      <c r="F18" s="1">
-        <v>53</v>
-      </c>
-      <c r="G18" s="1">
-        <v>-2</v>
-      </c>
-      <c r="H18" s="1">
-        <v>-2</v>
-      </c>
+      <c r="D18" s="2">
+        <v>7</v>
+      </c>
+      <c r="E18" s="2">
+        <v>-165</v>
+      </c>
+      <c r="F18" s="2">
+        <v>60</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4"/>
       <c r="I18" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:9">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" ht="28.8" spans="1:9">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>259</v>
+        <v>182</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D19" s="1">
-        <v>12</v>
-      </c>
-      <c r="E19" s="1">
-        <v>-70</v>
-      </c>
-      <c r="F19" s="1">
-        <v>54</v>
-      </c>
-      <c r="G19" s="1">
-        <v>-2</v>
-      </c>
-      <c r="H19" s="1">
-        <v>-2</v>
+      <c r="D19" s="2">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2">
+        <v>165</v>
+      </c>
+      <c r="F19" s="2">
+        <v>50</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="2">
+        <v>0</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="20" customFormat="1" ht="28.8" spans="1:9">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>260</v>
+        <v>184</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D20" s="1">
-        <v>13</v>
-      </c>
-      <c r="E20" s="1">
-        <v>160</v>
-      </c>
-      <c r="F20" s="1">
-        <v>55</v>
-      </c>
-      <c r="G20" s="1">
-        <v>-2</v>
-      </c>
-      <c r="H20" s="1">
-        <v>-2</v>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2">
+        <v>-165</v>
+      </c>
+      <c r="F20" s="2">
+        <v>30</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="2">
+        <v>0</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="21" customFormat="1" ht="28.8" spans="1:9">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>261</v>
+        <v>185</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D21" s="1">
-        <v>13</v>
-      </c>
-      <c r="E21" s="1">
-        <v>-160</v>
-      </c>
-      <c r="F21" s="1">
-        <v>56</v>
-      </c>
-      <c r="G21" s="1">
-        <v>-2</v>
-      </c>
-      <c r="H21" s="1">
-        <v>-2</v>
+      <c r="D21" s="2">
+        <v>2</v>
+      </c>
+      <c r="E21" s="2">
+        <v>120</v>
+      </c>
+      <c r="F21" s="2">
+        <v>10</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="2">
+        <v>0</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="22" customFormat="1" ht="28.8" spans="1:9">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>262</v>
+        <v>186</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1">
-        <v>20</v>
-      </c>
-      <c r="F22" s="1">
-        <v>-1</v>
+      <c r="D22" s="2">
+        <v>2</v>
+      </c>
+      <c r="E22" s="2">
+        <v>-50</v>
+      </c>
+      <c r="F22" s="2">
+        <v>70</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="2">
+        <v>0</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="28.8" spans="1:9">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" ht="28.8" spans="1:9">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>263</v>
+        <v>187</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="2">
         <v>3</v>
       </c>
-      <c r="E23" s="1">
-        <v>20</v>
-      </c>
-      <c r="F23" s="1">
+      <c r="E23" s="2">
+        <v>165</v>
+      </c>
+      <c r="F23" s="2">
+        <v>60</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="2">
         <v>0</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="28.8" spans="1:9">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" ht="28.8" spans="1:9">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>264</v>
+        <v>188</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D24" s="1">
-        <v>5</v>
-      </c>
-      <c r="E24" s="1">
-        <v>20</v>
-      </c>
-      <c r="F24" s="1">
-        <v>101</v>
+      <c r="D24" s="2">
+        <v>3</v>
+      </c>
+      <c r="E24" s="2">
+        <v>-165</v>
+      </c>
+      <c r="F24" s="2">
+        <v>90</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="2">
+        <v>0</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="28.8" spans="1:9">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" ht="28.8" spans="1:9">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>265</v>
+        <v>189</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D25" s="1">
-        <v>1</v>
-      </c>
-      <c r="E25" s="1">
-        <v>-170</v>
-      </c>
-      <c r="F25" s="1">
+      <c r="D25" s="2">
+        <v>4</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
         <v>50</v>
       </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
       <c r="I25" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="28.8" spans="1:9">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" ht="28.8" spans="1:9">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>266</v>
+        <v>190</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D26" s="1">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1">
-        <v>170</v>
-      </c>
-      <c r="F26" s="1">
-        <v>50</v>
+      <c r="D26" s="2">
+        <v>4</v>
+      </c>
+      <c r="E26" s="2">
+        <v>-165</v>
+      </c>
+      <c r="F26" s="2">
+        <v>30</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="2">
+        <v>0</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="28.8" spans="1:9">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" ht="28.8" spans="1:9">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>267</v>
+        <v>191</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D27" s="1">
-        <v>2</v>
-      </c>
-      <c r="E27" s="1">
-        <v>-60</v>
-      </c>
-      <c r="F27" s="1">
-        <v>50</v>
+      <c r="D27" s="2">
+        <v>5</v>
+      </c>
+      <c r="E27" s="2">
+        <v>165</v>
+      </c>
+      <c r="F27" s="2">
+        <v>10</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="2">
+        <v>0</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="28.8" spans="1:9">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" ht="28.8" spans="1:9">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>268</v>
+        <v>192</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D28" s="1">
-        <v>2</v>
-      </c>
-      <c r="E28" s="1">
-        <v>130</v>
-      </c>
-      <c r="F28" s="1">
-        <v>50</v>
+      <c r="D28" s="2">
+        <v>5</v>
+      </c>
+      <c r="E28" s="2">
+        <v>-165</v>
+      </c>
+      <c r="F28" s="2">
+        <v>70</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="2">
+        <v>0</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="28.8" spans="1:9">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" ht="28.8" spans="1:9">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>269</v>
+        <v>193</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D29" s="1">
-        <v>3</v>
-      </c>
-      <c r="E29" s="1">
-        <v>-170</v>
-      </c>
-      <c r="F29" s="1">
-        <v>50</v>
+      <c r="D29" s="2">
+        <v>6</v>
+      </c>
+      <c r="E29" s="2">
+        <v>255</v>
+      </c>
+      <c r="F29" s="2">
+        <v>60</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="2">
+        <v>0</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="28.8" spans="1:9">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" ht="28.8" spans="1:9">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>270</v>
+        <v>194</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D30" s="1">
-        <v>3</v>
-      </c>
-      <c r="E30" s="1">
-        <v>170</v>
-      </c>
-      <c r="F30" s="1">
-        <v>50</v>
+      <c r="D30" s="2">
+        <v>6</v>
+      </c>
+      <c r="E30" s="2">
+        <v>-75</v>
+      </c>
+      <c r="F30" s="2">
+        <v>90</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="2">
+        <v>0</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="28.8" spans="1:9">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" ht="28.8" spans="1:9">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>271</v>
+        <v>195</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D31" s="1">
-        <v>4</v>
-      </c>
-      <c r="E31" s="1">
-        <v>-170</v>
-      </c>
-      <c r="F31" s="1">
-        <v>50</v>
+      <c r="D31" s="2">
+        <v>7</v>
+      </c>
+      <c r="E31" s="2">
+        <v>165</v>
+      </c>
+      <c r="F31" s="2">
+        <v>70</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="2">
+        <v>0</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="28.8" spans="1:9">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" ht="28.8" spans="1:9">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>272</v>
+        <v>196</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D32" s="1">
-        <v>4</v>
-      </c>
-      <c r="E32" s="1">
-        <v>2</v>
-      </c>
-      <c r="F32" s="1">
-        <v>50</v>
+      <c r="D32" s="2">
+        <v>7</v>
+      </c>
+      <c r="E32" s="2">
+        <v>-165</v>
+      </c>
+      <c r="F32" s="2">
+        <v>60</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="2">
+        <v>0</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" ht="28.8" spans="1:9">
-      <c r="A33" s="2">
-        <v>32</v>
-      </c>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A33" s="2"/>
       <c r="B33" s="1" t="s">
-        <v>273</v>
+        <v>245</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D33" s="1">
-        <v>5</v>
-      </c>
-      <c r="E33" s="1">
-        <v>-170</v>
-      </c>
-      <c r="F33" s="1">
-        <v>50</v>
+      <c r="D33" s="2">
+        <v>11</v>
+      </c>
+      <c r="E33" s="2">
+        <v>-55</v>
+      </c>
+      <c r="F33" s="2">
+        <v>30</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4">
+        <v>-2</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" ht="28.8" spans="1:9">
-      <c r="A34" s="2">
-        <v>33</v>
-      </c>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A34" s="2"/>
       <c r="B34" s="1" t="s">
-        <v>274</v>
+        <v>246</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D34" s="1">
-        <v>5</v>
-      </c>
-      <c r="E34" s="1">
-        <v>170</v>
-      </c>
-      <c r="F34" s="1">
-        <v>50</v>
+      <c r="D34" s="2">
+        <v>11</v>
+      </c>
+      <c r="E34" s="4">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2">
+        <v>10</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4">
+        <v>-2</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" ht="28.8" spans="1:9">
-      <c r="A35" s="2">
-        <v>34</v>
-      </c>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A35" s="2"/>
       <c r="B35" s="1" t="s">
-        <v>275</v>
+        <v>247</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D35" s="1">
-        <v>6</v>
-      </c>
-      <c r="E35" s="1">
-        <v>-80</v>
-      </c>
-      <c r="F35" s="1">
-        <v>50</v>
+      <c r="D35" s="2">
+        <v>12</v>
+      </c>
+      <c r="E35" s="2">
+        <v>-75</v>
+      </c>
+      <c r="F35" s="2">
+        <v>70</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4">
+        <v>-2</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" ht="28.8" spans="1:9">
-      <c r="A36" s="2">
-        <v>35</v>
-      </c>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A36" s="2"/>
       <c r="B36" s="1" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D36" s="1">
-        <v>6</v>
-      </c>
-      <c r="E36" s="1">
-        <v>260</v>
-      </c>
-      <c r="F36" s="1">
-        <v>50</v>
+      <c r="D36" s="2">
+        <v>12</v>
+      </c>
+      <c r="E36" s="2">
+        <v>245</v>
+      </c>
+      <c r="F36" s="2">
+        <v>60</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4">
+        <v>-2</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" ht="28.8" spans="1:9">
-      <c r="A37" s="2">
-        <v>36</v>
-      </c>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A37" s="2"/>
       <c r="B37" s="1" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D37" s="1">
-        <v>7</v>
-      </c>
-      <c r="E37" s="1">
-        <v>-170</v>
-      </c>
-      <c r="F37" s="1">
-        <v>50</v>
+      <c r="D37" s="2">
+        <v>13</v>
+      </c>
+      <c r="E37" s="2">
+        <v>-160</v>
+      </c>
+      <c r="F37" s="2">
+        <v>90</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4">
+        <v>-2</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="28.8" spans="1:9">
-      <c r="A38" s="2">
-        <v>37</v>
-      </c>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A38" s="2"/>
       <c r="B38" s="1" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D38" s="2">
+        <v>13</v>
+      </c>
+      <c r="E38" s="2">
+        <v>160</v>
+      </c>
+      <c r="F38" s="2">
+        <v>70</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4">
+        <v>-2</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" ht="43.2" spans="1:9">
+      <c r="A39" s="2">
+        <v>32</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D39" s="2">
+        <v>1</v>
+      </c>
+      <c r="E39" s="2">
+        <v>10</v>
+      </c>
+      <c r="F39" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" ht="43.2" spans="1:9">
+      <c r="A40" s="2">
+        <v>33</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D40" s="2">
+        <v>2</v>
+      </c>
+      <c r="E40" s="2">
+        <v>20</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" ht="43.2" spans="1:9">
+      <c r="A41" s="2">
+        <v>34</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D41" s="2">
+        <v>3</v>
+      </c>
+      <c r="E41" s="2">
+        <v>30</v>
+      </c>
+      <c r="F41" s="2">
+        <v>101</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" ht="43.2" spans="1:9">
+      <c r="A42" s="2">
+        <v>35</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D42" s="2">
+        <v>1</v>
+      </c>
+      <c r="E42" s="2">
+        <v>166</v>
+      </c>
+      <c r="F42" s="2">
+        <v>50</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" ht="43.2" spans="1:9">
+      <c r="A43" s="2">
+        <v>36</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D43" s="2">
+        <v>1</v>
+      </c>
+      <c r="E43" s="2">
+        <v>-166</v>
+      </c>
+      <c r="F43" s="2">
+        <v>50</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" ht="43.2" spans="1:9">
+      <c r="A44" s="2">
+        <v>37</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D44" s="2">
+        <v>2</v>
+      </c>
+      <c r="E44" s="2">
+        <v>-51</v>
+      </c>
+      <c r="F44" s="2">
+        <v>50</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" ht="43.2" spans="1:9">
+      <c r="A45" s="2">
+        <v>38</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D45" s="2">
+        <v>2</v>
+      </c>
+      <c r="E45" s="2">
+        <v>121</v>
+      </c>
+      <c r="F45" s="2">
+        <v>50</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" ht="43.2" spans="1:9">
+      <c r="A46" s="2">
+        <v>39</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D46" s="2">
+        <v>3</v>
+      </c>
+      <c r="E46" s="2">
+        <v>-166</v>
+      </c>
+      <c r="F46" s="2">
+        <v>50</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" ht="43.2" spans="1:9">
+      <c r="A47" s="2">
+        <v>40</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D47" s="2">
+        <v>3</v>
+      </c>
+      <c r="E47" s="2">
+        <v>166</v>
+      </c>
+      <c r="F47" s="2">
+        <v>50</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" ht="43.2" spans="1:9">
+      <c r="A48" s="2">
+        <v>41</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D48" s="2">
+        <v>4</v>
+      </c>
+      <c r="E48" s="2">
+        <v>166</v>
+      </c>
+      <c r="F48" s="2">
+        <v>50</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" ht="43.2" spans="1:9">
+      <c r="A49" s="2">
+        <v>42</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D49" s="2">
+        <v>4</v>
+      </c>
+      <c r="E49" s="2">
+        <v>2</v>
+      </c>
+      <c r="F49" s="2">
+        <v>50</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" ht="43.2" spans="1:9">
+      <c r="A50" s="2">
+        <v>43</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D50" s="2">
+        <v>5</v>
+      </c>
+      <c r="E50" s="2">
+        <v>-166</v>
+      </c>
+      <c r="F50" s="2">
+        <v>50</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" ht="43.2" spans="1:9">
+      <c r="A51" s="2">
+        <v>44</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D51" s="2">
+        <v>5</v>
+      </c>
+      <c r="E51" s="2">
+        <v>166</v>
+      </c>
+      <c r="F51" s="2">
+        <v>50</v>
+      </c>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" ht="43.2" spans="1:9">
+      <c r="A52" s="2">
+        <v>45</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D52" s="2">
+        <v>6</v>
+      </c>
+      <c r="E52" s="2">
+        <v>-76</v>
+      </c>
+      <c r="F52" s="2">
+        <v>50</v>
+      </c>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" ht="43.2" spans="1:9">
+      <c r="A53" s="2">
+        <v>46</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D53" s="2">
+        <v>6</v>
+      </c>
+      <c r="E53" s="2">
+        <v>256</v>
+      </c>
+      <c r="F53" s="2">
+        <v>50</v>
+      </c>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" ht="43.2" spans="1:9">
+      <c r="A54" s="2">
+        <v>47</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D54" s="2">
         <v>7</v>
       </c>
-      <c r="E38" s="1">
-        <v>170</v>
-      </c>
-      <c r="F38" s="1">
+      <c r="E54" s="2">
+        <v>-166</v>
+      </c>
+      <c r="F54" s="2">
         <v>50</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" ht="43.2" spans="1:9">
+      <c r="A55" s="2">
+        <v>48</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D55" s="2">
+        <v>7</v>
+      </c>
+      <c r="E55" s="2">
+        <v>166</v>
+      </c>
+      <c r="F55" s="2">
+        <v>50</v>
+      </c>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56" ht="43.2" spans="1:9">
+      <c r="A56" s="2">
+        <v>49</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D56" s="4">
+        <v>11</v>
+      </c>
+      <c r="E56" s="4">
+        <v>1</v>
+      </c>
+      <c r="F56" s="2">
+        <v>50</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="57" ht="43.2" spans="1:9">
+      <c r="A57" s="2">
+        <v>50</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D57" s="4">
+        <v>11</v>
+      </c>
+      <c r="E57" s="4">
+        <v>-56</v>
+      </c>
+      <c r="F57" s="2">
+        <v>50</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="58" ht="43.2" spans="1:9">
+      <c r="A58" s="2">
+        <v>51</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D58" s="4">
+        <v>12</v>
+      </c>
+      <c r="E58" s="4">
+        <v>246</v>
+      </c>
+      <c r="F58" s="2">
+        <v>50</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="59" ht="43.2" spans="1:9">
+      <c r="A59" s="2">
+        <v>52</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D59" s="4">
+        <v>12</v>
+      </c>
+      <c r="E59" s="4">
+        <v>-71</v>
+      </c>
+      <c r="F59" s="2">
+        <v>50</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="60" ht="43.2" spans="1:9">
+      <c r="A60" s="2">
+        <v>53</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D60" s="4">
+        <v>13</v>
+      </c>
+      <c r="E60" s="4">
+        <v>161</v>
+      </c>
+      <c r="F60" s="2">
+        <v>50</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="61" ht="43.2" spans="1:9">
+      <c r="A61" s="2">
+        <v>54</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D61" s="4">
+        <v>13</v>
+      </c>
+      <c r="E61" s="4">
+        <v>-161</v>
+      </c>
+      <c r="F61" s="2">
+        <v>50</v>
+      </c>
+      <c r="I61" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -7840,19 +8374,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -7863,19 +8397,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>143</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>34</v>
@@ -7933,13 +8467,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -7959,13 +8493,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="E3" s="1">
         <v>50</v>
@@ -7985,13 +8519,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -8011,13 +8545,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -8037,13 +8571,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
@@ -8057,13 +8591,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
@@ -8077,13 +8611,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
@@ -8097,13 +8631,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
@@ -8117,13 +8651,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
@@ -8137,13 +8671,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
@@ -8157,13 +8691,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
@@ -8177,13 +8711,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
@@ -8197,13 +8731,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
@@ -8217,13 +8751,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
@@ -8237,13 +8771,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
@@ -8257,13 +8791,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
@@ -8277,13 +8811,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
@@ -8297,13 +8831,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
@@ -8317,13 +8851,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="E20" s="1">
         <v>101</v>
@@ -8337,13 +8871,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="E21" s="1">
         <v>-1</v>
@@ -8364,11 +8898,11 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="5" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="6" customWidth="1"/>
     <col min="2" max="2" width="23.2222222222222" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="6" width="9" style="5"/>
+    <col min="5" max="6" width="9" style="6"/>
     <col min="7" max="7" width="13.7777777777778" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8417,7 +8951,7 @@
       </c>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:7">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -8431,7 +8965,7 @@
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:7">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -8477,7 +9011,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -8500,10 +9034,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -8529,10 +9063,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -8550,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -8558,10 +9092,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -8579,7 +9113,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -8587,10 +9121,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -8608,7 +9142,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -8616,10 +9150,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -8637,7 +9171,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -8645,10 +9179,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -8666,7 +9200,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" ht="28.8" spans="1:9">
@@ -8674,10 +9208,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -8697,10 +9231,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -8720,10 +9254,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
@@ -8743,10 +9277,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
@@ -8766,10 +9300,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D12" s="1">
         <v>3</v>
@@ -8789,10 +9323,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D13" s="1">
         <v>3</v>
@@ -8812,10 +9346,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
@@ -8835,10 +9369,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D15" s="1">
         <v>3</v>
@@ -8858,10 +9392,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D16" s="1">
         <v>4</v>
@@ -8881,10 +9415,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D17" s="1">
         <v>4</v>
@@ -8904,10 +9438,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -8927,10 +9461,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D19" s="1">
         <v>5</v>
@@ -8950,10 +9484,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D20" s="1">
         <v>6</v>
@@ -8973,10 +9507,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D21" s="1">
         <v>6</v>
@@ -8996,10 +9530,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -9019,10 +9553,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -9042,10 +9576,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D24" s="1">
         <v>7</v>
@@ -9065,10 +9599,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -9133,10 +9667,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -9156,10 +9690,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -9179,10 +9713,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -9196,10 +9730,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="D5" s="1">
         <v>-3</v>
@@ -9258,10 +9792,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -9279,10 +9813,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -9345,10 +9879,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -9368,10 +9902,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -9391,10 +9925,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="D4" s="1">
         <v>-3</v>
@@ -9408,10 +9942,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -9470,10 +10004,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -9493,10 +10027,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -9516,10 +10050,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="D4" s="1">
         <v>-3</v>
@@ -9533,10 +10067,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -9581,7 +10115,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -9598,13 +10132,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -9616,7 +10150,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="57.6" spans="1:8">
@@ -9624,13 +10158,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -9642,7 +10176,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="57.6" spans="1:8">
@@ -9650,13 +10184,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -9668,7 +10202,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="57.6" spans="1:8">
@@ -9676,13 +10210,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -9694,7 +10228,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" ht="57.6" spans="1:8">
@@ -9702,13 +10236,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -9720,7 +10254,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" ht="57" customHeight="1" spans="1:8">
@@ -9728,10 +10262,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -9743,7 +10277,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" ht="57.6" spans="1:8">
@@ -9751,10 +10285,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -9766,7 +10300,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" ht="57.6" spans="1:8">
@@ -9774,10 +10308,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -9789,7 +10323,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -9797,10 +10331,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="E10" s="1">
         <v>-1</v>
@@ -9814,10 +10348,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -9876,10 +10410,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -9896,10 +10430,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -9962,10 +10496,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -9985,10 +10519,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10008,10 +10542,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -10025,10 +10559,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -10073,7 +10607,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -10090,10 +10624,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -10116,10 +10650,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -10142,10 +10676,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="D4" s="1">
         <v>151</v>
@@ -10162,10 +10696,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -10182,10 +10716,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="D6" s="1">
         <v>201</v>
@@ -10202,10 +10736,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -10222,10 +10756,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -10242,10 +10776,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -10265,7 +10799,7 @@
         <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -10291,7 +10825,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -10342,7 +10876,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -10359,10 +10893,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10382,10 +10916,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10405,10 +10939,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -10422,10 +10956,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -10446,11 +10980,11 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="5" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="6" customWidth="1"/>
     <col min="2" max="2" width="23.2222222222222" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="6" width="9" style="5"/>
+    <col min="5" max="6" width="9" style="6"/>
     <col min="7" max="7" width="13.7777777777778" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10499,7 +11033,7 @@
       </c>
     </row>
     <row r="3" customFormat="1" ht="34" customHeight="1" spans="1:7">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -10508,14 +11042,14 @@
       <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
       <c r="G3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="1" ht="34" customHeight="1" spans="1:7">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -10524,8 +11058,8 @@
       <c r="C4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
       <c r="G4" s="1" t="s">
         <v>13</v>
       </c>
@@ -10566,7 +11100,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -10583,10 +11117,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -10609,10 +11143,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -10635,10 +11169,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="D4" s="1">
         <v>201</v>
@@ -10655,10 +11189,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -10675,10 +11209,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="D6" s="1">
         <v>401</v>
@@ -10695,10 +11229,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -10715,10 +11249,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -10735,10 +11269,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -10755,10 +11289,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -10781,10 +11315,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -10846,16 +11380,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>34</v>
@@ -10905,10 +11439,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -10969,16 +11503,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11033,16 +11567,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11097,16 +11631,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11161,16 +11695,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11208,13 +11742,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -11231,10 +11765,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -11260,10 +11794,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="D3" s="1">
         <v>255</v>
@@ -11289,10 +11823,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -11318,10 +11852,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="D5" s="1">
         <v>256</v>
@@ -11385,10 +11919,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -11449,10 +11983,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -11472,10 +12006,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -11495,10 +12029,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -11512,10 +12046,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -11536,7 +12070,7 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="5" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="6" customWidth="1"/>
     <col min="2" max="2" width="22.3333333333333" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="16.5555555555556" customWidth="1"/>
@@ -11589,7 +12123,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -11609,7 +12143,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -11680,10 +12214,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -11706,10 +12240,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -11732,10 +12266,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -11758,10 +12292,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -11784,10 +12318,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -11810,10 +12344,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -11836,10 +12370,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -11862,10 +12396,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -11882,10 +12416,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -11902,10 +12436,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -11922,10 +12456,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -11942,10 +12476,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -11954,10 +12488,10 @@
         <v>120</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -12012,17 +12546,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -12080,10 +12614,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12106,10 +12640,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12132,10 +12666,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12158,10 +12692,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12184,10 +12718,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12210,10 +12744,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12236,10 +12770,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12262,10 +12796,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -12282,10 +12816,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -12302,10 +12836,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -12322,10 +12856,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -12342,10 +12876,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -12354,10 +12888,10 @@
         <v>100</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -12412,19 +12946,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -12479,10 +13013,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="E2" s="1">
         <v>50</v>
@@ -12543,10 +13077,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="D2" s="1">
         <v>30</v>
@@ -12566,10 +13100,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="D3" s="1">
         <v>301</v>
@@ -12583,10 +13117,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="D4" s="1">
         <v>-301</v>
@@ -12600,10 +13134,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="D5" s="1">
         <v>21</v>
@@ -12674,10 +13208,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12703,10 +13237,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -12732,10 +13266,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -12761,10 +13295,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -12790,10 +13324,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -12819,10 +13353,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -12848,10 +13382,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -12877,10 +13411,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -12906,10 +13440,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -12935,10 +13469,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -12964,10 +13498,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -12993,10 +13527,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -13022,10 +13556,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -13051,10 +13585,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -13080,10 +13614,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -13103,10 +13637,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -13126,10 +13660,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -13149,7 +13683,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -13169,7 +13703,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -13216,7 +13750,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -13239,10 +13773,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13268,10 +13802,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13297,10 +13831,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13326,10 +13860,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13355,10 +13889,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -13384,10 +13918,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -13413,10 +13947,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -13436,10 +13970,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -13459,10 +13993,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -13482,10 +14016,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -13532,7 +14066,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -13555,10 +14089,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13584,10 +14118,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>487</v>
+        <v>469</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13613,10 +14147,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13634,7 +14168,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13642,10 +14176,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>489</v>
+        <v>471</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13663,7 +14197,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13671,10 +14205,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>490</v>
+        <v>472</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -13692,7 +14226,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13700,10 +14234,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>491</v>
+        <v>473</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -13721,7 +14255,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13729,10 +14263,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -13758,10 +14292,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -13787,10 +14321,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -13808,7 +14342,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13816,10 +14350,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -13837,7 +14371,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13845,10 +14379,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -13866,7 +14400,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13874,10 +14408,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>497</v>
+        <v>479</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -13895,7 +14429,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -13903,10 +14437,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -13926,10 +14460,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -13949,10 +14483,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>499</v>
+        <v>481</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -13972,10 +14506,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>499</v>
+        <v>481</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -14046,10 +14580,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>500</v>
+        <v>482</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14075,10 +14609,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14104,10 +14638,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14133,10 +14667,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14162,10 +14696,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>505</v>
+        <v>487</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14191,10 +14725,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14220,10 +14754,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>507</v>
+        <v>489</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14249,10 +14783,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14278,10 +14812,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>509</v>
+        <v>491</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14307,10 +14841,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14336,10 +14870,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14365,10 +14899,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14394,10 +14928,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>513</v>
+        <v>495</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -14423,10 +14957,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -14452,10 +14986,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>515</v>
+        <v>497</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -14475,10 +15009,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>516</v>
+        <v>498</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -14498,10 +15032,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -14521,7 +15055,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -14541,7 +15075,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -14899,7 +15433,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -14922,10 +15456,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>519</v>
+        <v>501</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14951,10 +15485,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14980,10 +15514,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>522</v>
+        <v>504</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -15001,7 +15535,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15009,10 +15543,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>523</v>
+        <v>505</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -15030,7 +15564,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15038,10 +15572,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -15059,7 +15593,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15067,10 +15601,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>525</v>
+        <v>507</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -15088,7 +15622,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15096,10 +15630,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -15125,10 +15659,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>527</v>
+        <v>509</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -15154,10 +15688,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>528</v>
+        <v>510</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -15175,7 +15709,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15183,10 +15717,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>529</v>
+        <v>511</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -15204,7 +15738,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15212,10 +15746,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>530</v>
+        <v>512</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -15233,7 +15767,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15241,10 +15775,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>531</v>
+        <v>513</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -15262,7 +15796,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15270,10 +15804,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>532</v>
+        <v>514</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -15293,10 +15827,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>532</v>
+        <v>514</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -15316,10 +15850,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>533</v>
+        <v>515</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -15339,10 +15873,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>533</v>
+        <v>515</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -15406,10 +15940,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>534</v>
+        <v>516</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>535</v>
+        <v>517</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -15475,10 +16009,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="D2" s="1">
         <v>45</v>
@@ -15501,10 +16035,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="D3" s="1">
         <v>-45</v>
@@ -15527,10 +16061,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="D4" s="1">
         <v>91</v>
@@ -15547,10 +16081,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="D5" s="1">
         <v>-91</v>
@@ -15567,10 +16101,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="D6" s="1">
         <v>45</v>
@@ -15587,10 +16121,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="D7" s="1">
         <v>45</v>
@@ -15635,10 +16169,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>540</v>
+        <v>522</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>541</v>
+        <v>523</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>145</v>
@@ -15658,16 +16192,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>542</v>
+        <v>524</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="F2" s="1">
         <v>50</v>
@@ -15687,16 +16221,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -15710,16 +16244,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="F4" s="1">
         <v>101</v>
@@ -15777,10 +16311,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -15800,10 +16334,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -15823,10 +16357,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -15846,10 +16380,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -15869,10 +16403,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
@@ -15892,10 +16426,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>548</v>
+        <v>530</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -15909,10 +16443,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
@@ -15976,10 +16510,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>549</v>
+        <v>531</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -15999,10 +16533,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>549</v>
+        <v>531</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16022,10 +16556,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16039,10 +16573,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -16106,10 +16640,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>551</v>
+        <v>533</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16174,13 +16708,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>552</v>
+        <v>534</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>554</v>
+        <v>536</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -16200,13 +16734,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>556</v>
+        <v>538</v>
       </c>
       <c r="E3" s="1">
         <v>30</v>
@@ -16226,13 +16760,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -16252,13 +16786,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>559</v>
+        <v>541</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>560</v>
+        <v>542</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -16278,19 +16812,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>561</v>
+        <v>543</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16298,19 +16832,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>565</v>
+        <v>547</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16318,19 +16852,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>566</v>
+        <v>548</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>567</v>
+        <v>549</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16338,19 +16872,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>566</v>
+        <v>548</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>569</v>
+        <v>551</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16358,19 +16892,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>570</v>
+        <v>552</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>571</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16378,19 +16912,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>572</v>
+        <v>554</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>573</v>
+        <v>555</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16398,19 +16932,19 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16418,19 +16952,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>576</v>
+        <v>558</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16438,19 +16972,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>577</v>
+        <v>559</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>578</v>
+        <v>560</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16458,19 +16992,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>579</v>
+        <v>561</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>580</v>
+        <v>562</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16478,19 +17012,19 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>581</v>
+        <v>563</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>582</v>
+        <v>564</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16498,19 +17032,19 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>583</v>
+        <v>565</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>584</v>
+        <v>566</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16518,19 +17052,19 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>585</v>
+        <v>567</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>586</v>
+        <v>568</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16538,19 +17072,19 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>588</v>
+        <v>570</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16558,19 +17092,19 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>589</v>
+        <v>571</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>590</v>
+        <v>572</v>
       </c>
       <c r="E20" s="1">
         <v>50</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16578,19 +17112,19 @@
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>591</v>
+        <v>573</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>592</v>
+        <v>574</v>
       </c>
       <c r="E21" s="1">
         <v>50</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16598,19 +17132,19 @@
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>593</v>
+        <v>575</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>594</v>
+        <v>576</v>
       </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16618,19 +17152,19 @@
         <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="E23" s="1">
         <v>50</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16638,19 +17172,19 @@
         <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>585</v>
+        <v>567</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="E24" s="1">
         <v>50</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16658,19 +17192,19 @@
         <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>598</v>
+        <v>580</v>
       </c>
       <c r="E25" s="1">
         <v>50</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16678,19 +17212,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>589</v>
+        <v>571</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>599</v>
+        <v>581</v>
       </c>
       <c r="E26" s="1">
         <v>50</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16698,19 +17232,19 @@
         <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>591</v>
+        <v>573</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>600</v>
+        <v>582</v>
       </c>
       <c r="E27" s="1">
         <v>50</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16718,19 +17252,19 @@
         <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>589</v>
+        <v>571</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>601</v>
+        <v>583</v>
       </c>
       <c r="E28" s="1">
         <v>50</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16738,19 +17272,19 @@
         <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>591</v>
+        <v>573</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>602</v>
+        <v>584</v>
       </c>
       <c r="E29" s="1">
         <v>50</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -16758,19 +17292,19 @@
         <v>19</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>554</v>
+        <v>536</v>
       </c>
       <c r="E30" s="1">
         <v>101</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -16778,19 +17312,19 @@
         <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>556</v>
+        <v>538</v>
       </c>
       <c r="E31" s="1">
         <v>-1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>
@@ -16827,7 +17361,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -16850,10 +17384,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>604</v>
+        <v>586</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -16879,10 +17413,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>606</v>
+        <v>588</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -16908,10 +17442,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>607</v>
+        <v>589</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -16937,10 +17471,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>608</v>
+        <v>590</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -16966,10 +17500,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>609</v>
+        <v>591</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -16995,10 +17529,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>610</v>
+        <v>592</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -17024,10 +17558,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>611</v>
+        <v>593</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -17053,10 +17587,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>612</v>
+        <v>594</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -17082,10 +17616,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>613</v>
+        <v>595</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -17111,10 +17645,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>614</v>
+        <v>596</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -17140,10 +17674,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>615</v>
+        <v>597</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -17169,10 +17703,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>616</v>
+        <v>598</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -17198,10 +17732,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>617</v>
+        <v>599</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -17221,10 +17755,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>617</v>
+        <v>599</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -17244,10 +17778,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>618</v>
+        <v>600</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -17267,10 +17801,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>618</v>
+        <v>600</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -17317,7 +17851,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -17340,10 +17874,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>619</v>
+        <v>601</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17369,10 +17903,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>621</v>
+        <v>603</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -17398,10 +17932,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>622</v>
+        <v>604</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -17419,7 +17953,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17427,10 +17961,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -17448,7 +17982,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17456,10 +17990,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>624</v>
+        <v>606</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -17477,7 +18011,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17485,10 +18019,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>625</v>
+        <v>607</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -17506,7 +18040,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17514,10 +18048,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>626</v>
+        <v>608</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -17543,10 +18077,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -17572,10 +18106,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>628</v>
+        <v>610</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -17593,7 +18127,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17601,10 +18135,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -17622,7 +18156,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17630,10 +18164,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>630</v>
+        <v>612</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -17651,7 +18185,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17659,10 +18193,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>631</v>
+        <v>613</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -17680,7 +18214,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -17688,10 +18222,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>632</v>
+        <v>614</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -17711,10 +18245,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>632</v>
+        <v>614</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -17734,10 +18268,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>633</v>
+        <v>615</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -17757,10 +18291,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>633</v>
+        <v>615</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -17787,11 +18321,11 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="5" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="6" customWidth="1"/>
     <col min="2" max="2" width="23.2222222222222" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="18.2222222222222" customWidth="1"/>
-    <col min="5" max="6" width="9" style="5"/>
+    <col min="5" max="6" width="9" style="6"/>
     <col min="7" max="7" width="13.7777777777778" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17840,7 +18374,7 @@
       </c>
     </row>
     <row r="3" customFormat="1" ht="22" customHeight="1" spans="1:7">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -17849,14 +18383,14 @@
       <c r="C3" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
       <c r="G3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="1" ht="22" customHeight="1" spans="1:7">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -17865,8 +18399,8 @@
       <c r="C4" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
       <c r="G4" s="1" t="s">
         <v>13</v>
       </c>
@@ -17903,7 +18437,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -17926,10 +18460,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>634</v>
+        <v>616</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17955,10 +18489,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>634</v>
+        <v>616</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -17984,10 +18518,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>634</v>
+        <v>616</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -18013,10 +18547,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>634</v>
+        <v>616</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18042,10 +18576,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>634</v>
+        <v>616</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18071,10 +18605,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>634</v>
+        <v>616</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18100,10 +18634,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>634</v>
+        <v>616</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18123,10 +18657,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>634</v>
+        <v>616</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -18146,10 +18680,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>634</v>
+        <v>616</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -18169,10 +18703,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>634</v>
+        <v>616</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -18239,10 +18773,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>635</v>
+        <v>617</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>636</v>
+        <v>618</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18256,10 +18790,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>635</v>
+        <v>617</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>636</v>
+        <v>618</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -18273,10 +18807,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>635</v>
+        <v>617</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>636</v>
+        <v>618</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -18290,10 +18824,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>635</v>
+        <v>617</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>636</v>
+        <v>618</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -18307,10 +18841,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>635</v>
+        <v>617</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>636</v>
+        <v>618</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -18324,10 +18858,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>635</v>
+        <v>617</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>636</v>
+        <v>618</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -18341,10 +18875,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>635</v>
+        <v>617</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>636</v>
+        <v>618</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -18402,10 +18936,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>635</v>
+        <v>617</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>636</v>
+        <v>618</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -18464,16 +18998,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>637</v>
+        <v>619</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>638</v>
+        <v>620</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>639</v>
+        <v>621</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>640</v>
+        <v>622</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>34</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="21" activeTab="26"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="21" activeTab="26"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -824,6 +824,9 @@
     <t>获取关节角度，关节（超限）</t>
   </si>
   <si>
+    <t>angle</t>
+  </si>
+  <si>
     <t>正确设置单关节角度，速度10</t>
   </si>
   <si>
@@ -1128,9 +1131,6 @@
   </si>
   <si>
     <t>[0, 20, 0, -90, 0, 90, 0]</t>
-  </si>
-  <si>
-    <t>angle</t>
   </si>
   <si>
     <t>判断当前角度是否在点位上（不在点位超过±1°）</t>
@@ -2584,7 +2584,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2602,9 +2602,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2963,11 +2960,11 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="4" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="6" width="14.7777777777778" style="6" customWidth="1"/>
+    <col min="5" max="6" width="14.7777777777778" style="4" customWidth="1"/>
     <col min="7" max="7" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3005,10 +3002,10 @@
         <v>8</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="7">
-        <v>2</v>
-      </c>
-      <c r="F2" s="7">
+      <c r="E2" s="6">
+        <v>2</v>
+      </c>
+      <c r="F2" s="6">
         <v>2</v>
       </c>
       <c r="G2" t="s">
@@ -3025,10 +3022,10 @@
       <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="8">
-        <v>2</v>
-      </c>
-      <c r="F3" s="8">
+      <c r="E3" s="7">
+        <v>2</v>
+      </c>
+      <c r="F3" s="7">
         <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -3045,10 +3042,10 @@
       <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="8">
-        <v>2</v>
-      </c>
-      <c r="F4" s="8">
+      <c r="E4" s="7">
+        <v>2</v>
+      </c>
+      <c r="F4" s="7">
         <v>2</v>
       </c>
       <c r="G4" t="s">
@@ -6754,7 +6751,7 @@
         <v>231</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>144</v>
+        <v>241</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>145</v>
@@ -6774,10 +6771,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -6803,10 +6800,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>242</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
@@ -6832,10 +6829,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -6864,7 +6861,7 @@
         <v>153</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -6891,7 +6888,7 @@
         <v>156</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -6918,7 +6915,7 @@
         <v>158</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D7" s="2">
         <v>2</v>
@@ -6945,7 +6942,7 @@
         <v>160</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -6972,7 +6969,7 @@
         <v>162</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D9" s="2">
         <v>3</v>
@@ -6999,7 +6996,7 @@
         <v>164</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D10" s="2">
         <v>3</v>
@@ -7026,7 +7023,7 @@
         <v>166</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D11" s="2">
         <v>4</v>
@@ -7053,7 +7050,7 @@
         <v>168</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D12" s="2">
         <v>4</v>
@@ -7080,7 +7077,7 @@
         <v>170</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D13" s="2">
         <v>5</v>
@@ -7107,7 +7104,7 @@
         <v>172</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D14" s="2">
         <v>5</v>
@@ -7134,7 +7131,7 @@
         <v>174</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D15" s="2">
         <v>6</v>
@@ -7161,7 +7158,7 @@
         <v>176</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D16" s="2">
         <v>6</v>
@@ -7188,7 +7185,7 @@
         <v>178</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D17" s="2">
         <v>7</v>
@@ -7215,7 +7212,7 @@
         <v>180</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D18" s="2">
         <v>7</v>
@@ -7242,7 +7239,7 @@
         <v>182</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D19" s="2">
         <v>1</v>
@@ -7269,7 +7266,7 @@
         <v>184</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D20" s="2">
         <v>1</v>
@@ -7296,7 +7293,7 @@
         <v>185</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D21" s="2">
         <v>2</v>
@@ -7323,7 +7320,7 @@
         <v>186</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D22" s="2">
         <v>2</v>
@@ -7350,7 +7347,7 @@
         <v>187</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D23" s="2">
         <v>3</v>
@@ -7377,7 +7374,7 @@
         <v>188</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D24" s="2">
         <v>3</v>
@@ -7404,7 +7401,7 @@
         <v>189</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D25" s="2">
         <v>4</v>
@@ -7431,7 +7428,7 @@
         <v>190</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D26" s="2">
         <v>4</v>
@@ -7458,7 +7455,7 @@
         <v>191</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D27" s="2">
         <v>5</v>
@@ -7485,7 +7482,7 @@
         <v>192</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D28" s="2">
         <v>5</v>
@@ -7512,7 +7509,7 @@
         <v>193</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D29" s="2">
         <v>6</v>
@@ -7539,7 +7536,7 @@
         <v>194</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D30" s="2">
         <v>6</v>
@@ -7566,7 +7563,7 @@
         <v>195</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D31" s="2">
         <v>7</v>
@@ -7593,7 +7590,7 @@
         <v>196</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D32" s="2">
         <v>7</v>
@@ -7615,10 +7612,10 @@
     <row r="33" customFormat="1" ht="28.8" spans="1:9">
       <c r="A33" s="2"/>
       <c r="B33" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D33" s="2">
         <v>11</v>
@@ -7640,10 +7637,10 @@
     <row r="34" customFormat="1" ht="28.8" spans="1:9">
       <c r="A34" s="2"/>
       <c r="B34" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D34" s="2">
         <v>11</v>
@@ -7665,10 +7662,10 @@
     <row r="35" customFormat="1" ht="28.8" spans="1:9">
       <c r="A35" s="2"/>
       <c r="B35" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D35" s="2">
         <v>12</v>
@@ -7690,10 +7687,10 @@
     <row r="36" customFormat="1" ht="28.8" spans="1:9">
       <c r="A36" s="2"/>
       <c r="B36" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D36" s="2">
         <v>12</v>
@@ -7715,10 +7712,10 @@
     <row r="37" customFormat="1" ht="28.8" spans="1:9">
       <c r="A37" s="2"/>
       <c r="B37" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D37" s="2">
         <v>13</v>
@@ -7740,10 +7737,10 @@
     <row r="38" customFormat="1" ht="28.8" spans="1:9">
       <c r="A38" s="2"/>
       <c r="B38" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D38" s="2">
         <v>13</v>
@@ -7767,10 +7764,10 @@
         <v>32</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D39" s="2">
         <v>1</v>
@@ -7792,10 +7789,10 @@
         <v>33</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D40" s="2">
         <v>2</v>
@@ -7817,10 +7814,10 @@
         <v>34</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D41" s="2">
         <v>3</v>
@@ -7842,10 +7839,10 @@
         <v>35</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D42" s="2">
         <v>1</v>
@@ -7867,10 +7864,10 @@
         <v>36</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D43" s="2">
         <v>1</v>
@@ -7895,7 +7892,7 @@
         <v>207</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D44" s="2">
         <v>2</v>
@@ -7920,7 +7917,7 @@
         <v>209</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D45" s="2">
         <v>2</v>
@@ -7945,7 +7942,7 @@
         <v>211</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D46" s="2">
         <v>3</v>
@@ -7970,7 +7967,7 @@
         <v>213</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D47" s="2">
         <v>3</v>
@@ -7995,7 +7992,7 @@
         <v>215</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D48" s="2">
         <v>4</v>
@@ -8020,7 +8017,7 @@
         <v>217</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D49" s="2">
         <v>4</v>
@@ -8045,7 +8042,7 @@
         <v>219</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D50" s="2">
         <v>5</v>
@@ -8070,7 +8067,7 @@
         <v>221</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D51" s="2">
         <v>5</v>
@@ -8095,7 +8092,7 @@
         <v>223</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D52" s="2">
         <v>6</v>
@@ -8120,7 +8117,7 @@
         <v>225</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D53" s="2">
         <v>6</v>
@@ -8145,7 +8142,7 @@
         <v>227</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D54" s="2">
         <v>7</v>
@@ -8170,7 +8167,7 @@
         <v>229</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D55" s="2">
         <v>7</v>
@@ -8192,10 +8189,10 @@
         <v>49</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D56" s="4">
         <v>11</v>
@@ -8215,10 +8212,10 @@
         <v>50</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D57" s="4">
         <v>11</v>
@@ -8238,10 +8235,10 @@
         <v>51</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D58" s="4">
         <v>12</v>
@@ -8261,10 +8258,10 @@
         <v>52</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D59" s="4">
         <v>12</v>
@@ -8284,10 +8281,10 @@
         <v>53</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D60" s="4">
         <v>13</v>
@@ -8307,10 +8304,10 @@
         <v>54</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D61" s="4">
         <v>13</v>
@@ -8374,19 +8371,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -8397,19 +8394,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>143</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>34</v>
@@ -8467,13 +8464,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -8493,13 +8490,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E3" s="1">
         <v>50</v>
@@ -8519,13 +8516,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -8545,13 +8542,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -8571,13 +8568,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
@@ -8591,13 +8588,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
@@ -8611,13 +8608,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
@@ -8631,13 +8628,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
@@ -8651,13 +8648,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
@@ -8671,13 +8668,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
@@ -8691,13 +8688,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
@@ -8711,13 +8708,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
@@ -8731,13 +8728,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
@@ -8751,13 +8748,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
@@ -8771,13 +8768,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
@@ -8791,13 +8788,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
@@ -8811,13 +8808,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
@@ -8831,13 +8828,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
@@ -8851,13 +8848,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E20" s="1">
         <v>101</v>
@@ -8871,13 +8868,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E21" s="1">
         <v>-1</v>
@@ -8898,11 +8895,11 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="4" customWidth="1"/>
     <col min="2" max="2" width="23.2222222222222" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="6" width="9" style="6"/>
+    <col min="5" max="6" width="9" style="4"/>
     <col min="7" max="7" width="13.7777777777778" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8951,7 +8948,7 @@
       </c>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:7">
-      <c r="A3" s="6">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -8965,7 +8962,7 @@
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:7">
-      <c r="A4" s="6">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -9011,7 +9008,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -9034,10 +9031,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -9063,10 +9060,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>303</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -9084,7 +9081,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -9092,10 +9089,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -9113,7 +9110,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -9121,10 +9118,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -9142,7 +9139,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -9150,10 +9147,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -9171,7 +9168,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -9179,10 +9176,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -9200,7 +9197,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" ht="28.8" spans="1:9">
@@ -9208,10 +9205,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -9231,10 +9228,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -9254,10 +9251,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
@@ -9277,10 +9274,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
@@ -9300,10 +9297,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D12" s="1">
         <v>3</v>
@@ -9323,10 +9320,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D13" s="1">
         <v>3</v>
@@ -9346,10 +9343,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
@@ -9369,10 +9366,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D15" s="1">
         <v>3</v>
@@ -9392,10 +9389,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D16" s="1">
         <v>4</v>
@@ -9415,10 +9412,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D17" s="1">
         <v>4</v>
@@ -9438,10 +9435,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -9461,10 +9458,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D19" s="1">
         <v>5</v>
@@ -9484,10 +9481,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D20" s="1">
         <v>6</v>
@@ -9507,10 +9504,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D21" s="1">
         <v>6</v>
@@ -9530,10 +9527,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -9553,10 +9550,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -9576,10 +9573,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D24" s="1">
         <v>7</v>
@@ -9599,10 +9596,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -9667,10 +9664,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -9690,10 +9687,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -9713,10 +9710,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>327</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -9730,10 +9727,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>327</v>
       </c>
       <c r="D5" s="1">
         <v>-3</v>
@@ -9792,10 +9789,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -9813,10 +9810,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -9879,10 +9876,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -9902,10 +9899,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>332</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -9925,10 +9922,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D4" s="1">
         <v>-3</v>
@@ -9942,10 +9939,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -10004,10 +10001,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10027,10 +10024,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>336</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10050,10 +10047,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D4" s="1">
         <v>-3</v>
@@ -10067,10 +10064,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -10115,7 +10112,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -10132,13 +10129,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -10150,7 +10147,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>343</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="57.6" spans="1:8">
@@ -10161,10 +10158,10 @@
         <v>344</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -10176,7 +10173,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>343</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="57.6" spans="1:8">
@@ -10187,7 +10184,7 @@
         <v>345</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>346</v>
@@ -10213,7 +10210,7 @@
         <v>348</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>346</v>
@@ -10239,7 +10236,7 @@
         <v>349</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>346</v>
@@ -10265,7 +10262,7 @@
         <v>350</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -10288,7 +10285,7 @@
         <v>352</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -10311,7 +10308,7 @@
         <v>353</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -10334,7 +10331,7 @@
         <v>354</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E10" s="1">
         <v>-1</v>
@@ -10351,7 +10348,7 @@
         <v>354</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -10607,7 +10604,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -10876,7 +10873,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -10980,11 +10977,11 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="4" customWidth="1"/>
     <col min="2" max="2" width="23.2222222222222" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="6" width="9" style="6"/>
+    <col min="5" max="6" width="9" style="4"/>
     <col min="7" max="7" width="13.7777777777778" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11033,7 +11030,7 @@
       </c>
     </row>
     <row r="3" customFormat="1" ht="34" customHeight="1" spans="1:7">
-      <c r="A3" s="6">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -11042,14 +11039,14 @@
       <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
       <c r="G3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="1" ht="34" customHeight="1" spans="1:7">
-      <c r="A4" s="6">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -11058,8 +11055,8 @@
       <c r="C4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
       <c r="G4" s="1" t="s">
         <v>13</v>
       </c>
@@ -11100,7 +11097,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -12070,7 +12067,7 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="4" customWidth="1"/>
     <col min="2" max="2" width="22.3333333333333" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="16.5555555555556" customWidth="1"/>
@@ -12123,7 +12120,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="6">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -12143,7 +12140,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="6">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -13750,7 +13747,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -14066,7 +14063,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -14168,7 +14165,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14197,7 +14194,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14226,7 +14223,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14255,7 +14252,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14342,7 +14339,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14371,7 +14368,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14400,7 +14397,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14429,7 +14426,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -15433,7 +15430,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -15535,7 +15532,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15564,7 +15561,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15593,7 +15590,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15622,7 +15619,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15709,7 +15706,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15738,7 +15735,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15767,7 +15764,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15796,7 +15793,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17361,7 +17358,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -17851,7 +17848,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -17953,7 +17950,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17982,7 +17979,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18011,7 +18008,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18040,7 +18037,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18127,7 +18124,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18156,7 +18153,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18185,7 +18182,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18214,7 +18211,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -18321,11 +18318,11 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="4" customWidth="1"/>
     <col min="2" max="2" width="23.2222222222222" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="18.2222222222222" customWidth="1"/>
-    <col min="5" max="6" width="9" style="6"/>
+    <col min="5" max="6" width="9" style="4"/>
     <col min="7" max="7" width="13.7777777777778" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -18374,7 +18371,7 @@
       </c>
     </row>
     <row r="3" customFormat="1" ht="22" customHeight="1" spans="1:7">
-      <c r="A3" s="6">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -18383,14 +18380,14 @@
       <c r="C3" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
       <c r="G3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="1" ht="22" customHeight="1" spans="1:7">
-      <c r="A4" s="6">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -18399,8 +18396,8 @@
       <c r="C4" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
       <c r="G4" s="1" t="s">
         <v>13</v>
       </c>
@@ -18437,7 +18434,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -7610,7 +7610,9 @@
       </c>
     </row>
     <row r="33" customFormat="1" ht="28.8" spans="1:9">
-      <c r="A33" s="2"/>
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
       <c r="B33" s="1" t="s">
         <v>246</v>
       </c>
@@ -7635,7 +7637,9 @@
       </c>
     </row>
     <row r="34" customFormat="1" ht="28.8" spans="1:9">
-      <c r="A34" s="2"/>
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
       <c r="B34" s="1" t="s">
         <v>247</v>
       </c>
@@ -7660,7 +7664,9 @@
       </c>
     </row>
     <row r="35" customFormat="1" ht="28.8" spans="1:9">
-      <c r="A35" s="2"/>
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
       <c r="B35" s="1" t="s">
         <v>248</v>
       </c>
@@ -7671,7 +7677,7 @@
         <v>12</v>
       </c>
       <c r="E35" s="2">
-        <v>-75</v>
+        <v>-70</v>
       </c>
       <c r="F35" s="2">
         <v>70</v>
@@ -7685,7 +7691,9 @@
       </c>
     </row>
     <row r="36" customFormat="1" ht="28.8" spans="1:9">
-      <c r="A36" s="2"/>
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
       <c r="B36" s="1" t="s">
         <v>249</v>
       </c>
@@ -7710,7 +7718,9 @@
       </c>
     </row>
     <row r="37" customFormat="1" ht="28.8" spans="1:9">
-      <c r="A37" s="2"/>
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
       <c r="B37" s="1" t="s">
         <v>250</v>
       </c>
@@ -7735,7 +7745,9 @@
       </c>
     </row>
     <row r="38" customFormat="1" ht="28.8" spans="1:9">
-      <c r="A38" s="2"/>
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
       <c r="B38" s="1" t="s">
         <v>251</v>
       </c>
@@ -7761,7 +7773,7 @@
     </row>
     <row r="39" customFormat="1" ht="43.2" spans="1:9">
       <c r="A39" s="2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>252</v>
@@ -7786,7 +7798,7 @@
     </row>
     <row r="40" customFormat="1" ht="43.2" spans="1:9">
       <c r="A40" s="2">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>253</v>
@@ -7811,7 +7823,7 @@
     </row>
     <row r="41" customFormat="1" ht="43.2" spans="1:9">
       <c r="A41" s="2">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>254</v>
@@ -7836,7 +7848,7 @@
     </row>
     <row r="42" customFormat="1" ht="43.2" spans="1:9">
       <c r="A42" s="2">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>255</v>
@@ -7861,7 +7873,7 @@
     </row>
     <row r="43" customFormat="1" ht="43.2" spans="1:9">
       <c r="A43" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>256</v>
@@ -7886,7 +7898,7 @@
     </row>
     <row r="44" customFormat="1" ht="43.2" spans="1:9">
       <c r="A44" s="2">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>207</v>
@@ -7911,7 +7923,7 @@
     </row>
     <row r="45" customFormat="1" ht="43.2" spans="1:9">
       <c r="A45" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>209</v>
@@ -7936,7 +7948,7 @@
     </row>
     <row r="46" customFormat="1" ht="43.2" spans="1:9">
       <c r="A46" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>211</v>
@@ -7961,7 +7973,7 @@
     </row>
     <row r="47" customFormat="1" ht="43.2" spans="1:9">
       <c r="A47" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>213</v>
@@ -7986,7 +7998,7 @@
     </row>
     <row r="48" customFormat="1" ht="43.2" spans="1:9">
       <c r="A48" s="2">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>215</v>
@@ -8011,7 +8023,7 @@
     </row>
     <row r="49" customFormat="1" ht="43.2" spans="1:9">
       <c r="A49" s="2">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>217</v>
@@ -8036,7 +8048,7 @@
     </row>
     <row r="50" customFormat="1" ht="43.2" spans="1:9">
       <c r="A50" s="2">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>219</v>
@@ -8061,7 +8073,7 @@
     </row>
     <row r="51" customFormat="1" ht="43.2" spans="1:9">
       <c r="A51" s="2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>221</v>
@@ -8086,7 +8098,7 @@
     </row>
     <row r="52" customFormat="1" ht="43.2" spans="1:9">
       <c r="A52" s="2">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>223</v>
@@ -8111,7 +8123,7 @@
     </row>
     <row r="53" customFormat="1" ht="43.2" spans="1:9">
       <c r="A53" s="2">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>225</v>
@@ -8136,7 +8148,7 @@
     </row>
     <row r="54" customFormat="1" ht="43.2" spans="1:9">
       <c r="A54" s="2">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>227</v>
@@ -8161,7 +8173,7 @@
     </row>
     <row r="55" customFormat="1" ht="43.2" spans="1:9">
       <c r="A55" s="2">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>229</v>
@@ -8186,7 +8198,7 @@
     </row>
     <row r="56" ht="43.2" spans="1:9">
       <c r="A56" s="2">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>257</v>
@@ -8209,7 +8221,7 @@
     </row>
     <row r="57" ht="43.2" spans="1:9">
       <c r="A57" s="2">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>258</v>
@@ -8232,7 +8244,7 @@
     </row>
     <row r="58" ht="43.2" spans="1:9">
       <c r="A58" s="2">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>259</v>
@@ -8255,7 +8267,7 @@
     </row>
     <row r="59" ht="43.2" spans="1:9">
       <c r="A59" s="2">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>260</v>
@@ -8278,7 +8290,7 @@
     </row>
     <row r="60" ht="43.2" spans="1:9">
       <c r="A60" s="2">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>261</v>
@@ -8301,7 +8313,7 @@
     </row>
     <row r="61" ht="43.2" spans="1:9">
       <c r="A61" s="2">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>261</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="21" activeTab="26"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="22" activeTab="27"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -896,7 +896,7 @@
     <t>None</t>
   </si>
   <si>
-    <t>[50.9, 0.0, 533.6, 15.77, -89.99, 164.21]</t>
+    <t>[51.0, 0.0, 533.6, 179.74, -89.98, 0.24]</t>
   </si>
   <si>
     <t>运动学正解返回角度</t>
@@ -8350,8 +8350,7 @@
     <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="5" max="6" width="48.2222222222222" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -8401,7 +8400,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" ht="43.2" spans="1:7">
+    <row r="3" ht="28.8" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="624">
   <si>
     <t>ID</t>
   </si>
@@ -896,7 +896,10 @@
     <t>None</t>
   </si>
   <si>
-    <t>[51.0, 0.0, 533.6, 179.74, -89.98, 0.24]</t>
+    <t>[51.0, 0.0, 533.6, -177.89, -89.98, -2.1]</t>
+  </si>
+  <si>
+    <t>[51.0, 0.0, 533.6, 168.96, -89.99, 11.03]</t>
   </si>
   <si>
     <t>运动学正解返回角度</t>
@@ -8394,7 +8397,7 @@
         <v>265</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -8405,7 +8408,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>263</v>
@@ -8414,10 +8417,10 @@
         <v>143</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>34</v>
@@ -8475,13 +8478,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -8501,13 +8504,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E3" s="1">
         <v>50</v>
@@ -8527,13 +8530,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -8553,13 +8556,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -8579,13 +8582,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
@@ -8599,13 +8602,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
@@ -8619,13 +8622,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
@@ -8639,13 +8642,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
@@ -8659,13 +8662,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
@@ -8679,13 +8682,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
@@ -8699,13 +8702,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
@@ -8719,13 +8722,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
@@ -8739,13 +8742,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
@@ -8759,13 +8762,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
@@ -8779,13 +8782,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
@@ -8799,13 +8802,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
@@ -8819,13 +8822,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
@@ -8839,13 +8842,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
@@ -8859,13 +8862,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E20" s="1">
         <v>101</v>
@@ -8879,13 +8882,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E21" s="1">
         <v>-1</v>
@@ -9019,7 +9022,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -9042,10 +9045,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -9071,10 +9074,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>304</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -9092,7 +9095,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -9100,10 +9103,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -9121,7 +9124,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -9129,10 +9132,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -9150,7 +9153,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -9158,10 +9161,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -9179,7 +9182,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -9187,10 +9190,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -9208,7 +9211,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" ht="28.8" spans="1:9">
@@ -9216,10 +9219,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -9239,10 +9242,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -9262,10 +9265,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
@@ -9285,10 +9288,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
@@ -9308,10 +9311,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D12" s="1">
         <v>3</v>
@@ -9331,10 +9334,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D13" s="1">
         <v>3</v>
@@ -9354,10 +9357,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
@@ -9377,10 +9380,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D15" s="1">
         <v>3</v>
@@ -9400,10 +9403,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D16" s="1">
         <v>4</v>
@@ -9423,10 +9426,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D17" s="1">
         <v>4</v>
@@ -9446,10 +9449,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -9469,10 +9472,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D19" s="1">
         <v>5</v>
@@ -9492,10 +9495,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D20" s="1">
         <v>6</v>
@@ -9515,10 +9518,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D21" s="1">
         <v>6</v>
@@ -9538,10 +9541,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -9561,10 +9564,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -9584,10 +9587,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D24" s="1">
         <v>7</v>
@@ -9607,10 +9610,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -9675,10 +9678,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -9698,10 +9701,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -9721,10 +9724,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -9738,10 +9741,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="D5" s="1">
         <v>-3</v>
@@ -9800,10 +9803,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -9821,10 +9824,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -9887,10 +9890,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -9910,10 +9913,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>333</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -9933,10 +9936,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D4" s="1">
         <v>-3</v>
@@ -9950,10 +9953,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -10012,10 +10015,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10035,10 +10038,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>337</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10058,10 +10061,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D4" s="1">
         <v>-3</v>
@@ -10075,10 +10078,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -10123,7 +10126,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -10140,13 +10143,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -10166,13 +10169,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -10192,13 +10195,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -10210,7 +10213,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="57.6" spans="1:8">
@@ -10218,25 +10221,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="6" ht="57.6" spans="1:8">
@@ -10244,13 +10247,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -10262,7 +10265,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" ht="57" customHeight="1" spans="1:8">
@@ -10270,10 +10273,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -10285,7 +10288,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" ht="57.6" spans="1:8">
@@ -10293,22 +10296,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E8" s="1">
-        <v>2</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="9" ht="57.6" spans="1:8">
@@ -10316,10 +10319,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -10331,7 +10334,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -10339,10 +10342,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E10" s="1">
         <v>-1</v>
@@ -10356,10 +10359,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -10418,10 +10421,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -10438,10 +10441,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>356</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -10504,10 +10507,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10527,10 +10530,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10550,10 +10553,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -10567,10 +10570,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -10615,7 +10618,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -10632,10 +10635,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -10658,10 +10661,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>362</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -10684,10 +10687,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D4" s="1">
         <v>151</v>
@@ -10704,10 +10707,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -10724,10 +10727,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D6" s="1">
         <v>201</v>
@@ -10744,10 +10747,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -10764,10 +10767,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -10784,10 +10787,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -10807,7 +10810,7 @@
         <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -10833,7 +10836,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -10884,7 +10887,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -10901,10 +10904,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10924,10 +10927,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>367</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10947,10 +10950,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -10964,10 +10967,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -11108,7 +11111,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -11125,10 +11128,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -11151,10 +11154,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>370</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -11177,10 +11180,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D4" s="1">
         <v>201</v>
@@ -11197,10 +11200,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -11217,10 +11220,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D6" s="1">
         <v>401</v>
@@ -11237,10 +11240,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -11257,10 +11260,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -11277,10 +11280,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -11297,10 +11300,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -11323,10 +11326,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -11388,16 +11391,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>34</v>
@@ -11447,10 +11450,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -11511,16 +11514,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11575,16 +11578,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11639,16 +11642,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11703,16 +11706,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11750,13 +11753,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -11773,10 +11776,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -11802,10 +11805,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D3" s="1">
         <v>255</v>
@@ -11831,10 +11834,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -11860,10 +11863,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>398</v>
       </c>
       <c r="D5" s="1">
         <v>256</v>
@@ -11927,10 +11930,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -11991,10 +11994,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12014,10 +12017,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -12037,10 +12040,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>403</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -12054,10 +12057,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>403</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -12222,10 +12225,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12248,10 +12251,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>406</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12274,10 +12277,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12300,10 +12303,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12326,10 +12329,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12352,10 +12355,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12378,10 +12381,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12404,10 +12407,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -12424,10 +12427,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -12444,10 +12447,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -12464,10 +12467,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -12484,10 +12487,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -12496,10 +12499,10 @@
         <v>120</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -12554,17 +12557,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -12622,10 +12625,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12648,10 +12651,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12674,10 +12677,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12700,10 +12703,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12726,10 +12729,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12752,10 +12755,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12778,10 +12781,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12804,10 +12807,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -12824,10 +12827,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -12844,10 +12847,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -12864,10 +12867,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -12884,10 +12887,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -12896,10 +12899,10 @@
         <v>100</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -12954,19 +12957,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -13021,10 +13024,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E2" s="1">
         <v>50</v>
@@ -13085,10 +13088,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D2" s="1">
         <v>30</v>
@@ -13108,10 +13111,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>437</v>
       </c>
       <c r="D3" s="1">
         <v>301</v>
@@ -13125,10 +13128,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>437</v>
       </c>
       <c r="D4" s="1">
         <v>-301</v>
@@ -13142,10 +13145,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D5" s="1">
         <v>21</v>
@@ -13216,10 +13219,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13245,10 +13248,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>440</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13274,10 +13277,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13303,10 +13306,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13332,10 +13335,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -13361,10 +13364,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -13390,10 +13393,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -13419,10 +13422,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -13448,10 +13451,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -13477,10 +13480,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -13506,10 +13509,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -13535,10 +13538,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -13564,10 +13567,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -13593,10 +13596,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -13622,10 +13625,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -13645,10 +13648,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -13668,10 +13671,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -13691,7 +13694,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -13711,7 +13714,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -13758,7 +13761,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -13781,10 +13784,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13810,10 +13813,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>459</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13839,10 +13842,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13868,10 +13871,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13897,10 +13900,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -13926,10 +13929,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -13955,10 +13958,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -13978,10 +13981,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -14001,10 +14004,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -14024,10 +14027,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -14074,7 +14077,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -14097,10 +14100,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14126,10 +14129,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>468</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14155,10 +14158,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14176,7 +14179,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14184,10 +14187,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14205,7 +14208,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14213,10 +14216,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14234,7 +14237,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14242,10 +14245,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14263,7 +14266,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14271,10 +14274,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14300,10 +14303,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14329,10 +14332,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14350,7 +14353,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14358,10 +14361,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14379,7 +14382,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14387,10 +14390,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14408,7 +14411,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14416,10 +14419,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14437,7 +14440,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14445,10 +14448,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -14468,10 +14471,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -14491,10 +14494,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -14514,10 +14517,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -14588,10 +14591,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14617,10 +14620,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>483</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14646,10 +14649,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14675,10 +14678,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14704,10 +14707,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14733,10 +14736,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14762,10 +14765,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14791,10 +14794,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14820,10 +14823,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14849,10 +14852,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14878,10 +14881,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14907,10 +14910,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14936,10 +14939,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -14965,10 +14968,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -14994,10 +14997,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -15017,10 +15020,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -15040,10 +15043,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -15063,7 +15066,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -15083,7 +15086,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -15441,7 +15444,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -15464,10 +15467,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -15493,10 +15496,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>503</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -15522,10 +15525,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -15543,7 +15546,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15551,10 +15554,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -15572,7 +15575,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15580,10 +15583,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -15601,7 +15604,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15609,10 +15612,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -15630,7 +15633,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15638,10 +15641,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -15667,10 +15670,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -15696,10 +15699,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -15717,7 +15720,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15725,10 +15728,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -15746,7 +15749,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15754,10 +15757,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -15775,7 +15778,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15783,10 +15786,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -15804,7 +15807,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15812,10 +15815,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -15835,10 +15838,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -15858,10 +15861,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -15881,10 +15884,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -15948,10 +15951,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16017,10 +16020,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D2" s="1">
         <v>45</v>
@@ -16043,10 +16046,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D3" s="1">
         <v>-45</v>
@@ -16069,10 +16072,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>520</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>519</v>
       </c>
       <c r="D4" s="1">
         <v>91</v>
@@ -16089,10 +16092,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>520</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>519</v>
       </c>
       <c r="D5" s="1">
         <v>-91</v>
@@ -16109,10 +16112,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D6" s="1">
         <v>45</v>
@@ -16129,10 +16132,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D7" s="1">
         <v>45</v>
@@ -16177,10 +16180,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>145</v>
@@ -16200,16 +16203,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F2" s="1">
         <v>50</v>
@@ -16229,16 +16232,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -16252,16 +16255,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F4" s="1">
         <v>101</v>
@@ -16319,10 +16322,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16342,10 +16345,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16365,10 +16368,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16388,10 +16391,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -16411,10 +16414,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
@@ -16434,10 +16437,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>530</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>529</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -16451,10 +16454,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
@@ -16518,10 +16521,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16541,10 +16544,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16564,10 +16567,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16581,10 +16584,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -16648,10 +16651,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16716,13 +16719,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -16742,13 +16745,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E3" s="1">
         <v>30</v>
@@ -16768,13 +16771,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -16794,13 +16797,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -16820,19 +16823,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16840,19 +16843,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16860,19 +16863,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16880,19 +16883,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16900,19 +16903,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16920,19 +16923,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16940,19 +16943,19 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16960,19 +16963,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16980,19 +16983,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17000,19 +17003,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17020,19 +17023,19 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17040,19 +17043,19 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17060,19 +17063,19 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17080,19 +17083,19 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17100,19 +17103,19 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E20" s="1">
         <v>50</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17120,19 +17123,19 @@
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E21" s="1">
         <v>50</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17140,19 +17143,19 @@
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17160,19 +17163,19 @@
         <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E23" s="1">
         <v>50</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17180,19 +17183,19 @@
         <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E24" s="1">
         <v>50</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17200,19 +17203,19 @@
         <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E25" s="1">
         <v>50</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17220,19 +17223,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E26" s="1">
         <v>50</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17240,19 +17243,19 @@
         <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E27" s="1">
         <v>50</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17260,19 +17263,19 @@
         <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E28" s="1">
         <v>50</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17280,19 +17283,19 @@
         <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E29" s="1">
         <v>50</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17300,19 +17303,19 @@
         <v>19</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E30" s="1">
         <v>101</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17320,19 +17323,19 @@
         <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E31" s="1">
         <v>-1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -17369,7 +17372,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -17392,10 +17395,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17421,10 +17424,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>588</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>587</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -17450,10 +17453,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -17479,10 +17482,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -17508,10 +17511,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -17537,10 +17540,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -17566,10 +17569,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -17595,10 +17598,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -17624,10 +17627,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -17653,10 +17656,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -17682,10 +17685,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -17711,10 +17714,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -17740,10 +17743,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -17763,10 +17766,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -17786,10 +17789,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -17809,10 +17812,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -17859,7 +17862,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -17882,10 +17885,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17911,10 +17914,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>602</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -17940,10 +17943,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -17961,7 +17964,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17969,10 +17972,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -17990,7 +17993,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17998,10 +18001,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18019,7 +18022,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18027,10 +18030,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18048,7 +18051,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18056,10 +18059,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18085,10 +18088,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -18114,10 +18117,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -18135,7 +18138,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18143,10 +18146,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -18164,7 +18167,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18172,10 +18175,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -18193,7 +18196,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18201,10 +18204,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -18222,7 +18225,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -18230,10 +18233,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -18253,10 +18256,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -18276,10 +18279,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -18299,10 +18302,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -18445,7 +18448,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -18468,10 +18471,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18497,10 +18500,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -18526,10 +18529,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -18555,10 +18558,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18584,10 +18587,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18613,10 +18616,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18642,10 +18645,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18665,10 +18668,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -18688,10 +18691,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -18711,10 +18714,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -18781,10 +18784,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18798,10 +18801,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -18815,10 +18818,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -18832,10 +18835,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -18849,10 +18852,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -18866,10 +18869,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -18883,10 +18886,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -18944,10 +18947,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -19006,16 +19009,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>34</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="22" activeTab="27"/>
+    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="22" activeTab="28"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2340" uniqueCount="626">
   <si>
     <t>ID</t>
   </si>
@@ -932,49 +932,55 @@
     <t>设置全坐标x轴超限（max）</t>
   </si>
   <si>
-    <t>[443, 0.0, 158.3, 179.99, 19.99, 0.0]</t>
+    <t>[567, 0.0, 158.3, 179.99, 19.99, 0.0]</t>
   </si>
   <si>
     <t>设置全坐标x轴超限（min）</t>
   </si>
   <si>
-    <t>[-443, 0.0, 158.3, 179.99, 19.99, 0.0]</t>
-  </si>
-  <si>
-    <t>设置全坐标y轴超限（max）</t>
-  </si>
-  <si>
-    <t>[322.5, 443, 158.3, 179.99, 19.99, 0.0]</t>
-  </si>
-  <si>
-    <t>设置全坐标y轴超限（min）</t>
-  </si>
-  <si>
-    <t>[322.5, -443, 158.3, 179.99, 19.99, 0.0]</t>
+    <t>[-352, 0.0, 158.3, 179.99, 19.99, 0.0]</t>
+  </si>
+  <si>
+    <t>设置全坐标y轴超限（max）左臂</t>
+  </si>
+  <si>
+    <t>[322.5, 646, 158.3, 179.99, 19.99, 0.0]</t>
+  </si>
+  <si>
+    <t>设置全坐标y轴超限（min）左臂</t>
+  </si>
+  <si>
+    <t>[322.5, -273, 158.3, 179.99, 19.99, 0.0]</t>
+  </si>
+  <si>
+    <t>设置全坐标y轴超限（max）右臂</t>
+  </si>
+  <si>
+    <t>[322.5, 273, 158.3, 179.99, 19.99, 0.0]</t>
+  </si>
+  <si>
+    <t>设置全坐标y轴超限（min）右臂</t>
+  </si>
+  <si>
+    <t>[322.5, -646, 158.3, 179.99, 19.99, 0.0]</t>
   </si>
   <si>
     <t>设置全坐标z轴超限（max）左臂</t>
   </si>
   <si>
-    <t>[322.5, 0.0, 630, 179.99, 19.99, 0.0]</t>
+    <t>[322.5, 0.0, 656, 179.99, 19.99, 0.0]</t>
   </si>
   <si>
     <t>设置全坐标z轴超限（min）左臂</t>
   </si>
   <si>
-    <t>[322.5, 0.0, -208, 179.99, 19.99, 0.0]</t>
+    <t>[322.5, 0.0, -263, 179.99, 19.99, 0.0]</t>
   </si>
   <si>
     <t>设置全坐标z轴超限（max）右臂</t>
   </si>
   <si>
-    <t>[322.5, 0.0, 208, 179.99, 19.99, 0.0]</t>
-  </si>
-  <si>
     <t>设置全坐标z轴超限（min）右臂</t>
-  </si>
-  <si>
-    <t>[322.5, 0.0, -630, 179.99, 19.99, 0.0]</t>
   </si>
   <si>
     <t>设置全坐标rx轴超限（max）右臂</t>
@@ -8435,7 +8441,7 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
@@ -8634,7 +8640,7 @@
         <v>50</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>42</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" ht="28.8" spans="1:8">
@@ -8654,12 +8660,12 @@
         <v>50</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>42</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" ht="28.8" spans="1:8">
       <c r="A10" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>284</v>
@@ -8674,12 +8680,12 @@
         <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="1:8">
       <c r="A11" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>286</v>
@@ -8694,12 +8700,12 @@
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" ht="28.8" spans="1:8">
       <c r="A12" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>288</v>
@@ -8714,12 +8720,12 @@
         <v>50</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="1:8">
       <c r="A13" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>290</v>
@@ -8734,12 +8740,12 @@
         <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" ht="28.8" spans="1:8">
       <c r="A14" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>292</v>
@@ -8748,47 +8754,47 @@
         <v>270</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>42</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" ht="28.8" spans="1:8">
       <c r="A15" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>270</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>42</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" ht="28.8" spans="1:8">
       <c r="A16" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>270</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
@@ -8799,16 +8805,16 @@
     </row>
     <row r="17" ht="28.8" spans="1:8">
       <c r="A17" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>270</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
@@ -8819,16 +8825,16 @@
     </row>
     <row r="18" ht="28.8" spans="1:8">
       <c r="A18" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>270</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
@@ -8839,10 +8845,10 @@
     </row>
     <row r="19" ht="28.8" spans="1:8">
       <c r="A19" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>270</v>
@@ -8859,19 +8865,19 @@
     </row>
     <row r="20" ht="28.8" spans="1:8">
       <c r="A20" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>270</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="E20" s="1">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>42</v>
@@ -8879,21 +8885,61 @@
     </row>
     <row r="21" ht="28.8" spans="1:8">
       <c r="A21" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>270</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E21" s="1">
+        <v>50</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" ht="28.8" spans="1:8">
+      <c r="A22" s="2">
+        <v>19</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E21" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H21" s="1" t="s">
+      <c r="E22" s="1">
+        <v>101</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" ht="28.8" spans="1:8">
+      <c r="A23" s="2">
+        <v>20</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -9022,7 +9068,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -9045,10 +9091,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -9074,10 +9120,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -9095,7 +9141,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -9103,10 +9149,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -9124,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -9132,10 +9178,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -9153,7 +9199,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -9161,10 +9207,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -9182,7 +9228,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -9190,10 +9236,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -9211,7 +9257,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" ht="28.8" spans="1:9">
@@ -9219,10 +9265,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -9242,10 +9288,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -9265,10 +9311,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
@@ -9288,10 +9334,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
@@ -9311,10 +9357,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D12" s="1">
         <v>3</v>
@@ -9334,10 +9380,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D13" s="1">
         <v>3</v>
@@ -9357,10 +9403,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
@@ -9380,10 +9426,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D15" s="1">
         <v>3</v>
@@ -9403,10 +9449,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D16" s="1">
         <v>4</v>
@@ -9426,10 +9472,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D17" s="1">
         <v>4</v>
@@ -9449,10 +9495,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -9472,10 +9518,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D19" s="1">
         <v>5</v>
@@ -9495,10 +9541,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D20" s="1">
         <v>6</v>
@@ -9518,10 +9564,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D21" s="1">
         <v>6</v>
@@ -9541,10 +9587,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -9564,10 +9610,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -9587,10 +9633,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D24" s="1">
         <v>7</v>
@@ -9610,10 +9656,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -9678,10 +9724,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -9701,10 +9747,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -9724,10 +9770,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -9741,10 +9787,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D5" s="1">
         <v>-3</v>
@@ -9803,10 +9849,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -9824,10 +9870,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -9890,10 +9936,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -9913,10 +9959,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -9936,10 +9982,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>334</v>
       </c>
       <c r="D4" s="1">
         <v>-3</v>
@@ -9953,10 +9999,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>334</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -10015,10 +10061,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10038,10 +10084,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10061,10 +10107,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="D4" s="1">
         <v>-3</v>
@@ -10078,10 +10124,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -10126,7 +10172,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -10143,13 +10189,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -10169,13 +10215,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -10195,13 +10241,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -10213,7 +10259,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="57.6" spans="1:8">
@@ -10221,14 +10267,14 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
@@ -10239,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" ht="57.6" spans="1:8">
@@ -10247,25 +10293,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="7" ht="57" customHeight="1" spans="1:8">
@@ -10273,10 +10319,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -10288,7 +10334,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="8" ht="57.6" spans="1:8">
@@ -10296,10 +10342,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -10311,7 +10357,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9" ht="57.6" spans="1:8">
@@ -10319,22 +10365,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="E9" s="1">
-        <v>2</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -10342,10 +10388,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E10" s="1">
         <v>-1</v>
@@ -10359,10 +10405,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -10421,10 +10467,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -10441,10 +10487,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -10507,10 +10553,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10530,10 +10576,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10553,10 +10599,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -10570,10 +10616,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -10618,7 +10664,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -10635,10 +10681,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -10661,10 +10707,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -10687,10 +10733,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="D4" s="1">
         <v>151</v>
@@ -10707,10 +10753,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -10727,10 +10773,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D6" s="1">
         <v>201</v>
@@ -10747,10 +10793,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -10767,10 +10813,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -10787,10 +10833,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -10810,7 +10856,7 @@
         <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -10836,7 +10882,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -10887,7 +10933,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -10904,10 +10950,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10927,10 +10973,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10950,10 +10996,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -10967,10 +11013,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -11111,7 +11157,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -11128,10 +11174,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -11154,10 +11200,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -11180,10 +11226,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>371</v>
       </c>
       <c r="D4" s="1">
         <v>201</v>
@@ -11200,10 +11246,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>371</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -11220,10 +11266,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D6" s="1">
         <v>401</v>
@@ -11240,10 +11286,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -11260,10 +11306,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -11280,10 +11326,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -11300,10 +11346,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -11326,10 +11372,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -11391,16 +11437,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>34</v>
@@ -11450,10 +11496,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -11514,16 +11560,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11578,16 +11624,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11642,16 +11688,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11706,16 +11752,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11753,13 +11799,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -11776,10 +11822,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -11805,10 +11851,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D3" s="1">
         <v>255</v>
@@ -11834,10 +11880,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -11863,10 +11909,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D5" s="1">
         <v>256</v>
@@ -11930,10 +11976,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -11994,10 +12040,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12017,10 +12063,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -12040,10 +12086,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -12057,10 +12103,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -12225,10 +12271,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12251,10 +12297,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12277,10 +12323,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12303,10 +12349,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12329,10 +12375,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12355,10 +12401,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12381,10 +12427,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12407,10 +12453,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -12427,10 +12473,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -12447,10 +12493,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -12467,10 +12513,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -12487,10 +12533,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -12499,10 +12545,10 @@
         <v>120</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -12557,17 +12603,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -12625,10 +12671,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12651,10 +12697,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12677,10 +12723,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12703,10 +12749,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12729,10 +12775,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12755,10 +12801,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12781,10 +12827,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12807,10 +12853,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -12827,10 +12873,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -12847,10 +12893,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -12867,10 +12913,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -12887,10 +12933,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -12899,10 +12945,10 @@
         <v>100</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -12957,19 +13003,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -13024,10 +13070,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E2" s="1">
         <v>50</v>
@@ -13088,10 +13134,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D2" s="1">
         <v>30</v>
@@ -13111,10 +13157,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D3" s="1">
         <v>301</v>
@@ -13128,10 +13174,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D4" s="1">
         <v>-301</v>
@@ -13145,10 +13191,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D5" s="1">
         <v>21</v>
@@ -13219,10 +13265,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13248,10 +13294,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13277,10 +13323,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>441</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13306,10 +13352,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13335,10 +13381,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -13364,10 +13410,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -13393,10 +13439,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -13422,10 +13468,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -13451,10 +13497,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -13480,10 +13526,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -13509,10 +13555,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -13538,10 +13584,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -13567,10 +13613,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -13596,10 +13642,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -13625,10 +13671,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -13648,10 +13694,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -13671,10 +13717,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -13694,7 +13740,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -13714,7 +13760,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -13761,7 +13807,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -13784,10 +13830,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13813,10 +13859,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13842,10 +13888,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>460</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13871,10 +13917,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13900,10 +13946,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -13929,10 +13975,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -13958,10 +14004,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -13981,10 +14027,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -14004,10 +14050,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -14027,10 +14073,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -14077,7 +14123,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -14100,10 +14146,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14129,10 +14175,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14158,10 +14204,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>471</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>469</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14179,7 +14225,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14187,10 +14233,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14208,7 +14254,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14216,10 +14262,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14237,7 +14283,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14245,10 +14291,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14266,7 +14312,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14274,10 +14320,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14303,10 +14349,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14332,10 +14378,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14353,7 +14399,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14361,10 +14407,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14382,7 +14428,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14390,10 +14436,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14411,7 +14457,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14419,10 +14465,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14440,7 +14486,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14448,10 +14494,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -14471,10 +14517,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -14494,10 +14540,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -14517,10 +14563,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -14591,10 +14637,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14620,10 +14666,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14649,10 +14695,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>484</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14678,10 +14724,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14707,10 +14753,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14736,10 +14782,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14765,10 +14811,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14794,10 +14840,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14823,10 +14869,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14852,10 +14898,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14881,10 +14927,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14910,10 +14956,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14939,10 +14985,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -14968,10 +15014,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -14997,10 +15043,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -15020,10 +15066,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -15043,10 +15089,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -15066,7 +15112,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -15086,7 +15132,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -15444,7 +15490,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -15467,10 +15513,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -15496,10 +15542,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -15525,10 +15571,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>503</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -15546,7 +15592,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15554,10 +15600,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -15575,7 +15621,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15583,10 +15629,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -15604,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15612,10 +15658,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -15633,7 +15679,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15641,10 +15687,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -15670,10 +15716,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -15699,10 +15745,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -15720,7 +15766,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15728,10 +15774,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -15749,7 +15795,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15757,10 +15803,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -15778,7 +15824,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15786,10 +15832,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -15807,7 +15853,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15815,10 +15861,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -15838,10 +15884,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -15861,10 +15907,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -15884,10 +15930,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -15951,10 +15997,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16020,10 +16066,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D2" s="1">
         <v>45</v>
@@ -16046,10 +16092,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D3" s="1">
         <v>-45</v>
@@ -16072,10 +16118,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D4" s="1">
         <v>91</v>
@@ -16092,10 +16138,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D5" s="1">
         <v>-91</v>
@@ -16112,10 +16158,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>522</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>520</v>
       </c>
       <c r="D6" s="1">
         <v>45</v>
@@ -16132,10 +16178,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>522</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>520</v>
       </c>
       <c r="D7" s="1">
         <v>45</v>
@@ -16180,10 +16226,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>145</v>
@@ -16203,16 +16249,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="F2" s="1">
         <v>50</v>
@@ -16232,16 +16278,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -16255,16 +16301,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="F4" s="1">
         <v>101</v>
@@ -16322,10 +16368,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16345,10 +16391,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16368,10 +16414,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16391,10 +16437,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -16414,10 +16460,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
@@ -16437,10 +16483,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -16454,10 +16500,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
@@ -16521,10 +16567,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>532</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>530</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16544,10 +16590,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>532</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>530</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16567,10 +16613,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16584,10 +16630,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -16651,10 +16697,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16719,13 +16765,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -16745,13 +16791,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>536</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E3" s="1">
         <v>30</v>
@@ -16771,13 +16817,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -16797,13 +16843,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -16823,19 +16869,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16843,19 +16889,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16863,19 +16909,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16883,19 +16929,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16903,19 +16949,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16923,19 +16969,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16943,19 +16989,19 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16963,19 +17009,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16983,19 +17029,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17003,19 +17049,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17023,19 +17069,19 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17043,19 +17089,19 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17063,19 +17109,19 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17083,19 +17129,19 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17103,19 +17149,19 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E20" s="1">
         <v>50</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17123,19 +17169,19 @@
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E21" s="1">
         <v>50</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17143,19 +17189,19 @@
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17163,19 +17209,19 @@
         <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E23" s="1">
         <v>50</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17183,19 +17229,19 @@
         <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E24" s="1">
         <v>50</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17203,19 +17249,19 @@
         <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E25" s="1">
         <v>50</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17223,19 +17269,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E26" s="1">
         <v>50</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17243,19 +17289,19 @@
         <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E27" s="1">
         <v>50</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17263,19 +17309,19 @@
         <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E28" s="1">
         <v>50</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17283,19 +17329,19 @@
         <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E29" s="1">
         <v>50</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17303,19 +17349,19 @@
         <v>19</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E30" s="1">
         <v>101</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17323,19 +17369,19 @@
         <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E31" s="1">
         <v>-1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -17372,7 +17418,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -17395,10 +17441,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17424,10 +17470,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -17453,10 +17499,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>590</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>588</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -17482,10 +17528,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -17511,10 +17557,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -17540,10 +17586,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -17569,10 +17615,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -17598,10 +17644,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -17627,10 +17673,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -17656,10 +17702,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -17685,10 +17731,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -17714,10 +17760,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -17743,10 +17789,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -17766,10 +17812,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -17789,10 +17835,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -17812,10 +17858,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -17862,7 +17908,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -17885,10 +17931,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17914,10 +17960,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -17943,10 +17989,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>603</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -17964,7 +18010,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17972,10 +18018,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -17993,7 +18039,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18001,10 +18047,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18022,7 +18068,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18030,10 +18076,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18051,7 +18097,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18059,10 +18105,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18088,10 +18134,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -18117,10 +18163,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -18138,7 +18184,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18146,10 +18192,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -18167,7 +18213,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18175,10 +18221,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -18196,7 +18242,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18204,10 +18250,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -18225,7 +18271,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -18233,10 +18279,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -18256,10 +18302,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -18279,10 +18325,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -18302,10 +18348,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -18448,7 +18494,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -18471,10 +18517,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18500,10 +18546,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -18529,10 +18575,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -18558,10 +18604,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18587,10 +18633,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18616,10 +18662,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18645,10 +18691,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18668,10 +18714,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -18691,10 +18737,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -18714,10 +18760,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -18784,10 +18830,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18801,10 +18847,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -18818,10 +18864,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -18835,10 +18881,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -18852,10 +18898,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -18869,10 +18915,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -18886,10 +18932,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -18947,10 +18993,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -19009,16 +19055,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>34</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="22" activeTab="28"/>
+    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="22" activeTab="29"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2340" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="624">
   <si>
     <t>ID</t>
   </si>
@@ -965,43 +965,37 @@
     <t>[322.5, -646, 158.3, 179.99, 19.99, 0.0]</t>
   </si>
   <si>
-    <t>设置全坐标z轴超限（max）左臂</t>
+    <t>设置全坐标z轴超限（max）</t>
   </si>
   <si>
     <t>[322.5, 0.0, 656, 179.99, 19.99, 0.0]</t>
   </si>
   <si>
-    <t>设置全坐标z轴超限（min）左臂</t>
+    <t>设置全坐标z轴超限（min）</t>
   </si>
   <si>
     <t>[322.5, 0.0, -263, 179.99, 19.99, 0.0]</t>
   </si>
   <si>
-    <t>设置全坐标z轴超限（max）右臂</t>
-  </si>
-  <si>
-    <t>设置全坐标z轴超限（min）右臂</t>
-  </si>
-  <si>
-    <t>设置全坐标rx轴超限（max）右臂</t>
+    <t>设置全坐标rx轴超限（max）</t>
   </si>
   <si>
     <t>[322.5, 0.0, 158.3, 181, 19.99, 0.0]</t>
   </si>
   <si>
-    <t>设置全坐标rx轴超限（min）右臂</t>
+    <t>设置全坐标rx轴超限（min）</t>
   </si>
   <si>
     <t>[322.5, 0.0, 158.3, -181, 19.99, 0.0]</t>
   </si>
   <si>
-    <t>设置全坐标ry轴超限（max）右臂</t>
+    <t>设置全坐标ry轴超限（max）</t>
   </si>
   <si>
     <t>[322.5, 0.0, 158.3, 179.99, 181, 0.0]</t>
   </si>
   <si>
-    <t>设置全坐标ry轴超限（min）右臂</t>
+    <t>设置全坐标ry轴超限（min）</t>
   </si>
   <si>
     <t>[322.5, 0.0, 158.3, 179.99, -181, 0.0]</t>
@@ -1049,22 +1043,22 @@
     <t>设置x轴运动超限（min）</t>
   </si>
   <si>
-    <t>设置y轴运动超限（max）</t>
-  </si>
-  <si>
-    <t>设置y轴运动超限（min）</t>
-  </si>
-  <si>
-    <t>设置z轴运动超限（max）左臂</t>
-  </si>
-  <si>
-    <t>设置z轴运动超限（min）左臂</t>
-  </si>
-  <si>
-    <t>设置z轴运动超限（max）右臂</t>
-  </si>
-  <si>
-    <t>设置z轴运动超限（min）右臂</t>
+    <t>设置y轴运动超限（max）左臂</t>
+  </si>
+  <si>
+    <t>设置y轴运动超限（min）左臂</t>
+  </si>
+  <si>
+    <t>设置y轴运动超限（max）右臂</t>
+  </si>
+  <si>
+    <t>设置y轴运动超限（min）右臂</t>
+  </si>
+  <si>
+    <t>设置z轴运动超限（max）</t>
+  </si>
+  <si>
+    <t>设置z轴运动超限（min）</t>
   </si>
   <si>
     <t>设置rx轴运动超限（max）</t>
@@ -8441,7 +8435,7 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
@@ -8720,7 +8714,7 @@
         <v>50</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>155</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="1:8">
@@ -8740,12 +8734,12 @@
         <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>155</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" ht="28.8" spans="1:8">
       <c r="A14" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>292</v>
@@ -8754,47 +8748,47 @@
         <v>270</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>183</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" ht="28.8" spans="1:8">
       <c r="A15" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>270</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>183</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" ht="28.8" spans="1:8">
       <c r="A16" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>270</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
@@ -8805,16 +8799,16 @@
     </row>
     <row r="17" ht="28.8" spans="1:8">
       <c r="A17" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>270</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
@@ -8825,16 +8819,16 @@
     </row>
     <row r="18" ht="28.8" spans="1:8">
       <c r="A18" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>270</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
@@ -8845,10 +8839,10 @@
     </row>
     <row r="19" ht="28.8" spans="1:8">
       <c r="A19" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>270</v>
@@ -8865,19 +8859,19 @@
     </row>
     <row r="20" ht="28.8" spans="1:8">
       <c r="A20" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>270</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>302</v>
+        <v>272</v>
       </c>
       <c r="E20" s="1">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>42</v>
@@ -8885,61 +8879,21 @@
     </row>
     <row r="21" ht="28.8" spans="1:8">
       <c r="A21" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>270</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="E21" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" ht="28.8" spans="1:8">
-      <c r="A22" s="2">
-        <v>19</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="E22" s="1">
-        <v>101</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" ht="28.8" spans="1:8">
-      <c r="A23" s="2">
-        <v>20</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -9068,7 +9022,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -9091,10 +9045,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -9120,10 +9074,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -9141,7 +9095,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -9149,10 +9103,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -9170,7 +9124,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -9178,10 +9132,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -9199,7 +9153,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -9207,10 +9161,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -9228,7 +9182,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -9236,10 +9190,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -9257,7 +9211,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" ht="28.8" spans="1:9">
@@ -9265,16 +9219,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
       </c>
       <c r="E8" s="1">
-        <v>443</v>
+        <v>567</v>
       </c>
       <c r="F8" s="1">
         <v>70</v>
@@ -9288,16 +9242,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
       </c>
       <c r="E9" s="1">
-        <v>-443</v>
+        <v>-352</v>
       </c>
       <c r="F9" s="1">
         <v>70</v>
@@ -9311,22 +9265,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
       </c>
       <c r="E10" s="1">
-        <v>443</v>
+        <v>646</v>
       </c>
       <c r="F10" s="1">
         <v>70</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>42</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="1:9">
@@ -9334,22 +9288,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
       <c r="E11" s="1">
-        <v>-443</v>
+        <v>-273</v>
       </c>
       <c r="F11" s="1">
         <v>70</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>42</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" ht="28.8" spans="1:9">
@@ -9357,22 +9311,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D12" s="1">
         <v>3</v>
       </c>
       <c r="E12" s="1">
-        <v>630</v>
+        <v>273</v>
       </c>
       <c r="F12" s="1">
         <v>70</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="1:9">
@@ -9380,22 +9334,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D13" s="1">
         <v>3</v>
       </c>
       <c r="E13" s="1">
-        <v>-208</v>
+        <v>-646</v>
       </c>
       <c r="F13" s="1">
         <v>70</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14" ht="28.8" spans="1:9">
@@ -9403,22 +9357,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
       </c>
       <c r="E14" s="1">
-        <v>208</v>
+        <v>656</v>
       </c>
       <c r="F14" s="1">
         <v>70</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>183</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" ht="28.8" spans="1:9">
@@ -9426,22 +9380,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D15" s="1">
         <v>3</v>
       </c>
       <c r="E15" s="1">
-        <v>-630</v>
+        <v>-263</v>
       </c>
       <c r="F15" s="1">
         <v>70</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>183</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" ht="28.8" spans="1:9">
@@ -9449,10 +9403,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D16" s="1">
         <v>4</v>
@@ -9472,10 +9426,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D17" s="1">
         <v>4</v>
@@ -9495,10 +9449,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -9518,10 +9472,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D19" s="1">
         <v>5</v>
@@ -9541,10 +9495,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D20" s="1">
         <v>6</v>
@@ -9564,10 +9518,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D21" s="1">
         <v>6</v>
@@ -9587,10 +9541,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -9610,10 +9564,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -9622,7 +9576,7 @@
         <v>350</v>
       </c>
       <c r="F23" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>42</v>
@@ -9633,10 +9587,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D24" s="1">
         <v>7</v>
@@ -9656,10 +9610,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -9724,10 +9678,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -9747,10 +9701,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -9770,10 +9724,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -9787,10 +9741,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D5" s="1">
         <v>-3</v>
@@ -9849,10 +9803,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -9870,10 +9824,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -9936,10 +9890,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -9959,10 +9913,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -9982,10 +9936,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D4" s="1">
         <v>-3</v>
@@ -9999,10 +9953,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -10061,10 +10015,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10084,10 +10038,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10107,10 +10061,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D4" s="1">
         <v>-3</v>
@@ -10124,10 +10078,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -10172,7 +10126,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -10189,13 +10143,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>346</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -10215,13 +10169,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -10241,25 +10195,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="57.6" spans="1:8">
@@ -10267,13 +10221,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -10285,7 +10239,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" ht="57.6" spans="1:8">
@@ -10293,13 +10247,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -10311,7 +10265,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" ht="57" customHeight="1" spans="1:8">
@@ -10319,10 +10273,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -10334,7 +10288,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" ht="57.6" spans="1:8">
@@ -10342,10 +10296,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -10357,7 +10311,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" ht="57.6" spans="1:8">
@@ -10365,10 +10319,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -10380,7 +10334,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -10388,10 +10342,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E10" s="1">
         <v>-1</v>
@@ -10405,10 +10359,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -10467,10 +10421,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -10487,10 +10441,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -10553,10 +10507,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10576,10 +10530,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10599,10 +10553,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -10616,10 +10570,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -10664,7 +10618,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -10681,10 +10635,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -10707,10 +10661,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -10733,10 +10687,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D4" s="1">
         <v>151</v>
@@ -10753,10 +10707,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -10773,10 +10727,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D6" s="1">
         <v>201</v>
@@ -10793,10 +10747,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -10813,10 +10767,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -10833,10 +10787,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -10856,7 +10810,7 @@
         <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -10882,7 +10836,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -10933,7 +10887,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -10950,10 +10904,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10973,10 +10927,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10996,10 +10950,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -11013,10 +10967,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -11157,7 +11111,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -11174,10 +11128,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -11200,10 +11154,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -11226,10 +11180,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D4" s="1">
         <v>201</v>
@@ -11246,10 +11200,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -11266,10 +11220,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D6" s="1">
         <v>401</v>
@@ -11286,10 +11240,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -11306,10 +11260,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -11326,10 +11280,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -11346,10 +11300,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -11372,10 +11326,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -11437,16 +11391,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>382</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>34</v>
@@ -11496,10 +11450,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -11560,16 +11514,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>388</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11624,16 +11578,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11688,16 +11642,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11752,16 +11706,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>396</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11799,13 +11753,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>399</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -11822,10 +11776,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -11851,10 +11805,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D3" s="1">
         <v>255</v>
@@ -11880,10 +11834,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -11909,10 +11863,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D5" s="1">
         <v>256</v>
@@ -11976,10 +11930,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -12040,10 +11994,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12063,10 +12017,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -12086,10 +12040,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -12103,10 +12057,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -12271,10 +12225,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12297,10 +12251,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12323,10 +12277,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12349,10 +12303,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12375,10 +12329,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12401,10 +12355,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12427,10 +12381,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12453,10 +12407,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -12473,10 +12427,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -12493,10 +12447,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -12513,10 +12467,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -12533,10 +12487,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -12545,10 +12499,10 @@
         <v>120</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -12603,17 +12557,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -12671,10 +12625,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12697,10 +12651,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12723,10 +12677,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12749,10 +12703,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12775,10 +12729,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12801,10 +12755,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12827,10 +12781,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12853,10 +12807,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -12873,10 +12827,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -12893,10 +12847,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -12913,10 +12867,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -12933,10 +12887,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -12945,10 +12899,10 @@
         <v>100</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -13003,19 +12957,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -13070,10 +13024,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E2" s="1">
         <v>50</v>
@@ -13134,10 +13088,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D2" s="1">
         <v>30</v>
@@ -13157,10 +13111,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D3" s="1">
         <v>301</v>
@@ -13174,10 +13128,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D4" s="1">
         <v>-301</v>
@@ -13191,10 +13145,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D5" s="1">
         <v>21</v>
@@ -13265,10 +13219,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13294,10 +13248,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13323,10 +13277,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13352,10 +13306,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13381,10 +13335,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -13410,10 +13364,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -13439,10 +13393,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -13468,10 +13422,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -13497,10 +13451,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -13526,10 +13480,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -13555,10 +13509,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -13584,10 +13538,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -13613,10 +13567,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -13642,10 +13596,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -13671,10 +13625,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -13694,10 +13648,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -13717,10 +13671,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -13740,7 +13694,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -13760,7 +13714,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -13807,7 +13761,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -13830,10 +13784,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13859,10 +13813,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13888,10 +13842,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13917,10 +13871,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13946,10 +13900,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -13975,10 +13929,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14004,10 +13958,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14027,10 +13981,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -14050,10 +14004,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -14073,10 +14027,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -14123,7 +14077,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -14146,10 +14100,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14175,10 +14129,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14204,10 +14158,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14225,7 +14179,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14233,10 +14187,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14254,7 +14208,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14262,10 +14216,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14283,7 +14237,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14291,10 +14245,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14312,7 +14266,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14320,10 +14274,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14349,10 +14303,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14378,10 +14332,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14399,7 +14353,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14407,10 +14361,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14428,7 +14382,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14436,10 +14390,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14457,7 +14411,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14465,10 +14419,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14486,7 +14440,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14494,10 +14448,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -14517,10 +14471,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -14540,10 +14494,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -14563,10 +14517,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -14637,10 +14591,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14666,10 +14620,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14695,10 +14649,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14724,10 +14678,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14753,10 +14707,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14782,10 +14736,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14811,10 +14765,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14840,10 +14794,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14869,10 +14823,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14898,10 +14852,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14927,10 +14881,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14956,10 +14910,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14985,10 +14939,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -15014,10 +14968,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -15043,10 +14997,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -15066,10 +15020,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -15089,10 +15043,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -15112,7 +15066,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -15132,7 +15086,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -15490,7 +15444,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -15513,10 +15467,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -15542,10 +15496,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -15571,10 +15525,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -15592,7 +15546,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15600,10 +15554,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -15621,7 +15575,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15629,10 +15583,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -15650,7 +15604,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15658,10 +15612,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -15679,7 +15633,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15687,10 +15641,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -15716,10 +15670,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -15745,10 +15699,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -15766,7 +15720,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15774,10 +15728,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -15795,7 +15749,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15803,10 +15757,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -15824,7 +15778,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15832,10 +15786,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -15853,7 +15807,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15861,10 +15815,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -15884,10 +15838,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -15907,10 +15861,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -15930,10 +15884,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -15997,10 +15951,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16066,10 +16020,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D2" s="1">
         <v>45</v>
@@ -16092,10 +16046,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D3" s="1">
         <v>-45</v>
@@ -16118,10 +16072,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D4" s="1">
         <v>91</v>
@@ -16138,10 +16092,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D5" s="1">
         <v>-91</v>
@@ -16158,10 +16112,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D6" s="1">
         <v>45</v>
@@ -16178,10 +16132,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D7" s="1">
         <v>45</v>
@@ -16226,10 +16180,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>145</v>
@@ -16249,16 +16203,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>530</v>
       </c>
       <c r="F2" s="1">
         <v>50</v>
@@ -16278,16 +16232,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>530</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -16301,16 +16255,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>530</v>
       </c>
       <c r="F4" s="1">
         <v>101</v>
@@ -16368,10 +16322,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16391,10 +16345,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16414,10 +16368,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16437,10 +16391,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -16460,10 +16414,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
@@ -16483,10 +16437,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -16500,10 +16454,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
@@ -16567,10 +16521,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16590,10 +16544,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16613,10 +16567,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16630,10 +16584,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -16697,10 +16651,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16765,13 +16719,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>539</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -16791,13 +16745,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E3" s="1">
         <v>30</v>
@@ -16817,13 +16771,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -16843,13 +16797,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -16869,19 +16823,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16889,19 +16843,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16909,19 +16863,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16929,19 +16883,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16949,19 +16903,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16969,19 +16923,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16989,19 +16943,19 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17009,19 +16963,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>561</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17029,19 +16983,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17049,19 +17003,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17069,19 +17023,19 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17089,19 +17043,19 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17109,19 +17063,19 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17129,19 +17083,19 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17149,19 +17103,19 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E20" s="1">
         <v>50</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17169,19 +17123,19 @@
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E21" s="1">
         <v>50</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17189,19 +17143,19 @@
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17209,19 +17163,19 @@
         <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E23" s="1">
         <v>50</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17229,19 +17183,19 @@
         <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E24" s="1">
         <v>50</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17249,19 +17203,19 @@
         <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E25" s="1">
         <v>50</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17269,19 +17223,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E26" s="1">
         <v>50</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17289,19 +17243,19 @@
         <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E27" s="1">
         <v>50</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17309,19 +17263,19 @@
         <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E28" s="1">
         <v>50</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17329,19 +17283,19 @@
         <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E29" s="1">
         <v>50</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17349,19 +17303,19 @@
         <v>19</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E30" s="1">
         <v>101</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17369,19 +17323,19 @@
         <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E31" s="1">
         <v>-1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -17418,7 +17372,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -17441,10 +17395,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17470,10 +17424,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -17499,10 +17453,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -17528,10 +17482,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -17557,10 +17511,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -17586,10 +17540,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -17615,10 +17569,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -17644,10 +17598,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -17673,10 +17627,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -17702,10 +17656,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -17731,10 +17685,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -17760,10 +17714,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -17789,10 +17743,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -17812,10 +17766,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -17835,10 +17789,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -17858,10 +17812,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -17908,7 +17862,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -17931,10 +17885,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17960,10 +17914,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -17989,10 +17943,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -18010,7 +17964,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18018,10 +17972,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18039,7 +17993,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18047,10 +18001,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18068,7 +18022,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18076,10 +18030,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18097,7 +18051,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18105,10 +18059,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18134,10 +18088,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -18163,10 +18117,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -18184,7 +18138,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18192,10 +18146,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -18213,7 +18167,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18221,10 +18175,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -18242,7 +18196,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18250,10 +18204,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -18271,7 +18225,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -18279,10 +18233,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -18302,10 +18256,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -18325,10 +18279,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -18348,10 +18302,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -18494,7 +18448,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -18517,10 +18471,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18546,10 +18500,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -18575,10 +18529,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -18604,10 +18558,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18633,10 +18587,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18662,10 +18616,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18691,10 +18645,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18714,10 +18668,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -18737,10 +18691,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -18760,10 +18714,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -18830,10 +18784,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18847,10 +18801,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -18864,10 +18818,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -18881,10 +18835,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -18898,10 +18852,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -18915,10 +18869,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -18932,10 +18886,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -18993,10 +18947,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -19055,16 +19009,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>623</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>625</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>34</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="22" activeTab="29"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="22" activeTab="29"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -9317,7 +9317,7 @@
         <v>305</v>
       </c>
       <c r="D12" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="1">
         <v>273</v>
@@ -9340,7 +9340,7 @@
         <v>305</v>
       </c>
       <c r="D13" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" s="1">
         <v>-646</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="22" activeTab="29"/>
+    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="24" activeTab="34"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2349" uniqueCount="628">
   <si>
     <t>ID</t>
   </si>
@@ -1145,9 +1145,6 @@
     <t>[322.5, 0.0, 158.3, -180.0, 20.0, 0.0]</t>
   </si>
   <si>
-    <t>coords</t>
-  </si>
-  <si>
     <t>判读当前坐标是否在点位上（不在点位超过±0.2mm）</t>
   </si>
   <si>
@@ -1157,13 +1154,28 @@
     <t>判读当前base坐标是否在点位上（在点位±0.2mm，欧拉角±一度）</t>
   </si>
   <si>
-    <t>base_coords</t>
+    <t>[375.0, 213.1, 196.1, 89.99, 0.0, -31.99]</t>
   </si>
   <si>
     <t>判读当前base坐标是否在点位上（不在点位超过±0.2mm）</t>
   </si>
   <si>
+    <t>[376.0, 213.1, 196.1, 89.99, 0.0, -31.99]</t>
+  </si>
+  <si>
     <t>判读当前base坐标是否在点位上（不在点位欧拉角超过1°）</t>
+  </si>
+  <si>
+    <t>[375.0, 213.1, 196.1, 89.99, 1.2, -31.99]</t>
+  </si>
+  <si>
+    <t>[375.0, -213.1, 196.1, -89.99, 0.0, 32.0]</t>
+  </si>
+  <si>
+    <t>[375.0, -214, 196.1, -89.99, 0.0, 32.0]</t>
+  </si>
+  <si>
+    <t>[375.0, -213.1, 196.1, -92, 0.0, 32.0]</t>
   </si>
   <si>
     <t>设置mode超限</t>
@@ -10099,13 +10111,13 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="38.5555555555556" style="1" customWidth="1"/>
     <col min="5" max="6" width="17.2222222222222" style="1" customWidth="1"/>
     <col min="7" max="7" width="18" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.8888888888889" style="1" customWidth="1"/>
@@ -10161,7 +10173,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>241</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="57.6" spans="1:8">
@@ -10187,7 +10199,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>241</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="57.6" spans="1:8">
@@ -10213,7 +10225,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>348</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="57.6" spans="1:8">
@@ -10221,7 +10233,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>343</v>
@@ -10239,7 +10251,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>348</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" ht="57.6" spans="1:8">
@@ -10247,7 +10259,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>343</v>
@@ -10265,7 +10277,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>348</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" ht="57" customHeight="1" spans="1:8">
@@ -10273,11 +10285,14 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>343</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>351</v>
+      </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
@@ -10288,7 +10303,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>352</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" ht="57.6" spans="1:8">
@@ -10296,11 +10311,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>343</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>353</v>
+      </c>
       <c r="E8" s="1">
         <v>2</v>
       </c>
@@ -10311,7 +10329,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>352</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" ht="57.6" spans="1:8">
@@ -10324,6 +10342,9 @@
       <c r="C9" s="1" t="s">
         <v>343</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>355</v>
+      </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
@@ -10334,40 +10355,106 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" ht="72" spans="1:8">
       <c r="B10" s="1" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>343</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>356</v>
+      </c>
       <c r="E10" s="1">
-        <v>-1</v>
+        <v>2</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="11" ht="57.6" spans="1:8">
       <c r="B11" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>343</v>
       </c>
+      <c r="D11" s="1" t="s">
+        <v>357</v>
+      </c>
       <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" ht="57.6" spans="1:8">
+      <c r="B12" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="13" ht="28.8" spans="1:8">
+      <c r="A13" s="2">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="E13" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" ht="28.8" spans="1:8">
+      <c r="A14" s="2">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E14" s="1">
         <v>3</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -10421,10 +10508,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -10441,10 +10528,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -10507,10 +10594,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10530,10 +10617,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10553,10 +10640,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -10570,10 +10657,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -10635,10 +10722,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -10661,10 +10748,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -10687,10 +10774,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D4" s="1">
         <v>151</v>
@@ -10707,10 +10794,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -10727,10 +10814,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D6" s="1">
         <v>201</v>
@@ -10747,10 +10834,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -10767,10 +10854,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -10787,10 +10874,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -10810,7 +10897,7 @@
         <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -10836,7 +10923,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -10904,10 +10991,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10927,10 +11014,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10950,10 +11037,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -10967,10 +11054,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -11128,10 +11215,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -11154,10 +11241,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -11180,10 +11267,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D4" s="1">
         <v>201</v>
@@ -11200,10 +11287,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -11220,10 +11307,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D6" s="1">
         <v>401</v>
@@ -11240,10 +11327,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -11260,10 +11347,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -11280,10 +11367,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -11300,10 +11387,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>371</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -11326,10 +11413,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -11391,16 +11478,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>34</v>
@@ -11450,10 +11537,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -11514,16 +11601,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11578,16 +11665,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11642,16 +11729,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11706,16 +11793,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11753,13 +11840,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -11776,10 +11863,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -11805,10 +11892,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D3" s="1">
         <v>255</v>
@@ -11834,10 +11921,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -11863,10 +11950,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D5" s="1">
         <v>256</v>
@@ -11930,10 +12017,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -11994,10 +12081,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12017,10 +12104,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -12040,10 +12127,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -12057,10 +12144,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -12225,10 +12312,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12251,10 +12338,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12277,10 +12364,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12303,10 +12390,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12329,10 +12416,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12355,10 +12442,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12381,10 +12468,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12407,10 +12494,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -12427,10 +12514,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -12447,10 +12534,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -12467,10 +12554,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -12487,10 +12574,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -12499,10 +12586,10 @@
         <v>120</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -12557,17 +12644,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -12625,10 +12712,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12651,10 +12738,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12677,10 +12764,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12703,10 +12790,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12729,10 +12816,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12755,10 +12842,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12781,10 +12868,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12807,10 +12894,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -12827,10 +12914,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -12847,10 +12934,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -12867,10 +12954,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -12887,10 +12974,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -12899,10 +12986,10 @@
         <v>100</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -12957,19 +13044,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -13024,10 +13111,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E2" s="1">
         <v>50</v>
@@ -13088,10 +13175,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D2" s="1">
         <v>30</v>
@@ -13111,10 +13198,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D3" s="1">
         <v>301</v>
@@ -13128,10 +13215,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D4" s="1">
         <v>-301</v>
@@ -13145,10 +13232,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D5" s="1">
         <v>21</v>
@@ -13219,10 +13306,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13248,10 +13335,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13277,10 +13364,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13306,10 +13393,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13335,10 +13422,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>441</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -13364,10 +13451,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -13393,10 +13480,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -13422,10 +13509,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -13451,10 +13538,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -13480,10 +13567,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -13509,10 +13596,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -13538,10 +13625,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -13567,10 +13654,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -13596,10 +13683,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -13625,10 +13712,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -13648,10 +13735,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -13671,10 +13758,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -13694,7 +13781,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -13714,7 +13801,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -13784,10 +13871,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13813,10 +13900,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13842,10 +13929,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13871,10 +13958,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13900,10 +13987,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>460</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -13929,10 +14016,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -13958,10 +14045,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -13981,10 +14068,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -14004,10 +14091,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -14027,10 +14114,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -14100,10 +14187,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14129,10 +14216,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14158,10 +14245,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14187,10 +14274,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14216,10 +14303,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>469</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14245,10 +14332,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14274,10 +14361,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14303,10 +14390,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14332,10 +14419,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14361,10 +14448,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14390,10 +14477,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14419,10 +14506,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14448,10 +14535,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -14471,10 +14558,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -14494,10 +14581,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -14517,10 +14604,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -14591,10 +14678,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14620,10 +14707,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14649,10 +14736,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14678,10 +14765,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14707,10 +14794,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>484</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14736,10 +14823,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14765,10 +14852,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14794,10 +14881,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14823,10 +14910,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14852,10 +14939,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14881,10 +14968,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14910,10 +14997,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14939,10 +15026,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -14968,10 +15055,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -14997,10 +15084,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -15020,10 +15107,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -15043,10 +15130,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -15066,7 +15153,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -15086,7 +15173,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -15467,10 +15554,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -15496,10 +15583,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -15525,10 +15612,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -15554,10 +15641,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -15583,10 +15670,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>507</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>503</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -15612,10 +15699,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -15641,10 +15728,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -15670,10 +15757,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -15699,10 +15786,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -15728,10 +15815,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -15757,10 +15844,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -15786,10 +15873,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -15815,10 +15902,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -15838,10 +15925,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -15861,10 +15948,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -15884,10 +15971,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -15951,10 +16038,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16020,10 +16107,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="D2" s="1">
         <v>45</v>
@@ -16046,10 +16133,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="D3" s="1">
         <v>-45</v>
@@ -16072,10 +16159,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="D4" s="1">
         <v>91</v>
@@ -16092,10 +16179,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="D5" s="1">
         <v>-91</v>
@@ -16112,10 +16199,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="D6" s="1">
         <v>45</v>
@@ -16132,10 +16219,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="D7" s="1">
         <v>45</v>
@@ -16180,10 +16267,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>145</v>
@@ -16203,16 +16290,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="F2" s="1">
         <v>50</v>
@@ -16232,16 +16319,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -16255,16 +16342,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="F4" s="1">
         <v>101</v>
@@ -16322,10 +16409,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16345,10 +16432,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16368,10 +16455,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16391,10 +16478,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -16414,10 +16501,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
@@ -16437,10 +16524,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -16454,10 +16541,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
@@ -16521,10 +16608,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16544,10 +16631,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16567,10 +16654,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16584,10 +16671,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -16651,10 +16738,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>534</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>530</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16719,13 +16806,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -16745,13 +16832,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E3" s="1">
         <v>30</v>
@@ -16771,13 +16858,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>536</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -16797,13 +16884,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -16823,19 +16910,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16843,19 +16930,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16863,19 +16950,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16883,19 +16970,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16903,19 +16990,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16923,19 +17010,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16943,19 +17030,19 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16963,19 +17050,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16983,19 +17070,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17003,19 +17090,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17023,19 +17110,19 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17043,19 +17130,19 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17063,19 +17150,19 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17083,19 +17170,19 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17103,19 +17190,19 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="E20" s="1">
         <v>50</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17123,19 +17210,19 @@
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="E21" s="1">
         <v>50</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17143,19 +17230,19 @@
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17163,19 +17250,19 @@
         <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="E23" s="1">
         <v>50</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17183,19 +17270,19 @@
         <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E24" s="1">
         <v>50</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17203,19 +17290,19 @@
         <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="E25" s="1">
         <v>50</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17223,19 +17310,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="E26" s="1">
         <v>50</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17243,19 +17330,19 @@
         <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="E27" s="1">
         <v>50</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17263,19 +17350,19 @@
         <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E28" s="1">
         <v>50</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17283,19 +17370,19 @@
         <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="E29" s="1">
         <v>50</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17303,19 +17390,19 @@
         <v>19</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E30" s="1">
         <v>101</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17323,19 +17410,19 @@
         <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E31" s="1">
         <v>-1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>
@@ -17395,10 +17482,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17424,10 +17511,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -17453,10 +17540,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -17482,10 +17569,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -17511,10 +17598,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>588</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -17540,10 +17627,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -17569,10 +17656,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -17598,10 +17685,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -17627,10 +17714,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -17656,10 +17743,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -17685,10 +17772,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -17714,10 +17801,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -17743,10 +17830,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -17766,10 +17853,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -17789,10 +17876,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -17812,10 +17899,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -17885,10 +17972,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17914,10 +18001,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -17943,10 +18030,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -17972,10 +18059,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18001,10 +18088,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>603</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18030,10 +18117,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18059,10 +18146,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18088,10 +18175,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -18117,10 +18204,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -18146,10 +18233,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -18175,10 +18262,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -18204,10 +18291,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -18233,10 +18320,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -18256,10 +18343,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -18279,10 +18366,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -18302,10 +18389,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -18471,10 +18558,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18500,10 +18587,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -18529,10 +18616,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -18558,10 +18645,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18587,10 +18674,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18616,10 +18703,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18645,10 +18732,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18668,10 +18755,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -18691,10 +18778,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -18714,10 +18801,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -18784,10 +18871,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18801,10 +18888,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -18818,10 +18905,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -18835,10 +18922,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -18852,10 +18939,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -18869,10 +18956,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -18886,10 +18973,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -18947,10 +19034,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -19009,16 +19096,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>34</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="24" activeTab="34"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="24" activeTab="34"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2349" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2349" uniqueCount="631">
   <si>
     <t>ID</t>
   </si>
@@ -1139,16 +1139,25 @@
     <t>判断当前角度是否在点位上（不在点位超过±1°）</t>
   </si>
   <si>
+    <t>[1.1, 20, 0, -90, 0, 90, 0]</t>
+  </si>
+  <si>
     <t>判读当前坐标是否在点位上（在点位±0.2mm，欧拉角±一度）</t>
   </si>
   <si>
-    <t>[322.5, 0.0, 158.3, -180.0, 20.0, 0.0]</t>
+    <t>[322.5, 1, 158.3, -180.0, 20.0, 0.0]</t>
   </si>
   <si>
     <t>判读当前坐标是否在点位上（不在点位超过±0.2mm）</t>
   </si>
   <si>
+    <t>[322.5, 2, 158.3, -180.0, 20.0, 0.0]</t>
+  </si>
+  <si>
     <t>判读当前坐标是否在点位上（不在点位欧拉角超过1°）</t>
+  </si>
+  <si>
+    <t>[322.5, 0.0, 158.3, -180.0, 20.0, 2]</t>
   </si>
   <si>
     <t>判读当前base坐标是否在点位上（在点位±0.2mm，欧拉角±一度）</t>
@@ -10187,7 +10196,7 @@
         <v>343</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -10207,13 +10216,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>343</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -10233,13 +10242,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>343</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -10259,13 +10268,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>343</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -10285,13 +10294,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>343</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -10311,13 +10320,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>343</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -10337,13 +10346,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>343</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -10360,13 +10369,13 @@
     </row>
     <row r="10" ht="72" spans="1:8">
       <c r="B10" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>343</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -10380,13 +10389,13 @@
     </row>
     <row r="11" ht="57.6" spans="1:8">
       <c r="B11" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>343</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
@@ -10400,13 +10409,13 @@
     </row>
     <row r="12" ht="57.6" spans="1:8">
       <c r="B12" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>343</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -10423,13 +10432,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>343</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E13" s="1">
         <v>-1</v>
@@ -10443,13 +10452,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>343</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -10508,10 +10517,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -10528,10 +10537,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -10594,10 +10603,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10617,10 +10626,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10640,10 +10649,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -10657,10 +10666,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -10722,10 +10731,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -10748,10 +10757,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -10774,10 +10783,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D4" s="1">
         <v>151</v>
@@ -10794,10 +10803,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -10814,10 +10823,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>367</v>
       </c>
       <c r="D6" s="1">
         <v>201</v>
@@ -10834,10 +10843,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>367</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -10854,10 +10863,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -10874,10 +10883,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -10897,7 +10906,7 @@
         <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -10923,7 +10932,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -10991,10 +11000,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -11014,10 +11023,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -11037,10 +11046,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -11054,10 +11063,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -11215,10 +11224,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -11241,10 +11250,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -11267,10 +11276,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D4" s="1">
         <v>201</v>
@@ -11287,10 +11296,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -11307,10 +11316,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="D6" s="1">
         <v>401</v>
@@ -11327,10 +11336,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -11347,10 +11356,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -11367,10 +11376,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -11387,10 +11396,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -11413,10 +11422,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -11478,16 +11487,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>34</v>
@@ -11537,10 +11546,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -11601,16 +11610,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11665,16 +11674,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11729,16 +11738,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11793,16 +11802,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>393</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11840,13 +11849,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -11863,10 +11872,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -11892,10 +11901,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D3" s="1">
         <v>255</v>
@@ -11921,10 +11930,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -11950,10 +11959,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D5" s="1">
         <v>256</v>
@@ -12017,10 +12026,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -12081,10 +12090,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12104,10 +12113,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -12127,10 +12136,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -12144,10 +12153,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -12312,10 +12321,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12338,10 +12347,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12364,10 +12373,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12390,10 +12399,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>411</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12416,10 +12425,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12442,10 +12451,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12468,10 +12477,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12494,10 +12503,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -12514,10 +12523,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -12534,10 +12543,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -12554,10 +12563,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -12574,10 +12583,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -12586,10 +12595,10 @@
         <v>120</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -12644,17 +12653,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -12712,10 +12721,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12738,10 +12747,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12764,10 +12773,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12790,10 +12799,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>426</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12816,10 +12825,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12842,10 +12851,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12868,10 +12877,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12894,10 +12903,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -12914,10 +12923,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -12934,10 +12943,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -12954,10 +12963,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -12974,10 +12983,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -12986,10 +12995,10 @@
         <v>100</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -13044,19 +13053,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -13111,10 +13120,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E2" s="1">
         <v>50</v>
@@ -13175,10 +13184,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D2" s="1">
         <v>30</v>
@@ -13198,10 +13207,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D3" s="1">
         <v>301</v>
@@ -13215,10 +13224,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D4" s="1">
         <v>-301</v>
@@ -13232,10 +13241,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D5" s="1">
         <v>21</v>
@@ -13306,10 +13315,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13335,10 +13344,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13364,10 +13373,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13393,10 +13402,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>445</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13422,10 +13431,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -13451,10 +13460,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -13480,10 +13489,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -13509,10 +13518,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -13538,10 +13547,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -13567,10 +13576,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -13596,10 +13605,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -13625,10 +13634,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -13654,10 +13663,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -13683,10 +13692,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -13712,10 +13721,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -13735,10 +13744,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -13758,10 +13767,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -13781,7 +13790,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -13801,7 +13810,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -13871,10 +13880,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13900,10 +13909,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13929,10 +13938,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13958,10 +13967,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>464</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13987,10 +13996,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14016,10 +14025,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14045,10 +14054,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14068,10 +14077,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -14091,10 +14100,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -14114,10 +14123,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -14187,10 +14196,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14216,10 +14225,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14245,10 +14254,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14274,10 +14283,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14303,10 +14312,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14332,10 +14341,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14361,10 +14370,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14390,10 +14399,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14419,10 +14428,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14448,10 +14457,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14477,10 +14486,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14506,10 +14515,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14535,10 +14544,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -14558,10 +14567,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -14581,10 +14590,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -14604,10 +14613,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -14678,10 +14687,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14707,10 +14716,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14736,10 +14745,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14765,10 +14774,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>488</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14794,10 +14803,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14823,10 +14832,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14852,10 +14861,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14881,10 +14890,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14910,10 +14919,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14939,10 +14948,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14968,10 +14977,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14997,10 +15006,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -15026,10 +15035,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -15055,10 +15064,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -15084,10 +15093,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -15107,10 +15116,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -15130,10 +15139,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -15153,7 +15162,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -15173,7 +15182,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -15554,10 +15563,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -15583,10 +15592,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -15612,10 +15621,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -15641,10 +15650,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>507</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -15670,10 +15679,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -15699,10 +15708,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -15728,10 +15737,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -15757,10 +15766,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -15786,10 +15795,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -15815,10 +15824,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -15844,10 +15853,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -15873,10 +15882,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -15902,10 +15911,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -15925,10 +15934,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -15948,10 +15957,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -15971,10 +15980,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -16038,10 +16047,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16107,10 +16116,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D2" s="1">
         <v>45</v>
@@ -16133,10 +16142,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D3" s="1">
         <v>-45</v>
@@ -16159,10 +16168,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D4" s="1">
         <v>91</v>
@@ -16179,10 +16188,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D5" s="1">
         <v>-91</v>
@@ -16199,10 +16208,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D6" s="1">
         <v>45</v>
@@ -16219,10 +16228,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D7" s="1">
         <v>45</v>
@@ -16267,10 +16276,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>145</v>
@@ -16290,16 +16299,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F2" s="1">
         <v>50</v>
@@ -16319,16 +16328,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -16342,16 +16351,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F4" s="1">
         <v>101</v>
@@ -16409,10 +16418,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16432,10 +16441,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16455,10 +16464,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16478,10 +16487,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -16501,10 +16510,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
@@ -16524,10 +16533,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -16541,10 +16550,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
@@ -16608,10 +16617,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16631,10 +16640,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16654,10 +16663,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>534</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16671,10 +16680,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -16738,10 +16747,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16806,13 +16815,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -16832,13 +16841,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="E3" s="1">
         <v>30</v>
@@ -16858,13 +16867,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -16884,13 +16893,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -16910,19 +16919,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16930,19 +16939,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16950,19 +16959,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16970,19 +16979,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16990,19 +16999,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17010,19 +17019,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17030,19 +17039,19 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17050,19 +17059,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17070,19 +17079,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17090,19 +17099,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17110,19 +17119,19 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17130,19 +17139,19 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17150,19 +17159,19 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17170,19 +17179,19 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17190,19 +17199,19 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="E20" s="1">
         <v>50</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17210,19 +17219,19 @@
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="E21" s="1">
         <v>50</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17230,19 +17239,19 @@
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17250,19 +17259,19 @@
         <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E23" s="1">
         <v>50</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17270,19 +17279,19 @@
         <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="E24" s="1">
         <v>50</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17290,19 +17299,19 @@
         <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E25" s="1">
         <v>50</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17310,19 +17319,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E26" s="1">
         <v>50</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17330,19 +17339,19 @@
         <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E27" s="1">
         <v>50</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17350,19 +17359,19 @@
         <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="E28" s="1">
         <v>50</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17370,19 +17379,19 @@
         <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="E29" s="1">
         <v>50</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17390,19 +17399,19 @@
         <v>19</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E30" s="1">
         <v>101</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17410,19 +17419,19 @@
         <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="E31" s="1">
         <v>-1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
   </sheetData>
@@ -17482,10 +17491,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17511,10 +17520,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -17540,10 +17549,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -17569,10 +17578,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>595</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>592</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -17598,10 +17607,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -17627,10 +17636,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -17656,10 +17665,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -17685,10 +17694,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -17714,10 +17723,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -17743,10 +17752,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -17772,10 +17781,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -17801,10 +17810,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -17830,10 +17839,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -17853,10 +17862,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -17876,10 +17885,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -17899,10 +17908,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -17972,10 +17981,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18001,10 +18010,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -18030,10 +18039,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -18059,10 +18068,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>607</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18088,10 +18097,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18117,10 +18126,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18146,10 +18155,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18175,10 +18184,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -18204,10 +18213,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -18233,10 +18242,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -18262,10 +18271,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -18291,10 +18300,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -18320,10 +18329,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -18343,10 +18352,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -18366,10 +18375,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -18389,10 +18398,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -18558,10 +18567,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18587,10 +18596,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -18616,10 +18625,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -18645,10 +18654,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18674,10 +18683,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18703,10 +18712,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18732,10 +18741,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18755,10 +18764,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -18778,10 +18787,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -18801,10 +18810,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -18871,10 +18880,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18888,10 +18897,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -18905,10 +18914,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -18922,10 +18931,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -18939,10 +18948,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -18956,10 +18965,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -18973,10 +18982,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -19034,10 +19043,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -19096,16 +19105,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>34</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="24" activeTab="34"/>
+    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="24" activeTab="34"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="24" activeTab="34"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="24" activeTab="34"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2349" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2349" uniqueCount="633">
   <si>
     <t>ID</t>
   </si>
@@ -1169,25 +1169,31 @@
     <t>判读当前base坐标是否在点位上（不在点位超过±0.2mm）</t>
   </si>
   <si>
-    <t>[376.0, 213.1, 196.1, 89.99, 0.0, -31.99]</t>
+    <t>[378, 213.1, 196.1, 89.99, 0.0, -31.99]</t>
   </si>
   <si>
     <t>判读当前base坐标是否在点位上（不在点位欧拉角超过1°）</t>
   </si>
   <si>
-    <t>[375.0, 213.1, 196.1, 89.99, 1.2, -31.99]</t>
+    <t>[375.0, 213.1, 196.1, 89.99, 1.1, -31.99]</t>
   </si>
   <si>
     <t>[375.0, -213.1, 196.1, -89.99, 0.0, 32.0]</t>
   </si>
   <si>
+    <t>[378.0, -213.1, 196.1, -89.99, 0.0, 32.0]</t>
+  </si>
+  <si>
+    <t>[375.0, -213.1, 196.1, -89.99,2, 32.0]</t>
+  </si>
+  <si>
+    <t>设置mode超限</t>
+  </si>
+  <si>
     <t>[375.0, -214, 196.1, -89.99, 0.0, 32.0]</t>
   </si>
   <si>
     <t>[375.0, -213.1, 196.1, -92, 0.0, 32.0]</t>
-  </si>
-  <si>
-    <t>设置mode超限</t>
   </si>
   <si>
     <t>机械臂运动状态下查看是否在运动</t>
@@ -10368,6 +10374,9 @@
       </c>
     </row>
     <row r="10" ht="72" spans="1:8">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
       <c r="B10" s="1" t="s">
         <v>353</v>
       </c>
@@ -10388,6 +10397,9 @@
       </c>
     </row>
     <row r="11" ht="57.6" spans="1:8">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
       <c r="B11" s="1" t="s">
         <v>355</v>
       </c>
@@ -10408,6 +10420,9 @@
       </c>
     </row>
     <row r="12" ht="57.6" spans="1:8">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
       <c r="B12" s="1" t="s">
         <v>357</v>
       </c>
@@ -10429,7 +10444,7 @@
     </row>
     <row r="13" ht="28.8" spans="1:8">
       <c r="A13" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>362</v>
@@ -10438,7 +10453,7 @@
         <v>343</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E13" s="1">
         <v>-1</v>
@@ -10449,7 +10464,7 @@
     </row>
     <row r="14" ht="28.8" spans="1:8">
       <c r="A14" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>362</v>
@@ -10458,7 +10473,7 @@
         <v>343</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -10517,10 +10532,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -10537,10 +10552,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -10603,10 +10618,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10626,10 +10641,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10652,7 +10667,7 @@
         <v>362</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -10669,7 +10684,7 @@
         <v>362</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -10731,10 +10746,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -10757,10 +10772,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -10783,10 +10798,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>370</v>
       </c>
       <c r="D4" s="1">
         <v>151</v>
@@ -10803,10 +10818,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>370</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -10823,10 +10838,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D6" s="1">
         <v>201</v>
@@ -10843,10 +10858,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -10866,7 +10881,7 @@
         <v>362</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -10886,7 +10901,7 @@
         <v>362</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -10906,7 +10921,7 @@
         <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -10932,7 +10947,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -11000,10 +11015,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -11023,10 +11038,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -11049,7 +11064,7 @@
         <v>362</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -11066,7 +11081,7 @@
         <v>362</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -11224,10 +11239,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -11250,10 +11265,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -11276,10 +11291,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="D4" s="1">
         <v>201</v>
@@ -11296,10 +11311,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -11316,10 +11331,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D6" s="1">
         <v>401</v>
@@ -11336,10 +11351,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -11359,7 +11374,7 @@
         <v>362</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -11379,7 +11394,7 @@
         <v>362</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -11396,10 +11411,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -11422,10 +11437,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -11487,16 +11502,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>34</v>
@@ -11546,10 +11561,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -11610,16 +11625,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11674,16 +11689,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11738,16 +11753,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11802,16 +11817,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11849,13 +11864,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -11872,10 +11887,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -11901,10 +11916,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D3" s="1">
         <v>255</v>
@@ -11930,10 +11945,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -11959,10 +11974,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D5" s="1">
         <v>256</v>
@@ -12026,10 +12041,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -12090,10 +12105,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12113,10 +12128,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -12136,10 +12151,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -12153,10 +12168,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -12321,10 +12336,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12347,10 +12362,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12373,10 +12388,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>414</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12399,10 +12414,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12425,10 +12440,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12451,10 +12466,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12477,10 +12492,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12503,10 +12518,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -12523,10 +12538,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -12543,10 +12558,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -12563,10 +12578,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -12583,10 +12598,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -12595,10 +12610,10 @@
         <v>120</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -12653,17 +12668,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -12721,10 +12736,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12747,10 +12762,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12773,10 +12788,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>429</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12799,10 +12814,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12825,10 +12840,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12851,10 +12866,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12877,10 +12892,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12903,10 +12918,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -12923,10 +12938,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -12943,10 +12958,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -12963,10 +12978,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -12983,10 +12998,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -12995,10 +13010,10 @@
         <v>100</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -13053,19 +13068,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -13120,10 +13135,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E2" s="1">
         <v>50</v>
@@ -13184,10 +13199,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D2" s="1">
         <v>30</v>
@@ -13207,10 +13222,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D3" s="1">
         <v>301</v>
@@ -13224,10 +13239,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D4" s="1">
         <v>-301</v>
@@ -13241,10 +13256,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D5" s="1">
         <v>21</v>
@@ -13315,10 +13330,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13344,10 +13359,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13373,10 +13388,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>448</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13402,10 +13417,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13431,10 +13446,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -13460,10 +13475,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -13489,10 +13504,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -13518,10 +13533,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -13547,10 +13562,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -13576,10 +13591,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -13605,10 +13620,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -13634,10 +13649,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -13663,10 +13678,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -13692,10 +13707,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -13721,10 +13736,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -13744,10 +13759,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -13767,10 +13782,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -13790,7 +13805,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -13810,7 +13825,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -13880,10 +13895,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13909,10 +13924,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13938,10 +13953,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>467</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13967,10 +13982,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13996,10 +14011,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14025,10 +14040,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14054,10 +14069,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14077,10 +14092,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -14100,10 +14115,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -14123,10 +14138,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -14196,10 +14211,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14225,10 +14240,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14254,10 +14269,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>476</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14283,10 +14298,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14312,10 +14327,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14341,10 +14356,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14370,10 +14385,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14399,10 +14414,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14428,10 +14443,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14457,10 +14472,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14486,10 +14501,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14515,10 +14530,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14544,10 +14559,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -14567,10 +14582,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -14590,10 +14605,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -14613,10 +14628,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -14687,10 +14702,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14716,10 +14731,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14745,10 +14760,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>491</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14774,10 +14789,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14803,10 +14818,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14832,10 +14847,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14861,10 +14876,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14890,10 +14905,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14919,10 +14934,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14948,10 +14963,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14977,10 +14992,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -15006,10 +15021,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -15035,10 +15050,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -15064,10 +15079,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -15093,10 +15108,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -15116,10 +15131,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -15139,10 +15154,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -15162,7 +15177,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -15182,7 +15197,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -15563,10 +15578,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -15592,10 +15607,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -15621,10 +15636,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>510</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -15650,10 +15665,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -15679,10 +15694,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -15708,10 +15723,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -15737,10 +15752,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -15766,10 +15781,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -15795,10 +15810,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -15824,10 +15839,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -15853,10 +15868,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -15882,10 +15897,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -15911,10 +15926,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -15934,10 +15949,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -15957,10 +15972,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -15980,10 +15995,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -16047,10 +16062,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16116,10 +16131,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D2" s="1">
         <v>45</v>
@@ -16142,10 +16157,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D3" s="1">
         <v>-45</v>
@@ -16168,10 +16183,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D4" s="1">
         <v>91</v>
@@ -16188,10 +16203,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D5" s="1">
         <v>-91</v>
@@ -16208,10 +16223,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>529</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>527</v>
       </c>
       <c r="D6" s="1">
         <v>45</v>
@@ -16228,10 +16243,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>529</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>527</v>
       </c>
       <c r="D7" s="1">
         <v>45</v>
@@ -16276,10 +16291,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>145</v>
@@ -16299,16 +16314,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F2" s="1">
         <v>50</v>
@@ -16328,16 +16343,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -16351,16 +16366,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F4" s="1">
         <v>101</v>
@@ -16418,10 +16433,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16441,10 +16456,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16464,10 +16479,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16487,10 +16502,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -16510,10 +16525,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
@@ -16533,10 +16548,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -16550,10 +16565,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
@@ -16617,10 +16632,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>537</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16640,10 +16655,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>537</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16663,10 +16678,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16680,10 +16695,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -16747,10 +16762,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16815,13 +16830,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -16841,13 +16856,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>543</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E3" s="1">
         <v>30</v>
@@ -16867,13 +16882,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -16893,13 +16908,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -16919,19 +16934,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16939,19 +16954,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16959,19 +16974,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16979,19 +16994,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16999,19 +17014,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17019,19 +17034,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17039,19 +17054,19 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17059,19 +17074,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17079,19 +17094,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17099,19 +17114,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17119,19 +17134,19 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17139,19 +17154,19 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17159,19 +17174,19 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17179,19 +17194,19 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17199,19 +17214,19 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E20" s="1">
         <v>50</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17219,19 +17234,19 @@
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E21" s="1">
         <v>50</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17239,19 +17254,19 @@
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17259,19 +17274,19 @@
         <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E23" s="1">
         <v>50</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17279,19 +17294,19 @@
         <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E24" s="1">
         <v>50</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17299,19 +17314,19 @@
         <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E25" s="1">
         <v>50</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17319,19 +17334,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E26" s="1">
         <v>50</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17339,19 +17354,19 @@
         <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E27" s="1">
         <v>50</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17359,19 +17374,19 @@
         <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E28" s="1">
         <v>50</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17379,19 +17394,19 @@
         <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E29" s="1">
         <v>50</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17399,19 +17414,19 @@
         <v>19</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E30" s="1">
         <v>101</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17419,19 +17434,19 @@
         <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E31" s="1">
         <v>-1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>
@@ -17491,10 +17506,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17520,10 +17535,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -17549,10 +17564,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>597</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>595</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -17578,10 +17593,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -17607,10 +17622,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -17636,10 +17651,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -17665,10 +17680,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -17694,10 +17709,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -17723,10 +17738,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -17752,10 +17767,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -17781,10 +17796,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -17810,10 +17825,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -17839,10 +17854,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -17862,10 +17877,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -17885,10 +17900,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -17908,10 +17923,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -17981,10 +17996,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18010,10 +18025,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -18039,10 +18054,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>612</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>610</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -18068,10 +18083,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18097,10 +18112,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18126,10 +18141,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18155,10 +18170,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18184,10 +18199,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -18213,10 +18228,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -18242,10 +18257,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -18271,10 +18286,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -18300,10 +18315,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -18329,10 +18344,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -18352,10 +18367,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -18375,10 +18390,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -18398,10 +18413,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -18567,10 +18582,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18596,10 +18611,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -18625,10 +18640,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -18654,10 +18669,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18683,10 +18698,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18712,10 +18727,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18741,10 +18756,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18764,10 +18779,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -18787,10 +18802,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -18810,10 +18825,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -18880,10 +18895,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18897,10 +18912,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -18914,10 +18929,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -18931,10 +18946,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -18948,10 +18963,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -18965,10 +18980,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -18982,10 +18997,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -19043,10 +19058,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -19105,16 +19120,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>34</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -1178,7 +1178,7 @@
     <t>[375.0, 213.1, 196.1, 89.99, 1.1, -31.99]</t>
   </si>
   <si>
-    <t>[375.0, -213.1, 196.1, -89.99, 0.0, 32.0]</t>
+    <t>[375.0, -213.1, 196.1, -89.99, 2, 32.0]</t>
   </si>
   <si>
     <t>[378.0, -213.1, 196.1, -89.99, 0.0, 32.0]</t>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="24" activeTab="34"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="51" activeTab="55"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -13345,10 +13345,10 @@
         <v>10</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>34</v>
@@ -13374,10 +13374,10 @@
         <v>10</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>34</v>
@@ -13403,10 +13403,10 @@
         <v>50</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>34</v>
@@ -13432,10 +13432,10 @@
         <v>50</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>34</v>
@@ -13461,10 +13461,10 @@
         <v>90</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>34</v>
@@ -13490,10 +13490,10 @@
         <v>50</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>34</v>
@@ -13519,10 +13519,10 @@
         <v>50</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>34</v>
@@ -13548,10 +13548,10 @@
         <v>50</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>34</v>
@@ -13577,10 +13577,10 @@
         <v>50</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>34</v>
@@ -13606,10 +13606,10 @@
         <v>50</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>34</v>
@@ -13635,10 +13635,10 @@
         <v>50</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>34</v>
@@ -13664,10 +13664,10 @@
         <v>50</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>34</v>
@@ -13693,10 +13693,10 @@
         <v>50</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>34</v>
@@ -13722,10 +13722,10 @@
         <v>50</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>34</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="51" activeTab="55"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="51" activeTab="56"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -13910,10 +13910,10 @@
         <v>50</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>34</v>
@@ -13939,10 +13939,10 @@
         <v>50</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>34</v>
@@ -13968,10 +13968,10 @@
         <v>60</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>34</v>
@@ -13997,10 +13997,10 @@
         <v>60</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>34</v>
@@ -14026,10 +14026,10 @@
         <v>30</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>34</v>
@@ -14055,10 +14055,10 @@
         <v>30</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>34</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="51" activeTab="56"/>
+    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="52" activeTab="57"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -14226,10 +14226,10 @@
         <v>50</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>34</v>
@@ -14255,10 +14255,10 @@
         <v>50</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>34</v>
@@ -14284,10 +14284,10 @@
         <v>60</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>307</v>
@@ -14313,10 +14313,10 @@
         <v>60</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>307</v>
@@ -14342,10 +14342,10 @@
         <v>30</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>307</v>
@@ -14371,10 +14371,10 @@
         <v>30</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>307</v>
@@ -14400,10 +14400,10 @@
         <v>50</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>34</v>
@@ -14429,10 +14429,10 @@
         <v>50</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>34</v>
@@ -14458,10 +14458,10 @@
         <v>60</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>307</v>
@@ -14487,10 +14487,10 @@
         <v>60</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>307</v>
@@ -14516,10 +14516,10 @@
         <v>30</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>307</v>
@@ -14545,10 +14545,10 @@
         <v>30</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>307</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="52" activeTab="57"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="53" activeTab="58"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2349" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2372" uniqueCount="634">
   <si>
     <t>ID</t>
   </si>
@@ -1632,6 +1632,9 @@
   </si>
   <si>
     <t>设置关节jog_increment_angle运动，关节超限</t>
+  </si>
+  <si>
+    <t>设置关节jog_increment_angle运动，增量超限</t>
   </si>
   <si>
     <t>正确设置x轴jog_increment_coord正向运动</t>
@@ -14655,7 +14658,7 @@
 <file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
@@ -15179,6 +15182,9 @@
       <c r="B19" s="1" t="s">
         <v>510</v>
       </c>
+      <c r="C19" s="1" t="s">
+        <v>493</v>
+      </c>
       <c r="D19" s="1">
         <v>8</v>
       </c>
@@ -15199,6 +15205,9 @@
       <c r="B20" s="1" t="s">
         <v>510</v>
       </c>
+      <c r="C20" s="1" t="s">
+        <v>493</v>
+      </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
@@ -15209,6 +15218,167 @@
         <v>50</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" ht="57.6" spans="1:9">
+      <c r="A21" s="2">
+        <v>26</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>331</v>
+      </c>
+      <c r="F21" s="1">
+        <v>50</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" ht="57.6" spans="1:9">
+      <c r="A22" s="2">
+        <v>27</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1">
+        <v>171</v>
+      </c>
+      <c r="F22" s="1">
+        <v>50</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" ht="57.6" spans="1:9">
+      <c r="A23" s="2">
+        <v>28</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3</v>
+      </c>
+      <c r="E23" s="1">
+        <v>331</v>
+      </c>
+      <c r="F23" s="1">
+        <v>50</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" ht="57.6" spans="1:9">
+      <c r="A24" s="2">
+        <v>29</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D24" s="1">
+        <v>4</v>
+      </c>
+      <c r="E24" s="1">
+        <v>167</v>
+      </c>
+      <c r="F24" s="1">
+        <v>50</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" ht="57.6" spans="1:9">
+      <c r="A25" s="2">
+        <v>30</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D25" s="1">
+        <v>5</v>
+      </c>
+      <c r="E25" s="1">
+        <v>331</v>
+      </c>
+      <c r="F25" s="1">
+        <v>50</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" ht="57.6" spans="1:9">
+      <c r="A26" s="2">
+        <v>31</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D26" s="1">
+        <v>6</v>
+      </c>
+      <c r="E26" s="1">
+        <v>331</v>
+      </c>
+      <c r="F26" s="1">
+        <v>50</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" ht="57.6" spans="1:9">
+      <c r="A27" s="2">
+        <v>32</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D27" s="1">
+        <v>7</v>
+      </c>
+      <c r="E27" s="1">
+        <v>331</v>
+      </c>
+      <c r="F27" s="1">
+        <v>50</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -15578,10 +15748,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -15607,10 +15777,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>512</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -15636,10 +15806,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -15665,10 +15835,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -15694,10 +15864,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -15723,10 +15893,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -15752,10 +15922,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -15781,10 +15951,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -15810,10 +15980,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -15839,10 +16009,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -15868,10 +16038,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -15897,10 +16067,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -15926,10 +16096,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -15949,10 +16119,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -15972,10 +16142,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -15995,10 +16165,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -16062,10 +16232,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16131,10 +16301,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D2" s="1">
         <v>45</v>
@@ -16157,10 +16327,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D3" s="1">
         <v>-45</v>
@@ -16183,10 +16353,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>530</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>529</v>
       </c>
       <c r="D4" s="1">
         <v>91</v>
@@ -16203,10 +16373,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>530</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>529</v>
       </c>
       <c r="D5" s="1">
         <v>-91</v>
@@ -16223,10 +16393,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D6" s="1">
         <v>45</v>
@@ -16243,10 +16413,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D7" s="1">
         <v>45</v>
@@ -16291,10 +16461,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>145</v>
@@ -16314,16 +16484,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F2" s="1">
         <v>50</v>
@@ -16343,16 +16513,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -16366,16 +16536,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F4" s="1">
         <v>101</v>
@@ -16433,10 +16603,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16456,10 +16626,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16479,10 +16649,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16502,10 +16672,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -16525,10 +16695,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
@@ -16548,10 +16718,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>540</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>539</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -16568,7 +16738,7 @@
         <v>425</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
@@ -16632,10 +16802,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16655,10 +16825,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16678,10 +16848,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16698,7 +16868,7 @@
         <v>425</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -16762,10 +16932,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16830,13 +17000,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -16856,13 +17026,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E3" s="1">
         <v>30</v>
@@ -16882,13 +17052,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -16908,13 +17078,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -16934,19 +17104,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16954,19 +17124,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16974,19 +17144,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -16994,19 +17164,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17014,19 +17184,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17034,19 +17204,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17054,19 +17224,19 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17074,19 +17244,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17094,19 +17264,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17114,19 +17284,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17134,19 +17304,19 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17154,19 +17324,19 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17174,19 +17344,19 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17194,19 +17364,19 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17214,19 +17384,19 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E20" s="1">
         <v>50</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17234,19 +17404,19 @@
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E21" s="1">
         <v>50</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17254,19 +17424,19 @@
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17274,19 +17444,19 @@
         <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E23" s="1">
         <v>50</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17294,19 +17464,19 @@
         <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E24" s="1">
         <v>50</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17314,19 +17484,19 @@
         <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E25" s="1">
         <v>50</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17334,19 +17504,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E26" s="1">
         <v>50</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17354,19 +17524,19 @@
         <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E27" s="1">
         <v>50</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17374,19 +17544,19 @@
         <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E28" s="1">
         <v>50</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17394,19 +17564,19 @@
         <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E29" s="1">
         <v>50</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17414,19 +17584,19 @@
         <v>19</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E30" s="1">
         <v>101</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17434,19 +17604,19 @@
         <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E31" s="1">
         <v>-1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>
@@ -17506,10 +17676,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17535,10 +17705,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>598</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>597</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -17564,10 +17734,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -17593,10 +17763,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -17622,10 +17792,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -17651,10 +17821,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -17680,10 +17850,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -17709,10 +17879,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -17738,10 +17908,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -17767,10 +17937,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -17796,10 +17966,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -17825,10 +17995,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -17854,10 +18024,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -17877,10 +18047,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -17900,10 +18070,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -17923,10 +18093,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -17996,10 +18166,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18025,10 +18195,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>613</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>612</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -18054,10 +18224,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -18083,10 +18253,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18112,10 +18282,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18141,10 +18311,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18170,10 +18340,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18199,10 +18369,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -18228,10 +18398,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -18257,10 +18427,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -18286,10 +18456,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -18315,10 +18485,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -18344,10 +18514,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -18367,10 +18537,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -18390,10 +18560,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -18413,10 +18583,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -18585,7 +18755,7 @@
         <v>468</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18614,7 +18784,7 @@
         <v>470</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -18643,7 +18813,7 @@
         <v>471</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -18672,7 +18842,7 @@
         <v>472</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18701,7 +18871,7 @@
         <v>473</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18730,7 +18900,7 @@
         <v>474</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18759,7 +18929,7 @@
         <v>475</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18782,7 +18952,7 @@
         <v>475</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -18805,7 +18975,7 @@
         <v>476</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -18828,7 +18998,7 @@
         <v>476</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -18895,10 +19065,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18912,10 +19082,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -18929,10 +19099,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -18946,10 +19116,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -18963,10 +19133,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -18980,10 +19150,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -18997,10 +19167,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -19058,10 +19228,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -19120,16 +19290,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>34</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="53" activeTab="58"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="19" activeTab="21"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -4378,10 +4378,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>34</v>
@@ -4424,10 +4424,10 @@
         <v>6</v>
       </c>
       <c r="E7" s="1">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="F7" s="1">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>34</v>
@@ -4447,10 +4447,10 @@
         <v>7</v>
       </c>
       <c r="E8" s="1">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="F8" s="1">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>34</v>
@@ -4965,6 +4965,9 @@
       <c r="D9" s="1">
         <v>8</v>
       </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
       <c r="H9" s="1" t="s">
         <v>42</v>
       </c>
@@ -4980,6 +4983,9 @@
         <v>122</v>
       </c>
       <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2372" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2402" uniqueCount="646">
   <si>
     <t>ID</t>
   </si>
@@ -491,7 +491,25 @@
     <t>设置关节软件限位最大值关节（超限）</t>
   </si>
   <si>
-    <t>设置关节软件限位最大值（超限）</t>
+    <t>设置关节软件限位最大值1关节（超限）</t>
+  </si>
+  <si>
+    <t>设置关节软件限位最大值2关节（超限）</t>
+  </si>
+  <si>
+    <t>设置关节软件限位最大值3关节（超限）</t>
+  </si>
+  <si>
+    <t>设置关节软件限位最大值4关节（超限）</t>
+  </si>
+  <si>
+    <t>设置关节软件限位最大值5关节（超限）</t>
+  </si>
+  <si>
+    <t>设置关节软件限位最大值6关节（超限）</t>
+  </si>
+  <si>
+    <t>设置关节软件限位最大值7关节（超限）</t>
   </si>
   <si>
     <t>正确设置1关节软件限位最小值</t>
@@ -521,7 +539,25 @@
     <t>设置关节软件限位最小值关节（超限）</t>
   </si>
   <si>
-    <t>设置关节软件限位最小值（超限）</t>
+    <t>设置关节软件限位最小值1关节（超限）</t>
+  </si>
+  <si>
+    <t>设置关节软件限位最小值2关节（超限）</t>
+  </si>
+  <si>
+    <t>设置关节软件限位最小值3关节（超限）</t>
+  </si>
+  <si>
+    <t>设置关节软件限位最小值4关节（超限）</t>
+  </si>
+  <si>
+    <t>设置关节软件限位最小值5关节（超限）</t>
+  </si>
+  <si>
+    <t>设置关节软件限位最小值6关节（超限）</t>
+  </si>
+  <si>
+    <t>设置关节软件限位最小值7关节（超限）</t>
   </si>
   <si>
     <t>正确获取机械臂全角度</t>
@@ -4735,7 +4771,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
@@ -5006,36 +5042,130 @@
         <v>1</v>
       </c>
       <c r="E11" s="1">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" ht="28.8" spans="1:8">
+    <row r="12" ht="43.2" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>122</v>
       </c>
       <c r="D12" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="1">
-        <v>160</v>
-      </c>
-      <c r="F12" s="1">
-        <v>165</v>
-      </c>
-      <c r="G12" s="1">
-        <v>165</v>
+        <v>121</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" ht="43.2" spans="1:8">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" s="1">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1">
+        <v>166</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" ht="43.2" spans="1:8">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" s="1">
+        <v>4</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" ht="43.2" spans="1:8">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" s="1">
+        <v>5</v>
+      </c>
+      <c r="E15" s="1">
+        <v>166</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" ht="43.2" spans="1:8">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" s="1">
+        <v>6</v>
+      </c>
+      <c r="E16" s="1">
+        <v>256</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" ht="43.2" spans="1:8">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" s="1">
+        <v>7</v>
+      </c>
+      <c r="E17" s="1">
+        <v>166</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -5047,7 +5177,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
@@ -5087,10 +5217,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -5113,10 +5243,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -5139,10 +5269,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -5165,10 +5295,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -5191,10 +5321,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -5217,10 +5347,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -5243,10 +5373,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -5269,13 +5399,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D9" s="1">
         <v>8</v>
+      </c>
+      <c r="E9" s="1">
+        <v>-160</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>42</v>
@@ -5286,13 +5419,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>-160</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>42</v>
@@ -5303,45 +5439,151 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
       </c>
       <c r="E11" s="1">
-        <v>-170</v>
+        <v>-166</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" ht="28.8" spans="1:8">
+    <row r="12" customFormat="1" ht="43.2" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>44</v>
+        <v>147</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="D12" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="1">
-        <v>-160</v>
-      </c>
-      <c r="F12" s="1">
-        <v>-165</v>
-      </c>
-      <c r="G12" s="1">
-        <v>-165</v>
-      </c>
+        <v>-51</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" s="1">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1">
+        <v>-166</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" s="1">
+        <v>4</v>
+      </c>
+      <c r="E14" s="1">
+        <v>-166</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D15" s="1">
+        <v>5</v>
+      </c>
+      <c r="E15" s="1">
+        <v>-166</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="1">
+        <v>6</v>
+      </c>
+      <c r="E16" s="1">
+        <v>-76</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D17" s="1">
+        <v>7</v>
+      </c>
+      <c r="E17" s="1">
+        <v>-166</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -5393,17 +5635,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -5441,10 +5683,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -5461,13 +5703,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="E2" s="1">
         <v>10</v>
@@ -5487,13 +5729,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="E3" s="1">
         <v>50</v>
@@ -5513,13 +5755,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="E4" s="1">
         <v>90</v>
@@ -5539,13 +5781,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="E5" s="1">
         <v>50</v>
@@ -5554,7 +5796,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" customFormat="1" ht="28.8" spans="1:8">
@@ -5562,13 +5804,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="E6" s="1">
         <v>30</v>
@@ -5577,7 +5819,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="28.8" spans="1:8">
@@ -5585,13 +5827,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="E7" s="1">
         <v>10</v>
@@ -5600,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" customFormat="1" ht="28.8" spans="1:8">
@@ -5608,13 +5850,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="E8" s="1">
         <v>70</v>
@@ -5623,7 +5865,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" customFormat="1" ht="28.8" spans="1:8">
@@ -5631,13 +5873,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E9" s="1">
         <v>60</v>
@@ -5646,7 +5888,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" customFormat="1" ht="28.8" spans="1:8">
@@ -5654,13 +5896,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="E10" s="1">
         <v>90</v>
@@ -5669,7 +5911,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" customFormat="1" ht="28.8" spans="1:8">
@@ -5677,13 +5919,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
@@ -5692,7 +5934,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" customFormat="1" ht="28.8" spans="1:8">
@@ -5700,13 +5942,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="E12" s="1">
         <v>30</v>
@@ -5715,7 +5957,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" customFormat="1" ht="28.8" spans="1:8">
@@ -5723,13 +5965,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="E13" s="1">
         <v>10</v>
@@ -5738,7 +5980,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="28.8" spans="1:8">
@@ -5746,13 +5988,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="E14" s="1">
         <v>70</v>
@@ -5761,7 +6003,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" customFormat="1" ht="28.8" spans="1:8">
@@ -5769,13 +6011,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="E15" s="1">
         <v>60</v>
@@ -5784,7 +6026,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" customFormat="1" ht="28.8" spans="1:8">
@@ -5792,13 +6034,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="E16" s="1">
         <v>90</v>
@@ -5807,7 +6049,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" customFormat="1" ht="28.8" spans="1:8">
@@ -5815,13 +6057,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="E17" s="1">
         <v>70</v>
@@ -5830,7 +6072,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" customFormat="1" ht="28.8" spans="1:8">
@@ -5838,13 +6080,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="E18" s="1">
         <v>60</v>
@@ -5853,7 +6095,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" customFormat="1" ht="28.8" spans="1:8">
@@ -5861,13 +6103,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
@@ -5876,7 +6118,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" customFormat="1" ht="28.8" spans="1:8">
@@ -5884,13 +6126,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="E20" s="1">
         <v>30</v>
@@ -5899,7 +6141,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" customFormat="1" ht="28.8" spans="1:8">
@@ -5907,13 +6149,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="E21" s="1">
         <v>10</v>
@@ -5922,7 +6164,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" customFormat="1" ht="28.8" spans="1:8">
@@ -5930,13 +6172,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="E22" s="1">
         <v>70</v>
@@ -5945,7 +6187,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" customFormat="1" ht="28.8" spans="1:8">
@@ -5953,13 +6195,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E23" s="1">
         <v>60</v>
@@ -5968,7 +6210,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" customFormat="1" ht="28.8" spans="1:8">
@@ -5976,13 +6218,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="E24" s="1">
         <v>90</v>
@@ -5991,7 +6233,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" customFormat="1" ht="28.8" spans="1:8">
@@ -5999,13 +6241,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E25" s="1">
         <v>50</v>
@@ -6014,7 +6256,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" customFormat="1" ht="28.8" spans="1:8">
@@ -6022,13 +6264,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="E26" s="1">
         <v>30</v>
@@ -6037,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" customFormat="1" ht="28.8" spans="1:8">
@@ -6045,13 +6287,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="E27" s="1">
         <v>10</v>
@@ -6060,7 +6302,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" customFormat="1" ht="28.8" spans="1:8">
@@ -6068,13 +6310,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="E28" s="1">
         <v>70</v>
@@ -6083,7 +6325,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" customFormat="1" ht="28.8" spans="1:8">
@@ -6091,13 +6333,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="E29" s="1">
         <v>60</v>
@@ -6106,7 +6348,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" customFormat="1" ht="28.8" spans="1:8">
@@ -6114,13 +6356,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="E30" s="1">
         <v>90</v>
@@ -6129,7 +6371,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" customFormat="1" ht="28.8" spans="1:8">
@@ -6137,13 +6379,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="E31" s="1">
         <v>70</v>
@@ -6152,7 +6394,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" customFormat="1" ht="28.8" spans="1:8">
@@ -6160,13 +6402,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="E32" s="1">
         <v>60</v>
@@ -6175,7 +6417,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" customFormat="1" ht="43.2" spans="1:8">
@@ -6183,13 +6425,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E33" s="1">
         <v>-1</v>
@@ -6203,13 +6445,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="E34" s="1">
         <v>0</v>
@@ -6223,13 +6465,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="E35" s="1">
         <v>101</v>
@@ -6243,13 +6485,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="E36" s="1">
         <v>50</v>
@@ -6263,13 +6505,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="E37" s="1">
         <v>50</v>
@@ -6283,13 +6525,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="E38" s="1">
         <v>50</v>
@@ -6303,13 +6545,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="E39" s="1">
         <v>50</v>
@@ -6323,13 +6565,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="E40" s="1">
         <v>50</v>
@@ -6343,13 +6585,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="E41" s="1">
         <v>50</v>
@@ -6363,13 +6605,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E42" s="1">
         <v>50</v>
@@ -6383,13 +6625,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="E43" s="1">
         <v>50</v>
@@ -6403,13 +6645,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="E44" s="1">
         <v>50</v>
@@ -6423,13 +6665,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="E45" s="1">
         <v>50</v>
@@ -6443,13 +6685,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E46" s="1">
         <v>50</v>
@@ -6463,13 +6705,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="E47" s="1">
         <v>50</v>
@@ -6483,13 +6725,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="E48" s="1">
         <v>50</v>
@@ -6503,13 +6745,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="E49" s="1">
         <v>50</v>
@@ -6547,7 +6789,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -6564,10 +6806,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -6587,10 +6829,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -6610,10 +6852,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -6633,10 +6875,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -6656,10 +6898,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -6679,10 +6921,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -6702,10 +6944,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -6725,10 +6967,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="D9" s="1">
         <v>8</v>
@@ -6742,10 +6984,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -6787,13 +7029,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>4</v>
@@ -6810,10 +7052,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -6839,10 +7081,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
@@ -6868,10 +7110,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -6897,10 +7139,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -6916,7 +7158,7 @@
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" customFormat="1" ht="28.8" spans="1:9">
@@ -6924,10 +7166,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -6943,7 +7185,7 @@
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="28.8" spans="1:9">
@@ -6951,10 +7193,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D7" s="2">
         <v>2</v>
@@ -6970,7 +7212,7 @@
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" customFormat="1" ht="28.8" spans="1:9">
@@ -6978,10 +7220,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -6997,7 +7239,7 @@
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" customFormat="1" ht="28.8" spans="1:9">
@@ -7005,10 +7247,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D9" s="2">
         <v>3</v>
@@ -7024,7 +7266,7 @@
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" customFormat="1" ht="28.8" spans="1:9">
@@ -7032,10 +7274,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D10" s="2">
         <v>3</v>
@@ -7051,7 +7293,7 @@
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" customFormat="1" ht="28.8" spans="1:9">
@@ -7059,10 +7301,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D11" s="2">
         <v>4</v>
@@ -7078,7 +7320,7 @@
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" customFormat="1" ht="28.8" spans="1:9">
@@ -7086,10 +7328,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D12" s="2">
         <v>4</v>
@@ -7105,7 +7347,7 @@
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" customFormat="1" ht="28.8" spans="1:9">
@@ -7113,10 +7355,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D13" s="2">
         <v>5</v>
@@ -7132,7 +7374,7 @@
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="28.8" spans="1:9">
@@ -7140,10 +7382,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D14" s="2">
         <v>5</v>
@@ -7159,7 +7401,7 @@
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" customFormat="1" ht="28.8" spans="1:9">
@@ -7167,10 +7409,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D15" s="2">
         <v>6</v>
@@ -7186,7 +7428,7 @@
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" customFormat="1" ht="28.8" spans="1:9">
@@ -7194,10 +7436,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D16" s="2">
         <v>6</v>
@@ -7213,7 +7455,7 @@
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" customFormat="1" ht="28.8" spans="1:9">
@@ -7221,10 +7463,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D17" s="2">
         <v>7</v>
@@ -7240,7 +7482,7 @@
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" customFormat="1" ht="28.8" spans="1:9">
@@ -7248,10 +7490,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D18" s="2">
         <v>7</v>
@@ -7267,7 +7509,7 @@
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" customFormat="1" ht="28.8" spans="1:9">
@@ -7275,10 +7517,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D19" s="2">
         <v>1</v>
@@ -7294,7 +7536,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" customFormat="1" ht="28.8" spans="1:9">
@@ -7302,10 +7544,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D20" s="2">
         <v>1</v>
@@ -7321,7 +7563,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" customFormat="1" ht="28.8" spans="1:9">
@@ -7329,10 +7571,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D21" s="2">
         <v>2</v>
@@ -7348,7 +7590,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" customFormat="1" ht="28.8" spans="1:9">
@@ -7356,10 +7598,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D22" s="2">
         <v>2</v>
@@ -7375,7 +7617,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" customFormat="1" ht="28.8" spans="1:9">
@@ -7383,10 +7625,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D23" s="2">
         <v>3</v>
@@ -7402,7 +7644,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" customFormat="1" ht="28.8" spans="1:9">
@@ -7410,10 +7652,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D24" s="2">
         <v>3</v>
@@ -7429,7 +7671,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" customFormat="1" ht="28.8" spans="1:9">
@@ -7437,10 +7679,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D25" s="2">
         <v>4</v>
@@ -7456,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" customFormat="1" ht="28.8" spans="1:9">
@@ -7464,10 +7706,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D26" s="2">
         <v>4</v>
@@ -7483,7 +7725,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" customFormat="1" ht="28.8" spans="1:9">
@@ -7491,10 +7733,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D27" s="2">
         <v>5</v>
@@ -7510,7 +7752,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" customFormat="1" ht="28.8" spans="1:9">
@@ -7518,10 +7760,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D28" s="2">
         <v>5</v>
@@ -7537,7 +7779,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" customFormat="1" ht="28.8" spans="1:9">
@@ -7545,10 +7787,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D29" s="2">
         <v>6</v>
@@ -7564,7 +7806,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" customFormat="1" ht="28.8" spans="1:9">
@@ -7572,10 +7814,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D30" s="2">
         <v>6</v>
@@ -7591,7 +7833,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" customFormat="1" ht="28.8" spans="1:9">
@@ -7599,10 +7841,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D31" s="2">
         <v>7</v>
@@ -7618,7 +7860,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" customFormat="1" ht="28.8" spans="1:9">
@@ -7626,10 +7868,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D32" s="2">
         <v>7</v>
@@ -7645,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" customFormat="1" ht="28.8" spans="1:9">
@@ -7653,10 +7895,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D33" s="2">
         <v>11</v>
@@ -7672,7 +7914,7 @@
         <v>-2</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" customFormat="1" ht="28.8" spans="1:9">
@@ -7680,10 +7922,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D34" s="2">
         <v>11</v>
@@ -7699,7 +7941,7 @@
         <v>-2</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="35" customFormat="1" ht="28.8" spans="1:9">
@@ -7707,10 +7949,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D35" s="2">
         <v>12</v>
@@ -7726,7 +7968,7 @@
         <v>-2</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" customFormat="1" ht="28.8" spans="1:9">
@@ -7734,10 +7976,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D36" s="2">
         <v>12</v>
@@ -7753,7 +7995,7 @@
         <v>-2</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="37" customFormat="1" ht="28.8" spans="1:9">
@@ -7761,10 +8003,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D37" s="2">
         <v>13</v>
@@ -7780,7 +8022,7 @@
         <v>-2</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" customFormat="1" ht="28.8" spans="1:9">
@@ -7788,10 +8030,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D38" s="2">
         <v>13</v>
@@ -7807,7 +8049,7 @@
         <v>-2</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" customFormat="1" ht="43.2" spans="1:9">
@@ -7815,10 +8057,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D39" s="2">
         <v>1</v>
@@ -7840,10 +8082,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D40" s="2">
         <v>2</v>
@@ -7865,10 +8107,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D41" s="2">
         <v>3</v>
@@ -7890,10 +8132,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="D42" s="2">
         <v>1</v>
@@ -7915,10 +8157,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D43" s="2">
         <v>1</v>
@@ -7940,10 +8182,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D44" s="2">
         <v>2</v>
@@ -7965,10 +8207,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D45" s="2">
         <v>2</v>
@@ -7990,10 +8232,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D46" s="2">
         <v>3</v>
@@ -8015,10 +8257,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D47" s="2">
         <v>3</v>
@@ -8040,10 +8282,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D48" s="2">
         <v>4</v>
@@ -8065,10 +8307,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D49" s="2">
         <v>4</v>
@@ -8090,10 +8332,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D50" s="2">
         <v>5</v>
@@ -8115,10 +8357,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D51" s="2">
         <v>5</v>
@@ -8140,10 +8382,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D52" s="2">
         <v>6</v>
@@ -8165,10 +8407,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D53" s="2">
         <v>6</v>
@@ -8190,10 +8432,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D54" s="2">
         <v>7</v>
@@ -8215,10 +8457,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D55" s="2">
         <v>7</v>
@@ -8240,10 +8482,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D56" s="4">
         <v>11</v>
@@ -8263,10 +8505,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D57" s="4">
         <v>11</v>
@@ -8286,10 +8528,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D58" s="4">
         <v>12</v>
@@ -8309,10 +8551,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D59" s="4">
         <v>12</v>
@@ -8332,10 +8574,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D60" s="4">
         <v>13</v>
@@ -8355,10 +8597,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D61" s="4">
         <v>13</v>
@@ -8421,19 +8663,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -8444,19 +8686,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>34</v>
@@ -8497,7 +8739,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -8514,13 +8756,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -8540,13 +8782,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E3" s="1">
         <v>50</v>
@@ -8566,13 +8808,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -8592,13 +8834,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -8618,13 +8860,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
@@ -8638,13 +8880,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
@@ -8658,19 +8900,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" ht="28.8" spans="1:8">
@@ -8678,19 +8920,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="D9" s="1" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" ht="28.8" spans="1:8">
@@ -8698,19 +8940,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="1:8">
@@ -8718,19 +8960,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" ht="28.8" spans="1:8">
@@ -8738,13 +8980,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
@@ -8758,13 +9000,13 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
@@ -8778,13 +9020,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
@@ -8798,13 +9040,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
@@ -8818,13 +9060,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
@@ -8838,13 +9080,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
@@ -8858,13 +9100,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
@@ -8878,13 +9120,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
@@ -8898,13 +9140,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E20" s="1">
         <v>101</v>
@@ -8918,13 +9160,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
@@ -9058,13 +9300,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -9081,10 +9323,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -9110,10 +9352,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -9131,7 +9373,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -9139,10 +9381,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -9160,7 +9402,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -9168,10 +9410,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -9189,7 +9431,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -9197,10 +9439,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -9218,7 +9460,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -9226,10 +9468,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -9247,7 +9489,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" ht="28.8" spans="1:9">
@@ -9255,10 +9497,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -9278,10 +9520,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -9301,10 +9543,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
@@ -9316,7 +9558,7 @@
         <v>70</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="1:9">
@@ -9324,10 +9566,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
@@ -9339,7 +9581,7 @@
         <v>70</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" ht="28.8" spans="1:9">
@@ -9347,10 +9589,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -9362,7 +9604,7 @@
         <v>70</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="1:9">
@@ -9370,10 +9612,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>305</v>
       </c>
       <c r="D13" s="1">
         <v>2</v>
@@ -9385,7 +9627,7 @@
         <v>70</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" ht="28.8" spans="1:9">
@@ -9393,10 +9635,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
@@ -9416,10 +9658,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D15" s="1">
         <v>3</v>
@@ -9439,10 +9681,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D16" s="1">
         <v>4</v>
@@ -9462,10 +9704,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D17" s="1">
         <v>4</v>
@@ -9485,10 +9727,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -9508,10 +9750,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D19" s="1">
         <v>5</v>
@@ -9531,10 +9773,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D20" s="1">
         <v>6</v>
@@ -9554,10 +9796,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D21" s="1">
         <v>6</v>
@@ -9577,10 +9819,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -9600,10 +9842,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -9623,10 +9865,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D24" s="1">
         <v>7</v>
@@ -9646,10 +9888,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -9714,10 +9956,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -9737,10 +9979,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -9760,10 +10002,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -9777,10 +10019,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="D5" s="1">
         <v>-3</v>
@@ -9839,10 +10081,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -9860,10 +10102,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -9926,10 +10168,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -9949,10 +10191,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -9972,10 +10214,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="D4" s="1">
         <v>-3</v>
@@ -9989,10 +10231,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -10051,10 +10293,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10074,10 +10316,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10097,10 +10339,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="D4" s="1">
         <v>-3</v>
@@ -10114,10 +10356,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -10162,7 +10404,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -10179,13 +10421,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -10205,13 +10447,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -10231,13 +10473,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -10257,13 +10499,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -10283,13 +10525,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -10309,13 +10551,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -10327,7 +10569,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" ht="57.6" spans="1:8">
@@ -10335,13 +10577,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -10353,7 +10595,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" ht="57.6" spans="1:8">
@@ -10361,13 +10603,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -10379,7 +10621,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" ht="72" spans="1:8">
@@ -10387,13 +10629,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -10402,7 +10644,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" ht="57.6" spans="1:8">
@@ -10410,13 +10652,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="D11" s="1" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
@@ -10425,7 +10667,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" ht="57.6" spans="1:8">
@@ -10433,13 +10675,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -10448,7 +10690,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="1:8">
@@ -10456,13 +10698,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="E13" s="1">
         <v>-1</v>
@@ -10476,13 +10718,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -10541,10 +10783,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -10561,10 +10803,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -10627,10 +10869,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10650,10 +10892,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10673,10 +10915,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -10690,10 +10932,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -10738,7 +10980,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -10755,10 +10997,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -10781,10 +11023,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -10807,10 +11049,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="D4" s="1">
         <v>151</v>
@@ -10827,10 +11069,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -10847,10 +11089,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="D6" s="1">
         <v>201</v>
@@ -10867,10 +11109,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -10887,10 +11129,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -10907,10 +11149,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -10930,7 +11172,7 @@
         <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -10956,7 +11198,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -11007,7 +11249,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -11024,10 +11266,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -11047,10 +11289,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -11070,10 +11312,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -11087,10 +11329,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -11231,7 +11473,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -11248,10 +11490,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -11274,10 +11516,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -11300,10 +11542,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D4" s="1">
         <v>201</v>
@@ -11320,10 +11562,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -11340,10 +11582,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D6" s="1">
         <v>401</v>
@@ -11360,10 +11602,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -11380,10 +11622,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -11400,10 +11642,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -11420,10 +11662,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -11446,10 +11688,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -11511,16 +11753,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>34</v>
@@ -11570,10 +11812,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -11634,16 +11876,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11698,16 +11940,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11762,16 +12004,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11826,16 +12068,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11873,13 +12115,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -11896,10 +12138,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -11925,10 +12167,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="D3" s="1">
         <v>255</v>
@@ -11954,10 +12196,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -11983,10 +12225,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="D5" s="1">
         <v>256</v>
@@ -12050,10 +12292,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -12114,10 +12356,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12137,10 +12379,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -12160,10 +12402,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -12177,10 +12419,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -12325,7 +12567,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -12345,10 +12587,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12371,10 +12613,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12397,10 +12639,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12423,10 +12665,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12449,10 +12691,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12475,10 +12717,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12501,10 +12743,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12527,10 +12769,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -12547,10 +12789,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -12567,10 +12809,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -12587,10 +12829,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -12607,10 +12849,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -12619,10 +12861,10 @@
         <v>120</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -12677,17 +12919,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -12725,7 +12967,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -12745,10 +12987,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12771,10 +13013,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12797,10 +13039,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12823,10 +13065,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12849,10 +13091,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12875,10 +13117,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12901,10 +13143,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12927,10 +13169,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -12947,10 +13189,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -12967,10 +13209,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -12987,10 +13229,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -13007,10 +13249,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -13019,10 +13261,10 @@
         <v>100</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -13077,19 +13319,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -13144,10 +13386,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="E2" s="1">
         <v>50</v>
@@ -13208,10 +13450,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="D2" s="1">
         <v>30</v>
@@ -13231,10 +13473,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="D3" s="1">
         <v>301</v>
@@ -13248,10 +13490,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="D4" s="1">
         <v>-301</v>
@@ -13265,10 +13507,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="D5" s="1">
         <v>21</v>
@@ -13316,13 +13558,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -13339,10 +13581,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13368,10 +13610,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13397,10 +13639,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13426,10 +13668,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13455,10 +13697,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -13484,10 +13726,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -13513,10 +13755,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -13542,10 +13784,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -13571,10 +13813,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -13600,10 +13842,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -13629,10 +13871,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -13658,10 +13900,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -13687,10 +13929,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>450</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -13716,10 +13958,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -13745,10 +13987,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -13768,10 +14010,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -13791,10 +14033,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -13814,7 +14056,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -13834,7 +14076,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -13881,13 +14123,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -13904,10 +14146,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13933,10 +14175,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13962,10 +14204,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13991,10 +14233,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14020,10 +14262,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14049,10 +14291,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14078,10 +14320,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14101,10 +14343,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -14124,10 +14366,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -14147,10 +14389,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -14197,13 +14439,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -14220,10 +14462,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14249,10 +14491,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14278,10 +14520,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14299,7 +14541,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14307,10 +14549,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14328,7 +14570,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14336,10 +14578,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14357,7 +14599,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14365,10 +14607,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14386,7 +14628,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14394,10 +14636,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14423,10 +14665,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14452,10 +14694,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14473,7 +14715,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14481,10 +14723,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14502,7 +14744,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14510,10 +14752,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14531,7 +14773,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14539,10 +14781,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14560,7 +14802,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14568,10 +14810,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>478</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -14591,10 +14833,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>478</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -14614,10 +14856,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -14637,10 +14879,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -14688,13 +14930,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -14711,10 +14953,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14740,10 +14982,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14769,10 +15011,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14798,10 +15040,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14827,10 +15069,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14856,10 +15098,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14885,10 +15127,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14914,10 +15156,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14943,10 +15185,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14972,10 +15214,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -15001,10 +15243,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -15030,10 +15272,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -15059,10 +15301,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>493</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -15088,10 +15330,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -15117,10 +15359,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -15140,10 +15382,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -15163,10 +15405,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -15186,10 +15428,10 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -15209,10 +15451,10 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -15232,10 +15474,10 @@
         <v>26</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
@@ -15255,10 +15497,10 @@
         <v>27</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
@@ -15278,10 +15520,10 @@
         <v>28</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D23" s="1">
         <v>3</v>
@@ -15301,10 +15543,10 @@
         <v>29</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D24" s="1">
         <v>4</v>
@@ -15324,10 +15566,10 @@
         <v>30</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D25" s="1">
         <v>5</v>
@@ -15347,10 +15589,10 @@
         <v>31</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D26" s="1">
         <v>6</v>
@@ -15370,10 +15612,10 @@
         <v>32</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D27" s="1">
         <v>7</v>
@@ -15731,13 +15973,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -15754,10 +15996,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -15783,10 +16025,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -15812,10 +16054,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -15833,7 +16075,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15841,10 +16083,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -15862,7 +16104,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15870,10 +16112,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -15891,7 +16133,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15899,10 +16141,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -15920,7 +16162,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -15928,10 +16170,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -15957,10 +16199,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -15986,10 +16228,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -16007,7 +16249,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16015,10 +16257,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -16036,7 +16278,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16044,10 +16286,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -16065,7 +16307,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16073,10 +16315,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -16094,7 +16336,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16102,10 +16344,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>513</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -16125,10 +16367,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>513</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -16148,10 +16390,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -16171,10 +16413,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -16238,10 +16480,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16290,7 +16532,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -16307,10 +16549,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="D2" s="1">
         <v>45</v>
@@ -16333,10 +16575,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="D3" s="1">
         <v>-45</v>
@@ -16359,10 +16601,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="D4" s="1">
         <v>91</v>
@@ -16379,10 +16621,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="D5" s="1">
         <v>-91</v>
@@ -16399,10 +16641,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="D6" s="1">
         <v>45</v>
@@ -16419,10 +16661,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="D7" s="1">
         <v>45</v>
@@ -16467,13 +16709,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -16490,16 +16732,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="F2" s="1">
         <v>50</v>
@@ -16519,16 +16761,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -16542,16 +16784,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="F4" s="1">
         <v>101</v>
@@ -16609,10 +16851,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16632,10 +16874,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16655,10 +16897,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16678,10 +16920,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -16701,10 +16943,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
@@ -16724,10 +16966,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -16741,10 +16983,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
@@ -16808,10 +17050,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16831,10 +17073,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16854,10 +17096,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16871,10 +17113,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -16938,10 +17180,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16989,7 +17231,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -17006,13 +17248,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -17024,7 +17266,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17032,13 +17274,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="E3" s="1">
         <v>30</v>
@@ -17050,7 +17292,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17058,13 +17300,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -17076,7 +17318,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17084,13 +17326,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -17102,7 +17344,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17110,19 +17352,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17130,19 +17372,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17150,19 +17392,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17170,19 +17412,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17190,19 +17432,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17210,19 +17452,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17230,19 +17472,19 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17250,19 +17492,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17270,19 +17512,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17290,19 +17532,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17310,19 +17552,19 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17330,19 +17572,19 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17350,19 +17592,19 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17370,19 +17612,19 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17390,19 +17632,19 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="E20" s="1">
         <v>50</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17410,19 +17652,19 @@
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="E21" s="1">
         <v>50</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17430,19 +17672,19 @@
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17450,19 +17692,19 @@
         <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="E23" s="1">
         <v>50</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17470,19 +17712,19 @@
         <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="E24" s="1">
         <v>50</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17490,19 +17732,19 @@
         <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="E25" s="1">
         <v>50</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17510,19 +17752,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="E26" s="1">
         <v>50</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17530,19 +17772,19 @@
         <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="E27" s="1">
         <v>50</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17550,19 +17792,19 @@
         <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="E28" s="1">
         <v>50</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17570,19 +17812,19 @@
         <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="E29" s="1">
         <v>50</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17590,19 +17832,19 @@
         <v>19</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="E30" s="1">
         <v>101</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17610,19 +17852,19 @@
         <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="E31" s="1">
         <v>-1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
     </row>
   </sheetData>
@@ -17659,13 +17901,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -17682,10 +17924,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17703,7 +17945,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17711,10 +17953,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -17732,7 +17974,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17740,10 +17982,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -17761,7 +18003,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17769,10 +18011,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -17790,7 +18032,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17798,10 +18040,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -17819,7 +18061,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17827,10 +18069,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -17848,7 +18090,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17856,10 +18098,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -17877,7 +18119,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17885,10 +18127,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -17906,7 +18148,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17914,10 +18156,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -17935,7 +18177,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17943,10 +18185,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -17964,7 +18206,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -17972,10 +18214,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -17993,7 +18235,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18001,10 +18243,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -18022,7 +18264,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" ht="28.8" spans="1:9">
@@ -18030,10 +18272,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>598</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -18053,10 +18295,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>598</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -18076,10 +18318,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -18099,10 +18341,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -18149,13 +18391,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -18172,10 +18414,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18201,10 +18443,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -18230,10 +18472,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -18251,7 +18493,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18259,10 +18501,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18280,7 +18522,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18288,10 +18530,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18309,7 +18551,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18317,10 +18559,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18338,7 +18580,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18346,10 +18588,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18375,10 +18617,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>620</v>
+        <v>632</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -18404,10 +18646,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -18425,7 +18667,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18433,10 +18675,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -18454,7 +18696,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18462,10 +18704,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -18483,7 +18725,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18491,10 +18733,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -18512,7 +18754,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -18520,10 +18762,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>625</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>613</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -18543,10 +18785,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>625</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>613</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -18566,10 +18808,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -18589,10 +18831,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -18735,13 +18977,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -18758,10 +19000,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18787,10 +19029,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -18816,10 +19058,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -18845,10 +19087,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18874,10 +19116,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18903,10 +19145,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18932,10 +19174,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18955,10 +19197,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -18978,10 +19220,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -19001,10 +19243,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -19051,7 +19293,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -19071,10 +19313,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -19088,10 +19330,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -19105,10 +19347,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -19122,10 +19364,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -19139,10 +19381,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -19156,10 +19398,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -19173,10 +19415,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -19234,10 +19476,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -19296,16 +19538,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>34</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4898,7 +4898,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4898,7 +4898,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="19" activeTab="21"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="58" activeTab="62"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2402" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2402" uniqueCount="647">
   <si>
     <t>ID</t>
   </si>
@@ -1749,6 +1749,9 @@
   </si>
   <si>
     <t>[5, 20, 0, -70, 0, 90, 0]</t>
+  </si>
+  <si>
+    <t>[15, 20, 0, -65, 0, 90, 0]</t>
   </si>
   <si>
     <t>[15, 20, 0, -60, 0, 90, 0]</t>
@@ -4898,7 +4901,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -16770,7 +16773,7 @@
         <v>549</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -16793,7 +16796,7 @@
         <v>549</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F4" s="1">
         <v>101</v>
@@ -16851,10 +16854,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16874,10 +16877,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16897,10 +16900,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16920,10 +16923,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -16943,10 +16946,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
@@ -16966,10 +16969,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>552</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -16986,7 +16989,7 @@
         <v>437</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
@@ -17050,10 +17053,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -17073,10 +17076,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -17096,10 +17099,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -17116,7 +17119,7 @@
         <v>437</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -17180,10 +17183,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -17248,13 +17251,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -17274,13 +17277,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E3" s="1">
         <v>30</v>
@@ -17300,13 +17303,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -17326,13 +17329,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -17352,19 +17355,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17372,19 +17375,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17392,19 +17395,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17412,19 +17415,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17432,19 +17435,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17452,19 +17455,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17472,19 +17475,19 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17492,19 +17495,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17512,19 +17515,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17532,19 +17535,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17552,19 +17555,19 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17572,19 +17575,19 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17592,19 +17595,19 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17612,19 +17615,19 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17632,19 +17635,19 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E20" s="1">
         <v>50</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17652,19 +17655,19 @@
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E21" s="1">
         <v>50</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17672,19 +17675,19 @@
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17692,19 +17695,19 @@
         <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E23" s="1">
         <v>50</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17712,19 +17715,19 @@
         <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E24" s="1">
         <v>50</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17732,19 +17735,19 @@
         <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E25" s="1">
         <v>50</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17752,19 +17755,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E26" s="1">
         <v>50</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17772,19 +17775,19 @@
         <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E27" s="1">
         <v>50</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17792,19 +17795,19 @@
         <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E28" s="1">
         <v>50</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17812,19 +17815,19 @@
         <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E29" s="1">
         <v>50</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17832,19 +17835,19 @@
         <v>19</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E30" s="1">
         <v>101</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17852,19 +17855,19 @@
         <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E31" s="1">
         <v>-1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
   </sheetData>
@@ -17924,10 +17927,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17953,10 +17956,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>611</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>610</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -17982,10 +17985,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -18011,10 +18014,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -18040,10 +18043,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -18069,10 +18072,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -18098,10 +18101,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -18127,10 +18130,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -18156,10 +18159,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -18185,10 +18188,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -18214,10 +18217,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -18243,10 +18246,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -18272,10 +18275,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -18295,10 +18298,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -18318,10 +18321,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -18341,10 +18344,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -18414,10 +18417,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18443,10 +18446,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>626</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>625</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -18472,10 +18475,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -18501,10 +18504,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18530,10 +18533,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18559,10 +18562,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18588,10 +18591,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18617,10 +18620,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -18646,10 +18649,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -18675,10 +18678,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -18704,10 +18707,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -18733,10 +18736,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -18762,10 +18765,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -18785,10 +18788,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -18808,10 +18811,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -18831,10 +18834,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -19003,7 +19006,7 @@
         <v>480</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -19032,7 +19035,7 @@
         <v>482</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -19061,7 +19064,7 @@
         <v>483</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -19090,7 +19093,7 @@
         <v>484</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -19119,7 +19122,7 @@
         <v>485</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -19148,7 +19151,7 @@
         <v>486</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -19177,7 +19180,7 @@
         <v>487</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -19200,7 +19203,7 @@
         <v>487</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -19223,7 +19226,7 @@
         <v>488</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -19246,7 +19249,7 @@
         <v>488</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -19313,10 +19316,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -19330,10 +19333,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -19347,10 +19350,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -19364,10 +19367,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -19381,10 +19384,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -19398,10 +19401,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -19415,10 +19418,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -19476,10 +19479,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -19538,16 +19541,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>34</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="58" activeTab="62"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="42" activeTab="42"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2402" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2402" uniqueCount="646">
   <si>
     <t>ID</t>
   </si>
@@ -1319,10 +1319,7 @@
     <t>get_base_coords</t>
   </si>
   <si>
-    <t>[424.5, 90.3, 196.1, 89.99, 0.0, -50.0]</t>
-  </si>
-  <si>
-    <t>[425.5, -91.1, 196.1, -90.0, 0.0, 49.71]</t>
+    <t>[375.0, 213.1, 196.1, 89.99, 0.0, -32.0]</t>
   </si>
   <si>
     <t>正确获取机械臂关节速度</t>
@@ -11888,7 +11885,7 @@
         <v>406</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11943,16 +11940,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -12007,16 +12004,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -12071,16 +12068,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>415</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -12118,13 +12115,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>418</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -12141,10 +12138,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>420</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -12170,10 +12167,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>420</v>
       </c>
       <c r="D3" s="1">
         <v>255</v>
@@ -12199,10 +12196,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>420</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -12228,10 +12225,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D5" s="1">
         <v>256</v>
@@ -12295,10 +12292,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -12359,10 +12356,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>425</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12382,10 +12379,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>425</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -12405,10 +12402,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -12422,10 +12419,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -12590,10 +12587,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>428</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12616,10 +12613,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12642,10 +12639,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12668,10 +12665,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12694,10 +12691,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12720,10 +12717,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12746,10 +12743,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12772,10 +12769,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -12792,10 +12789,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -12812,10 +12809,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -12832,10 +12829,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -12852,10 +12849,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -12864,10 +12861,10 @@
         <v>120</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -12922,17 +12919,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>440</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -12990,10 +12987,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>443</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13016,10 +13013,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -13042,10 +13039,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -13068,10 +13065,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -13094,10 +13091,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -13120,10 +13117,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -13146,10 +13143,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -13172,10 +13169,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -13192,10 +13189,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -13212,10 +13209,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -13232,10 +13229,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -13252,10 +13249,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -13264,10 +13261,10 @@
         <v>100</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -13322,19 +13319,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>454</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -13389,10 +13386,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>457</v>
       </c>
       <c r="E2" s="1">
         <v>50</v>
@@ -13453,10 +13450,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>459</v>
       </c>
       <c r="D2" s="1">
         <v>30</v>
@@ -13476,10 +13473,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D3" s="1">
         <v>301</v>
@@ -13493,10 +13490,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D4" s="1">
         <v>-301</v>
@@ -13510,10 +13507,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D5" s="1">
         <v>21</v>
@@ -13584,10 +13581,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>462</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13613,10 +13610,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13642,10 +13639,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13671,10 +13668,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13700,10 +13697,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -13729,10 +13726,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -13758,10 +13755,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -13787,10 +13784,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -13816,10 +13813,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -13845,10 +13842,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -13874,10 +13871,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -13903,10 +13900,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -13932,10 +13929,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -13961,10 +13958,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -13990,10 +13987,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -14013,10 +14010,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -14036,10 +14033,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -14059,7 +14056,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -14079,7 +14076,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -14149,10 +14146,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>480</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>481</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14178,10 +14175,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14207,10 +14204,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14236,10 +14233,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14265,10 +14262,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14294,10 +14291,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14323,10 +14320,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14346,10 +14343,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -14369,10 +14366,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -14392,10 +14389,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -14465,10 +14462,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>490</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14494,10 +14491,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14523,10 +14520,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14552,10 +14549,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14581,10 +14578,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14610,10 +14607,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14639,10 +14636,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14668,10 +14665,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14697,10 +14694,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14726,10 +14723,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14755,10 +14752,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14784,10 +14781,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14813,10 +14810,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -14836,10 +14833,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -14859,10 +14856,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -14882,10 +14879,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -14956,10 +14953,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14985,10 +14982,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -15014,10 +15011,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -15043,10 +15040,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -15072,10 +15069,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -15101,10 +15098,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -15130,10 +15127,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -15159,10 +15156,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -15188,10 +15185,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -15217,10 +15214,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -15246,10 +15243,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -15275,10 +15272,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -15304,10 +15301,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -15333,10 +15330,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -15362,10 +15359,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -15385,10 +15382,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -15408,10 +15405,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -15431,10 +15428,10 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -15454,10 +15451,10 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -15477,10 +15474,10 @@
         <v>26</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
@@ -15500,10 +15497,10 @@
         <v>27</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
@@ -15523,10 +15520,10 @@
         <v>28</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D23" s="1">
         <v>3</v>
@@ -15546,10 +15543,10 @@
         <v>29</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D24" s="1">
         <v>4</v>
@@ -15569,10 +15566,10 @@
         <v>30</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D25" s="1">
         <v>5</v>
@@ -15592,10 +15589,10 @@
         <v>31</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D26" s="1">
         <v>6</v>
@@ -15615,10 +15612,10 @@
         <v>32</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D27" s="1">
         <v>7</v>
@@ -15999,10 +15996,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>524</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>525</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -16028,10 +16025,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16057,10 +16054,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16086,10 +16083,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -16115,10 +16112,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -16144,10 +16141,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -16173,10 +16170,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -16202,10 +16199,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -16231,10 +16228,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -16260,10 +16257,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -16289,10 +16286,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -16318,10 +16315,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -16347,10 +16344,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -16370,10 +16367,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -16393,10 +16390,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -16416,10 +16413,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -16483,10 +16480,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>540</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16552,10 +16549,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>542</v>
       </c>
       <c r="D2" s="1">
         <v>45</v>
@@ -16578,10 +16575,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>542</v>
       </c>
       <c r="D3" s="1">
         <v>-45</v>
@@ -16604,10 +16601,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D4" s="1">
         <v>91</v>
@@ -16624,10 +16621,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D5" s="1">
         <v>-91</v>
@@ -16644,10 +16641,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D6" s="1">
         <v>45</v>
@@ -16664,10 +16661,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D7" s="1">
         <v>45</v>
@@ -16712,10 +16709,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>545</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>546</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>157</v>
@@ -16735,16 +16732,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>549</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>550</v>
       </c>
       <c r="F2" s="1">
         <v>50</v>
@@ -16764,16 +16761,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>549</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -16787,16 +16784,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>549</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F4" s="1">
         <v>101</v>
@@ -16854,10 +16851,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>553</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16877,10 +16874,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>553</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16900,10 +16897,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>553</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16923,10 +16920,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>553</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -16946,10 +16943,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>553</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
@@ -16969,10 +16966,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -16986,10 +16983,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
@@ -17053,10 +17050,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -17076,10 +17073,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -17099,10 +17096,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -17116,10 +17113,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -17183,10 +17180,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -17251,13 +17248,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>560</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -17277,13 +17274,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>562</v>
       </c>
       <c r="E3" s="1">
         <v>30</v>
@@ -17303,13 +17300,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>563</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>564</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -17329,13 +17326,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>566</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -17355,19 +17352,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>567</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>568</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17375,19 +17372,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>570</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>571</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17395,19 +17392,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>572</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>573</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17415,19 +17412,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17435,19 +17432,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>576</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>577</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17455,19 +17452,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>578</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>579</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17475,19 +17472,19 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>580</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>581</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17495,19 +17492,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17515,19 +17512,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>583</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>584</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17535,19 +17532,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>585</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>586</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17555,19 +17552,19 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>587</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>588</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17575,19 +17572,19 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>589</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>590</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17595,19 +17592,19 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>591</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>592</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17615,19 +17612,19 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>594</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17635,19 +17632,19 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>595</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>596</v>
       </c>
       <c r="E20" s="1">
         <v>50</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17655,19 +17652,19 @@
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>597</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>598</v>
       </c>
       <c r="E21" s="1">
         <v>50</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17675,19 +17672,19 @@
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>600</v>
       </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17695,19 +17692,19 @@
         <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>602</v>
       </c>
       <c r="E23" s="1">
         <v>50</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17715,19 +17712,19 @@
         <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E24" s="1">
         <v>50</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17735,19 +17732,19 @@
         <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E25" s="1">
         <v>50</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17755,19 +17752,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E26" s="1">
         <v>50</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17775,19 +17772,19 @@
         <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E27" s="1">
         <v>50</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17795,19 +17792,19 @@
         <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E28" s="1">
         <v>50</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17815,19 +17812,19 @@
         <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E29" s="1">
         <v>50</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17835,19 +17832,19 @@
         <v>19</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>560</v>
       </c>
       <c r="E30" s="1">
         <v>101</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17855,19 +17852,19 @@
         <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E31" s="1">
         <v>-1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
   </sheetData>
@@ -17927,10 +17924,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>611</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17956,10 +17953,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -17985,10 +17982,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -18014,10 +18011,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -18043,10 +18040,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -18072,10 +18069,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -18101,10 +18098,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -18130,10 +18127,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -18159,10 +18156,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -18188,10 +18185,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -18217,10 +18214,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -18246,10 +18243,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -18275,10 +18272,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -18298,10 +18295,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -18321,10 +18318,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -18344,10 +18341,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -18417,10 +18414,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>625</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>626</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18446,10 +18443,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -18475,10 +18472,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -18504,10 +18501,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18533,10 +18530,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18562,10 +18559,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18591,10 +18588,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18620,10 +18617,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -18649,10 +18646,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -18678,10 +18675,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -18707,10 +18704,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -18736,10 +18733,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -18765,10 +18762,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -18788,10 +18785,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -18811,10 +18808,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -18834,10 +18831,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -19003,10 +19000,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -19032,10 +19029,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -19061,10 +19058,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -19090,10 +19087,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -19119,10 +19116,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -19148,10 +19145,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -19177,10 +19174,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -19200,10 +19197,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -19223,10 +19220,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -19246,10 +19243,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -19316,10 +19313,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>641</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>642</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -19333,10 +19330,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>641</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>642</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -19350,10 +19347,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>641</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>642</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -19367,10 +19364,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>641</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>642</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -19384,10 +19381,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>641</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>642</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -19401,10 +19398,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>641</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>642</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -19418,10 +19415,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>641</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>642</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -19479,10 +19476,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>641</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>642</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -19541,16 +19538,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>645</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>646</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>34</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="42" activeTab="42"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="64" activeTab="68"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -18429,10 +18429,10 @@
         <v>50</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>34</v>
@@ -18458,10 +18458,10 @@
         <v>50</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>34</v>
@@ -18487,10 +18487,10 @@
         <v>60</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>319</v>
@@ -18516,10 +18516,10 @@
         <v>60</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>319</v>
@@ -18545,10 +18545,10 @@
         <v>30</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>319</v>
@@ -18574,10 +18574,10 @@
         <v>30</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>319</v>
@@ -18603,10 +18603,10 @@
         <v>50</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>34</v>
@@ -18632,10 +18632,10 @@
         <v>50</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>34</v>
@@ -18661,10 +18661,10 @@
         <v>60</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>319</v>
@@ -18690,10 +18690,10 @@
         <v>60</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>319</v>
@@ -18719,10 +18719,10 @@
         <v>30</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>319</v>
@@ -18748,10 +18748,10 @@
         <v>30</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>319</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="64" activeTab="68"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="64" activeTab="69"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -19015,10 +19015,10 @@
         <v>50</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>34</v>
@@ -19044,10 +19044,10 @@
         <v>50</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>34</v>
@@ -19073,10 +19073,10 @@
         <v>60</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>34</v>
@@ -19102,10 +19102,10 @@
         <v>60</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>34</v>
@@ -19131,10 +19131,10 @@
         <v>30</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>34</v>
@@ -19160,10 +19160,10 @@
         <v>30</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>34</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="64" activeTab="69"/>
+    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="66" activeTab="72"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2402" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2407" uniqueCount="646">
   <si>
     <t>ID</t>
   </si>
@@ -19494,8 +19494,8 @@
 <file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="7"/>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
@@ -19549,8 +19549,40 @@
       <c r="E2" s="1" t="s">
         <v>645</v>
       </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
       <c r="H2" s="1" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="3" ht="28.8" spans="1:8">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2407" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2409" uniqueCount="649">
   <si>
     <t>ID</t>
   </si>
@@ -2037,6 +2037,15 @@
   </si>
   <si>
     <t>[0,20,0,-90,0,90,0]</t>
+  </si>
+  <si>
+    <t>[0.001, 18.588, 0.0, -80.417, -0.009, 79.005, 0.0]</t>
+  </si>
+  <si>
+    <t>设置逆解位置超限</t>
+  </si>
+  <si>
+    <t>[166,20,0,-90,0,90,0]</t>
   </si>
 </sst>
 </file>
@@ -19549,11 +19558,11 @@
       <c r="E2" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="F2" s="1">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1</v>
+      <c r="F2" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>646</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>34</v>
@@ -19564,7 +19573,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>643</v>
@@ -19573,14 +19582,10 @@
         <v>644</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="F3" s="1">
-        <v>1</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1</v>
-      </c>
+        <v>648</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
         <v>42</v>
       </c>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="66" activeTab="72"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="66" activeTab="70"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -19330,6 +19330,12 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
+      <c r="F2" s="1">
+        <v>1069884406</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1069884406</v>
+      </c>
       <c r="H2" s="1" t="s">
         <v>34</v>
       </c>
@@ -19346,6 +19352,12 @@
       </c>
       <c r="D3" s="1">
         <v>2</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1076287791</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1076287791</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>34</v>
@@ -19364,6 +19376,12 @@
       <c r="D4" s="1">
         <v>3</v>
       </c>
+      <c r="F4" s="1">
+        <v>1075177799</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1075177799</v>
+      </c>
       <c r="H4" s="1" t="s">
         <v>34</v>
       </c>
@@ -19381,6 +19399,12 @@
       <c r="D5" s="1">
         <v>4</v>
       </c>
+      <c r="F5" s="1">
+        <v>1073747231</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1073747231</v>
+      </c>
       <c r="H5" s="1" t="s">
         <v>34</v>
       </c>
@@ -19398,6 +19422,12 @@
       <c r="D6" s="1">
         <v>5</v>
       </c>
+      <c r="F6" s="1">
+        <v>1074859588</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1074859588</v>
+      </c>
       <c r="H6" s="1" t="s">
         <v>34</v>
       </c>
@@ -19415,6 +19445,12 @@
       <c r="D7" s="1">
         <v>6</v>
       </c>
+      <c r="F7" s="1">
+        <v>1083770726</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1083770726</v>
+      </c>
       <c r="H7" s="1" t="s">
         <v>34</v>
       </c>
@@ -19431,6 +19467,12 @@
       </c>
       <c r="D8" s="1">
         <v>7</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1049139757</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1049139757</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>34</v>
@@ -19584,8 +19626,6 @@
       <c r="E3" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
         <v>42</v>
       </c>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="66" activeTab="70"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="67" activeTab="71"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2409" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="651">
   <si>
     <t>ID</t>
   </si>
@@ -2025,6 +2025,12 @@
   </si>
   <si>
     <t>get_servo_encoder</t>
+  </si>
+  <si>
+    <t>[1069884419, 1076287775, 1075177861, 1073747201, 1074859830, 1083770771, 1049139745]</t>
+  </si>
+  <si>
+    <t>[1072078335, 1075501457, 1071738217, 1077951697, 1074167434, 1073300060, 1054710528]</t>
   </si>
   <si>
     <t>正确获取机械臂运动学逆解</t>
@@ -19494,8 +19500,8 @@
     <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37" style="1" customWidth="1"/>
+    <col min="6" max="6" width="47" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -19531,6 +19537,12 @@
       </c>
       <c r="C2" s="1" t="s">
         <v>641</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>643</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -19589,22 +19601,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>34</v>
@@ -19615,16 +19627,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>42</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="67" activeTab="71"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="54" activeTab="59"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2420" uniqueCount="654">
   <si>
     <t>ID</t>
   </si>
@@ -1713,6 +1713,15 @@
   </si>
   <si>
     <t>设置jog_increment_coord运动速度超限</t>
+  </si>
+  <si>
+    <t>设置jog_increment_coord X轴增量超限</t>
+  </si>
+  <si>
+    <t>设置jog_increment_coord y轴增量超限</t>
+  </si>
+  <si>
+    <t>设置jog_increment_coord z轴增量超限</t>
   </si>
   <si>
     <t>正确获取当前冗余臂角</t>
@@ -4250,10 +4259,10 @@
         <v>15</v>
       </c>
       <c r="E2" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>9</v>
@@ -4270,10 +4279,10 @@
         <v>15</v>
       </c>
       <c r="E3" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>11</v>
@@ -4290,10 +4299,10 @@
         <v>15</v>
       </c>
       <c r="E4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>13</v>
@@ -15965,7 +15974,7 @@
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.1111111111111" style="1" customWidth="1"/>
@@ -16443,6 +16452,75 @@
         <v>101</v>
       </c>
       <c r="I17" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" ht="43.2" spans="1:9">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>918</v>
+      </c>
+      <c r="F18" s="1">
+        <v>10</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" ht="43.2" spans="1:9">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="1">
+        <v>918</v>
+      </c>
+      <c r="F19" s="1">
+        <v>10</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" ht="43.2" spans="1:9">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="D20" s="1">
+        <v>3</v>
+      </c>
+      <c r="E20" s="1">
+        <v>918</v>
+      </c>
+      <c r="F20" s="1">
+        <v>10</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -16495,10 +16573,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16564,10 +16642,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D2" s="1">
         <v>45</v>
@@ -16590,10 +16668,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D3" s="1">
         <v>-45</v>
@@ -16616,10 +16694,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D4" s="1">
         <v>91</v>
@@ -16636,10 +16714,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D5" s="1">
         <v>-91</v>
@@ -16656,10 +16734,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D6" s="1">
         <v>45</v>
@@ -16676,10 +16754,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D7" s="1">
         <v>45</v>
@@ -16724,10 +16802,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>157</v>
@@ -16747,16 +16825,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F2" s="1">
         <v>50</v>
@@ -16776,16 +16854,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -16799,16 +16877,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="F4" s="1">
         <v>101</v>
@@ -16866,10 +16944,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16889,10 +16967,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16912,10 +16990,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16935,10 +17013,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -16958,10 +17036,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
@@ -16981,10 +17059,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -17001,7 +17079,7 @@
         <v>436</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
@@ -17065,10 +17143,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -17088,10 +17166,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -17111,10 +17189,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>555</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>552</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -17131,7 +17209,7 @@
         <v>436</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -17195,10 +17273,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -17263,13 +17341,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -17289,13 +17367,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="E3" s="1">
         <v>30</v>
@@ -17315,13 +17393,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -17341,13 +17419,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -17367,19 +17445,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17387,19 +17465,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17407,19 +17485,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17427,19 +17505,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17447,19 +17525,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17467,19 +17545,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17487,19 +17565,19 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17507,19 +17585,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17527,19 +17605,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17547,19 +17625,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17567,19 +17645,19 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17587,19 +17665,19 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17607,19 +17685,19 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17627,19 +17705,19 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17647,19 +17725,19 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="E20" s="1">
         <v>50</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17667,19 +17745,19 @@
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E21" s="1">
         <v>50</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17687,19 +17765,19 @@
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17707,19 +17785,19 @@
         <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E23" s="1">
         <v>50</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17727,19 +17805,19 @@
         <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E24" s="1">
         <v>50</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17747,19 +17825,19 @@
         <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E25" s="1">
         <v>50</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17767,19 +17845,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="E26" s="1">
         <v>50</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17787,19 +17865,19 @@
         <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="E27" s="1">
         <v>50</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17807,19 +17885,19 @@
         <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E28" s="1">
         <v>50</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17827,19 +17905,19 @@
         <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E29" s="1">
         <v>50</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17847,19 +17925,19 @@
         <v>19</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E30" s="1">
         <v>101</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17867,19 +17945,19 @@
         <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="E31" s="1">
         <v>-1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
   </sheetData>
@@ -17939,10 +18017,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -17968,10 +18046,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -17997,10 +18075,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -18026,10 +18104,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>613</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>610</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -18055,10 +18133,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -18084,10 +18162,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -18113,10 +18191,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -18142,10 +18220,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -18171,10 +18249,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -18200,10 +18278,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -18229,10 +18307,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -18258,10 +18336,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -18287,10 +18365,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -18310,10 +18388,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -18333,10 +18411,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -18356,10 +18434,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -18429,10 +18507,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18458,10 +18536,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -18487,10 +18565,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -18516,10 +18594,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>628</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>625</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18545,10 +18623,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18574,10 +18652,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18603,10 +18681,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18632,10 +18710,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -18661,10 +18739,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -18690,10 +18768,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -18719,10 +18797,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -18748,10 +18826,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -18777,10 +18855,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -18800,10 +18878,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -18823,10 +18901,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -18846,10 +18924,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -19018,7 +19096,7 @@
         <v>479</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -19047,7 +19125,7 @@
         <v>481</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -19076,7 +19154,7 @@
         <v>482</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -19105,7 +19183,7 @@
         <v>483</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -19134,7 +19212,7 @@
         <v>484</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -19163,7 +19241,7 @@
         <v>485</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -19192,7 +19270,7 @@
         <v>486</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -19215,7 +19293,7 @@
         <v>486</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -19238,7 +19316,7 @@
         <v>487</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -19261,7 +19339,7 @@
         <v>487</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -19328,10 +19406,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -19351,10 +19429,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -19374,10 +19452,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -19397,10 +19475,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -19420,10 +19498,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -19443,10 +19521,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -19466,10 +19544,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -19533,16 +19611,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -19601,22 +19679,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>34</v>
@@ -19627,16 +19705,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>646</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>42</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="54" activeTab="59"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="7" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -19793,6 +19793,12 @@
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="E3" s="1">
+        <v>2</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
       <c r="G3" s="1" t="s">
         <v>42</v>
       </c>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="7" activeTab="7"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="7" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -3259,6 +3259,12 @@
       <c r="C5" s="1" t="s">
         <v>56</v>
       </c>
+      <c r="E5" s="2">
+        <v>2</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
       <c r="G5" s="1" t="s">
         <v>60</v>
       </c>
@@ -3440,7 +3446,12 @@
       <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="5">
+        <v>2</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
       <c r="G3" s="1" t="s">
         <v>60</v>
       </c>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="7" activeTab="11"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="21" activeTab="26"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2420" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2423" uniqueCount="666">
   <si>
     <t>ID</t>
   </si>
@@ -906,6 +906,42 @@
   </si>
   <si>
     <t>设置单关节角度，1关节超限（166）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，2关节超限（-51）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，2关节超限（121）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，3关节超限（-166）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，3关节超限（166）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，4关节超限（-166）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，4关节超限（2）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，5关节超限（-166）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，5关节超限（166）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，6关节超限（-76）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，6关节超限（256）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，7关节超限（-166）</t>
+  </si>
+  <si>
+    <t>设置单关节角度，7关节超限（166）</t>
   </si>
   <si>
     <t>设置单关节角度，11关节超限（1）</t>
@@ -3793,8 +3829,8 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="6"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
@@ -3852,27 +3888,27 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:7">
+    <row r="3" customFormat="1" ht="28.8" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D3" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" ht="28.8" spans="1:7">
@@ -3886,7 +3922,7 @@
         <v>87</v>
       </c>
       <c r="D4" s="1">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
@@ -3903,13 +3939,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
@@ -3918,6 +3954,29 @@
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" ht="28.8" spans="1:7">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>46</v>
       </c>
     </row>
@@ -8217,7 +8276,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>219</v>
+        <v>269</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>255</v>
@@ -8242,7 +8301,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>221</v>
+        <v>270</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>255</v>
@@ -8267,7 +8326,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>223</v>
+        <v>271</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>255</v>
@@ -8292,7 +8351,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>225</v>
+        <v>272</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>255</v>
@@ -8317,7 +8376,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>227</v>
+        <v>273</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>255</v>
@@ -8342,7 +8401,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>229</v>
+        <v>274</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>255</v>
@@ -8367,7 +8426,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>255</v>
@@ -8392,7 +8451,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>255</v>
@@ -8417,7 +8476,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>255</v>
@@ -8442,7 +8501,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>237</v>
+        <v>278</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>255</v>
@@ -8467,7 +8526,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>239</v>
+        <v>279</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>255</v>
@@ -8492,7 +8551,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>241</v>
+        <v>280</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>255</v>
@@ -8517,7 +8576,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>255</v>
@@ -8540,7 +8599,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>255</v>
@@ -8563,7 +8622,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>255</v>
@@ -8586,7 +8645,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>255</v>
@@ -8609,7 +8668,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>255</v>
@@ -8632,7 +8691,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>255</v>
@@ -8698,19 +8757,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -8721,19 +8780,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>155</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>34</v>
@@ -8791,13 +8850,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -8817,13 +8876,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="E3" s="1">
         <v>50</v>
@@ -8843,13 +8902,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -8869,13 +8928,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -8895,13 +8954,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
@@ -8915,13 +8974,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
@@ -8935,13 +8994,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
@@ -8955,13 +9014,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="D9" s="1" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
@@ -8975,13 +9034,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
@@ -8995,13 +9054,13 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
@@ -9015,13 +9074,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
@@ -9035,13 +9094,13 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
@@ -9055,13 +9114,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
@@ -9075,13 +9134,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
@@ -9095,13 +9154,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
@@ -9115,13 +9174,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
@@ -9135,13 +9194,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
@@ -9155,13 +9214,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
@@ -9175,13 +9234,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="E20" s="1">
         <v>101</v>
@@ -9195,13 +9254,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
@@ -9335,7 +9394,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -9358,10 +9417,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -9387,10 +9446,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -9408,7 +9467,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -9416,10 +9475,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -9437,7 +9496,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -9445,10 +9504,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -9466,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -9474,10 +9533,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -9495,7 +9554,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -9503,10 +9562,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -9524,7 +9583,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8" ht="28.8" spans="1:9">
@@ -9532,10 +9591,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -9555,10 +9614,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -9578,10 +9637,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
@@ -9601,10 +9660,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
@@ -9624,10 +9683,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -9647,10 +9706,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>317</v>
       </c>
       <c r="D13" s="1">
         <v>2</v>
@@ -9670,10 +9729,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
@@ -9693,10 +9752,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D15" s="1">
         <v>3</v>
@@ -9716,10 +9775,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D16" s="1">
         <v>4</v>
@@ -9739,10 +9798,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D17" s="1">
         <v>4</v>
@@ -9762,10 +9821,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -9785,10 +9844,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D19" s="1">
         <v>5</v>
@@ -9808,10 +9867,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D20" s="1">
         <v>6</v>
@@ -9831,10 +9890,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D21" s="1">
         <v>6</v>
@@ -9854,10 +9913,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -9877,10 +9936,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -9900,10 +9959,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D24" s="1">
         <v>7</v>
@@ -9923,10 +9982,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -9991,10 +10050,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10014,10 +10073,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10037,10 +10096,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -10054,10 +10113,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="D5" s="1">
         <v>-3</v>
@@ -10116,10 +10175,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -10137,10 +10196,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -10203,10 +10262,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10226,10 +10285,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10249,10 +10308,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="D4" s="1">
         <v>-3</v>
@@ -10266,10 +10325,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -10328,10 +10387,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10351,10 +10410,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10374,10 +10433,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="D4" s="1">
         <v>-3</v>
@@ -10391,10 +10450,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -10439,7 +10498,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -10456,13 +10515,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -10482,13 +10541,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -10508,13 +10567,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -10534,13 +10593,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -10560,13 +10619,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -10586,13 +10645,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -10612,13 +10671,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -10638,13 +10697,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -10664,13 +10723,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -10687,13 +10746,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="D11" s="1" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
@@ -10710,13 +10769,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -10733,13 +10792,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="E13" s="1">
         <v>-1</v>
@@ -10753,13 +10812,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -10818,10 +10877,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -10838,10 +10897,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -10904,10 +10963,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10927,10 +10986,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -10950,10 +11009,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -10967,10 +11026,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -11015,7 +11074,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -11032,10 +11091,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -11058,10 +11117,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -11084,10 +11143,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D4" s="1">
         <v>151</v>
@@ -11104,10 +11163,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -11124,10 +11183,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D6" s="1">
         <v>201</v>
@@ -11144,10 +11203,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -11164,10 +11223,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -11184,10 +11243,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -11207,7 +11266,7 @@
         <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -11233,7 +11292,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -11284,7 +11343,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -11301,10 +11360,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -11324,10 +11383,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -11347,10 +11406,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -11364,10 +11423,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -11508,7 +11567,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -11525,10 +11584,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="D2" s="1">
         <v>140</v>
@@ -11551,10 +11610,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="D3" s="1">
         <v>150</v>
@@ -11577,10 +11636,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="D4" s="1">
         <v>201</v>
@@ -11597,10 +11656,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -11617,10 +11676,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="D6" s="1">
         <v>401</v>
@@ -11637,10 +11696,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -11657,10 +11716,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -11677,10 +11736,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -11697,10 +11756,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
@@ -11723,10 +11782,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -11788,16 +11847,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>34</v>
@@ -11847,10 +11906,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -11911,16 +11970,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -11975,16 +12034,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -12039,16 +12098,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -12103,16 +12162,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -12150,13 +12209,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -12173,10 +12232,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -12202,10 +12261,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="D3" s="1">
         <v>255</v>
@@ -12231,10 +12290,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -12260,10 +12319,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="D5" s="1">
         <v>256</v>
@@ -12327,10 +12386,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -12391,10 +12450,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12414,10 +12473,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -12437,10 +12496,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -12454,10 +12513,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -12622,10 +12681,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12648,10 +12707,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12674,10 +12733,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12700,10 +12759,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12726,10 +12785,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12752,10 +12811,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12778,10 +12837,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12804,10 +12863,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -12824,10 +12883,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -12844,10 +12903,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -12864,10 +12923,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -12884,10 +12943,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -12896,10 +12955,10 @@
         <v>120</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -12954,17 +13013,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -13022,10 +13081,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13048,10 +13107,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -13074,10 +13133,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -13100,10 +13159,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -13126,10 +13185,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -13152,10 +13211,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -13178,10 +13237,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -13204,10 +13263,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -13224,10 +13283,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -13244,10 +13303,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -13264,10 +13323,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -13284,10 +13343,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -13296,10 +13355,10 @@
         <v>100</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>46</v>
@@ -13354,19 +13413,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -13421,10 +13480,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="E2" s="1">
         <v>50</v>
@@ -13485,10 +13544,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="D2" s="1">
         <v>30</v>
@@ -13508,10 +13567,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="D3" s="1">
         <v>301</v>
@@ -13525,10 +13584,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="D4" s="1">
         <v>-301</v>
@@ -13542,10 +13601,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="D5" s="1">
         <v>21</v>
@@ -13616,10 +13675,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13645,10 +13704,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13674,10 +13733,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13703,10 +13762,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -13732,10 +13791,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -13761,10 +13820,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -13790,10 +13849,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -13819,10 +13878,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -13848,10 +13907,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -13877,10 +13936,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -13906,10 +13965,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -13935,10 +13994,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -13964,10 +14023,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>461</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -13993,10 +14052,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -14022,10 +14081,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -14045,10 +14104,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -14068,10 +14127,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -14091,7 +14150,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -14111,7 +14170,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -14158,7 +14217,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -14181,10 +14240,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14210,10 +14269,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14239,10 +14298,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14268,10 +14327,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14297,10 +14356,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14326,10 +14385,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14355,10 +14414,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14378,10 +14437,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -14401,10 +14460,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -14424,10 +14483,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -14474,7 +14533,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -14497,10 +14556,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14526,10 +14585,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14555,10 +14614,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14576,7 +14635,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14584,10 +14643,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14605,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14613,10 +14672,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14634,7 +14693,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14642,10 +14701,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14663,7 +14722,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14671,10 +14730,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14700,10 +14759,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14729,10 +14788,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14750,7 +14809,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14758,10 +14817,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14779,7 +14838,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14787,10 +14846,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14808,7 +14867,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14816,10 +14875,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14837,7 +14896,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -14845,10 +14904,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>489</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -14868,10 +14927,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>489</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -14891,10 +14950,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -14914,10 +14973,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -14988,10 +15047,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -15017,10 +15076,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -15046,10 +15105,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -15075,10 +15134,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -15104,10 +15163,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -15133,10 +15192,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -15162,10 +15221,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -15191,10 +15250,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -15220,10 +15279,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -15249,10 +15308,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -15278,10 +15337,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -15307,10 +15366,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -15336,10 +15395,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>516</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -15365,10 +15424,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -15394,10 +15453,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -15417,10 +15476,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -15440,10 +15499,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -15463,10 +15522,10 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -15486,10 +15545,10 @@
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -15509,10 +15568,10 @@
         <v>26</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
@@ -15532,10 +15591,10 @@
         <v>27</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
@@ -15555,10 +15614,10 @@
         <v>28</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D23" s="1">
         <v>3</v>
@@ -15578,10 +15637,10 @@
         <v>29</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D24" s="1">
         <v>4</v>
@@ -15601,10 +15660,10 @@
         <v>30</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D25" s="1">
         <v>5</v>
@@ -15624,10 +15683,10 @@
         <v>31</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D26" s="1">
         <v>6</v>
@@ -15647,10 +15706,10 @@
         <v>32</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D27" s="1">
         <v>7</v>
@@ -16008,7 +16067,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -16031,10 +16090,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -16060,10 +16119,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16089,10 +16148,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16110,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16118,10 +16177,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -16139,7 +16198,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16147,10 +16206,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -16168,7 +16227,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16176,10 +16235,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -16197,7 +16256,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16205,10 +16264,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -16234,10 +16293,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -16263,10 +16322,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -16284,7 +16343,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16292,10 +16351,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -16313,7 +16372,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16321,10 +16380,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -16342,7 +16401,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16350,10 +16409,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -16371,7 +16430,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -16379,10 +16438,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>536</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>524</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -16402,10 +16461,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>536</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>524</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -16425,10 +16484,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -16448,10 +16507,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -16471,10 +16530,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
@@ -16494,10 +16553,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="D19" s="1">
         <v>2</v>
@@ -16517,10 +16576,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="D20" s="1">
         <v>3</v>
@@ -16584,10 +16643,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -16653,10 +16712,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="D2" s="1">
         <v>45</v>
@@ -16679,10 +16738,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="D3" s="1">
         <v>-45</v>
@@ -16705,10 +16764,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="D4" s="1">
         <v>91</v>
@@ -16725,10 +16784,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="D5" s="1">
         <v>-91</v>
@@ -16745,10 +16804,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="D6" s="1">
         <v>45</v>
@@ -16765,10 +16824,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="D7" s="1">
         <v>45</v>
@@ -16813,10 +16872,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>157</v>
@@ -16836,16 +16895,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="F2" s="1">
         <v>50</v>
@@ -16865,16 +16924,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -16888,16 +16947,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="F4" s="1">
         <v>101</v>
@@ -16955,10 +17014,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16978,10 +17037,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -17001,10 +17060,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -17024,10 +17083,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -17047,10 +17106,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
@@ -17070,10 +17129,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -17087,10 +17146,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
@@ -17154,10 +17213,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -17177,10 +17236,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -17200,10 +17259,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -17217,10 +17276,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -17284,10 +17343,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -17352,13 +17411,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -17378,13 +17437,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="E3" s="1">
         <v>30</v>
@@ -17404,13 +17463,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="E4" s="1">
         <v>60</v>
@@ -17430,13 +17489,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="E5" s="1">
         <v>70</v>
@@ -17456,19 +17515,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="E6" s="1">
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17476,19 +17535,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="E7" s="1">
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17496,19 +17555,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="E8" s="1">
         <v>50</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17516,19 +17575,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17536,19 +17595,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17556,19 +17615,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17576,19 +17635,19 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17596,19 +17655,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17616,19 +17675,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17636,19 +17695,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17656,19 +17715,19 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="E16" s="1">
         <v>50</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17676,19 +17735,19 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="E17" s="1">
         <v>50</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17696,19 +17755,19 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="E18" s="1">
         <v>50</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17716,19 +17775,19 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="E19" s="1">
         <v>50</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17736,19 +17795,19 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="E20" s="1">
         <v>50</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17756,19 +17815,19 @@
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="E21" s="1">
         <v>50</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17776,19 +17835,19 @@
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17796,19 +17855,19 @@
         <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="E23" s="1">
         <v>50</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17816,19 +17875,19 @@
         <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="E24" s="1">
         <v>50</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17836,19 +17895,19 @@
         <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="E25" s="1">
         <v>50</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17856,19 +17915,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
       <c r="E26" s="1">
         <v>50</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17876,19 +17935,19 @@
         <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="E27" s="1">
         <v>50</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17896,19 +17955,19 @@
         <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="E28" s="1">
         <v>50</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -17916,19 +17975,19 @@
         <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
       <c r="E29" s="1">
         <v>50</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17936,19 +17995,19 @@
         <v>19</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="E30" s="1">
         <v>101</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -17956,19 +18015,19 @@
         <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="E31" s="1">
         <v>-1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>
@@ -18005,7 +18064,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -18028,10 +18087,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18057,10 +18116,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -18086,10 +18145,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -18115,10 +18174,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -18144,10 +18203,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -18173,10 +18232,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -18202,10 +18261,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -18231,10 +18290,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>620</v>
+        <v>632</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -18260,10 +18319,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -18289,10 +18348,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -18318,10 +18377,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -18347,10 +18406,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -18376,10 +18435,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>625</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>613</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -18399,10 +18458,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>625</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>613</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -18422,10 +18481,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -18445,10 +18504,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -18495,7 +18554,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -18518,10 +18577,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -18547,10 +18606,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -18576,10 +18635,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -18597,7 +18656,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18605,10 +18664,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -18626,7 +18685,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18634,10 +18693,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -18655,7 +18714,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18663,10 +18722,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -18684,7 +18743,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18692,10 +18751,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -18721,10 +18780,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -18750,10 +18809,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -18771,7 +18830,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18779,10 +18838,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -18800,7 +18859,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18808,10 +18867,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -18829,7 +18888,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
@@ -18837,10 +18896,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>639</v>
+        <v>651</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -18858,7 +18917,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
@@ -18866,10 +18925,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>640</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>628</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -18889,10 +18948,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>640</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>628</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -18912,10 +18971,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -18935,10 +18994,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -19081,7 +19140,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -19104,10 +19163,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -19133,10 +19192,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -19162,10 +19221,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -19191,10 +19250,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -19220,10 +19279,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -19249,10 +19308,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -19278,10 +19337,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -19301,10 +19360,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -19324,10 +19383,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -19347,10 +19406,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -19417,10 +19476,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -19440,10 +19499,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -19463,10 +19522,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -19486,10 +19545,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -19509,10 +19568,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -19532,10 +19591,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -19555,10 +19614,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -19622,16 +19681,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -19690,22 +19749,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>34</v>
@@ -19716,16 +19775,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>42</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="21" activeTab="26"/>
+    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="53" activeTab="59"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -16539,7 +16539,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="1">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="F18" s="1">
         <v>10</v>
@@ -16562,7 +16562,7 @@
         <v>2</v>
       </c>
       <c r="E19" s="1">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="F19" s="1">
         <v>10</v>
@@ -16585,7 +16585,7 @@
         <v>3</v>
       </c>
       <c r="E20" s="1">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="F20" s="1">
         <v>10</v>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="53" activeTab="59"/>
+    <workbookView windowWidth="25600" windowHeight="11870" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="4" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2423" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2419" uniqueCount="666">
   <si>
     <t>ID</t>
   </si>
@@ -116,58 +116,58 @@
     <t>l_expect_data</t>
   </si>
   <si>
+    <t>test_type</t>
+  </si>
+  <si>
+    <t>正确获取固件版本号</t>
+  </si>
+  <si>
+    <t>get_system_version</t>
+  </si>
+  <si>
+    <t>power_on</t>
+  </si>
+  <si>
+    <t>仅上电获取固件版本号</t>
+  </si>
+  <si>
+    <t>power_on_only</t>
+  </si>
+  <si>
+    <t>断电获取固件版本号</t>
+  </si>
+  <si>
+    <t>power_off</t>
+  </si>
+  <si>
+    <t>正确获取修正版本号</t>
+  </si>
+  <si>
+    <t>get_modified_verssion</t>
+  </si>
+  <si>
+    <t>仅上电获取修正版本号</t>
+  </si>
+  <si>
+    <t>断电获取修正版本号</t>
+  </si>
+  <si>
+    <t>parameter</t>
+  </si>
+  <si>
+    <t>正确获取atom版本号</t>
+  </si>
+  <si>
+    <t>get_atom_version</t>
+  </si>
+  <si>
+    <t>仅上电获取atom版本号</t>
+  </si>
+  <si>
+    <t>断电获取atom版本号</t>
+  </si>
+  <si>
     <t>r_expect_data</t>
-  </si>
-  <si>
-    <t>test_type</t>
-  </si>
-  <si>
-    <t>正确获取固件版本号</t>
-  </si>
-  <si>
-    <t>get_system_version</t>
-  </si>
-  <si>
-    <t>power_on</t>
-  </si>
-  <si>
-    <t>仅上电获取固件版本号</t>
-  </si>
-  <si>
-    <t>power_on_only</t>
-  </si>
-  <si>
-    <t>断电获取固件版本号</t>
-  </si>
-  <si>
-    <t>power_off</t>
-  </si>
-  <si>
-    <t>正确获取修正版本号</t>
-  </si>
-  <si>
-    <t>get_modified_verssion</t>
-  </si>
-  <si>
-    <t>仅上电获取修正版本号</t>
-  </si>
-  <si>
-    <t>断电获取修正版本号</t>
-  </si>
-  <si>
-    <t>parameter</t>
-  </si>
-  <si>
-    <t>正确获取atom版本号</t>
-  </si>
-  <si>
-    <t>get_atom_version</t>
-  </si>
-  <si>
-    <t>仅上电获取atom版本号</t>
-  </si>
-  <si>
-    <t>断电获取atom版本号</t>
   </si>
   <si>
     <t>正确获取atom更正版本号</t>
@@ -2713,7 +2713,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2734,9 +2734,6 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3086,18 +3083,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="4" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="4" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="6" width="14.7777777777778" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7777777777778" customWidth="1"/>
+    <col min="4" max="4" width="14.7818181818182" customWidth="1"/>
+    <col min="5" max="5" width="14.7818181818182" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.7818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:7">
+    <row r="1" ht="34" customHeight="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3113,72 +3110,60 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" ht="28.8" spans="1:7">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="6">
-        <v>2</v>
-      </c>
-      <c r="F2" s="6">
-        <v>2</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="28.8" spans="1:7">
+        <v>1.1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" ht="28" spans="1:6">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1.1</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="7">
-        <v>2</v>
-      </c>
-      <c r="F3" s="7">
-        <v>2</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" ht="28.8" spans="1:7">
+    </row>
+    <row r="4" ht="28" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="6">
+        <v>1.1</v>
+      </c>
+      <c r="F4" t="s">
         <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="7">
-        <v>2</v>
-      </c>
-      <c r="F4" s="7">
-        <v>2</v>
-      </c>
-      <c r="G4" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -3191,18 +3176,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.6666666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.6636363636364" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="6" width="9" style="2"/>
-    <col min="7" max="7" width="15.1111111111111" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.1090909090909" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3213,16 +3198,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -3242,10 +3227,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="28.8" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -3262,10 +3247,10 @@
         <v>0</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" ht="43.2" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="42" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3282,10 +3267,10 @@
         <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" ht="28.8" spans="1:7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" ht="28" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -3315,18 +3300,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.6666666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.6636363636364" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="6" width="9" style="2"/>
-    <col min="7" max="7" width="15.1111111111111" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.1090909090909" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3337,16 +3322,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -3366,10 +3351,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -3386,10 +3371,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3406,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3419,13 +3404,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="7" width="16.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="7" width="16.3363636363636" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -3440,16 +3425,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -3460,7 +3445,7 @@
         <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -3472,7 +3457,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:7">
+    <row r="3" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -3480,7 +3465,7 @@
         <v>66</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" s="5">
         <v>2</v>
@@ -3492,7 +3477,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:7">
+    <row r="4" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3500,7 +3485,7 @@
         <v>67</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" s="1">
         <v>-1</v>
@@ -3522,13 +3507,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="30.6666666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.6636363636364" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="7" width="16.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="7" width="16.3363636363636" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -3543,16 +3528,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -3575,7 +3560,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -3605,16 +3590,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.8888888888889" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.8909090909091" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:7">
+    <row r="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3625,19 +3610,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" ht="43.2" spans="1:7">
+    </row>
+    <row r="2" ht="42" spans="1:7">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -3657,7 +3642,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" ht="43.2" spans="1:7">
+    <row r="3" ht="42" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -3687,19 +3672,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="25.7777777777778" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.2222222222222" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.4444444444444" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.7818181818182" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.2181818181818" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.4454545454545" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3710,16 +3695,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -3739,10 +3724,10 @@
         <v>80</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="86.4" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" ht="84" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -3759,7 +3744,7 @@
         <v>83</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3772,18 +3757,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.3333333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.3363636363636" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="17.6666666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6636363636364" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1090909090909" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3794,13 +3779,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
@@ -3830,19 +3815,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.3333333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.3363636363636" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="17.6666666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6636363636364" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1090909090909" style="1" customWidth="1"/>
     <col min="7" max="7" width="14" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3853,16 +3838,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -3888,7 +3873,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="28.8" spans="1:7">
+    <row r="3" customFormat="1" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -3911,7 +3896,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:7">
+    <row r="4" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3934,7 +3919,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:7">
+    <row r="5" ht="28" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -3957,7 +3942,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" ht="28.8" spans="1:7">
+    <row r="6" ht="28" spans="1:7">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -3990,19 +3975,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.3333333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.3363636363636" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="17.6666666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6636363636364" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1090909090909" style="1" customWidth="1"/>
     <col min="7" max="7" width="14" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4013,16 +3998,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -4046,7 +4031,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="43.2" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="42" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -4077,15 +4062,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4102,7 +4087,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
@@ -4125,7 +4110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:6">
+    <row r="3" ht="28" spans="1:6">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -4145,7 +4130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:6">
+    <row r="4" ht="28" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -4165,7 +4150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:6">
+    <row r="5" ht="28" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -4185,7 +4170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="28.8" spans="1:6">
+    <row r="6" ht="28" spans="1:6">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -4205,7 +4190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" ht="28.8" spans="1:6">
+    <row r="7" ht="28" spans="1:6">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -4225,7 +4210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" ht="28.8" spans="1:6">
+    <row r="8" ht="28" spans="1:6">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -4245,7 +4230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" ht="28.8" spans="1:6">
+    <row r="9" ht="28" spans="1:6">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -4259,7 +4244,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" ht="28.8" spans="1:6">
+    <row r="10" ht="28" spans="1:6">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -4282,20 +4267,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="22.5555555555556" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.6666666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.3333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5545454545455" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.6636363636364" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.3363636363636" style="1" customWidth="1"/>
     <col min="5" max="5" width="19" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.2222222222222" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.7777777777778" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="13.7818181818182" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1" spans="1:7">
+    <row r="1" ht="48" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4311,71 +4295,59 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1" spans="1:7">
+    </row>
+    <row r="2" ht="32" customHeight="1" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="E2" s="2">
-        <v>3</v>
-      </c>
-      <c r="F2" s="2">
-        <v>3</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1" spans="1:7">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2">
-        <v>3</v>
-      </c>
-      <c r="F3" s="2">
-        <v>3</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1" spans="1:7">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2">
-        <v>3</v>
-      </c>
-      <c r="F4" s="2">
-        <v>3</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -4394,15 +4366,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4419,10 +4391,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -4448,7 +4420,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -4471,7 +4443,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -4494,7 +4466,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -4517,7 +4489,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -4540,7 +4512,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -4563,7 +4535,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="8" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -4586,7 +4558,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:7">
+    <row r="9" s="1" customFormat="1" ht="42" spans="1:7">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -4603,7 +4575,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:7">
+    <row r="10" s="1" customFormat="1" ht="42" spans="1:7">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -4630,15 +4602,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4655,10 +4627,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -4684,7 +4656,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -4707,7 +4679,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -4730,7 +4702,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -4753,7 +4725,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -4776,7 +4748,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -4799,7 +4771,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="8" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -4822,7 +4794,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:7">
+    <row r="9" s="1" customFormat="1" ht="42" spans="1:7">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -4839,7 +4811,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:7">
+    <row r="10" s="1" customFormat="1" ht="42" spans="1:7">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -4866,15 +4838,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4888,16 +4860,16 @@
         <v>93</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
@@ -4926,7 +4898,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -4952,7 +4924,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -4978,7 +4950,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -5004,7 +4976,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -5030,7 +5002,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -5056,7 +5028,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -5082,7 +5054,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -5102,7 +5074,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -5122,7 +5094,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" ht="43.2" spans="1:8">
+    <row r="11" ht="42" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -5142,7 +5114,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" ht="43.2" spans="1:8">
+    <row r="12" ht="42" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -5162,7 +5134,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" ht="43.2" spans="1:8">
+    <row r="13" ht="42" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -5182,7 +5154,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" ht="43.2" spans="1:8">
+    <row r="14" ht="42" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -5202,7 +5174,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" ht="43.2" spans="1:8">
+    <row r="15" ht="42" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -5222,7 +5194,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" ht="43.2" spans="1:8">
+    <row r="16" ht="42" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -5242,7 +5214,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" ht="43.2" spans="1:8">
+    <row r="17" ht="42" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -5272,15 +5244,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5294,16 +5266,16 @@
         <v>93</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
@@ -5332,7 +5304,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -5358,7 +5330,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -5384,7 +5356,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -5410,7 +5382,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -5436,7 +5408,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -5462,7 +5434,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -5488,7 +5460,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -5508,7 +5480,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -5528,7 +5500,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -5548,7 +5520,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" customFormat="1" ht="43.2" spans="1:8">
+    <row r="12" customFormat="1" ht="42" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -5570,7 +5542,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" customFormat="1" ht="43.2" spans="1:8">
+    <row r="13" customFormat="1" ht="42" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -5592,7 +5564,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" customFormat="1" ht="43.2" spans="1:8">
+    <row r="14" customFormat="1" ht="42" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -5614,7 +5586,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" customFormat="1" ht="43.2" spans="1:8">
+    <row r="15" customFormat="1" ht="42" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -5636,7 +5608,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" customFormat="1" ht="43.2" spans="1:8">
+    <row r="16" customFormat="1" ht="42" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -5658,7 +5630,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" customFormat="1" ht="43.2" spans="1:8">
+    <row r="17" customFormat="1" ht="42" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -5690,18 +5662,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5712,16 +5684,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -5755,13 +5727,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="32.7777777777778" customWidth="1"/>
-    <col min="5" max="6" width="17.2222222222222" customWidth="1"/>
+    <col min="4" max="4" width="32.7818181818182" customWidth="1"/>
+    <col min="5" max="6" width="17.2181818181818" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
@@ -5786,10 +5758,10 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="51" customHeight="1" spans="1:8">
@@ -5870,7 +5842,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" customFormat="1" ht="28.8" spans="1:8">
+    <row r="5" customFormat="1" ht="28" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -5893,7 +5865,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="6" customFormat="1" ht="28.8" spans="1:8">
+    <row r="6" customFormat="1" ht="28" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -5916,7 +5888,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="7" customFormat="1" ht="28.8" spans="1:8">
+    <row r="7" customFormat="1" ht="28" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -5939,7 +5911,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="8" customFormat="1" ht="28.8" spans="1:8">
+    <row r="8" customFormat="1" ht="28" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -5962,7 +5934,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="9" customFormat="1" ht="28.8" spans="1:8">
+    <row r="9" customFormat="1" ht="28" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -5985,7 +5957,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="10" customFormat="1" ht="28.8" spans="1:8">
+    <row r="10" customFormat="1" ht="28" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -6008,7 +5980,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="11" customFormat="1" ht="28.8" spans="1:8">
+    <row r="11" customFormat="1" ht="28" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -6031,7 +6003,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="12" customFormat="1" ht="28.8" spans="1:8">
+    <row r="12" customFormat="1" ht="28" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -6054,7 +6026,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="13" customFormat="1" ht="28.8" spans="1:8">
+    <row r="13" customFormat="1" ht="28" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -6077,7 +6049,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="14" customFormat="1" ht="28.8" spans="1:8">
+    <row r="14" customFormat="1" ht="28" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -6100,7 +6072,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="15" customFormat="1" ht="28.8" spans="1:8">
+    <row r="15" customFormat="1" ht="28" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -6123,7 +6095,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="16" customFormat="1" ht="28.8" spans="1:8">
+    <row r="16" customFormat="1" ht="28" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -6146,7 +6118,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="17" customFormat="1" ht="28.8" spans="1:8">
+    <row r="17" customFormat="1" ht="28" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -6169,7 +6141,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="18" customFormat="1" ht="28.8" spans="1:8">
+    <row r="18" customFormat="1" ht="28" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -6192,7 +6164,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="19" customFormat="1" ht="28.8" spans="1:8">
+    <row r="19" customFormat="1" ht="28" spans="1:8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -6215,7 +6187,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="20" customFormat="1" ht="28.8" spans="1:8">
+    <row r="20" customFormat="1" ht="28" spans="1:8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -6238,7 +6210,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="21" customFormat="1" ht="28.8" spans="1:8">
+    <row r="21" customFormat="1" ht="28" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -6261,7 +6233,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="22" customFormat="1" ht="28.8" spans="1:8">
+    <row r="22" customFormat="1" ht="28" spans="1:8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -6284,7 +6256,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="23" customFormat="1" ht="28.8" spans="1:8">
+    <row r="23" customFormat="1" ht="28" spans="1:8">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -6307,7 +6279,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="24" customFormat="1" ht="28.8" spans="1:8">
+    <row r="24" customFormat="1" ht="28" spans="1:8">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -6330,7 +6302,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="25" customFormat="1" ht="28.8" spans="1:8">
+    <row r="25" customFormat="1" ht="28" spans="1:8">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -6353,7 +6325,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="26" customFormat="1" ht="28.8" spans="1:8">
+    <row r="26" customFormat="1" ht="28" spans="1:8">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -6376,7 +6348,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="27" customFormat="1" ht="28.8" spans="1:8">
+    <row r="27" customFormat="1" ht="28" spans="1:8">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -6399,7 +6371,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="28" customFormat="1" ht="28.8" spans="1:8">
+    <row r="28" customFormat="1" ht="28" spans="1:8">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -6422,7 +6394,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" customFormat="1" ht="28.8" spans="1:8">
+    <row r="29" customFormat="1" ht="28" spans="1:8">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -6445,7 +6417,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="30" customFormat="1" ht="28.8" spans="1:8">
+    <row r="30" customFormat="1" ht="28" spans="1:8">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -6468,7 +6440,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="31" customFormat="1" ht="28.8" spans="1:8">
+    <row r="31" customFormat="1" ht="28" spans="1:8">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -6491,7 +6463,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="32" customFormat="1" ht="28.8" spans="1:8">
+    <row r="32" customFormat="1" ht="28" spans="1:8">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -6514,7 +6486,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="33" customFormat="1" ht="43.2" spans="1:8">
+    <row r="33" customFormat="1" ht="42" spans="1:8">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -6534,7 +6506,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" customFormat="1" ht="43.2" spans="1:8">
+    <row r="34" customFormat="1" ht="42" spans="1:8">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -6554,7 +6526,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" customFormat="1" ht="43.2" spans="1:8">
+    <row r="35" customFormat="1" ht="42" spans="1:8">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -6574,7 +6546,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" customFormat="1" ht="43.2" spans="1:8">
+    <row r="36" customFormat="1" ht="42" spans="1:8">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -6594,7 +6566,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="37" customFormat="1" ht="43.2" spans="1:8">
+    <row r="37" customFormat="1" ht="42" spans="1:8">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -6614,7 +6586,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" customFormat="1" ht="43.2" spans="1:8">
+    <row r="38" customFormat="1" ht="42" spans="1:8">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -6634,7 +6606,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="39" customFormat="1" ht="43.2" spans="1:8">
+    <row r="39" customFormat="1" ht="42" spans="1:8">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -6654,7 +6626,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="40" customFormat="1" ht="43.2" spans="1:8">
+    <row r="40" customFormat="1" ht="42" spans="1:8">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -6674,7 +6646,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="41" customFormat="1" ht="43.2" spans="1:8">
+    <row r="41" customFormat="1" ht="42" spans="1:8">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -6694,7 +6666,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" customFormat="1" ht="43.2" spans="1:8">
+    <row r="42" customFormat="1" ht="42" spans="1:8">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -6714,7 +6686,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" customFormat="1" ht="43.2" spans="1:8">
+    <row r="43" customFormat="1" ht="42" spans="1:8">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -6734,7 +6706,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="43.2" spans="1:8">
+    <row r="44" customFormat="1" ht="42" spans="1:8">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -6754,7 +6726,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" customFormat="1" ht="43.2" spans="1:8">
+    <row r="45" customFormat="1" ht="42" spans="1:8">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -6774,7 +6746,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="46" customFormat="1" ht="43.2" spans="1:8">
+    <row r="46" customFormat="1" ht="42" spans="1:8">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -6794,7 +6766,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="47" customFormat="1" ht="43.2" spans="1:8">
+    <row r="47" customFormat="1" ht="42" spans="1:8">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -6814,7 +6786,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="48" customFormat="1" ht="43.2" spans="1:8">
+    <row r="48" customFormat="1" ht="42" spans="1:8">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -6834,7 +6806,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="49" customFormat="1" ht="43.2" spans="1:8">
+    <row r="49" customFormat="1" ht="42" spans="1:8">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -6864,15 +6836,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -6889,10 +6861,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -6918,7 +6890,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -6941,7 +6913,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -6964,7 +6936,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -6987,7 +6959,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -7010,7 +6982,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -7033,7 +7005,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="8" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -7056,7 +7028,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="9" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -7073,7 +7045,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="10" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -7100,13 +7072,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="5" width="32.7777777777778" style="4" customWidth="1"/>
-    <col min="6" max="7" width="17.2222222222222" style="4" customWidth="1"/>
+    <col min="4" max="5" width="32.7818181818182" style="4" customWidth="1"/>
+    <col min="6" max="7" width="17.2181818181818" style="4" customWidth="1"/>
     <col min="8" max="8" width="18" style="4" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
     <col min="16384" max="16384" width="9" style="1"/>
@@ -7135,10 +7107,10 @@
         <v>4</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="51" customHeight="1" spans="1:9">
@@ -7228,7 +7200,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" customFormat="1" ht="28.8" spans="1:9">
+    <row r="5" customFormat="1" ht="28" spans="1:9">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -7255,7 +7227,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="6" customFormat="1" ht="28.8" spans="1:9">
+    <row r="6" customFormat="1" ht="28" spans="1:9">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -7282,7 +7254,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="7" customFormat="1" ht="28.8" spans="1:9">
+    <row r="7" customFormat="1" ht="28" spans="1:9">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -7309,7 +7281,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="8" customFormat="1" ht="28.8" spans="1:9">
+    <row r="8" customFormat="1" ht="28" spans="1:9">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -7336,7 +7308,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="9" customFormat="1" ht="28.8" spans="1:9">
+    <row r="9" customFormat="1" ht="28" spans="1:9">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -7363,7 +7335,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="10" customFormat="1" ht="28.8" spans="1:9">
+    <row r="10" customFormat="1" ht="28" spans="1:9">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -7390,7 +7362,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="11" customFormat="1" ht="28.8" spans="1:9">
+    <row r="11" customFormat="1" ht="28" spans="1:9">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -7417,7 +7389,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="12" customFormat="1" ht="28.8" spans="1:9">
+    <row r="12" customFormat="1" ht="28" spans="1:9">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -7444,7 +7416,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="13" customFormat="1" ht="28.8" spans="1:9">
+    <row r="13" customFormat="1" ht="28" spans="1:9">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -7471,7 +7443,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="14" customFormat="1" ht="28.8" spans="1:9">
+    <row r="14" customFormat="1" ht="28" spans="1:9">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -7498,7 +7470,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="15" customFormat="1" ht="28.8" spans="1:9">
+    <row r="15" customFormat="1" ht="28" spans="1:9">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -7525,7 +7497,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="16" customFormat="1" ht="28.8" spans="1:9">
+    <row r="16" customFormat="1" ht="28" spans="1:9">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -7552,7 +7524,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="17" customFormat="1" ht="28.8" spans="1:9">
+    <row r="17" customFormat="1" ht="28" spans="1:9">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -7579,7 +7551,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="18" customFormat="1" ht="28.8" spans="1:9">
+    <row r="18" customFormat="1" ht="28" spans="1:9">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -7606,7 +7578,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="19" customFormat="1" ht="28.8" spans="1:9">
+    <row r="19" customFormat="1" ht="28" spans="1:9">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -7633,7 +7605,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="20" customFormat="1" ht="28.8" spans="1:9">
+    <row r="20" customFormat="1" ht="28" spans="1:9">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -7660,7 +7632,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="21" customFormat="1" ht="28.8" spans="1:9">
+    <row r="21" customFormat="1" ht="28" spans="1:9">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -7687,7 +7659,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="22" customFormat="1" ht="28.8" spans="1:9">
+    <row r="22" customFormat="1" ht="28" spans="1:9">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -7714,7 +7686,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="23" customFormat="1" ht="28.8" spans="1:9">
+    <row r="23" customFormat="1" ht="28" spans="1:9">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -7741,7 +7713,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="24" customFormat="1" ht="28.8" spans="1:9">
+    <row r="24" customFormat="1" ht="28" spans="1:9">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -7768,7 +7740,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="25" customFormat="1" ht="28.8" spans="1:9">
+    <row r="25" customFormat="1" ht="28" spans="1:9">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -7795,7 +7767,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="26" customFormat="1" ht="28.8" spans="1:9">
+    <row r="26" customFormat="1" ht="28" spans="1:9">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -7822,7 +7794,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="27" customFormat="1" ht="28.8" spans="1:9">
+    <row r="27" customFormat="1" ht="28" spans="1:9">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -7849,7 +7821,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="28" customFormat="1" ht="28.8" spans="1:9">
+    <row r="28" customFormat="1" ht="28" spans="1:9">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -7876,7 +7848,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" customFormat="1" ht="28.8" spans="1:9">
+    <row r="29" customFormat="1" ht="28" spans="1:9">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -7903,7 +7875,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="30" customFormat="1" ht="28.8" spans="1:9">
+    <row r="30" customFormat="1" ht="28" spans="1:9">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -7930,7 +7902,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="31" customFormat="1" ht="28.8" spans="1:9">
+    <row r="31" customFormat="1" ht="28" spans="1:9">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -7957,7 +7929,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="32" customFormat="1" ht="28.8" spans="1:9">
+    <row r="32" customFormat="1" ht="28" spans="1:9">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -7984,7 +7956,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="33" customFormat="1" ht="28.8" spans="1:9">
+    <row r="33" customFormat="1" ht="28" spans="1:9">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -8011,7 +7983,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="34" customFormat="1" ht="28.8" spans="1:9">
+    <row r="34" customFormat="1" ht="28" spans="1:9">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -8038,7 +8010,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="35" customFormat="1" ht="28.8" spans="1:9">
+    <row r="35" customFormat="1" ht="28" spans="1:9">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -8065,7 +8037,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="36" customFormat="1" ht="28.8" spans="1:9">
+    <row r="36" customFormat="1" ht="28" spans="1:9">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -8092,7 +8064,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="37" customFormat="1" ht="28.8" spans="1:9">
+    <row r="37" customFormat="1" ht="28" spans="1:9">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -8119,7 +8091,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="38" customFormat="1" ht="28.8" spans="1:9">
+    <row r="38" customFormat="1" ht="28" spans="1:9">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -8146,7 +8118,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="39" customFormat="1" ht="43.2" spans="1:9">
+    <row r="39" customFormat="1" ht="42" spans="1:9">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -8171,7 +8143,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="40" customFormat="1" ht="43.2" spans="1:9">
+    <row r="40" customFormat="1" ht="42" spans="1:9">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -8196,7 +8168,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="41" customFormat="1" ht="43.2" spans="1:9">
+    <row r="41" customFormat="1" ht="42" spans="1:9">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -8221,7 +8193,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" customFormat="1" ht="43.2" spans="1:9">
+    <row r="42" customFormat="1" ht="42" spans="1:9">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -8246,7 +8218,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" customFormat="1" ht="43.2" spans="1:9">
+    <row r="43" customFormat="1" ht="42" spans="1:9">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -8271,7 +8243,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="43.2" spans="1:9">
+    <row r="44" customFormat="1" ht="42" spans="1:9">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -8296,7 +8268,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" customFormat="1" ht="43.2" spans="1:9">
+    <row r="45" customFormat="1" ht="42" spans="1:9">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -8321,7 +8293,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="46" customFormat="1" ht="43.2" spans="1:9">
+    <row r="46" customFormat="1" ht="42" spans="1:9">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -8346,7 +8318,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="47" customFormat="1" ht="43.2" spans="1:9">
+    <row r="47" customFormat="1" ht="42" spans="1:9">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -8371,7 +8343,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="48" customFormat="1" ht="43.2" spans="1:9">
+    <row r="48" customFormat="1" ht="42" spans="1:9">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -8396,7 +8368,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="49" customFormat="1" ht="43.2" spans="1:9">
+    <row r="49" customFormat="1" ht="42" spans="1:9">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -8421,7 +8393,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="50" customFormat="1" ht="43.2" spans="1:9">
+    <row r="50" customFormat="1" ht="42" spans="1:9">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -8446,7 +8418,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" customFormat="1" ht="43.2" spans="1:9">
+    <row r="51" customFormat="1" ht="42" spans="1:9">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -8471,7 +8443,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="52" customFormat="1" ht="43.2" spans="1:9">
+    <row r="52" customFormat="1" ht="42" spans="1:9">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -8496,7 +8468,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="53" customFormat="1" ht="43.2" spans="1:9">
+    <row r="53" customFormat="1" ht="42" spans="1:9">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -8521,7 +8493,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="54" customFormat="1" ht="43.2" spans="1:9">
+    <row r="54" customFormat="1" ht="42" spans="1:9">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -8546,7 +8518,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="55" customFormat="1" ht="43.2" spans="1:9">
+    <row r="55" customFormat="1" ht="42" spans="1:9">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -8571,7 +8543,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" ht="43.2" spans="1:9">
+    <row r="56" ht="42" spans="1:9">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -8594,7 +8566,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="57" ht="43.2" spans="1:9">
+    <row r="57" ht="42" spans="1:9">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -8617,7 +8589,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="58" ht="43.2" spans="1:9">
+    <row r="58" ht="42" spans="1:9">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -8640,7 +8612,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="59" ht="43.2" spans="1:9">
+    <row r="59" ht="42" spans="1:9">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -8663,7 +8635,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="60" ht="43.2" spans="1:9">
+    <row r="60" ht="42" spans="1:9">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -8686,7 +8658,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="61" ht="43.2" spans="1:9">
+    <row r="61" ht="42" spans="1:9">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -8719,17 +8691,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="6" width="48.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="6" width="48.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8740,16 +8712,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -8775,7 +8747,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:7">
+    <row r="3" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -8808,18 +8780,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="46.7777777777778" style="1" customWidth="1"/>
-    <col min="5" max="6" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46.7818181818182" style="1" customWidth="1"/>
+    <col min="5" max="6" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="7" width="18" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8830,7 +8802,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>157</v>
@@ -8839,10 +8811,10 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
@@ -8871,7 +8843,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -8897,7 +8869,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" ht="43.2" spans="1:8">
+    <row r="4" ht="42" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -8923,7 +8895,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" ht="43.2" spans="1:8">
+    <row r="5" ht="42" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -8949,7 +8921,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" ht="28.8" spans="1:8">
+    <row r="6" ht="28" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -8969,7 +8941,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" ht="28.8" spans="1:8">
+    <row r="7" ht="28" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -8989,7 +8961,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" ht="28.8" spans="1:8">
+    <row r="8" ht="28" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -9009,7 +8981,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="9" ht="28.8" spans="1:8">
+    <row r="9" ht="28" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -9029,7 +9001,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="10" ht="28.8" spans="1:8">
+    <row r="10" ht="28" spans="1:8">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -9049,7 +9021,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="11" ht="28.8" spans="1:8">
+    <row r="11" ht="28" spans="1:8">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -9069,7 +9041,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="12" ht="28.8" spans="1:8">
+    <row r="12" ht="28" spans="1:8">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -9089,7 +9061,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" ht="28.8" spans="1:8">
+    <row r="13" ht="28" spans="1:8">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -9109,7 +9081,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" ht="28.8" spans="1:8">
+    <row r="14" ht="28" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -9129,7 +9101,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" ht="28.8" spans="1:8">
+    <row r="15" ht="28" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -9149,7 +9121,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" ht="28.8" spans="1:8">
+    <row r="16" ht="28" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -9169,7 +9141,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" ht="28.8" spans="1:8">
+    <row r="17" ht="28" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -9189,7 +9161,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" ht="28.8" spans="1:8">
+    <row r="18" ht="28" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -9209,7 +9181,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" ht="28.8" spans="1:8">
+    <row r="19" ht="28" spans="1:8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -9229,7 +9201,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" ht="28.8" spans="1:8">
+    <row r="20" ht="28" spans="1:8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -9249,7 +9221,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" ht="28.8" spans="1:8">
+    <row r="21" ht="28" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -9278,18 +9250,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="4" customWidth="1"/>
-    <col min="2" max="2" width="23.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="4" customWidth="1"/>
+    <col min="2" max="2" width="23.2181818181818" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="6" width="9" style="4"/>
-    <col min="7" max="7" width="13.7777777777778" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="4"/>
+    <col min="6" max="6" width="13.7818181818182" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:7">
+    <row r="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9300,65 +9272,59 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:7">
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
         <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="2">
         <v>1.2</v>
       </c>
-      <c r="F2" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:7">
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:6">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:7">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:6">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -9372,18 +9338,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="1"/>
-    <col min="2" max="2" width="22.1111111111111" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.8888888888889" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.88888888888889" style="1"/>
-    <col min="5" max="5" width="17.3333333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.89090909090909" style="1"/>
+    <col min="2" max="2" width="22.1090909090909" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.8909090909091" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.89090909090909" style="1"/>
+    <col min="5" max="5" width="17.3363636363636" style="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88888888888889" style="1"/>
+    <col min="7" max="16384" width="8.89090909090909" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9397,7 +9363,7 @@
         <v>327</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>157</v>
@@ -9406,10 +9372,10 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -9586,7 +9552,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="8" ht="28.8" spans="1:9">
+    <row r="8" ht="28" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -9609,7 +9575,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" ht="28.8" spans="1:9">
+    <row r="9" ht="28" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -9632,7 +9598,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" ht="28.8" spans="1:9">
+    <row r="10" ht="28" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -9655,7 +9621,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="11" ht="28.8" spans="1:9">
+    <row r="11" ht="28" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -9678,7 +9644,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="12" ht="28.8" spans="1:9">
+    <row r="12" ht="28" spans="1:9">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -9701,7 +9667,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="13" ht="28.8" spans="1:9">
+    <row r="13" ht="28" spans="1:9">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -9724,7 +9690,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="14" ht="28.8" spans="1:9">
+    <row r="14" ht="28" spans="1:9">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -9747,7 +9713,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" ht="28.8" spans="1:9">
+    <row r="15" ht="28" spans="1:9">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -9770,7 +9736,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" ht="28.8" spans="1:9">
+    <row r="16" ht="28" spans="1:9">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -9793,7 +9759,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" ht="28.8" spans="1:9">
+    <row r="17" ht="28" spans="1:9">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -9816,7 +9782,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" ht="28.8" spans="1:9">
+    <row r="18" ht="28" spans="1:9">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -9839,7 +9805,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" ht="28.8" spans="1:9">
+    <row r="19" ht="28" spans="1:9">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -9862,7 +9828,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" ht="28.8" spans="1:9">
+    <row r="20" ht="28" spans="1:9">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -9885,7 +9851,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" ht="28.8" spans="1:9">
+    <row r="21" ht="28" spans="1:9">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -9908,7 +9874,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" ht="28.8" spans="1:9">
+    <row r="22" ht="28" spans="1:9">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -9931,7 +9897,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" ht="28.8" spans="1:9">
+    <row r="23" ht="28" spans="1:9">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -9954,7 +9920,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" ht="28.8" spans="1:9">
+    <row r="24" ht="28" spans="1:9">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -9977,7 +9943,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" ht="28.8" spans="1:9">
+    <row r="25" ht="28" spans="1:9">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -10010,15 +9976,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.8888888888889" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.8909090909091" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -10033,16 +9999,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -10068,7 +10034,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -10091,7 +10057,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:7">
+    <row r="4" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -10108,7 +10074,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:7">
+    <row r="5" ht="28" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -10135,15 +10101,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.8888888888889" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.8909090909091" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -10158,16 +10124,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -10191,7 +10157,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -10222,15 +10188,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.8888888888889" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.8909090909091" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -10245,16 +10211,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -10280,7 +10246,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="43.2" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="42" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -10303,7 +10269,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -10320,7 +10286,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:7">
+    <row r="5" ht="28" spans="1:7">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -10347,15 +10313,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.8888888888889" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.8909090909091" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -10370,16 +10336,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -10405,7 +10371,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="43.2" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="42" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -10428,7 +10394,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -10445,7 +10411,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -10472,15 +10438,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="38.5555555555556" style="1" customWidth="1"/>
-    <col min="5" max="6" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="38.5545454545455" style="1" customWidth="1"/>
+    <col min="5" max="6" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="7" width="18" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.8888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.8909090909091" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -10495,7 +10461,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>365</v>
@@ -10504,10 +10470,10 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="50" customHeight="1" spans="1:8">
@@ -10536,7 +10502,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="57.6" spans="1:8">
+    <row r="3" s="1" customFormat="1" ht="56" spans="1:8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -10562,7 +10528,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="57.6" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="56" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -10588,7 +10554,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="57.6" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="56" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -10614,7 +10580,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" ht="57.6" spans="1:8">
+    <row r="6" ht="56" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -10666,7 +10632,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="8" ht="57.6" spans="1:8">
+    <row r="8" ht="56" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -10692,7 +10658,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="9" ht="57.6" spans="1:8">
+    <row r="9" ht="56" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -10718,7 +10684,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="10" ht="72" spans="1:8">
+    <row r="10" ht="70" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -10741,7 +10707,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="11" ht="57.6" spans="1:8">
+    <row r="11" ht="56" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -10764,7 +10730,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="12" ht="57.6" spans="1:8">
+    <row r="12" ht="56" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -10787,7 +10753,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="13" ht="28.8" spans="1:8">
+    <row r="13" ht="28" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -10807,7 +10773,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" ht="28.8" spans="1:8">
+    <row r="14" ht="28" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -10837,15 +10803,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.8888888888889" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.8909090909091" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -10860,16 +10826,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -10892,7 +10858,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="43.2" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="42" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -10923,15 +10889,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.8888888888889" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.8909090909091" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -10946,16 +10912,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -10981,7 +10947,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:7">
+    <row r="3" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -11048,15 +11014,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="6" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="6" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="7" width="18" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.8888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.8909090909091" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -11071,7 +11037,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>365</v>
@@ -11080,10 +11046,10 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
@@ -11112,7 +11078,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:8">
+    <row r="3" ht="28" spans="1:8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -11138,7 +11104,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:8">
+    <row r="4" ht="28" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -11158,7 +11124,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:8">
+    <row r="5" ht="28" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -11178,7 +11144,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" ht="28.8" spans="1:8">
+    <row r="6" ht="28" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -11198,7 +11164,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" ht="28.8" spans="1:8">
+    <row r="7" ht="28" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -11320,15 +11286,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.8888888888889" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.8909090909091" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -11349,10 +11315,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -11378,7 +11344,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -11445,17 +11411,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="4" customWidth="1"/>
-    <col min="2" max="2" width="23.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="4" customWidth="1"/>
+    <col min="2" max="2" width="23.2181818181818" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="6" width="9" style="4"/>
-    <col min="7" max="7" width="13.7777777777778" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7818181818182" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:7">
+    <row r="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -11466,16 +11432,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:7">
@@ -11486,7 +11452,7 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="2">
@@ -11496,7 +11462,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="34" customHeight="1" spans="1:7">
@@ -11507,12 +11473,12 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="1" ht="34" customHeight="1" spans="1:7">
@@ -11523,12 +11489,12 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -11541,15 +11507,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="6" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="6" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="7" width="18" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.8888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.8909090909091" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -11564,7 +11530,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>365</v>
@@ -11573,10 +11539,10 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
@@ -11605,7 +11571,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -11631,7 +11597,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -11651,7 +11617,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -11671,7 +11637,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -11691,7 +11657,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -11751,7 +11717,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -11777,7 +11743,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -11813,16 +11779,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="5" width="17.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="5" width="17.3363636363636" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -11836,10 +11802,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
@@ -11872,16 +11838,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="5" width="17.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="5" width="17.3363636363636" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -11895,10 +11861,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
@@ -11931,18 +11897,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -11953,16 +11919,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -11995,18 +11961,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -12017,16 +11983,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -12059,18 +12025,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -12081,16 +12047,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -12123,18 +12089,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -12145,16 +12111,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -12187,18 +12153,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="7" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="7" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="8" max="8" width="18" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -12221,10 +12187,10 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:9">
@@ -12256,7 +12222,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:9">
+    <row r="3" ht="28" spans="1:9">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -12285,7 +12251,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:9">
+    <row r="4" ht="28" spans="1:9">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -12314,7 +12280,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:9">
+    <row r="5" ht="28" spans="1:9">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -12347,18 +12313,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -12369,16 +12335,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -12411,18 +12377,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -12433,16 +12399,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -12468,7 +12434,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:7">
+    <row r="3" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -12491,7 +12457,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:7">
+    <row r="4" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -12508,7 +12474,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:7">
+    <row r="5" ht="28" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -12534,18 +12500,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="4" customWidth="1"/>
-    <col min="2" max="2" width="22.3333333333333" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="4" customWidth="1"/>
+    <col min="2" max="2" width="22.3363636363636" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="16.5555555555556" customWidth="1"/>
-    <col min="5" max="6" width="14.1111111111111" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="4" max="4" width="16.5545454545455" customWidth="1"/>
+    <col min="5" max="5" width="14.1090909090909" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -12561,14 +12527,11 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -12580,16 +12543,13 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="2">
-        <v>4501</v>
-      </c>
-      <c r="F2" s="2">
-        <v>4502</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>4500</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -12600,16 +12560,13 @@
         <v>27</v>
       </c>
       <c r="E3" s="2">
-        <v>4501</v>
-      </c>
-      <c r="F3" s="2">
-        <v>4502</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>4500</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -12620,13 +12577,10 @@
         <v>27</v>
       </c>
       <c r="E4" s="2">
-        <v>4501</v>
-      </c>
-      <c r="F4" s="2">
-        <v>4502</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>13</v>
+        <v>4500</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -12639,18 +12593,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="4" width="18" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="7" width="18" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -12664,16 +12618,16 @@
         <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
@@ -12702,7 +12656,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="3" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -12728,7 +12682,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -12754,7 +12708,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -12780,7 +12734,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -12806,7 +12760,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -12832,7 +12786,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -12858,7 +12812,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -12878,7 +12832,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -12898,7 +12852,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" ht="43.2" spans="1:8">
+    <row r="11" ht="42" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -12918,7 +12872,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" ht="43.2" spans="1:8">
+    <row r="12" ht="42" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -12938,7 +12892,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" ht="43.2" spans="1:8">
+    <row r="13" ht="42" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -12974,18 +12928,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -12996,16 +12950,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -13039,18 +12993,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="4" width="18" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="7" width="18" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -13064,16 +13018,16 @@
         <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
@@ -13102,7 +13056,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="3" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -13128,7 +13082,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -13154,7 +13108,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -13180,7 +13134,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -13206,7 +13160,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -13232,7 +13186,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -13258,7 +13212,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -13278,7 +13232,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -13298,7 +13252,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -13318,7 +13272,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="12" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -13338,7 +13292,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="13" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -13374,18 +13328,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -13396,16 +13350,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -13441,18 +13395,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -13463,16 +13417,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -13505,18 +13459,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -13527,16 +13481,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -13562,7 +13516,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:7">
+    <row r="3" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -13579,7 +13533,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:7">
+    <row r="4" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -13596,7 +13550,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:7">
+    <row r="5" ht="28" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -13629,13 +13583,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="4" width="18" style="1" customWidth="1"/>
-    <col min="5" max="5" width="26.6666666666667" style="1" customWidth="1"/>
-    <col min="6" max="7" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26.6636363636364" style="1" customWidth="1"/>
+    <col min="6" max="7" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="8" max="8" width="18" style="1" customWidth="1"/>
     <col min="9" max="9" width="13" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
@@ -13655,7 +13609,7 @@
         <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>157</v>
@@ -13664,10 +13618,10 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="51" customHeight="1" spans="1:9">
@@ -14047,7 +14001,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="15" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -14076,7 +14030,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="16" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A16" s="2">
         <v>21</v>
       </c>
@@ -14099,7 +14053,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="17" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A17" s="2">
         <v>22</v>
       </c>
@@ -14122,7 +14076,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="18" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A18" s="2">
         <v>23</v>
       </c>
@@ -14145,7 +14099,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" ht="28.8" spans="1:9">
+    <row r="19" ht="28" spans="1:9">
       <c r="A19" s="2">
         <v>24</v>
       </c>
@@ -14165,7 +14119,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" ht="28.8" spans="1:9">
+    <row r="20" ht="28" spans="1:9">
       <c r="A20" s="2">
         <v>25</v>
       </c>
@@ -14195,18 +14149,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.1111111111111" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.1111111111111" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.8888888888889" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.88888888888889" style="1"/>
-    <col min="5" max="5" width="17.3333333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1090909090909" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1090909090909" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.8909090909091" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.89090909090909" style="1"/>
+    <col min="5" max="5" width="17.3363636363636" style="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88888888888889" style="1"/>
+    <col min="7" max="16384" width="8.89090909090909" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -14220,7 +14174,7 @@
         <v>327</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>157</v>
@@ -14229,13 +14183,13 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="28.8" spans="1:9">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -14264,7 +14218,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -14293,7 +14247,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -14322,7 +14276,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -14351,7 +14305,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -14380,7 +14334,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -14409,7 +14363,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="8" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -14432,7 +14386,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" ht="28.8" spans="1:9">
+    <row r="9" ht="28" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -14455,7 +14409,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" ht="28.8" spans="1:9">
+    <row r="10" ht="28" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -14478,7 +14432,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" ht="28.8" spans="1:9">
+    <row r="11" ht="28" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -14511,18 +14465,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.1111111111111" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.1111111111111" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.8888888888889" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.88888888888889" style="1"/>
-    <col min="5" max="5" width="17.3333333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1090909090909" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1090909090909" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.8909090909091" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.89090909090909" style="1"/>
+    <col min="5" max="5" width="17.3363636363636" style="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88888888888889" style="1"/>
+    <col min="7" max="16384" width="8.89090909090909" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -14536,7 +14490,7 @@
         <v>327</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>157</v>
@@ -14545,13 +14499,13 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="28.8" spans="1:9">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -14580,7 +14534,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -14609,7 +14563,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -14638,7 +14592,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -14667,7 +14621,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -14696,7 +14650,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -14725,7 +14679,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="8" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -14754,7 +14708,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="9" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -14783,7 +14737,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="10" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -14812,7 +14766,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="11" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -14841,7 +14795,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="12" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -14870,7 +14824,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="13" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -14899,7 +14853,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="14" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -14922,7 +14876,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="15" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -14945,7 +14899,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="16" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -14968,7 +14922,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="17" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -15001,13 +14955,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="4" width="18" style="1" customWidth="1"/>
-    <col min="5" max="5" width="26.6666666666667" style="1" customWidth="1"/>
-    <col min="6" max="7" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26.6636363636364" style="1" customWidth="1"/>
+    <col min="6" max="7" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="8" max="8" width="18" style="1" customWidth="1"/>
     <col min="9" max="9" width="13" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
@@ -15027,7 +14981,7 @@
         <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>157</v>
@@ -15036,10 +14990,10 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="51" customHeight="1" spans="1:9">
@@ -15419,7 +15373,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="15" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -15448,7 +15402,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="57.6" spans="1:9">
+    <row r="16" s="1" customFormat="1" ht="56" spans="1:9">
       <c r="A16" s="2">
         <v>21</v>
       </c>
@@ -15471,7 +15425,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="57.6" spans="1:9">
+    <row r="17" s="1" customFormat="1" ht="56" spans="1:9">
       <c r="A17" s="2">
         <v>22</v>
       </c>
@@ -15494,7 +15448,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="57.6" spans="1:9">
+    <row r="18" s="1" customFormat="1" ht="56" spans="1:9">
       <c r="A18" s="2">
         <v>23</v>
       </c>
@@ -15517,7 +15471,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="57.6" spans="1:9">
+    <row r="19" s="1" customFormat="1" ht="56" spans="1:9">
       <c r="A19" s="2">
         <v>24</v>
       </c>
@@ -15540,7 +15494,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="57.6" spans="1:9">
+    <row r="20" s="1" customFormat="1" ht="56" spans="1:9">
       <c r="A20" s="2">
         <v>25</v>
       </c>
@@ -15563,7 +15517,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" ht="57.6" spans="1:9">
+    <row r="21" ht="56" spans="1:9">
       <c r="A21" s="2">
         <v>26</v>
       </c>
@@ -15586,7 +15540,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" ht="57.6" spans="1:9">
+    <row r="22" ht="56" spans="1:9">
       <c r="A22" s="2">
         <v>27</v>
       </c>
@@ -15609,7 +15563,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" ht="57.6" spans="1:9">
+    <row r="23" ht="56" spans="1:9">
       <c r="A23" s="2">
         <v>28</v>
       </c>
@@ -15632,7 +15586,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" ht="57.6" spans="1:9">
+    <row r="24" ht="56" spans="1:9">
       <c r="A24" s="2">
         <v>29</v>
       </c>
@@ -15655,7 +15609,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" ht="57.6" spans="1:9">
+    <row r="25" ht="56" spans="1:9">
       <c r="A25" s="2">
         <v>30</v>
       </c>
@@ -15678,7 +15632,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" ht="57.6" spans="1:9">
+    <row r="26" ht="56" spans="1:9">
       <c r="A26" s="2">
         <v>31</v>
       </c>
@@ -15701,7 +15655,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" ht="57.6" spans="1:9">
+    <row r="27" ht="56" spans="1:9">
       <c r="A27" s="2">
         <v>32</v>
       </c>
@@ -15734,19 +15688,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="25.7777777777778" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="25.7818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6666666666667" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.3333333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.6636363636364" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.3363636363636" style="2" customWidth="1"/>
     <col min="6" max="7" width="9" style="2"/>
-    <col min="8" max="8" width="14.6666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6636363636364" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:8">
+    <row r="1" ht="28" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -15766,10 +15720,10 @@
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -15876,7 +15830,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" ht="28.8" spans="1:8">
+    <row r="6" ht="28" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -15902,7 +15856,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" ht="28.8" spans="1:8">
+    <row r="7" ht="28" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -16045,18 +15999,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I20"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.1111111111111" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.1111111111111" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.8888888888889" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.88888888888889" style="1"/>
-    <col min="5" max="5" width="17.3333333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1090909090909" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1090909090909" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.8909090909091" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.89090909090909" style="1"/>
+    <col min="5" max="5" width="17.3363636363636" style="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88888888888889" style="1"/>
+    <col min="7" max="16384" width="8.89090909090909" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -16070,7 +16024,7 @@
         <v>327</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>157</v>
@@ -16079,13 +16033,13 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="43.2" spans="1:9">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -16114,7 +16068,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="3" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -16143,7 +16097,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="4" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -16172,7 +16126,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="5" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -16201,7 +16155,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="6" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -16230,7 +16184,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="7" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -16259,7 +16213,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="8" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -16288,7 +16242,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="9" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -16317,7 +16271,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="10" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -16346,7 +16300,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="11" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -16375,7 +16329,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="12" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -16404,7 +16358,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="13" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -16433,7 +16387,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="14" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -16456,7 +16410,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="15" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -16479,7 +16433,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="16" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -16502,7 +16456,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="17" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -16525,7 +16479,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" ht="43.2" spans="1:9">
+    <row r="18" ht="42" spans="1:9">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -16548,7 +16502,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" ht="43.2" spans="1:9">
+    <row r="19" ht="42" spans="1:9">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -16571,7 +16525,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" ht="43.2" spans="1:9">
+    <row r="20" ht="42" spans="1:9">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -16604,18 +16558,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -16626,16 +16580,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -16669,15 +16623,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="6" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="6" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="7" width="18" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.6666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6636363636364" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -16692,7 +16646,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>157</v>
@@ -16701,10 +16655,10 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
@@ -16733,7 +16687,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:8">
+    <row r="3" ht="28" spans="1:8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -16759,7 +16713,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:8">
+    <row r="4" ht="28" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -16779,7 +16733,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:8">
+    <row r="5" ht="28" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -16799,7 +16753,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" ht="28.8" spans="1:8">
+    <row r="6" ht="28" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -16819,7 +16773,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" ht="28.8" spans="1:8">
+    <row r="7" ht="28" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -16849,15 +16803,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="7" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="7" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="8" max="8" width="18" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6666666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.6636363636364" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -16884,10 +16838,10 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:9">
@@ -16919,7 +16873,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A3" s="2">
         <v>5</v>
       </c>
@@ -16942,7 +16896,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A4" s="2">
         <v>6</v>
       </c>
@@ -16975,18 +16929,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -16997,16 +16951,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -17032,7 +16986,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:7">
+    <row r="3" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -17055,7 +17009,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:7">
+    <row r="4" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -17078,7 +17032,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:7">
+    <row r="5" ht="28" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -17101,7 +17055,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" ht="28.8" spans="1:7">
+    <row r="6" ht="28" spans="1:7">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -17124,7 +17078,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" ht="28.8" spans="1:7">
+    <row r="7" ht="28" spans="1:7">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -17141,7 +17095,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" ht="28.8" spans="1:7">
+    <row r="8" ht="28" spans="1:7">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -17174,18 +17128,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -17196,16 +17150,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -17231,7 +17185,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -17254,7 +17208,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>6</v>
       </c>
@@ -17271,7 +17225,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A5" s="2">
         <v>7</v>
       </c>
@@ -17304,18 +17258,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -17326,16 +17280,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -17369,18 +17323,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="46.7777777777778" style="1" customWidth="1"/>
-    <col min="5" max="6" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46.7818181818182" style="1" customWidth="1"/>
+    <col min="5" max="6" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="7" width="18" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -17391,7 +17345,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>157</v>
@@ -17400,10 +17354,10 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="68" customHeight="1" spans="1:8">
@@ -17432,7 +17386,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="3" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -17458,7 +17412,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -17484,7 +17438,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -17510,7 +17464,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -17530,7 +17484,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -17550,7 +17504,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -17570,7 +17524,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -17590,7 +17544,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -17610,7 +17564,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -17630,7 +17584,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="12" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A12" s="2">
         <v>5</v>
       </c>
@@ -17650,7 +17604,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="13" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A13" s="2">
         <v>6</v>
       </c>
@@ -17670,7 +17624,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="14" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A14" s="2">
         <v>9</v>
       </c>
@@ -17690,7 +17644,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="15" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A15" s="2">
         <v>10</v>
       </c>
@@ -17710,7 +17664,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="16" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A16" s="2">
         <v>11</v>
       </c>
@@ -17730,7 +17684,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="17" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A17" s="2">
         <v>12</v>
       </c>
@@ -17750,7 +17704,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="18" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A18" s="2">
         <v>13</v>
       </c>
@@ -17770,7 +17724,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="19" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A19" s="2">
         <v>14</v>
       </c>
@@ -17790,7 +17744,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="20" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A20" s="2">
         <v>15</v>
       </c>
@@ -17810,7 +17764,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="21" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A21" s="2">
         <v>16</v>
       </c>
@@ -17830,7 +17784,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="22" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A22" s="2">
         <v>17</v>
       </c>
@@ -17850,7 +17804,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="23" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A23" s="2">
         <v>18</v>
       </c>
@@ -17870,7 +17824,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="24" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A24" s="2">
         <v>13</v>
       </c>
@@ -17890,7 +17844,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="25" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A25" s="2">
         <v>14</v>
       </c>
@@ -17910,7 +17864,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="26" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A26" s="2">
         <v>15</v>
       </c>
@@ -17930,7 +17884,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="27" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A27" s="2">
         <v>16</v>
       </c>
@@ -17950,7 +17904,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="28" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A28" s="2">
         <v>17</v>
       </c>
@@ -17970,7 +17924,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="29" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A29" s="2">
         <v>18</v>
       </c>
@@ -17990,7 +17944,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="30" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A30" s="2">
         <v>19</v>
       </c>
@@ -18010,7 +17964,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="31" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A31" s="2">
         <v>20</v>
       </c>
@@ -18040,20 +17994,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="4" width="18" style="1" customWidth="1"/>
-    <col min="5" max="5" width="34.4444444444444" style="1" customWidth="1"/>
-    <col min="6" max="7" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="5" max="5" width="34.4454545454545" style="1" customWidth="1"/>
+    <col min="6" max="7" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="8" max="8" width="18" style="1" customWidth="1"/>
     <col min="9" max="11" width="9" style="1"/>
-    <col min="12" max="12" width="25.5555555555556" style="1" customWidth="1"/>
+    <col min="12" max="12" width="25.5545454545455" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -18067,7 +18021,7 @@
         <v>327</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>157</v>
@@ -18076,10 +18030,10 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="68" customHeight="1" spans="1:9">
@@ -18111,7 +18065,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="3" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -18140,7 +18094,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="4" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -18169,7 +18123,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="5" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -18198,7 +18152,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="6" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -18227,7 +18181,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="7" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -18256,7 +18210,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="8" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -18285,7 +18239,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="9" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -18314,7 +18268,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="10" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -18343,7 +18297,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="11" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -18372,7 +18326,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="12" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -18401,7 +18355,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="13" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -18430,7 +18384,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="14" ht="28.8" spans="1:9">
+    <row r="14" ht="28" spans="1:9">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -18453,7 +18407,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" ht="28.8" spans="1:9">
+    <row r="15" ht="28" spans="1:9">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -18476,7 +18430,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" ht="28.8" spans="1:9">
+    <row r="16" ht="28" spans="1:9">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -18499,7 +18453,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" ht="28.8" spans="1:9">
+    <row r="17" ht="28" spans="1:9">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -18532,18 +18486,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.1111111111111" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.1111111111111" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.8888888888889" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.88888888888889" style="1"/>
-    <col min="5" max="5" width="17.3333333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1090909090909" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1090909090909" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.8909090909091" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.89090909090909" style="1"/>
+    <col min="5" max="5" width="17.3363636363636" style="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88888888888889" style="1"/>
+    <col min="7" max="16384" width="8.89090909090909" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -18557,7 +18511,7 @@
         <v>327</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>157</v>
@@ -18566,13 +18520,13 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="43.2" spans="1:9">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -18601,7 +18555,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="3" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -18630,7 +18584,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="4" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -18659,7 +18613,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="5" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -18688,7 +18642,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="6" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -18717,7 +18671,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="7" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -18746,7 +18700,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="8" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -18775,7 +18729,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="9" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -18804,7 +18758,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="10" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -18833,7 +18787,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="11" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -18862,7 +18816,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="12" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -18891,7 +18845,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="13" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -18920,7 +18874,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="14" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -18943,7 +18897,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="15" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -18966,7 +18920,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="16" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -18989,7 +18943,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="17" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -19022,17 +18976,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="4" customWidth="1"/>
-    <col min="2" max="2" width="23.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="4" customWidth="1"/>
+    <col min="2" max="2" width="23.2181818181818" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18.2222222222222" customWidth="1"/>
+    <col min="4" max="4" width="18.2181818181818" customWidth="1"/>
     <col min="5" max="6" width="9" style="4"/>
-    <col min="7" max="7" width="13.7777777777778" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7818181818182" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:7">
+    <row r="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -19043,16 +18997,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -19073,7 +19027,7 @@
         <v>45</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="22" customHeight="1" spans="1:7">
@@ -19089,7 +19043,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="1" ht="22" customHeight="1" spans="1:7">
@@ -19105,7 +19059,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -19118,18 +19072,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.1111111111111" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.1111111111111" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.8888888888889" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.88888888888889" style="1"/>
-    <col min="5" max="5" width="17.3333333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1090909090909" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1090909090909" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.8909090909091" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.89090909090909" style="1"/>
+    <col min="5" max="5" width="17.3363636363636" style="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88888888888889" style="1"/>
+    <col min="7" max="16384" width="8.89090909090909" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -19143,7 +19097,7 @@
         <v>327</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>157</v>
@@ -19152,13 +19106,13 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="28.8" spans="1:9">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -19187,7 +19141,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -19216,7 +19170,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -19245,7 +19199,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -19274,7 +19228,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -19303,7 +19257,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -19332,7 +19286,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="8" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -19355,7 +19309,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="9" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -19378,7 +19332,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="10" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -19401,7 +19355,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="11" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -19434,18 +19388,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="5" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="5" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="7" width="18" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -19459,16 +19413,16 @@
         <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
@@ -19494,7 +19448,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:8">
+    <row r="3" ht="28" spans="1:8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -19517,7 +19471,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:8">
+    <row r="4" ht="28" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -19540,7 +19494,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:8">
+    <row r="5" ht="28" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -19563,7 +19517,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" ht="28.8" spans="1:8">
+    <row r="6" ht="28" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -19586,7 +19540,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" ht="28.8" spans="1:8">
+    <row r="7" ht="28" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -19609,7 +19563,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" ht="28.8" spans="1:8">
+    <row r="8" ht="28" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -19642,18 +19596,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
     <col min="5" max="5" width="37" style="1" customWidth="1"/>
     <col min="6" max="6" width="47" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -19664,16 +19618,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -19706,19 +19660,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="43" style="1" customWidth="1"/>
-    <col min="5" max="5" width="29.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="7" width="18" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -19729,7 +19683,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>30</v>
@@ -19738,10 +19692,10 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
@@ -19770,7 +19724,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:8">
+    <row r="3" ht="28" spans="1:8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -19800,17 +19754,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -19821,16 +19775,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -19841,7 +19795,7 @@
         <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -19853,7 +19807,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:7">
+    <row r="3" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -19861,7 +19815,7 @@
         <v>52</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" s="1">
         <v>2</v>
@@ -19883,18 +19837,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="6" width="9" style="2"/>
-    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -19905,16 +19859,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
@@ -19925,7 +19879,7 @@
         <v>53</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -19937,7 +19891,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -19945,7 +19899,7 @@
         <v>54</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>

--- a/test_data/mercury.xlsx
+++ b/test_data/mercury.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="11870" firstSheet="74" activeTab="79"/>
+    <workbookView windowWidth="24750" windowHeight="11870" firstSheet="70" activeTab="75"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
@@ -49,44 +49,40 @@
     <sheet name="set_max_acc" sheetId="40" r:id="rId40"/>
     <sheet name="get_model_direction" sheetId="41" r:id="rId41"/>
     <sheet name="set_model_direction" sheetId="76" r:id="rId42"/>
-    <sheet name="get_base_coords" sheetId="43" r:id="rId43"/>
-    <sheet name="get_servo_speeds" sheetId="44" r:id="rId44"/>
-    <sheet name="get_servo_currents" sheetId="45" r:id="rId45"/>
-    <sheet name="get_servo_status" sheetId="46" r:id="rId46"/>
-    <sheet name="set_color" sheetId="47" r:id="rId47"/>
-    <sheet name="get_collision_mode" sheetId="48" r:id="rId48"/>
-    <sheet name="set_collision_mode" sheetId="49" r:id="rId49"/>
-    <sheet name="set_collision_threshold" sheetId="50" r:id="rId50"/>
-    <sheet name="get_collision_threshold" sheetId="51" r:id="rId51"/>
-    <sheet name="set_torque_comp" sheetId="52" r:id="rId52"/>
-    <sheet name="get_torque_comp" sheetId="53" r:id="rId53"/>
-    <sheet name="get_pos_over_shoot" sheetId="54" r:id="rId54"/>
-    <sheet name="set_pos_over_shoot" sheetId="55" r:id="rId55"/>
-    <sheet name="jog_angle" sheetId="56" r:id="rId56"/>
-    <sheet name="jog_rpy" sheetId="57" r:id="rId57"/>
-    <sheet name="jog_coord" sheetId="58" r:id="rId58"/>
-    <sheet name="jog_increment_angle" sheetId="59" r:id="rId59"/>
-    <sheet name="jog_increment_coord" sheetId="60" r:id="rId60"/>
-    <sheet name="get_solution_angles" sheetId="61" r:id="rId61"/>
-    <sheet name="set_solution_angles" sheetId="62" r:id="rId62"/>
-    <sheet name="write_move_c" sheetId="63" r:id="rId63"/>
-    <sheet name="set_movement_type" sheetId="64" r:id="rId64"/>
-    <sheet name="get_movement_type" sheetId="42" r:id="rId65"/>
-    <sheet name="set_end_type" sheetId="65" r:id="rId66"/>
-    <sheet name="get_end_type" sheetId="66" r:id="rId67"/>
-    <sheet name="send_base_coords" sheetId="67" r:id="rId68"/>
-    <sheet name="send_base_coord" sheetId="68" r:id="rId69"/>
-    <sheet name="jog_base_coord" sheetId="69" r:id="rId70"/>
-    <sheet name="jog_base_rpy" sheetId="70" r:id="rId71"/>
-    <sheet name="get_servo_encoder" sheetId="71" r:id="rId72"/>
-    <sheet name="get_servo_encoders" sheetId="72" r:id="rId73"/>
-    <sheet name="solve_inv_kinematics" sheetId="73" r:id="rId74"/>
-    <sheet name="set_tool_reference" sheetId="77" r:id="rId75"/>
-    <sheet name="get_tool_reference" sheetId="78" r:id="rId76"/>
-    <sheet name="set_world_reference" sheetId="80" r:id="rId77"/>
-    <sheet name="get_world_reference" sheetId="79" r:id="rId78"/>
-    <sheet name="set_reference_frame" sheetId="82" r:id="rId79"/>
-    <sheet name="get_reference_frame" sheetId="81" r:id="rId80"/>
+    <sheet name="get_servo_speeds" sheetId="44" r:id="rId43"/>
+    <sheet name="get_servo_currents" sheetId="45" r:id="rId44"/>
+    <sheet name="get_servo_status" sheetId="46" r:id="rId45"/>
+    <sheet name="set_color" sheetId="47" r:id="rId46"/>
+    <sheet name="get_collision_mode" sheetId="48" r:id="rId47"/>
+    <sheet name="set_collision_mode" sheetId="49" r:id="rId48"/>
+    <sheet name="set_collision_threshold" sheetId="50" r:id="rId49"/>
+    <sheet name="get_collision_threshold" sheetId="51" r:id="rId50"/>
+    <sheet name="set_torque_comp" sheetId="52" r:id="rId51"/>
+    <sheet name="get_torque_comp" sheetId="53" r:id="rId52"/>
+    <sheet name="get_pos_over_shoot" sheetId="54" r:id="rId53"/>
+    <sheet name="set_pos_over_shoot" sheetId="55" r:id="rId54"/>
+    <sheet name="jog_angle" sheetId="56" r:id="rId55"/>
+    <sheet name="jog_rpy" sheetId="57" r:id="rId56"/>
+    <sheet name="jog_coord" sheetId="58" r:id="rId57"/>
+    <sheet name="jog_increment_angle" sheetId="59" r:id="rId58"/>
+    <sheet name="jog_increment_coord" sheetId="60" r:id="rId59"/>
+    <sheet name="get_solution_angles" sheetId="61" r:id="rId60"/>
+    <sheet name="set_solution_angles" sheetId="62" r:id="rId61"/>
+    <sheet name="write_move_c" sheetId="63" r:id="rId62"/>
+    <sheet name="set_movement_type" sheetId="64" r:id="rId63"/>
+    <sheet name="get_movement_type" sheetId="42" r:id="rId64"/>
+    <sheet name="set_end_type" sheetId="65" r:id="rId65"/>
+    <sheet name="get_end_type" sheetId="66" r:id="rId66"/>
+    <sheet name="get_servo_encoder" sheetId="71" r:id="rId67"/>
+    <sheet name="get_servo_encoders" sheetId="72" r:id="rId68"/>
+    <sheet name="solve_inv_kinematics" sheetId="73" r:id="rId69"/>
+    <sheet name="set_tool_reference" sheetId="77" r:id="rId70"/>
+    <sheet name="get_tool_reference" sheetId="78" r:id="rId71"/>
+    <sheet name="set_world_reference" sheetId="80" r:id="rId72"/>
+    <sheet name="get_world_reference" sheetId="79" r:id="rId73"/>
+    <sheet name="set_reference_frame" sheetId="82" r:id="rId74"/>
+    <sheet name="get_reference_frame" sheetId="81" r:id="rId75"/>
+    <sheet name="servo_restore" sheetId="83" r:id="rId76"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -106,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2764" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2585" uniqueCount="727">
   <si>
     <t>ID</t>
   </si>
@@ -1503,18 +1499,6 @@
     <t>获取机械臂运动模式（下电）</t>
   </si>
   <si>
-    <t>r_expect_data</t>
-  </si>
-  <si>
-    <t>正确获取机械臂Base全坐标</t>
-  </si>
-  <si>
-    <t>get_base_coords</t>
-  </si>
-  <si>
-    <t>[375.0, 213.1, 196.1, 89.99, 0.0, -32.0]</t>
-  </si>
-  <si>
     <t>正确获取机械臂关节速度</t>
   </si>
   <si>
@@ -2139,177 +2123,6 @@
     <t>获取机械臂末端坐标系（下电）</t>
   </si>
   <si>
-    <t>正确设置机械臂base_全坐标(x,y.z)机械臂</t>
-  </si>
-  <si>
-    <t>sen_base_coords</t>
-  </si>
-  <si>
-    <t>[400.5, 80.3, 210, 89.99, 0.0, -50.0]</t>
-  </si>
-  <si>
-    <t>正确设置机械臂base_全坐标(rx,ry.rz)机械臂</t>
-  </si>
-  <si>
-    <t>[400.5, 80.3, 210, 80, 20, -40.0]</t>
-  </si>
-  <si>
-    <t>设置base_全坐标x轴超限（max）机械臂</t>
-  </si>
-  <si>
-    <t>[568,80.3, 210, 89.99, 0.0, -50.0]</t>
-  </si>
-  <si>
-    <t>exception_left</t>
-  </si>
-  <si>
-    <t>设置base_全坐标x轴超限（min）机械臂</t>
-  </si>
-  <si>
-    <t>[-353, 80.3, 210, 89.99, 0.0, -50.0]</t>
-  </si>
-  <si>
-    <t>设置base_全坐标y轴超限（max）机械臂</t>
-  </si>
-  <si>
-    <t>[400.5, 647, 210, 89.99, 0.0, -50.0]</t>
-  </si>
-  <si>
-    <t>设置base_全坐标y轴超限（min）机械臂</t>
-  </si>
-  <si>
-    <t>[400.5, -274, 210, 89.99, 0.0, -50.0]</t>
-  </si>
-  <si>
-    <t>设置base_全坐标z轴超限（max）机械臂</t>
-  </si>
-  <si>
-    <t>[400.5, 80.3, 657, 89.99, 0.0, -50.0]</t>
-  </si>
-  <si>
-    <t>设置base_全坐标z轴超限（min）机械臂</t>
-  </si>
-  <si>
-    <t>[400.5, 80.3, -264, 89.99, 0.0, -50.0]</t>
-  </si>
-  <si>
-    <t>设置base_全坐标rx轴超限（max）机械臂</t>
-  </si>
-  <si>
-    <t>[400.5, 80.3, 210, 181, 0.0, -50.0]</t>
-  </si>
-  <si>
-    <t>设置base_全坐标rx轴超限（min）机械臂</t>
-  </si>
-  <si>
-    <t>[400.5, 80.3, 210, -181, 0.0, -50.0]</t>
-  </si>
-  <si>
-    <t>设置base_全坐标ry轴超限（max）机械臂</t>
-  </si>
-  <si>
-    <t>[400.5, 80.3, 210, 89.99, 181, -50.0]</t>
-  </si>
-  <si>
-    <t>设置base_全坐标ry轴超限（min）机械臂</t>
-  </si>
-  <si>
-    <t>[400.5, 80.3, 210, 89.99, -181, -50.0]</t>
-  </si>
-  <si>
-    <t>设置base_全坐标rz轴超限（max）机械臂</t>
-  </si>
-  <si>
-    <t>[400.5, 80.3, 210, 89.99, 0.0, 181]</t>
-  </si>
-  <si>
-    <t>设置base_全坐标rz轴超限（min）机械臂</t>
-  </si>
-  <si>
-    <t>[400.5, 80.3, 210, 89.99, 0.0, -181]</t>
-  </si>
-  <si>
-    <t>设置base_全坐标速度超限</t>
-  </si>
-  <si>
-    <t>正确设置机械臂base_单坐标X轴机械臂</t>
-  </si>
-  <si>
-    <t>sen_base_coord</t>
-  </si>
-  <si>
-    <t>正确设置机械臂base_单坐标Y轴机械臂</t>
-  </si>
-  <si>
-    <t>正确设置机械臂base_单坐标Z轴机械臂</t>
-  </si>
-  <si>
-    <t>正确设置机械臂base_单坐标RX轴机械臂</t>
-  </si>
-  <si>
-    <t>正确设置机械臂base_单坐标RY轴机械臂</t>
-  </si>
-  <si>
-    <t>正确设置机械臂base_单坐标RZ轴机械臂</t>
-  </si>
-  <si>
-    <t>设置机械臂base_单坐标axis超限</t>
-  </si>
-  <si>
-    <t>设置机械臂base_单坐标速度超限</t>
-  </si>
-  <si>
-    <t>正确设置x轴jog_base_coord正向运动</t>
-  </si>
-  <si>
-    <t>jog_base_coord</t>
-  </si>
-  <si>
-    <t>正确设置x轴jog_base_coord负向运动</t>
-  </si>
-  <si>
-    <t>正确设置y轴jog_base_coord正向运动</t>
-  </si>
-  <si>
-    <t>noraml</t>
-  </si>
-  <si>
-    <t>正确设置y轴jog_base_coord负向运动</t>
-  </si>
-  <si>
-    <t>正确设置z轴jog_base_coord正向运动</t>
-  </si>
-  <si>
-    <t>正确设置z轴jog_base_coord负向运动</t>
-  </si>
-  <si>
-    <t>正确设置rx轴jog_base_coord正向运动</t>
-  </si>
-  <si>
-    <t>正确设置rx轴jog_base_coord负向运动</t>
-  </si>
-  <si>
-    <t>正确设置ry轴jog_base_coord正向运动</t>
-  </si>
-  <si>
-    <t>正确设置ry轴jog_base_coord负向运动</t>
-  </si>
-  <si>
-    <t>正确设置rz轴jog_base_coord正向运动</t>
-  </si>
-  <si>
-    <t>正确设置rz轴jog_base_coord负向运动</t>
-  </si>
-  <si>
-    <t>设置jog_base_coord运动超限</t>
-  </si>
-  <si>
-    <t>设置jog_base_coord运动速度超限</t>
-  </si>
-  <si>
-    <t>jog_base_rpy</t>
-  </si>
-  <si>
     <t>正确获取机械臂关节编码值</t>
   </si>
   <si>
@@ -2440,18 +2253,49 @@
   </si>
   <si>
     <t>get_reference_frame</t>
+  </si>
+  <si>
+    <t>关节异常恢复（1关节）</t>
+  </si>
+  <si>
+    <t>servo_restore</t>
+  </si>
+  <si>
+    <t>关节异常恢复（2关节）</t>
+  </si>
+  <si>
+    <t>关节异常恢复（3关节）</t>
+  </si>
+  <si>
+    <t>关节异常恢复（4关节）</t>
+  </si>
+  <si>
+    <t>关节异常恢复（5关节）</t>
+  </si>
+  <si>
+    <t>关节异常恢复（6关节）</t>
+  </si>
+  <si>
+    <t>关节异常恢复，关节超限</t>
+  </si>
+  <si>
+    <t>关节异常恢复（仅上电）</t>
+  </si>
+  <si>
+    <t>关节异常恢复（下电）</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="177" formatCode="0.0_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -3062,7 +2906,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3071,6 +2915,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3082,7 +2929,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3436,12 +3283,12 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2181818181818" style="4" customWidth="1"/>
-    <col min="2" max="2" width="16.1090909090909" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.7818181818182" style="3" customWidth="1"/>
-    <col min="5" max="5" width="14.7818181818182" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.7818181818182" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="5" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18" style="4" customWidth="1"/>
+    <col min="4" max="4" width="14.7818181818182" style="4" customWidth="1"/>
+    <col min="5" max="5" width="14.7818181818182" style="5" customWidth="1"/>
+    <col min="6" max="6" width="14.7818181818182" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
@@ -3475,7 +3322,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <v>1.1</v>
       </c>
       <c r="F2" t="s">
@@ -3492,7 +3339,7 @@
       <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="8">
         <v>1.1</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -3509,7 +3356,7 @@
       <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="8">
         <v>1.1</v>
       </c>
       <c r="F4" t="s">
@@ -3787,7 +3634,7 @@
       <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="7">
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -4982,7 +4829,7 @@
       <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4999,7 +4846,7 @@
       <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -5229,7 +5076,7 @@
       <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5246,7 +5093,7 @@
       <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -5649,7 +5496,7 @@
       <c r="E18" s="1">
         <v>160</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5669,7 +5516,7 @@
       <c r="E19" s="1">
         <v>160</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -6072,7 +5919,7 @@
       <c r="E18" s="1">
         <v>-150</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6092,7 +5939,7 @@
       <c r="E19" s="1">
         <v>-150</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -6201,12 +6048,12 @@
   <dimension ref="A1:G49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2181818181818" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.1090909090909" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18" style="3" customWidth="1"/>
-    <col min="4" max="4" width="32.7818181818182" style="3" customWidth="1"/>
-    <col min="5" max="6" width="17.2181818181818" style="3" customWidth="1"/>
-    <col min="7" max="7" width="13" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="4" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18" style="4" customWidth="1"/>
+    <col min="4" max="4" width="32.7818181818182" style="4" customWidth="1"/>
+    <col min="5" max="6" width="17.2181818181818" style="4" customWidth="1"/>
+    <col min="7" max="7" width="13" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:7">
@@ -7280,12 +7127,12 @@
   <dimension ref="A1:H51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2181818181818" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.1090909090909" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18" style="3" customWidth="1"/>
-    <col min="4" max="5" width="32.7818181818182" style="4" customWidth="1"/>
-    <col min="6" max="7" width="17.2181818181818" style="4" customWidth="1"/>
-    <col min="8" max="8" width="13" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="4" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18" style="4" customWidth="1"/>
+    <col min="4" max="5" width="32.7818181818182" style="5" customWidth="1"/>
+    <col min="6" max="7" width="17.2181818181818" style="5" customWidth="1"/>
+    <col min="8" max="8" width="13" style="4" customWidth="1"/>
     <col min="16383" max="16383" width="9" style="1" customWidth="1"/>
     <col min="16384" max="16384" width="9" style="1"/>
   </cols>
@@ -8159,10 +8006,10 @@
       <c r="C36" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D36" s="4">
-        <v>0</v>
-      </c>
-      <c r="E36" s="4">
+      <c r="D36" s="5">
+        <v>0</v>
+      </c>
+      <c r="E36" s="5">
         <v>0</v>
       </c>
       <c r="F36" s="2">
@@ -8182,10 +8029,10 @@
       <c r="C37" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="5">
         <v>8</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E37" s="5">
         <v>0</v>
       </c>
       <c r="F37" s="2">
@@ -8205,10 +8052,10 @@
       <c r="C38" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D38" s="4">
-        <v>1</v>
-      </c>
-      <c r="E38" s="4">
+      <c r="D38" s="5">
+        <v>1</v>
+      </c>
+      <c r="E38" s="5">
         <v>0</v>
       </c>
       <c r="F38" s="2">
@@ -8231,10 +8078,10 @@
       <c r="C39" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D39" s="4">
-        <v>2</v>
-      </c>
-      <c r="E39" s="4">
+      <c r="D39" s="5">
+        <v>2</v>
+      </c>
+      <c r="E39" s="5">
         <v>0</v>
       </c>
       <c r="F39" s="2">
@@ -8257,10 +8104,10 @@
       <c r="C40" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="5">
         <v>3</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E40" s="5">
         <v>0</v>
       </c>
       <c r="F40" s="2">
@@ -8283,10 +8130,10 @@
       <c r="C41" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="5">
         <v>4</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E41" s="5">
         <v>0</v>
       </c>
       <c r="F41" s="2">
@@ -8309,10 +8156,10 @@
       <c r="C42" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="5">
         <v>5</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E42" s="5">
         <v>0</v>
       </c>
       <c r="F42" s="2">
@@ -8335,10 +8182,10 @@
       <c r="C43" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="5">
         <v>6</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E43" s="5">
         <v>90</v>
       </c>
       <c r="F43" s="2">
@@ -8361,10 +8208,10 @@
       <c r="C44" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="5">
         <v>7</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E44" s="5">
         <v>0</v>
       </c>
       <c r="F44" s="2">
@@ -8387,10 +8234,10 @@
       <c r="C45" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D45" s="4">
-        <v>1</v>
-      </c>
-      <c r="E45" s="4">
+      <c r="D45" s="5">
+        <v>1</v>
+      </c>
+      <c r="E45" s="5">
         <v>0</v>
       </c>
       <c r="F45" s="2">
@@ -8413,10 +8260,10 @@
       <c r="C46" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D46" s="4">
-        <v>2</v>
-      </c>
-      <c r="E46" s="4">
+      <c r="D46" s="5">
+        <v>2</v>
+      </c>
+      <c r="E46" s="5">
         <v>0</v>
       </c>
       <c r="F46" s="2">
@@ -8439,10 +8286,10 @@
       <c r="C47" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="5">
         <v>3</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E47" s="5">
         <v>0</v>
       </c>
       <c r="F47" s="2">
@@ -8465,10 +8312,10 @@
       <c r="C48" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="5">
         <v>4</v>
       </c>
-      <c r="E48" s="4">
+      <c r="E48" s="5">
         <v>0</v>
       </c>
       <c r="F48" s="2">
@@ -8491,10 +8338,10 @@
       <c r="C49" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="5">
         <v>5</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E49" s="5">
         <v>0</v>
       </c>
       <c r="F49" s="2">
@@ -8517,10 +8364,10 @@
       <c r="C50" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50" s="5">
         <v>6</v>
       </c>
-      <c r="E50" s="4">
+      <c r="E50" s="5">
         <v>90</v>
       </c>
       <c r="F50" s="2">
@@ -8543,10 +8390,10 @@
       <c r="C51" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="5">
         <v>7</v>
       </c>
-      <c r="E51" s="4">
+      <c r="E51" s="5">
         <v>0</v>
       </c>
       <c r="F51" s="2">
@@ -9197,11 +9044,11 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2181818181818" style="4" customWidth="1"/>
-    <col min="2" max="2" width="23.2181818181818" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9" style="4" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="5" customWidth="1"/>
+    <col min="2" max="2" width="23.2181818181818" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18" style="4" customWidth="1"/>
+    <col min="4" max="4" width="15" style="4" customWidth="1"/>
+    <col min="5" max="5" width="9" style="5" customWidth="1"/>
     <col min="6" max="6" width="13.7818181818182" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9244,7 +9091,7 @@
       </c>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:6">
-      <c r="A3" s="4">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -9258,7 +9105,7 @@
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:6">
-      <c r="A4" s="4">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -11527,11 +11374,11 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2181818181818" style="4" customWidth="1"/>
-    <col min="2" max="2" width="23.2181818181818" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9" style="4" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="5" customWidth="1"/>
+    <col min="2" max="2" width="23.2181818181818" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18" style="4" customWidth="1"/>
+    <col min="4" max="4" width="15" style="4" customWidth="1"/>
+    <col min="5" max="5" width="9" style="5" customWidth="1"/>
     <col min="6" max="6" width="13.7818181818182" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11574,7 +11421,7 @@
       </c>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:6">
-      <c r="A3" s="4">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -11588,7 +11435,7 @@
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:6">
-      <c r="A4" s="4">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -12191,19 +12038,19 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
     <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
     <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="6" max="16383" width="9" style="1" customWidth="1"/>
+    <col min="16384" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -12220,30 +12067,52 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" ht="28" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>33</v>
+      <c r="C3" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" ht="28" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -12292,13 +12161,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>33</v>
@@ -12312,7 +12181,7 @@
         <v>472</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>10</v>
@@ -12323,10 +12192,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>12</v>
@@ -12378,13 +12247,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>475</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>33</v>
@@ -12395,10 +12264,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>10</v>
@@ -12412,7 +12281,7 @@
         <v>476</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>12</v>
@@ -12425,6 +12294,246 @@
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="7" width="17.2181818181818" style="1" customWidth="1"/>
+    <col min="8" max="16383" width="9" style="1" customWidth="1"/>
+    <col min="16384" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>255</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:8">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D3" s="1">
+        <v>255</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:8">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>255</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1" spans="1:8">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D5" s="1">
+        <v>256</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:8">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>256</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:8">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>256</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:8">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>255</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" ht="28" spans="1:8">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>255</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
@@ -12464,13 +12573,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>471</v>
+        <v>486</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>33</v>
@@ -12481,268 +12590,24 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="F3"/>
     </row>
     <row r="4" ht="28" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
-  <cols>
-    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
-    <col min="5" max="7" width="17.2181818181818" style="1" customWidth="1"/>
-    <col min="8" max="16383" width="9" style="1" customWidth="1"/>
-    <col min="16384" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0</v>
-      </c>
-      <c r="E2" s="1">
-        <v>255</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:8">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="D3" s="1">
-        <v>255</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
-        <v>0</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:8">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1">
-        <v>255</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:8">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="D5" s="1">
-        <v>256</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" ht="28" spans="1:8">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1">
-        <v>256</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" ht="28" spans="1:8">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
-        <v>256</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" ht="28" spans="1:8">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
-        <v>255</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" ht="28" spans="1:8">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1">
-        <v>255</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="F4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12751,6 +12616,595 @@
 </file>
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
+    <col min="6" max="16383" width="9" style="1" customWidth="1"/>
+    <col min="16384" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D4" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1" spans="1:6">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:6">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:6">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
+    <col min="3" max="4" width="18" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.2181818181818" style="1" customWidth="1"/>
+    <col min="7" max="16383" width="9" style="1" customWidth="1"/>
+    <col min="16384" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>100</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>100</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>100</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>100</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1">
+        <v>100</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1">
+        <v>100</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D8" s="1">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1">
+        <v>100</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>100</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D10" s="1">
+        <v>8</v>
+      </c>
+      <c r="E10" s="1">
+        <v>100</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1" spans="1:7">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>251</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1" spans="1:7">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2</v>
+      </c>
+      <c r="E12" s="1">
+        <v>49</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1" spans="1:7">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>120</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" ht="28" spans="1:7">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>120</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" ht="28" spans="1:7">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>120</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.2181818181818" style="5" customWidth="1"/>
+    <col min="2" max="2" width="22.3363636363636" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18" style="4" customWidth="1"/>
+    <col min="4" max="4" width="16.5545454545455" style="4" customWidth="1"/>
+    <col min="5" max="5" width="14.1090909090909" style="4" customWidth="1"/>
+    <col min="6" max="6" width="16" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="2">
+        <v>4500</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="2">
+        <v>4500</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="2">
+        <v>4500</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
@@ -12790,13 +13244,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0</v>
+        <v>509</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>510</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>33</v>
@@ -12807,24 +13262,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="F3"/>
+        <v>509</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" ht="28" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>492</v>
+        <v>512</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="F4"/>
+        <v>509</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12832,248 +13291,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="5"/>
-  <cols>
-    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
-    <col min="6" max="16383" width="9" style="1" customWidth="1"/>
-    <col min="16384" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="D2" s="1">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:6">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="D4" s="1">
-        <v>-1</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:6">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="D5" s="1">
-        <v>2</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" ht="28" spans="1:6">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" ht="28" spans="1:6">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
-  <cols>
-    <col min="1" max="1" width="13.2181818181818" style="4" customWidth="1"/>
-    <col min="2" max="2" width="22.3363636363636" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18" style="3" customWidth="1"/>
-    <col min="4" max="4" width="16.5545454545455" style="3" customWidth="1"/>
-    <col min="5" max="5" width="14.1090909090909" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16" style="3" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="2">
-        <v>4500</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="2">
-        <v>4500</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="2">
-        <v>4500</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G15"/>
@@ -13116,10 +13334,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13139,10 +13357,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -13162,10 +13380,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -13185,10 +13403,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -13208,10 +13426,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -13231,10 +13449,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -13254,10 +13472,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -13277,10 +13495,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -13297,10 +13515,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -13312,15 +13530,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" ht="42" customHeight="1" spans="1:7">
+    <row r="11" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -13332,44 +13550,44 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1" spans="1:7">
+    <row r="12" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
       </c>
       <c r="E12" s="1">
-        <v>49</v>
+        <v>-1</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1" spans="1:7">
+    <row r="13" s="1" customFormat="1" ht="28" customHeight="1" spans="1:7">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
       </c>
       <c r="E13" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>53</v>
@@ -13380,16 +13598,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
       </c>
       <c r="E14" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>10</v>
@@ -13400,16 +13618,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
       </c>
       <c r="E15" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>12</v>
@@ -13421,7 +13639,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
@@ -13461,14 +13679,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="D2" s="1"/>
+        <v>527</v>
+      </c>
+      <c r="D2" s="1">
+        <v>100</v>
+      </c>
       <c r="E2" s="1" t="s">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>33</v>
@@ -13479,10 +13699,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>10</v>
@@ -13493,360 +13713,12 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
-  <cols>
-    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
-    <col min="3" max="4" width="18" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.3363636363636" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.2181818181818" style="1" customWidth="1"/>
-    <col min="7" max="16383" width="9" style="1" customWidth="1"/>
-    <col min="16384" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="D2" s="1">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1">
-        <v>100</v>
-      </c>
-      <c r="F2" s="1">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="D3" s="1">
-        <v>2</v>
-      </c>
-      <c r="E3" s="1">
-        <v>100</v>
-      </c>
-      <c r="F3" s="1">
-        <v>1</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="D4" s="1">
-        <v>3</v>
-      </c>
-      <c r="E4" s="1">
-        <v>100</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="D5" s="1">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1">
-        <v>100</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="D6" s="1">
-        <v>5</v>
-      </c>
-      <c r="E6" s="1">
-        <v>100</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="D7" s="1">
-        <v>6</v>
-      </c>
-      <c r="E7" s="1">
-        <v>100</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="D8" s="1">
-        <v>7</v>
-      </c>
-      <c r="E8" s="1">
-        <v>100</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1">
-        <v>100</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="D10" s="1">
-        <v>8</v>
-      </c>
-      <c r="E10" s="1">
-        <v>100</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1">
-        <v>251</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="42" customHeight="1" spans="1:7">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="D12" s="1">
-        <v>2</v>
-      </c>
-      <c r="E12" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="28" customHeight="1" spans="1:7">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1">
-        <v>100</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" ht="28" spans="1:7">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1">
-        <v>100</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" ht="28" spans="1:7">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1">
-        <v>100</v>
-      </c>
-      <c r="G15" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -13896,22 +13768,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="D2" s="1">
-        <v>100</v>
-      </c>
-      <c r="E2" s="1" t="s">
         <v>532</v>
       </c>
+      <c r="E2" s="1">
+        <v>50</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" ht="28" spans="1:6">
+    <row r="3" ht="42" spans="1:6">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -13919,7 +13788,7 @@
         <v>533</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>10</v>
@@ -13933,7 +13802,7 @@
         <v>534</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>12</v>
@@ -13946,92 +13815,6 @@
 </file>
 
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
-  <cols>
-    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3363636363636" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2181818181818" style="1" customWidth="1"/>
-    <col min="6" max="16383" width="9" style="1" customWidth="1"/>
-    <col min="16384" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="E2" s="1">
-        <v>50</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" ht="42" spans="1:6">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" ht="42" spans="1:6">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F7"/>
@@ -14071,10 +13854,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D2" s="1">
         <v>30</v>
@@ -14091,10 +13874,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D3" s="1">
         <v>301</v>
@@ -14108,10 +13891,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D4" s="1">
         <v>-301</v>
@@ -14125,10 +13908,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D5" s="1">
         <v>21</v>
@@ -14145,10 +13928,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D6" s="1">
         <v>30</v>
@@ -14157,15 +13940,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="42" spans="1:6">
+    <row r="7" ht="28" spans="1:6">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D7" s="1">
         <v>30</v>
@@ -14180,7 +13963,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H24"/>
@@ -14227,10 +14010,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14253,10 +14036,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14279,10 +14062,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14305,10 +14088,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14331,10 +14114,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14357,10 +14140,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14383,10 +14166,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14409,10 +14192,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14435,10 +14218,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14461,10 +14244,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14487,10 +14270,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14513,10 +14296,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14539,10 +14322,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -14565,10 +14348,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -14591,10 +14374,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -14614,10 +14397,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -14637,10 +14420,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -14660,10 +14443,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -14683,10 +14466,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -14706,10 +14489,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
@@ -14729,10 +14512,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -14752,10 +14535,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -14778,10 +14561,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
@@ -14805,7 +14588,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H16"/>
@@ -14852,10 +14635,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14878,10 +14661,